--- a/database/VIVA3.xlsx
+++ b/database/VIVA3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1712"/>
+  <dimension ref="A1:F1713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>43749</v>
       </c>
       <c r="B2" t="n">
-        <v>21.18223571777344</v>
+        <v>21.1822395324707</v>
       </c>
       <c r="C2" t="n">
-        <v>21.75352347985466</v>
+        <v>21.75352739743483</v>
       </c>
       <c r="D2" t="n">
-        <v>21.17330916027268</v>
+        <v>21.17331297336237</v>
       </c>
       <c r="E2" t="n">
-        <v>21.69103757734936</v>
+        <v>21.69104148367647</v>
       </c>
       <c r="F2" t="n">
         <v>7077400</v>
@@ -472,16 +472,16 @@
         <v>43752</v>
       </c>
       <c r="B3" t="n">
-        <v>20.98585510253906</v>
+        <v>20.98585891723633</v>
       </c>
       <c r="C3" t="n">
-        <v>21.26257155557164</v>
+        <v>21.26257542056896</v>
       </c>
       <c r="D3" t="n">
-        <v>20.61987478326695</v>
+        <v>20.61987853143826</v>
       </c>
       <c r="E3" t="n">
-        <v>21.18223424621273</v>
+        <v>21.18223809660675</v>
       </c>
       <c r="F3" t="n">
         <v>4214500</v>
@@ -492,16 +492,16 @@
         <v>43753</v>
       </c>
       <c r="B4" t="n">
-        <v>21.02156448364258</v>
+        <v>21.02156257629395</v>
       </c>
       <c r="C4" t="n">
-        <v>21.10190181156005</v>
+        <v>21.10189989692218</v>
       </c>
       <c r="D4" t="n">
-        <v>20.75377452562902</v>
+        <v>20.75377264257776</v>
       </c>
       <c r="E4" t="n">
-        <v>21.06619727835619</v>
+        <v>21.0661953669579</v>
       </c>
       <c r="F4" t="n">
         <v>1133500</v>
@@ -512,16 +512,16 @@
         <v>43754</v>
       </c>
       <c r="B5" t="n">
-        <v>21.51251220703125</v>
+        <v>21.51251411437988</v>
       </c>
       <c r="C5" t="n">
-        <v>21.51251220703125</v>
+        <v>21.51251411437988</v>
       </c>
       <c r="D5" t="n">
-        <v>20.80732946554403</v>
+        <v>20.80733131036954</v>
       </c>
       <c r="E5" t="n">
-        <v>21.02156174455403</v>
+        <v>21.02156360837387</v>
       </c>
       <c r="F5" t="n">
         <v>1946600</v>
@@ -532,16 +532,16 @@
         <v>43755</v>
       </c>
       <c r="B6" t="n">
-        <v>21.60177421569824</v>
+        <v>21.60177803039551</v>
       </c>
       <c r="C6" t="n">
-        <v>21.60177421569824</v>
+        <v>21.60177803039551</v>
       </c>
       <c r="D6" t="n">
-        <v>21.2893515306752</v>
+        <v>21.28935529020116</v>
       </c>
       <c r="E6" t="n">
-        <v>21.42324648066603</v>
+        <v>21.42325026383675</v>
       </c>
       <c r="F6" t="n">
         <v>904400</v>
@@ -552,16 +552,16 @@
         <v>43756</v>
       </c>
       <c r="B7" t="n">
-        <v>21.55714416503906</v>
+        <v>21.55713844299316</v>
       </c>
       <c r="C7" t="n">
-        <v>21.55714416503906</v>
+        <v>21.55713844299316</v>
       </c>
       <c r="D7" t="n">
-        <v>21.2536479985278</v>
+        <v>21.25364235704076</v>
       </c>
       <c r="E7" t="n">
-        <v>21.52143963504373</v>
+        <v>21.52143392247511</v>
       </c>
       <c r="F7" t="n">
         <v>1051300</v>
@@ -572,16 +572,16 @@
         <v>43759</v>
       </c>
       <c r="B8" t="n">
-        <v>21.43217849731445</v>
+        <v>21.43217468261719</v>
       </c>
       <c r="C8" t="n">
-        <v>21.63748425310449</v>
+        <v>21.63748040186501</v>
       </c>
       <c r="D8" t="n">
-        <v>21.39647226018553</v>
+        <v>21.39646845184359</v>
       </c>
       <c r="E8" t="n">
-        <v>21.5571469221315</v>
+        <v>21.5571430851912</v>
       </c>
       <c r="F8" t="n">
         <v>3309600</v>
@@ -592,16 +592,16 @@
         <v>43760</v>
       </c>
       <c r="B9" t="n">
-        <v>21.28935241699219</v>
+        <v>21.28935432434082</v>
       </c>
       <c r="C9" t="n">
-        <v>21.51251124378966</v>
+        <v>21.51251317113147</v>
       </c>
       <c r="D9" t="n">
-        <v>21.16438231624022</v>
+        <v>21.16438421239258</v>
       </c>
       <c r="E9" t="n">
-        <v>21.45002704469704</v>
+        <v>21.45002896644079</v>
       </c>
       <c r="F9" t="n">
         <v>928900</v>
@@ -632,16 +632,16 @@
         <v>43762</v>
       </c>
       <c r="B11" t="n">
-        <v>20.53061294555664</v>
+        <v>20.53061485290527</v>
       </c>
       <c r="C11" t="n">
-        <v>21.075121051108</v>
+        <v>21.07512300904288</v>
       </c>
       <c r="D11" t="n">
-        <v>20.53061294555664</v>
+        <v>20.53061485290527</v>
       </c>
       <c r="E11" t="n">
-        <v>20.97693061828613</v>
+        <v>20.97693256709887</v>
       </c>
       <c r="F11" t="n">
         <v>2568000</v>
@@ -652,16 +652,16 @@
         <v>43763</v>
       </c>
       <c r="B12" t="n">
-        <v>20.64665603637695</v>
+        <v>20.64665412902832</v>
       </c>
       <c r="C12" t="n">
-        <v>20.78947926662442</v>
+        <v>20.7894773460817</v>
       </c>
       <c r="D12" t="n">
-        <v>20.30745533377737</v>
+        <v>20.30745345776426</v>
       </c>
       <c r="E12" t="n">
-        <v>20.57524527253668</v>
+        <v>20.57524337178501</v>
       </c>
       <c r="F12" t="n">
         <v>1225500</v>
@@ -692,16 +692,16 @@
         <v>43767</v>
       </c>
       <c r="B14" t="n">
-        <v>20.66450881958008</v>
+        <v>20.66451072692871</v>
       </c>
       <c r="C14" t="n">
-        <v>20.84303657758388</v>
+        <v>20.84303850141075</v>
       </c>
       <c r="D14" t="n">
-        <v>20.53061385236067</v>
+        <v>20.5306157473507</v>
       </c>
       <c r="E14" t="n">
-        <v>20.81625690311325</v>
+        <v>20.81625882446833</v>
       </c>
       <c r="F14" t="n">
         <v>1277000</v>
@@ -712,16 +712,16 @@
         <v>43768</v>
       </c>
       <c r="B15" t="n">
-        <v>21.3250617980957</v>
+        <v>21.32505798339844</v>
       </c>
       <c r="C15" t="n">
-        <v>21.3250617980957</v>
+        <v>21.32505798339844</v>
       </c>
       <c r="D15" t="n">
-        <v>20.42349972830643</v>
+        <v>20.42349607488356</v>
       </c>
       <c r="E15" t="n">
-        <v>20.7180693786283</v>
+        <v>20.71806567251184</v>
       </c>
       <c r="F15" t="n">
         <v>1086200</v>
@@ -732,16 +732,16 @@
         <v>43769</v>
       </c>
       <c r="B16" t="n">
-        <v>21.63748168945312</v>
+        <v>21.63747978210449</v>
       </c>
       <c r="C16" t="n">
-        <v>21.63748168945312</v>
+        <v>21.63747978210449</v>
       </c>
       <c r="D16" t="n">
-        <v>20.81625706102618</v>
+        <v>20.81625522606868</v>
       </c>
       <c r="E16" t="n">
-        <v>21.15545946329323</v>
+        <v>21.15545759843496</v>
       </c>
       <c r="F16" t="n">
         <v>554600</v>
@@ -772,16 +772,16 @@
         <v>43773</v>
       </c>
       <c r="B18" t="n">
-        <v>21.60177421569824</v>
+        <v>21.60177803039551</v>
       </c>
       <c r="C18" t="n">
-        <v>21.60177421569824</v>
+        <v>21.60177803039551</v>
       </c>
       <c r="D18" t="n">
-        <v>21.15545658068437</v>
+        <v>21.15546031656558</v>
       </c>
       <c r="E18" t="n">
-        <v>21.38754025263292</v>
+        <v>21.38754402949821</v>
       </c>
       <c r="F18" t="n">
         <v>2002400</v>
@@ -792,16 +792,16 @@
         <v>43774</v>
       </c>
       <c r="B19" t="n">
-        <v>21.69103813171387</v>
+        <v>21.6910400390625</v>
       </c>
       <c r="C19" t="n">
-        <v>21.69103813171387</v>
+        <v>21.6910400390625</v>
       </c>
       <c r="D19" t="n">
-        <v>21.20901593232103</v>
+        <v>21.20901779728422</v>
       </c>
       <c r="E19" t="n">
-        <v>21.51251208483633</v>
+        <v>21.51251397648671</v>
       </c>
       <c r="F19" t="n">
         <v>2102900</v>
@@ -812,16 +812,16 @@
         <v>43775</v>
       </c>
       <c r="B20" t="n">
-        <v>21.42325210571289</v>
+        <v>21.42325019836426</v>
       </c>
       <c r="C20" t="n">
-        <v>21.79815908566555</v>
+        <v>21.79815714493831</v>
       </c>
       <c r="D20" t="n">
-        <v>21.42325210571289</v>
+        <v>21.42325019836426</v>
       </c>
       <c r="E20" t="n">
-        <v>21.69104207600746</v>
+        <v>21.69104014481703</v>
       </c>
       <c r="F20" t="n">
         <v>809000</v>
@@ -832,16 +832,16 @@
         <v>43776</v>
       </c>
       <c r="B21" t="n">
-        <v>21.28935241699219</v>
+        <v>21.28935432434082</v>
       </c>
       <c r="C21" t="n">
-        <v>21.49465812902984</v>
+        <v>21.49466005477216</v>
       </c>
       <c r="D21" t="n">
-        <v>21.22686821789957</v>
+        <v>21.22687011965014</v>
       </c>
       <c r="E21" t="n">
-        <v>21.47680501427003</v>
+        <v>21.47680693841286</v>
       </c>
       <c r="F21" t="n">
         <v>641700</v>
@@ -852,16 +852,16 @@
         <v>43777</v>
       </c>
       <c r="B22" t="n">
-        <v>21.2000904083252</v>
+        <v>21.20009231567383</v>
       </c>
       <c r="C22" t="n">
-        <v>21.26257461290745</v>
+        <v>21.26257652587772</v>
       </c>
       <c r="D22" t="n">
-        <v>20.64665572011528</v>
+        <v>20.64665757767201</v>
       </c>
       <c r="E22" t="n">
-        <v>21.26257461290745</v>
+        <v>21.26257652587772</v>
       </c>
       <c r="F22" t="n">
         <v>1346600</v>
@@ -872,16 +872,16 @@
         <v>43780</v>
       </c>
       <c r="B23" t="n">
-        <v>21.42325210571289</v>
+        <v>21.42325019836426</v>
       </c>
       <c r="C23" t="n">
-        <v>21.42325210571289</v>
+        <v>21.42325019836426</v>
       </c>
       <c r="D23" t="n">
-        <v>20.93230325931714</v>
+        <v>20.93230139567853</v>
       </c>
       <c r="E23" t="n">
-        <v>20.93230325931714</v>
+        <v>20.93230139567853</v>
       </c>
       <c r="F23" t="n">
         <v>717400</v>
@@ -892,16 +892,16 @@
         <v>43781</v>
       </c>
       <c r="B24" t="n">
-        <v>20.89659690856934</v>
+        <v>20.89659309387207</v>
       </c>
       <c r="C24" t="n">
-        <v>21.39647231160594</v>
+        <v>21.39646840565586</v>
       </c>
       <c r="D24" t="n">
-        <v>20.5216899306501</v>
+        <v>20.52168618439253</v>
       </c>
       <c r="E24" t="n">
-        <v>21.39647231160594</v>
+        <v>21.39646840565586</v>
       </c>
       <c r="F24" t="n">
         <v>1578700</v>
@@ -912,16 +912,16 @@
         <v>43782</v>
       </c>
       <c r="B25" t="n">
-        <v>20.42349624633789</v>
+        <v>20.42349815368652</v>
       </c>
       <c r="C25" t="n">
-        <v>20.8787404833246</v>
+        <v>20.87874243318845</v>
       </c>
       <c r="D25" t="n">
-        <v>20.20033740678952</v>
+        <v>20.20033929329736</v>
       </c>
       <c r="E25" t="n">
-        <v>20.8787404833246</v>
+        <v>20.87874243318845</v>
       </c>
       <c r="F25" t="n">
         <v>1400300</v>
@@ -932,16 +932,16 @@
         <v>43783</v>
       </c>
       <c r="B26" t="n">
-        <v>21.2000904083252</v>
+        <v>21.20009231567383</v>
       </c>
       <c r="C26" t="n">
-        <v>21.2000904083252</v>
+        <v>21.20009231567383</v>
       </c>
       <c r="D26" t="n">
-        <v>20.35208611096543</v>
+        <v>20.35208794202006</v>
       </c>
       <c r="E26" t="n">
-        <v>20.53061386911493</v>
+        <v>20.5306157162315</v>
       </c>
       <c r="F26" t="n">
         <v>1359400</v>
@@ -952,16 +952,16 @@
         <v>43787</v>
       </c>
       <c r="B27" t="n">
-        <v>21.36076354980469</v>
+        <v>21.36076545715332</v>
       </c>
       <c r="C27" t="n">
-        <v>21.40539463492381</v>
+        <v>21.40539654625765</v>
       </c>
       <c r="D27" t="n">
-        <v>20.89659277327204</v>
+        <v>20.89659463917386</v>
       </c>
       <c r="E27" t="n">
-        <v>21.2090154768062</v>
+        <v>21.20901737060492</v>
       </c>
       <c r="F27" t="n">
         <v>523400</v>
@@ -972,16 +972,16 @@
         <v>43788</v>
       </c>
       <c r="B28" t="n">
-        <v>21.2715015411377</v>
+        <v>21.27149963378906</v>
       </c>
       <c r="C28" t="n">
-        <v>21.51251350806239</v>
+        <v>21.51251157910298</v>
       </c>
       <c r="D28" t="n">
-        <v>21.06619580749084</v>
+        <v>21.06619391855132</v>
       </c>
       <c r="E28" t="n">
-        <v>21.40539651079578</v>
+        <v>21.4053945914412</v>
       </c>
       <c r="F28" t="n">
         <v>1162900</v>
@@ -992,16 +992,16 @@
         <v>43790</v>
       </c>
       <c r="B29" t="n">
-        <v>21.11082458496094</v>
+        <v>21.11083030700684</v>
       </c>
       <c r="C29" t="n">
-        <v>21.45895351103337</v>
+        <v>21.4589593274389</v>
       </c>
       <c r="D29" t="n">
-        <v>20.97692962996388</v>
+        <v>20.97693531571782</v>
       </c>
       <c r="E29" t="n">
-        <v>21.3875410522971</v>
+        <v>21.38754684934643</v>
       </c>
       <c r="F29" t="n">
         <v>1121600</v>
@@ -1032,16 +1032,16 @@
         <v>43794</v>
       </c>
       <c r="B31" t="n">
-        <v>21.22686958312988</v>
+        <v>21.22687149047852</v>
       </c>
       <c r="C31" t="n">
-        <v>21.22686958312988</v>
+        <v>21.22687149047852</v>
       </c>
       <c r="D31" t="n">
-        <v>20.60202414688262</v>
+        <v>20.60202599808553</v>
       </c>
       <c r="E31" t="n">
-        <v>20.87874063319014</v>
+        <v>20.87874250925751</v>
       </c>
       <c r="F31" t="n">
         <v>2173000</v>
@@ -1052,16 +1052,16 @@
         <v>43795</v>
       </c>
       <c r="B32" t="n">
-        <v>20.93230056762695</v>
+        <v>20.93230247497559</v>
       </c>
       <c r="C32" t="n">
-        <v>21.18223738707788</v>
+        <v>21.18223931720072</v>
       </c>
       <c r="D32" t="n">
-        <v>20.74484625047187</v>
+        <v>20.74484814073969</v>
       </c>
       <c r="E32" t="n">
-        <v>21.18223738707788</v>
+        <v>21.18223931720072</v>
       </c>
       <c r="F32" t="n">
         <v>1173300</v>
@@ -1072,16 +1072,16 @@
         <v>43796</v>
       </c>
       <c r="B33" t="n">
-        <v>20.66450881958008</v>
+        <v>20.66451072692871</v>
       </c>
       <c r="C33" t="n">
-        <v>21.03941574933456</v>
+        <v>21.03941769128736</v>
       </c>
       <c r="D33" t="n">
-        <v>20.66450881958008</v>
+        <v>20.66451072692871</v>
       </c>
       <c r="E33" t="n">
-        <v>20.95015187033266</v>
+        <v>20.95015380404634</v>
       </c>
       <c r="F33" t="n">
         <v>1619200</v>
@@ -1092,16 +1092,16 @@
         <v>43797</v>
       </c>
       <c r="B34" t="n">
-        <v>20.97693252563477</v>
+        <v>20.9769287109375</v>
       </c>
       <c r="C34" t="n">
-        <v>21.19116482371619</v>
+        <v>21.19116097006035</v>
       </c>
       <c r="D34" t="n">
-        <v>20.66450978580341</v>
+        <v>20.66450602792085</v>
       </c>
       <c r="E34" t="n">
-        <v>20.7716267861276</v>
+        <v>20.7716230087656</v>
       </c>
       <c r="F34" t="n">
         <v>581800</v>
@@ -1112,16 +1112,16 @@
         <v>43798</v>
       </c>
       <c r="B35" t="n">
-        <v>21.22686958312988</v>
+        <v>21.22687149047852</v>
       </c>
       <c r="C35" t="n">
-        <v>21.22686958312988</v>
+        <v>21.22687149047852</v>
       </c>
       <c r="D35" t="n">
-        <v>20.76269878492145</v>
+        <v>20.76270065056184</v>
       </c>
       <c r="E35" t="n">
-        <v>20.86088921984892</v>
+        <v>20.86089109431225</v>
       </c>
       <c r="F35" t="n">
         <v>599200</v>
@@ -1152,16 +1152,16 @@
         <v>43802</v>
       </c>
       <c r="B37" t="n">
-        <v>20.84303283691406</v>
+        <v>20.8430347442627</v>
       </c>
       <c r="C37" t="n">
-        <v>21.09296961018332</v>
+        <v>21.09297154040371</v>
       </c>
       <c r="D37" t="n">
-        <v>20.70913789372459</v>
+        <v>20.70913978882048</v>
       </c>
       <c r="E37" t="n">
-        <v>20.96800122354869</v>
+        <v>20.9680031423332</v>
       </c>
       <c r="F37" t="n">
         <v>608900</v>
@@ -1192,16 +1192,16 @@
         <v>43804</v>
       </c>
       <c r="B39" t="n">
-        <v>21.36076354980469</v>
+        <v>21.36076545715332</v>
       </c>
       <c r="C39" t="n">
-        <v>21.37861666487904</v>
+        <v>21.37861857382182</v>
       </c>
       <c r="D39" t="n">
-        <v>20.67343394254289</v>
+        <v>20.67343578851838</v>
       </c>
       <c r="E39" t="n">
-        <v>21.01263631868858</v>
+        <v>21.01263819495218</v>
       </c>
       <c r="F39" t="n">
         <v>1835400</v>
@@ -1232,16 +1232,16 @@
         <v>43808</v>
       </c>
       <c r="B41" t="n">
-        <v>24.18149375915527</v>
+        <v>24.18149566650391</v>
       </c>
       <c r="C41" t="n">
-        <v>24.23505140784727</v>
+        <v>24.23505331942033</v>
       </c>
       <c r="D41" t="n">
-        <v>22.61045520946548</v>
+        <v>22.61045699289629</v>
       </c>
       <c r="E41" t="n">
-        <v>23.08355259685113</v>
+        <v>23.08355441759815</v>
       </c>
       <c r="F41" t="n">
         <v>2077700</v>
@@ -1252,16 +1252,16 @@
         <v>43809</v>
       </c>
       <c r="B42" t="n">
-        <v>23.92263031005859</v>
+        <v>23.92262840270996</v>
       </c>
       <c r="C42" t="n">
-        <v>25.10091058007437</v>
+        <v>25.10090857878158</v>
       </c>
       <c r="D42" t="n">
-        <v>23.77980876870524</v>
+        <v>23.77980687274376</v>
       </c>
       <c r="E42" t="n">
-        <v>24.10115808803382</v>
+        <v>24.10115616645119</v>
       </c>
       <c r="F42" t="n">
         <v>2767000</v>
@@ -1292,16 +1292,16 @@
         <v>43811</v>
       </c>
       <c r="B44" t="n">
-        <v>24.99379348754883</v>
+        <v>24.99378967285156</v>
       </c>
       <c r="C44" t="n">
-        <v>24.99379348754883</v>
+        <v>24.99378967285156</v>
       </c>
       <c r="D44" t="n">
-        <v>23.68161994237666</v>
+        <v>23.68161632795091</v>
       </c>
       <c r="E44" t="n">
-        <v>24.11008456497569</v>
+        <v>24.11008088515518</v>
       </c>
       <c r="F44" t="n">
         <v>2905500</v>
@@ -1312,16 +1312,16 @@
         <v>43812</v>
       </c>
       <c r="B45" t="n">
-        <v>25.2615795135498</v>
+        <v>25.26158332824707</v>
       </c>
       <c r="C45" t="n">
-        <v>25.2615795135498</v>
+        <v>25.26158332824707</v>
       </c>
       <c r="D45" t="n">
-        <v>24.51176568959024</v>
+        <v>24.51176939105973</v>
       </c>
       <c r="E45" t="n">
-        <v>24.9848630340735</v>
+        <v>24.9848668069844</v>
       </c>
       <c r="F45" t="n">
         <v>1395200</v>
@@ -1332,16 +1332,16 @@
         <v>43815</v>
       </c>
       <c r="B46" t="n">
-        <v>25.17231941223145</v>
+        <v>25.17231750488281</v>
       </c>
       <c r="C46" t="n">
-        <v>25.61863712023153</v>
+        <v>25.61863517906466</v>
       </c>
       <c r="D46" t="n">
-        <v>24.91345432435927</v>
+        <v>24.91345243662527</v>
       </c>
       <c r="E46" t="n">
-        <v>25.34191891542328</v>
+        <v>25.34191699522381</v>
       </c>
       <c r="F46" t="n">
         <v>2099900</v>
@@ -1372,16 +1372,16 @@
         <v>43817</v>
       </c>
       <c r="B48" t="n">
-        <v>25.17231941223145</v>
+        <v>25.17231750488281</v>
       </c>
       <c r="C48" t="n">
-        <v>25.21695050200468</v>
+        <v>25.21694859127427</v>
       </c>
       <c r="D48" t="n">
-        <v>24.72600170423136</v>
+        <v>24.72599983070097</v>
       </c>
       <c r="E48" t="n">
-        <v>24.72600170423136</v>
+        <v>24.72599983070097</v>
       </c>
       <c r="F48" t="n">
         <v>1181100</v>
@@ -1392,16 +1392,16 @@
         <v>43818</v>
       </c>
       <c r="B49" t="n">
-        <v>25.17231941223145</v>
+        <v>25.17231750488281</v>
       </c>
       <c r="C49" t="n">
-        <v>25.44903591447276</v>
+        <v>25.44903398615685</v>
       </c>
       <c r="D49" t="n">
-        <v>25.00271820647267</v>
+        <v>25.002716311975</v>
       </c>
       <c r="E49" t="n">
-        <v>25.24373017740878</v>
+        <v>25.24372826464923</v>
       </c>
       <c r="F49" t="n">
         <v>677100</v>
@@ -1452,16 +1452,16 @@
         <v>43825</v>
       </c>
       <c r="B52" t="n">
-        <v>26.22562789916992</v>
+        <v>26.22562599182129</v>
       </c>
       <c r="C52" t="n">
-        <v>26.70765184336195</v>
+        <v>26.70764990095647</v>
       </c>
       <c r="D52" t="n">
-        <v>26.06495495367286</v>
+        <v>26.06495305800972</v>
       </c>
       <c r="E52" t="n">
-        <v>26.2702606917249</v>
+        <v>26.27025878113019</v>
       </c>
       <c r="F52" t="n">
         <v>955400</v>
@@ -1472,16 +1472,16 @@
         <v>43826</v>
       </c>
       <c r="B53" t="n">
-        <v>25.87750053405762</v>
+        <v>25.87749862670898</v>
       </c>
       <c r="C53" t="n">
-        <v>26.57375677222922</v>
+        <v>26.57375481356175</v>
       </c>
       <c r="D53" t="n">
-        <v>25.63648856285588</v>
+        <v>25.63648667327147</v>
       </c>
       <c r="E53" t="n">
-        <v>26.35059791798323</v>
+        <v>26.35059597576409</v>
       </c>
       <c r="F53" t="n">
         <v>963000</v>
@@ -1532,16 +1532,16 @@
         <v>43833</v>
       </c>
       <c r="B56" t="n">
-        <v>26.03853034973145</v>
+        <v>26.03853607177734</v>
       </c>
       <c r="C56" t="n">
-        <v>26.26300043895327</v>
+        <v>26.26300621032715</v>
       </c>
       <c r="D56" t="n">
-        <v>25.25737368570832</v>
+        <v>25.25737923609267</v>
       </c>
       <c r="E56" t="n">
-        <v>26.03853034973145</v>
+        <v>26.03853607177734</v>
       </c>
       <c r="F56" t="n">
         <v>1128400</v>
@@ -1552,16 +1552,16 @@
         <v>43836</v>
       </c>
       <c r="B57" t="n">
-        <v>25.58061408996582</v>
+        <v>25.58061599731445</v>
       </c>
       <c r="C57" t="n">
-        <v>26.00261728947649</v>
+        <v>26.00261922829064</v>
       </c>
       <c r="D57" t="n">
-        <v>25.46389038374238</v>
+        <v>25.46389228238783</v>
       </c>
       <c r="E57" t="n">
-        <v>26.00261728947649</v>
+        <v>26.00261922829064</v>
       </c>
       <c r="F57" t="n">
         <v>445400</v>
@@ -1572,16 +1572,16 @@
         <v>43837</v>
       </c>
       <c r="B58" t="n">
-        <v>25.05086326599121</v>
+        <v>25.05086517333984</v>
       </c>
       <c r="C58" t="n">
-        <v>25.85895529794493</v>
+        <v>25.85895726682091</v>
       </c>
       <c r="D58" t="n">
-        <v>24.76354180685842</v>
+        <v>24.76354369233067</v>
       </c>
       <c r="E58" t="n">
-        <v>25.64346420359534</v>
+        <v>25.64346615606404</v>
       </c>
       <c r="F58" t="n">
         <v>1259500</v>
@@ -1592,16 +1592,16 @@
         <v>43838</v>
       </c>
       <c r="B59" t="n">
-        <v>25.09576034545898</v>
+        <v>25.09575653076172</v>
       </c>
       <c r="C59" t="n">
-        <v>25.40103984863807</v>
+        <v>25.40103598753659</v>
       </c>
       <c r="D59" t="n">
-        <v>24.47622232870483</v>
+        <v>24.47621860818084</v>
       </c>
       <c r="E59" t="n">
-        <v>25.05086529347905</v>
+        <v>25.05086148560608</v>
       </c>
       <c r="F59" t="n">
         <v>1739100</v>
@@ -1612,16 +1612,16 @@
         <v>43839</v>
       </c>
       <c r="B60" t="n">
-        <v>25.49980735778809</v>
+        <v>25.49980354309082</v>
       </c>
       <c r="C60" t="n">
-        <v>25.93078961212821</v>
+        <v>25.93078573295725</v>
       </c>
       <c r="D60" t="n">
-        <v>25.12269745709767</v>
+        <v>25.12269369881495</v>
       </c>
       <c r="E60" t="n">
-        <v>25.12269745709767</v>
+        <v>25.12269369881495</v>
       </c>
       <c r="F60" t="n">
         <v>1769000</v>
@@ -1632,16 +1632,16 @@
         <v>43840</v>
       </c>
       <c r="B61" t="n">
-        <v>25.9936408996582</v>
+        <v>25.99363899230957</v>
       </c>
       <c r="C61" t="n">
-        <v>25.9936408996582</v>
+        <v>25.99363899230957</v>
       </c>
       <c r="D61" t="n">
-        <v>25.51776362289931</v>
+        <v>25.51776175046936</v>
       </c>
       <c r="E61" t="n">
-        <v>25.51776362289931</v>
+        <v>25.51776175046936</v>
       </c>
       <c r="F61" t="n">
         <v>1402200</v>
@@ -1672,16 +1672,16 @@
         <v>43844</v>
       </c>
       <c r="B63" t="n">
-        <v>27.20577812194824</v>
+        <v>27.20577430725098</v>
       </c>
       <c r="C63" t="n">
-        <v>27.33148255491168</v>
+        <v>27.33147872258859</v>
       </c>
       <c r="D63" t="n">
-        <v>26.84662626899083</v>
+        <v>26.84662250465256</v>
       </c>
       <c r="E63" t="n">
-        <v>26.93641466037296</v>
+        <v>26.93641088344488</v>
       </c>
       <c r="F63" t="n">
         <v>723900</v>
@@ -1712,16 +1712,16 @@
         <v>43846</v>
       </c>
       <c r="B65" t="n">
-        <v>28.7950267791748</v>
+        <v>28.79502487182617</v>
       </c>
       <c r="C65" t="n">
-        <v>29.23498972234781</v>
+        <v>29.23498778585654</v>
       </c>
       <c r="D65" t="n">
-        <v>28.24731913721867</v>
+        <v>28.24731726614954</v>
       </c>
       <c r="E65" t="n">
-        <v>28.39098158988137</v>
+        <v>28.39097970929621</v>
       </c>
       <c r="F65" t="n">
         <v>1262700</v>
@@ -1732,16 +1732,16 @@
         <v>43847</v>
       </c>
       <c r="B66" t="n">
-        <v>29.10030746459961</v>
+        <v>29.10030364990234</v>
       </c>
       <c r="C66" t="n">
-        <v>29.41456427598549</v>
+        <v>29.41456042009297</v>
       </c>
       <c r="D66" t="n">
-        <v>28.4717904166855</v>
+        <v>28.47178668437919</v>
       </c>
       <c r="E66" t="n">
-        <v>29.00154005955195</v>
+        <v>29.00153625780189</v>
       </c>
       <c r="F66" t="n">
         <v>1385800</v>
@@ -1792,16 +1792,16 @@
         <v>43852</v>
       </c>
       <c r="B69" t="n">
-        <v>27.60982131958008</v>
+        <v>27.60982513427734</v>
       </c>
       <c r="C69" t="n">
-        <v>28.39097799337256</v>
+        <v>28.39098191599795</v>
       </c>
       <c r="D69" t="n">
-        <v>27.25066951484769</v>
+        <v>27.25067327992292</v>
       </c>
       <c r="E69" t="n">
-        <v>28.02284546687961</v>
+        <v>28.02284933864215</v>
       </c>
       <c r="F69" t="n">
         <v>1068100</v>
@@ -1812,16 +1812,16 @@
         <v>43853</v>
       </c>
       <c r="B70" t="n">
-        <v>28.08570098876953</v>
+        <v>28.0856990814209</v>
       </c>
       <c r="C70" t="n">
-        <v>28.08570098876953</v>
+        <v>28.0856990814209</v>
       </c>
       <c r="D70" t="n">
-        <v>27.14292549220977</v>
+        <v>27.14292364888665</v>
       </c>
       <c r="E70" t="n">
-        <v>27.47514201101373</v>
+        <v>27.47514014512921</v>
       </c>
       <c r="F70" t="n">
         <v>1247300</v>
@@ -1852,16 +1852,16 @@
         <v>43857</v>
       </c>
       <c r="B72" t="n">
-        <v>27.38535308837891</v>
+        <v>27.38535499572754</v>
       </c>
       <c r="C72" t="n">
-        <v>27.69961158108762</v>
+        <v>27.69961351032389</v>
       </c>
       <c r="D72" t="n">
-        <v>26.48747265925173</v>
+        <v>26.48747450406434</v>
       </c>
       <c r="E72" t="n">
-        <v>27.38535308837891</v>
+        <v>27.38535499572754</v>
       </c>
       <c r="F72" t="n">
         <v>1743500</v>
@@ -1912,16 +1912,16 @@
         <v>43860</v>
       </c>
       <c r="B75" t="n">
-        <v>28.9117546081543</v>
+        <v>28.91175079345703</v>
       </c>
       <c r="C75" t="n">
-        <v>29.04643463656161</v>
+        <v>29.0464308040943</v>
       </c>
       <c r="D75" t="n">
-        <v>27.17884485986859</v>
+        <v>27.17884127381625</v>
       </c>
       <c r="E75" t="n">
-        <v>28.28323753349262</v>
+        <v>28.28323380172365</v>
       </c>
       <c r="F75" t="n">
         <v>1060800</v>
@@ -1972,16 +1972,16 @@
         <v>43865</v>
       </c>
       <c r="B78" t="n">
-        <v>29.36966896057129</v>
+        <v>29.36966705322266</v>
       </c>
       <c r="C78" t="n">
-        <v>29.98920866871232</v>
+        <v>29.98920672112904</v>
       </c>
       <c r="D78" t="n">
-        <v>28.92970945420953</v>
+        <v>28.9297075754331</v>
       </c>
       <c r="E78" t="n">
-        <v>29.62107781792014</v>
+        <v>29.62107589424431</v>
       </c>
       <c r="F78" t="n">
         <v>2096800</v>
@@ -2012,16 +2012,16 @@
         <v>43867</v>
       </c>
       <c r="B80" t="n">
-        <v>27.38535308837891</v>
+        <v>27.38535499572754</v>
       </c>
       <c r="C80" t="n">
-        <v>28.65136435644255</v>
+        <v>28.65136635196696</v>
       </c>
       <c r="D80" t="n">
-        <v>26.99028522004307</v>
+        <v>26.99028709987582</v>
       </c>
       <c r="E80" t="n">
-        <v>28.36404289313321</v>
+        <v>28.36404486864612</v>
       </c>
       <c r="F80" t="n">
         <v>4008000</v>
@@ -2072,16 +2072,16 @@
         <v>43872</v>
       </c>
       <c r="B83" t="n">
-        <v>26.84662246704102</v>
+        <v>26.84662628173828</v>
       </c>
       <c r="C83" t="n">
-        <v>26.97232688220252</v>
+        <v>26.97233071476141</v>
       </c>
       <c r="D83" t="n">
-        <v>25.54469697037434</v>
+        <v>25.54470060007807</v>
       </c>
       <c r="E83" t="n">
-        <v>25.96670012376491</v>
+        <v>25.96670381343202</v>
       </c>
       <c r="F83" t="n">
         <v>1581700</v>
@@ -2112,16 +2112,16 @@
         <v>43874</v>
       </c>
       <c r="B85" t="n">
-        <v>27.46616363525391</v>
+        <v>27.46616172790527</v>
       </c>
       <c r="C85" t="n">
-        <v>27.46616363525391</v>
+        <v>27.46616172790527</v>
       </c>
       <c r="D85" t="n">
-        <v>25.85895677654557</v>
+        <v>25.85895498080713</v>
       </c>
       <c r="E85" t="n">
-        <v>26.21811033356874</v>
+        <v>26.21810851288939</v>
       </c>
       <c r="F85" t="n">
         <v>1241900</v>
@@ -2132,16 +2132,16 @@
         <v>43875</v>
       </c>
       <c r="B86" t="n">
-        <v>27.38535308837891</v>
+        <v>27.38535499572754</v>
       </c>
       <c r="C86" t="n">
-        <v>27.78939996651454</v>
+        <v>27.78940190200443</v>
       </c>
       <c r="D86" t="n">
-        <v>26.67602672733435</v>
+        <v>26.67602858527947</v>
       </c>
       <c r="E86" t="n">
-        <v>27.46616246400603</v>
+        <v>27.46616437698292</v>
       </c>
       <c r="F86" t="n">
         <v>912400</v>
@@ -2172,16 +2172,16 @@
         <v>43879</v>
       </c>
       <c r="B88" t="n">
-        <v>28.32812690734863</v>
+        <v>28.32812881469727</v>
       </c>
       <c r="C88" t="n">
-        <v>28.32812690734863</v>
+        <v>28.32812881469727</v>
       </c>
       <c r="D88" t="n">
-        <v>27.31352277405306</v>
+        <v>27.31352461308783</v>
       </c>
       <c r="E88" t="n">
-        <v>27.66369559405021</v>
+        <v>27.66369745666231</v>
       </c>
       <c r="F88" t="n">
         <v>1121500</v>
@@ -2212,16 +2212,16 @@
         <v>43881</v>
       </c>
       <c r="B90" t="n">
-        <v>27.83429336547852</v>
+        <v>27.83429527282715</v>
       </c>
       <c r="C90" t="n">
-        <v>28.08570050272453</v>
+        <v>28.08570242730087</v>
       </c>
       <c r="D90" t="n">
-        <v>27.56492992116358</v>
+        <v>27.56493181005404</v>
       </c>
       <c r="E90" t="n">
-        <v>27.93306076092713</v>
+        <v>27.93306267504381</v>
       </c>
       <c r="F90" t="n">
         <v>884200</v>
@@ -2232,16 +2232,16 @@
         <v>43882</v>
       </c>
       <c r="B91" t="n">
-        <v>27.83429336547852</v>
+        <v>27.83429527282715</v>
       </c>
       <c r="C91" t="n">
-        <v>28.13957284907332</v>
+        <v>28.13957477734126</v>
       </c>
       <c r="D91" t="n">
-        <v>26.91845491469412</v>
+        <v>26.91845675928479</v>
       </c>
       <c r="E91" t="n">
-        <v>27.38535314990628</v>
+        <v>27.38535502649123</v>
       </c>
       <c r="F91" t="n">
         <v>843900</v>
@@ -2252,16 +2252,16 @@
         <v>43887</v>
       </c>
       <c r="B92" t="n">
-        <v>26.17321586608887</v>
+        <v>26.17321395874023</v>
       </c>
       <c r="C92" t="n">
-        <v>26.37972796718084</v>
+        <v>26.37972604478284</v>
       </c>
       <c r="D92" t="n">
-        <v>25.49980550051589</v>
+        <v>25.49980364224141</v>
       </c>
       <c r="E92" t="n">
-        <v>26.29892029887752</v>
+        <v>26.29891838236829</v>
       </c>
       <c r="F92" t="n">
         <v>1328900</v>
@@ -2292,16 +2292,16 @@
         <v>43889</v>
       </c>
       <c r="B94" t="n">
-        <v>25.22146606445312</v>
+        <v>25.22146415710449</v>
       </c>
       <c r="C94" t="n">
-        <v>25.38308484565359</v>
+        <v>25.3830829260827</v>
       </c>
       <c r="D94" t="n">
-        <v>23.41672586200012</v>
+        <v>23.4167240911332</v>
       </c>
       <c r="E94" t="n">
-        <v>25.38308484565359</v>
+        <v>25.3830829260827</v>
       </c>
       <c r="F94" t="n">
         <v>2372900</v>
@@ -2312,16 +2312,16 @@
         <v>43892</v>
       </c>
       <c r="B95" t="n">
-        <v>24.92516136169434</v>
+        <v>24.92516326904297</v>
       </c>
       <c r="C95" t="n">
-        <v>25.27533418726355</v>
+        <v>25.27533612140846</v>
       </c>
       <c r="D95" t="n">
-        <v>24.61090286339248</v>
+        <v>24.61090474669311</v>
       </c>
       <c r="E95" t="n">
-        <v>24.87128901450777</v>
+        <v>24.87129091773393</v>
       </c>
       <c r="F95" t="n">
         <v>2727300</v>
@@ -2332,16 +2332,16 @@
         <v>43893</v>
       </c>
       <c r="B96" t="n">
-        <v>24.64681816101074</v>
+        <v>24.64681625366211</v>
       </c>
       <c r="C96" t="n">
-        <v>25.64346426051859</v>
+        <v>25.64346227604229</v>
       </c>
       <c r="D96" t="n">
-        <v>24.47622040205784</v>
+        <v>24.47621850791129</v>
       </c>
       <c r="E96" t="n">
-        <v>25.36512181043721</v>
+        <v>25.36511984750106</v>
       </c>
       <c r="F96" t="n">
         <v>1967700</v>
@@ -2352,16 +2352,16 @@
         <v>43894</v>
       </c>
       <c r="B97" t="n">
-        <v>26.21810913085938</v>
+        <v>26.21811103820801</v>
       </c>
       <c r="C97" t="n">
-        <v>26.21810913085938</v>
+        <v>26.21811103820801</v>
       </c>
       <c r="D97" t="n">
-        <v>24.7186487505573</v>
+        <v>24.71865054882127</v>
       </c>
       <c r="E97" t="n">
-        <v>25.07780057853394</v>
+        <v>25.07780240292594</v>
       </c>
       <c r="F97" t="n">
         <v>1152200</v>
@@ -2372,16 +2372,16 @@
         <v>43895</v>
       </c>
       <c r="B98" t="n">
-        <v>23.74893760681152</v>
+        <v>23.74893951416016</v>
       </c>
       <c r="C98" t="n">
-        <v>25.96670161020296</v>
+        <v>25.96670369566689</v>
       </c>
       <c r="D98" t="n">
-        <v>23.56038182956102</v>
+        <v>23.56038372176618</v>
       </c>
       <c r="E98" t="n">
-        <v>25.85895520712111</v>
+        <v>25.8589572839316</v>
       </c>
       <c r="F98" t="n">
         <v>2079800</v>
@@ -2392,16 +2392,16 @@
         <v>43896</v>
       </c>
       <c r="B99" t="n">
-        <v>22.4021167755127</v>
+        <v>22.40212059020996</v>
       </c>
       <c r="C99" t="n">
-        <v>23.01267401196428</v>
+        <v>23.012677930629</v>
       </c>
       <c r="D99" t="n">
-        <v>21.49525736153167</v>
+        <v>21.49526102180629</v>
       </c>
       <c r="E99" t="n">
-        <v>22.80616192996282</v>
+        <v>22.80616581346207</v>
       </c>
       <c r="F99" t="n">
         <v>5887000</v>
@@ -2432,16 +2432,16 @@
         <v>43900</v>
       </c>
       <c r="B101" t="n">
-        <v>21.07325172424316</v>
+        <v>21.07325553894043</v>
       </c>
       <c r="C101" t="n">
-        <v>22.07887849488816</v>
+        <v>22.07888249162481</v>
       </c>
       <c r="D101" t="n">
-        <v>19.94192224948163</v>
+        <v>19.94192585938471</v>
       </c>
       <c r="E101" t="n">
-        <v>21.27976551145435</v>
+        <v>21.27976936353491</v>
       </c>
       <c r="F101" t="n">
         <v>2038000</v>
@@ -2452,16 +2452,16 @@
         <v>43901</v>
       </c>
       <c r="B102" t="n">
-        <v>19.57379531860352</v>
+        <v>19.57379341125488</v>
       </c>
       <c r="C102" t="n">
-        <v>20.79491341547675</v>
+        <v>20.7949113891375</v>
       </c>
       <c r="D102" t="n">
-        <v>18.52327500586904</v>
+        <v>18.52327320088729</v>
       </c>
       <c r="E102" t="n">
-        <v>20.77695539344715</v>
+        <v>20.7769533688578</v>
       </c>
       <c r="F102" t="n">
         <v>1408200</v>
@@ -2492,16 +2492,16 @@
         <v>43903</v>
       </c>
       <c r="B104" t="n">
-        <v>19.30442810058594</v>
+        <v>19.3044319152832</v>
       </c>
       <c r="C104" t="n">
-        <v>19.43910981458747</v>
+        <v>19.43911365589884</v>
       </c>
       <c r="D104" t="n">
-        <v>16.17082579116212</v>
+        <v>16.17082898663648</v>
       </c>
       <c r="E104" t="n">
-        <v>18.50531511328205</v>
+        <v>18.5053187700687</v>
       </c>
       <c r="F104" t="n">
         <v>7039400</v>
@@ -2532,16 +2532,16 @@
         <v>43907</v>
       </c>
       <c r="B106" t="n">
-        <v>14.14161777496338</v>
+        <v>14.14161586761475</v>
       </c>
       <c r="C106" t="n">
-        <v>14.76115579510074</v>
+        <v>14.76115380419201</v>
       </c>
       <c r="D106" t="n">
-        <v>13.11803370394132</v>
+        <v>13.11803193464844</v>
       </c>
       <c r="E106" t="n">
-        <v>14.57260000089757</v>
+        <v>14.57259803542027</v>
       </c>
       <c r="F106" t="n">
         <v>3479200</v>
@@ -2592,16 +2592,16 @@
         <v>43910</v>
       </c>
       <c r="B109" t="n">
-        <v>14.35710716247559</v>
+        <v>14.35710906982422</v>
       </c>
       <c r="C109" t="n">
-        <v>14.35710716247559</v>
+        <v>14.35710906982422</v>
       </c>
       <c r="D109" t="n">
-        <v>12.39074949447038</v>
+        <v>12.39075114058745</v>
       </c>
       <c r="E109" t="n">
-        <v>12.57032540036131</v>
+        <v>12.57032707033512</v>
       </c>
       <c r="F109" t="n">
         <v>4777400</v>
@@ -2612,16 +2612,16 @@
         <v>43913</v>
       </c>
       <c r="B110" t="n">
-        <v>12.57032775878906</v>
+        <v>12.57032489776611</v>
       </c>
       <c r="C110" t="n">
-        <v>13.91714859008789</v>
+        <v>13.91714542252677</v>
       </c>
       <c r="D110" t="n">
-        <v>11.51980744187313</v>
+        <v>11.51980481994997</v>
       </c>
       <c r="E110" t="n">
-        <v>13.86327538007026</v>
+        <v>13.86327222477075</v>
       </c>
       <c r="F110" t="n">
         <v>1044300</v>
@@ -2652,16 +2652,16 @@
         <v>43915</v>
       </c>
       <c r="B112" t="n">
-        <v>17.23032569885254</v>
+        <v>17.23032760620117</v>
       </c>
       <c r="C112" t="n">
-        <v>17.86781997352124</v>
+        <v>17.86782195143869</v>
       </c>
       <c r="D112" t="n">
-        <v>12.74990176279834</v>
+        <v>12.74990317417663</v>
       </c>
       <c r="E112" t="n">
-        <v>12.97437186727114</v>
+        <v>12.97437330349765</v>
       </c>
       <c r="F112" t="n">
         <v>1209000</v>
@@ -2672,16 +2672,16 @@
         <v>43916</v>
       </c>
       <c r="B113" t="n">
-        <v>17.41887855529785</v>
+        <v>17.41888046264648</v>
       </c>
       <c r="C113" t="n">
-        <v>17.77803035500661</v>
+        <v>17.77803230168198</v>
       </c>
       <c r="D113" t="n">
-        <v>16.25163477810168</v>
+        <v>16.25163655763836</v>
       </c>
       <c r="E113" t="n">
-        <v>16.61078657781044</v>
+        <v>16.61078839667386</v>
       </c>
       <c r="F113" t="n">
         <v>2254600</v>
@@ -2712,16 +2712,16 @@
         <v>43920</v>
       </c>
       <c r="B115" t="n">
-        <v>15.35375785827637</v>
+        <v>15.35375690460205</v>
       </c>
       <c r="C115" t="n">
-        <v>16.70057869299234</v>
+        <v>16.70057765566239</v>
       </c>
       <c r="D115" t="n">
-        <v>15.27294847118771</v>
+        <v>15.27294752253274</v>
       </c>
       <c r="E115" t="n">
-        <v>15.70393072727972</v>
+        <v>15.70392975185497</v>
       </c>
       <c r="F115" t="n">
         <v>1181300</v>
@@ -2732,16 +2732,16 @@
         <v>43921</v>
       </c>
       <c r="B116" t="n">
-        <v>14.15957450866699</v>
+        <v>14.15957641601562</v>
       </c>
       <c r="C116" t="n">
-        <v>15.61413981710936</v>
+        <v>15.61414192039348</v>
       </c>
       <c r="D116" t="n">
-        <v>13.93510440566049</v>
+        <v>13.93510628277215</v>
       </c>
       <c r="E116" t="n">
-        <v>15.47945809781966</v>
+        <v>15.47946018296163</v>
       </c>
       <c r="F116" t="n">
         <v>1259600</v>
@@ -2772,16 +2772,16 @@
         <v>43923</v>
       </c>
       <c r="B118" t="n">
-        <v>12.74092292785645</v>
+        <v>12.74092197418213</v>
       </c>
       <c r="C118" t="n">
-        <v>12.74990193766703</v>
+        <v>12.74990098332062</v>
       </c>
       <c r="D118" t="n">
-        <v>11.76223397821181</v>
+        <v>11.76223309779361</v>
       </c>
       <c r="E118" t="n">
-        <v>12.57032602288294</v>
+        <v>12.57032508197802</v>
       </c>
       <c r="F118" t="n">
         <v>2636100</v>
@@ -2792,16 +2792,16 @@
         <v>43924</v>
       </c>
       <c r="B119" t="n">
-        <v>12.52543163299561</v>
+        <v>12.52543258666992</v>
       </c>
       <c r="C119" t="n">
-        <v>13.01028702342494</v>
+        <v>13.01028801401567</v>
       </c>
       <c r="D119" t="n">
-        <v>11.61857220725087</v>
+        <v>11.61857309187778</v>
       </c>
       <c r="E119" t="n">
-        <v>12.68705038190055</v>
+        <v>12.68705134788036</v>
       </c>
       <c r="F119" t="n">
         <v>2075200</v>
@@ -2892,16 +2892,16 @@
         <v>43934</v>
       </c>
       <c r="B124" t="n">
-        <v>13.82735824584961</v>
+        <v>13.82735919952393</v>
       </c>
       <c r="C124" t="n">
-        <v>14.50974757649816</v>
+        <v>14.50974857723694</v>
       </c>
       <c r="D124" t="n">
-        <v>13.82735824584961</v>
+        <v>13.82735919952393</v>
       </c>
       <c r="E124" t="n">
-        <v>14.4109801814157</v>
+        <v>14.41098117534248</v>
       </c>
       <c r="F124" t="n">
         <v>1287900</v>
@@ -2912,16 +2912,16 @@
         <v>43935</v>
       </c>
       <c r="B125" t="n">
-        <v>14.79707050323486</v>
+        <v>14.79706859588623</v>
       </c>
       <c r="C125" t="n">
-        <v>15.05745667509506</v>
+        <v>15.05745473418254</v>
       </c>
       <c r="D125" t="n">
-        <v>13.83633862443985</v>
+        <v>13.83633684092996</v>
       </c>
       <c r="E125" t="n">
-        <v>14.40200430896385</v>
+        <v>14.40200245253942</v>
       </c>
       <c r="F125" t="n">
         <v>5420700</v>
@@ -2972,16 +2972,16 @@
         <v>43938</v>
       </c>
       <c r="B128" t="n">
-        <v>13.82735824584961</v>
+        <v>13.82735919952393</v>
       </c>
       <c r="C128" t="n">
-        <v>14.57259893243391</v>
+        <v>14.57259993750755</v>
       </c>
       <c r="D128" t="n">
-        <v>13.5400367829599</v>
+        <v>13.54003771681763</v>
       </c>
       <c r="E128" t="n">
-        <v>14.33915067197878</v>
+        <v>14.33915166095147</v>
       </c>
       <c r="F128" t="n">
         <v>3708800</v>
@@ -3012,16 +3012,16 @@
         <v>43943</v>
       </c>
       <c r="B130" t="n">
-        <v>15.2639684677124</v>
+        <v>15.26396942138672</v>
       </c>
       <c r="C130" t="n">
-        <v>15.71290871676277</v>
+        <v>15.71290969848633</v>
       </c>
       <c r="D130" t="n">
-        <v>14.16855402026955</v>
+        <v>14.1685549055037</v>
       </c>
       <c r="E130" t="n">
-        <v>14.25834241259385</v>
+        <v>14.25834330343787</v>
       </c>
       <c r="F130" t="n">
         <v>2916000</v>
@@ -3072,16 +3072,16 @@
         <v>43948</v>
       </c>
       <c r="B133" t="n">
-        <v>15.69495105743408</v>
+        <v>15.69494819641113</v>
       </c>
       <c r="C133" t="n">
-        <v>15.69495105743408</v>
+        <v>15.69494819641113</v>
       </c>
       <c r="D133" t="n">
-        <v>13.97999940355066</v>
+        <v>13.97999685514519</v>
       </c>
       <c r="E133" t="n">
-        <v>14.49179102524964</v>
+        <v>14.49178838354999</v>
       </c>
       <c r="F133" t="n">
         <v>1099600</v>
@@ -3092,16 +3092,16 @@
         <v>43949</v>
       </c>
       <c r="B134" t="n">
-        <v>17.05972862243652</v>
+        <v>17.05972671508789</v>
       </c>
       <c r="C134" t="n">
-        <v>17.23032638818079</v>
+        <v>17.23032446175861</v>
       </c>
       <c r="D134" t="n">
-        <v>15.61414054377574</v>
+        <v>15.61413879804987</v>
       </c>
       <c r="E134" t="n">
-        <v>15.98227139283316</v>
+        <v>15.98226960594873</v>
       </c>
       <c r="F134" t="n">
         <v>2159200</v>
@@ -3132,16 +3132,16 @@
         <v>43951</v>
       </c>
       <c r="B136" t="n">
-        <v>16.63772583007812</v>
+        <v>16.63772392272949</v>
       </c>
       <c r="C136" t="n">
-        <v>17.14951742717981</v>
+        <v>17.14951546115939</v>
       </c>
       <c r="D136" t="n">
-        <v>16.23367893101306</v>
+        <v>16.23367706998436</v>
       </c>
       <c r="E136" t="n">
-        <v>16.73649151784984</v>
+        <v>16.73648959917871</v>
       </c>
       <c r="F136" t="n">
         <v>3051000</v>
@@ -3152,16 +3152,16 @@
         <v>43955</v>
       </c>
       <c r="B137" t="n">
-        <v>15.82065391540527</v>
+        <v>15.82065486907959</v>
       </c>
       <c r="C137" t="n">
-        <v>16.47610621767813</v>
+        <v>16.47610721086333</v>
       </c>
       <c r="D137" t="n">
-        <v>15.308860632222</v>
+        <v>15.30886155504525</v>
       </c>
       <c r="E137" t="n">
-        <v>16.15286871515628</v>
+        <v>16.15286968885662</v>
       </c>
       <c r="F137" t="n">
         <v>1661100</v>
@@ -3232,16 +3232,16 @@
         <v>43959</v>
       </c>
       <c r="B141" t="n">
-        <v>15.61414241790771</v>
+        <v>15.6141414642334</v>
       </c>
       <c r="C141" t="n">
-        <v>15.70393081658028</v>
+        <v>15.7039298574219</v>
       </c>
       <c r="D141" t="n">
-        <v>14.60851714797452</v>
+        <v>14.60851625572138</v>
       </c>
       <c r="E141" t="n">
-        <v>15.3357999233369</v>
+        <v>15.33579898666308</v>
       </c>
       <c r="F141" t="n">
         <v>1248800</v>
@@ -3272,16 +3272,16 @@
         <v>43963</v>
       </c>
       <c r="B143" t="n">
-        <v>13.91714668273926</v>
+        <v>13.91714763641357</v>
       </c>
       <c r="C143" t="n">
-        <v>14.94970883604119</v>
+        <v>14.94970986047197</v>
       </c>
       <c r="D143" t="n">
-        <v>13.91714668273926</v>
+        <v>13.91714763641357</v>
       </c>
       <c r="E143" t="n">
-        <v>14.84196414334362</v>
+        <v>14.84196516039118</v>
       </c>
       <c r="F143" t="n">
         <v>2058100</v>
@@ -3392,16 +3392,16 @@
         <v>43971</v>
       </c>
       <c r="B149" t="n">
-        <v>15.83861064910889</v>
+        <v>15.8386116027832</v>
       </c>
       <c r="C149" t="n">
-        <v>15.97329408716855</v>
+        <v>15.97329504895243</v>
       </c>
       <c r="D149" t="n">
-        <v>15.41660745255896</v>
+        <v>15.41660838082363</v>
       </c>
       <c r="E149" t="n">
-        <v>15.41660745255896</v>
+        <v>15.41660838082363</v>
       </c>
       <c r="F149" t="n">
         <v>1491300</v>
@@ -3432,16 +3432,16 @@
         <v>43973</v>
       </c>
       <c r="B151" t="n">
-        <v>16.32347106933594</v>
+        <v>16.3234691619873</v>
       </c>
       <c r="C151" t="n">
-        <v>16.64670866281078</v>
+        <v>16.64670671769281</v>
       </c>
       <c r="D151" t="n">
-        <v>15.8924887530838</v>
+        <v>15.89248689609416</v>
       </c>
       <c r="E151" t="n">
-        <v>16.16185227259851</v>
+        <v>16.16185038413455</v>
       </c>
       <c r="F151" t="n">
         <v>2123900</v>
@@ -3472,16 +3472,16 @@
         <v>43977</v>
       </c>
       <c r="B153" t="n">
-        <v>16.60180854797363</v>
+        <v>16.60181045532227</v>
       </c>
       <c r="C153" t="n">
-        <v>17.65232869444154</v>
+        <v>17.65233072248234</v>
       </c>
       <c r="D153" t="n">
-        <v>16.57487151919257</v>
+        <v>16.57487342344646</v>
       </c>
       <c r="E153" t="n">
-        <v>17.23032551896403</v>
+        <v>17.23032749852172</v>
       </c>
       <c r="F153" t="n">
         <v>1845500</v>
@@ -3492,16 +3492,16 @@
         <v>43978</v>
       </c>
       <c r="B154" t="n">
-        <v>17.95760726928711</v>
+        <v>17.95761108398438</v>
       </c>
       <c r="C154" t="n">
-        <v>17.95760726928711</v>
+        <v>17.95761108398438</v>
       </c>
       <c r="D154" t="n">
-        <v>16.40427465151079</v>
+        <v>16.40427813623683</v>
       </c>
       <c r="E154" t="n">
-        <v>16.87117285152926</v>
+        <v>16.87117643543752</v>
       </c>
       <c r="F154" t="n">
         <v>2199800</v>
@@ -3512,16 +3512,16 @@
         <v>43979</v>
       </c>
       <c r="B155" t="n">
-        <v>17.41887855529785</v>
+        <v>17.41888046264648</v>
       </c>
       <c r="C155" t="n">
-        <v>17.87679774214059</v>
+        <v>17.87679969963088</v>
       </c>
       <c r="D155" t="n">
-        <v>17.26623882635027</v>
+        <v>17.26624071698502</v>
       </c>
       <c r="E155" t="n">
-        <v>17.86781873307651</v>
+        <v>17.86782068958361</v>
       </c>
       <c r="F155" t="n">
         <v>2182800</v>
@@ -3552,16 +3552,16 @@
         <v>43983</v>
       </c>
       <c r="B157" t="n">
-        <v>17.77803230285645</v>
+        <v>17.77803421020508</v>
       </c>
       <c r="C157" t="n">
-        <v>18.21799523234643</v>
+        <v>18.21799718689729</v>
       </c>
       <c r="D157" t="n">
-        <v>17.2841987382214</v>
+        <v>17.2842005925882</v>
       </c>
       <c r="E157" t="n">
-        <v>17.2841987382214</v>
+        <v>17.2842005925882</v>
       </c>
       <c r="F157" t="n">
         <v>2465800</v>
@@ -3592,16 +3592,16 @@
         <v>43985</v>
       </c>
       <c r="B159" t="n">
-        <v>18.72080993652344</v>
+        <v>18.7208080291748</v>
       </c>
       <c r="C159" t="n">
-        <v>19.27749492224544</v>
+        <v>19.27749295817959</v>
       </c>
       <c r="D159" t="n">
-        <v>18.15514422716096</v>
+        <v>18.15514237744454</v>
       </c>
       <c r="E159" t="n">
-        <v>18.40655139938553</v>
+        <v>18.40654952405477</v>
       </c>
       <c r="F159" t="n">
         <v>3291000</v>
@@ -3612,16 +3612,16 @@
         <v>43986</v>
       </c>
       <c r="B160" t="n">
-        <v>18.22697257995605</v>
+        <v>18.22697448730469</v>
       </c>
       <c r="C160" t="n">
-        <v>18.82855255424903</v>
+        <v>18.82855452454957</v>
       </c>
       <c r="D160" t="n">
-        <v>18.04739751621806</v>
+        <v>18.04739940477518</v>
       </c>
       <c r="E160" t="n">
-        <v>18.72080785852044</v>
+        <v>18.72080981754612</v>
       </c>
       <c r="F160" t="n">
         <v>1670100</v>
@@ -3632,16 +3632,16 @@
         <v>43987</v>
       </c>
       <c r="B161" t="n">
-        <v>19.70847702026367</v>
+        <v>19.7084789276123</v>
       </c>
       <c r="C161" t="n">
-        <v>19.94192443562303</v>
+        <v>19.94192636556426</v>
       </c>
       <c r="D161" t="n">
-        <v>18.7657014983248</v>
+        <v>18.76570331443342</v>
       </c>
       <c r="E161" t="n">
-        <v>18.85548988792437</v>
+        <v>18.85549171272254</v>
       </c>
       <c r="F161" t="n">
         <v>3626500</v>
@@ -3652,16 +3652,16 @@
         <v>43990</v>
       </c>
       <c r="B162" t="n">
-        <v>19.6635799407959</v>
+        <v>19.66358184814453</v>
       </c>
       <c r="C162" t="n">
-        <v>20.4447366233901</v>
+        <v>20.44473860651019</v>
       </c>
       <c r="D162" t="n">
-        <v>19.43013083694672</v>
+        <v>19.43013272165101</v>
       </c>
       <c r="E162" t="n">
-        <v>20.02273174957505</v>
+        <v>20.02273369176107</v>
       </c>
       <c r="F162" t="n">
         <v>2478400</v>
@@ -3712,16 +3712,16 @@
         <v>43994</v>
       </c>
       <c r="B165" t="n">
-        <v>17.62539100646973</v>
+        <v>17.62539291381836</v>
       </c>
       <c r="C165" t="n">
-        <v>18.0473958787352</v>
+        <v>18.04739783175149</v>
       </c>
       <c r="D165" t="n">
-        <v>16.7454686500491</v>
+        <v>16.74547046217609</v>
       </c>
       <c r="E165" t="n">
-        <v>17.06870613304888</v>
+        <v>17.06870798015533</v>
       </c>
       <c r="F165" t="n">
         <v>2432500</v>
@@ -3732,16 +3732,16 @@
         <v>43997</v>
       </c>
       <c r="B166" t="n">
-        <v>17.95760726928711</v>
+        <v>17.95761108398438</v>
       </c>
       <c r="C166" t="n">
-        <v>18.1820773601532</v>
+        <v>18.18208122253418</v>
       </c>
       <c r="D166" t="n">
-        <v>16.63772375152002</v>
+        <v>16.63772728583717</v>
       </c>
       <c r="E166" t="n">
-        <v>17.32011303326144</v>
+        <v>17.32011671253713</v>
       </c>
       <c r="F166" t="n">
         <v>1760900</v>
@@ -3752,16 +3752,16 @@
         <v>43998</v>
       </c>
       <c r="B167" t="n">
-        <v>18.2718677520752</v>
+        <v>18.27186965942383</v>
       </c>
       <c r="C167" t="n">
-        <v>19.01710846735297</v>
+        <v>19.01711045249518</v>
       </c>
       <c r="D167" t="n">
-        <v>17.91271590963489</v>
+        <v>17.91271777949268</v>
       </c>
       <c r="E167" t="n">
-        <v>18.67591293260638</v>
+        <v>18.67591488213215</v>
       </c>
       <c r="F167" t="n">
         <v>2649300</v>
@@ -3772,16 +3772,16 @@
         <v>43999</v>
       </c>
       <c r="B168" t="n">
-        <v>18.62204360961914</v>
+        <v>18.62203979492188</v>
       </c>
       <c r="C168" t="n">
-        <v>18.82855573849977</v>
+        <v>18.82855188149881</v>
       </c>
       <c r="D168" t="n">
-        <v>18.15514528231145</v>
+        <v>18.15514156325759</v>
       </c>
       <c r="E168" t="n">
-        <v>18.42451049232958</v>
+        <v>18.42450671809668</v>
       </c>
       <c r="F168" t="n">
         <v>1091500</v>
@@ -3792,16 +3792,16 @@
         <v>44000</v>
       </c>
       <c r="B169" t="n">
-        <v>18.85548973083496</v>
+        <v>18.85549163818359</v>
       </c>
       <c r="C169" t="n">
-        <v>19.59175143678953</v>
+        <v>19.59175341861555</v>
       </c>
       <c r="D169" t="n">
-        <v>18.28982579244119</v>
+        <v>18.28982764256943</v>
       </c>
       <c r="E169" t="n">
-        <v>18.54123122614016</v>
+        <v>18.54123310169962</v>
       </c>
       <c r="F169" t="n">
         <v>2623100</v>
@@ -3832,16 +3832,16 @@
         <v>44004</v>
       </c>
       <c r="B171" t="n">
-        <v>18.97221183776855</v>
+        <v>18.97221374511719</v>
       </c>
       <c r="C171" t="n">
-        <v>19.93294529112656</v>
+        <v>19.93294729506138</v>
       </c>
       <c r="D171" t="n">
-        <v>18.95425553156922</v>
+        <v>18.95425743711264</v>
       </c>
       <c r="E171" t="n">
-        <v>19.54685645042052</v>
+        <v>19.54685841554036</v>
       </c>
       <c r="F171" t="n">
         <v>1025800</v>
@@ -3892,16 +3892,16 @@
         <v>44007</v>
       </c>
       <c r="B174" t="n">
-        <v>18.85548973083496</v>
+        <v>18.85549163818359</v>
       </c>
       <c r="C174" t="n">
-        <v>18.85548973083496</v>
+        <v>18.85549163818359</v>
       </c>
       <c r="D174" t="n">
-        <v>18.25390975187214</v>
+        <v>18.25391159836727</v>
       </c>
       <c r="E174" t="n">
-        <v>18.58612627685146</v>
+        <v>18.58612815695233</v>
       </c>
       <c r="F174" t="n">
         <v>846400</v>
@@ -3912,16 +3912,16 @@
         <v>44008</v>
       </c>
       <c r="B175" t="n">
-        <v>18.12820625305176</v>
+        <v>18.12821006774902</v>
       </c>
       <c r="C175" t="n">
-        <v>18.81059558128857</v>
+        <v>18.81059953958022</v>
       </c>
       <c r="D175" t="n">
-        <v>18.12820625305176</v>
+        <v>18.12821006774902</v>
       </c>
       <c r="E175" t="n">
-        <v>18.76570053251384</v>
+        <v>18.76570448135829</v>
       </c>
       <c r="F175" t="n">
         <v>1028300</v>
@@ -3972,16 +3972,16 @@
         <v>44013</v>
       </c>
       <c r="B178" t="n">
-        <v>18.90038299560547</v>
+        <v>18.90038108825684</v>
       </c>
       <c r="C178" t="n">
-        <v>19.20566248897294</v>
+        <v>19.20566055081676</v>
       </c>
       <c r="D178" t="n">
-        <v>18.74774324892174</v>
+        <v>18.74774135697687</v>
       </c>
       <c r="E178" t="n">
-        <v>18.74774324892174</v>
+        <v>18.74774135697687</v>
       </c>
       <c r="F178" t="n">
         <v>691200</v>
@@ -3992,16 +3992,16 @@
         <v>44014</v>
       </c>
       <c r="B179" t="n">
-        <v>19.0171070098877</v>
+        <v>19.01711082458496</v>
       </c>
       <c r="C179" t="n">
-        <v>19.51094054132447</v>
+        <v>19.51094445508126</v>
       </c>
       <c r="D179" t="n">
-        <v>18.89140430281017</v>
+        <v>18.89140809229237</v>
       </c>
       <c r="E179" t="n">
-        <v>19.12485169807673</v>
+        <v>19.12485553438682</v>
       </c>
       <c r="F179" t="n">
         <v>1184800</v>
@@ -4012,16 +4012,16 @@
         <v>44015</v>
       </c>
       <c r="B180" t="n">
-        <v>18.72080993652344</v>
+        <v>18.7208080291748</v>
       </c>
       <c r="C180" t="n">
-        <v>19.19668553519366</v>
+        <v>19.19668357936098</v>
       </c>
       <c r="D180" t="n">
-        <v>18.60408450519475</v>
+        <v>18.60408260973855</v>
       </c>
       <c r="E180" t="n">
-        <v>18.99017341831521</v>
+        <v>18.99017148352279</v>
       </c>
       <c r="F180" t="n">
         <v>998600</v>
@@ -4032,16 +4032,16 @@
         <v>44018</v>
       </c>
       <c r="B181" t="n">
-        <v>18.81059455871582</v>
+        <v>18.81059646606445</v>
       </c>
       <c r="C181" t="n">
-        <v>19.23259771883149</v>
+        <v>19.23259966897022</v>
       </c>
       <c r="D181" t="n">
-        <v>18.47837806612666</v>
+        <v>18.47837993978934</v>
       </c>
       <c r="E181" t="n">
-        <v>19.07097897717032</v>
+        <v>19.07098091092131</v>
       </c>
       <c r="F181" t="n">
         <v>4549800</v>
@@ -4052,16 +4052,16 @@
         <v>44019</v>
       </c>
       <c r="B182" t="n">
-        <v>18.85548973083496</v>
+        <v>18.85549163818359</v>
       </c>
       <c r="C182" t="n">
-        <v>19.14281120510298</v>
+        <v>19.14281314151594</v>
       </c>
       <c r="D182" t="n">
-        <v>18.63101961499169</v>
+        <v>18.63102149963379</v>
       </c>
       <c r="E182" t="n">
-        <v>18.81059639269473</v>
+        <v>18.81059829550213</v>
       </c>
       <c r="F182" t="n">
         <v>1973600</v>
@@ -4072,16 +4072,16 @@
         <v>44020</v>
       </c>
       <c r="B183" t="n">
-        <v>20.1484375</v>
+        <v>20.14843940734863</v>
       </c>
       <c r="C183" t="n">
-        <v>20.47167329299951</v>
+        <v>20.47167523094721</v>
       </c>
       <c r="D183" t="n">
-        <v>18.93629856668151</v>
+        <v>18.93630035928321</v>
       </c>
       <c r="E183" t="n">
-        <v>19.02608695295899</v>
+        <v>19.02608875406049</v>
       </c>
       <c r="F183" t="n">
         <v>3489400</v>
@@ -4092,16 +4092,16 @@
         <v>44021</v>
       </c>
       <c r="B184" t="n">
-        <v>19.9688606262207</v>
+        <v>19.96886253356934</v>
       </c>
       <c r="C184" t="n">
-        <v>20.46269589195806</v>
+        <v>20.46269784647593</v>
       </c>
       <c r="D184" t="n">
-        <v>19.59175077582369</v>
+        <v>19.59175264715225</v>
       </c>
       <c r="E184" t="n">
-        <v>20.23822578368772</v>
+        <v>20.23822771676507</v>
       </c>
       <c r="F184" t="n">
         <v>1601400</v>
@@ -4112,16 +4112,16 @@
         <v>44022</v>
       </c>
       <c r="B185" t="n">
-        <v>19.95090293884277</v>
+        <v>19.95090484619141</v>
       </c>
       <c r="C185" t="n">
-        <v>19.97783996880944</v>
+        <v>19.97784187873331</v>
       </c>
       <c r="D185" t="n">
-        <v>19.51094172481347</v>
+        <v>19.51094359010088</v>
       </c>
       <c r="E185" t="n">
-        <v>19.96886095882055</v>
+        <v>19.96886286788601</v>
       </c>
       <c r="F185" t="n">
         <v>1037600</v>
@@ -4132,16 +4132,16 @@
         <v>44025</v>
       </c>
       <c r="B186" t="n">
-        <v>19.45706939697266</v>
+        <v>19.45707321166992</v>
       </c>
       <c r="C186" t="n">
-        <v>20.33699182591409</v>
+        <v>20.33699581312643</v>
       </c>
       <c r="D186" t="n">
-        <v>19.40319704955632</v>
+        <v>19.40320085369152</v>
       </c>
       <c r="E186" t="n">
-        <v>20.02273332627185</v>
+        <v>20.02273725187156</v>
       </c>
       <c r="F186" t="n">
         <v>1075500</v>
@@ -4152,16 +4152,16 @@
         <v>44026</v>
       </c>
       <c r="B187" t="n">
-        <v>19.57379531860352</v>
+        <v>19.57379341125488</v>
       </c>
       <c r="C187" t="n">
-        <v>19.71745606969787</v>
+        <v>19.71745414835036</v>
       </c>
       <c r="D187" t="n">
-        <v>19.13383405430566</v>
+        <v>19.1338321898286</v>
       </c>
       <c r="E187" t="n">
-        <v>19.45707160055357</v>
+        <v>19.45706970457896</v>
       </c>
       <c r="F187" t="n">
         <v>582100</v>
@@ -4172,16 +4172,16 @@
         <v>44027</v>
       </c>
       <c r="B188" t="n">
-        <v>19.88805198669434</v>
+        <v>19.8880558013916</v>
       </c>
       <c r="C188" t="n">
-        <v>20.15741715413597</v>
+        <v>20.15742102049976</v>
       </c>
       <c r="D188" t="n">
-        <v>19.61868853182378</v>
+        <v>19.61869229485485</v>
       </c>
       <c r="E188" t="n">
-        <v>19.84315864840627</v>
+        <v>19.84316245449261</v>
       </c>
       <c r="F188" t="n">
         <v>878000</v>
@@ -4192,16 +4192,16 @@
         <v>44028</v>
       </c>
       <c r="B189" t="n">
-        <v>19.80724334716797</v>
+        <v>19.80724143981934</v>
       </c>
       <c r="C189" t="n">
-        <v>20.03171347213043</v>
+        <v>20.03171154316633</v>
       </c>
       <c r="D189" t="n">
-        <v>19.2505583963009</v>
+        <v>19.25055654255853</v>
       </c>
       <c r="E189" t="n">
-        <v>19.89703173966718</v>
+        <v>19.89702982367233</v>
       </c>
       <c r="F189" t="n">
         <v>1051500</v>
@@ -4212,16 +4212,16 @@
         <v>44029</v>
       </c>
       <c r="B190" t="n">
-        <v>20.36392974853516</v>
+        <v>20.36392784118652</v>
       </c>
       <c r="C190" t="n">
-        <v>20.36392974853516</v>
+        <v>20.36392784118652</v>
       </c>
       <c r="D190" t="n">
-        <v>19.6186890117534</v>
+        <v>19.61868717420632</v>
       </c>
       <c r="E190" t="n">
-        <v>19.88805247321336</v>
+        <v>19.88805061043686</v>
       </c>
       <c r="F190" t="n">
         <v>1239200</v>
@@ -4232,16 +4232,16 @@
         <v>44032</v>
       </c>
       <c r="B191" t="n">
-        <v>21.47730445861816</v>
+        <v>21.4773006439209</v>
       </c>
       <c r="C191" t="n">
-        <v>21.51321879281369</v>
+        <v>21.51321497173749</v>
       </c>
       <c r="D191" t="n">
-        <v>20.48065642426472</v>
+        <v>20.48065278658737</v>
       </c>
       <c r="E191" t="n">
-        <v>20.49861444764817</v>
+        <v>20.4986108067812</v>
       </c>
       <c r="F191" t="n">
         <v>2793600</v>
@@ -4272,16 +4272,16 @@
         <v>44034</v>
       </c>
       <c r="B193" t="n">
-        <v>20.81286811828613</v>
+        <v>20.8128662109375</v>
       </c>
       <c r="C193" t="n">
-        <v>21.60300212329511</v>
+        <v>21.60300014353641</v>
       </c>
       <c r="D193" t="n">
-        <v>20.59737702601096</v>
+        <v>20.59737513841052</v>
       </c>
       <c r="E193" t="n">
-        <v>21.45036238552882</v>
+        <v>21.45036041975845</v>
       </c>
       <c r="F193" t="n">
         <v>1944500</v>
@@ -4392,16 +4392,16 @@
         <v>44042</v>
       </c>
       <c r="B199" t="n">
-        <v>20.31903648376465</v>
+        <v>20.31903266906738</v>
       </c>
       <c r="C199" t="n">
-        <v>20.46269895009325</v>
+        <v>20.46269510842478</v>
       </c>
       <c r="D199" t="n">
-        <v>19.84316087915773</v>
+        <v>19.84315715380138</v>
       </c>
       <c r="E199" t="n">
-        <v>20.02273596506875</v>
+        <v>20.02273220599896</v>
       </c>
       <c r="F199" t="n">
         <v>1101900</v>
@@ -4432,16 +4432,16 @@
         <v>44046</v>
       </c>
       <c r="B201" t="n">
-        <v>19.26851654052734</v>
+        <v>19.26851463317871</v>
       </c>
       <c r="C201" t="n">
-        <v>20.19333416000914</v>
+        <v>20.19333216111482</v>
       </c>
       <c r="D201" t="n">
-        <v>19.26851654052734</v>
+        <v>19.26851463317871</v>
       </c>
       <c r="E201" t="n">
-        <v>20.10354575895545</v>
+        <v>20.10354376894908</v>
       </c>
       <c r="F201" t="n">
         <v>1387700</v>
@@ -4452,16 +4452,16 @@
         <v>44047</v>
       </c>
       <c r="B202" t="n">
-        <v>19.30442810058594</v>
+        <v>19.3044319152832</v>
       </c>
       <c r="C202" t="n">
-        <v>19.46604684241614</v>
+        <v>19.46605068905046</v>
       </c>
       <c r="D202" t="n">
-        <v>18.59510178090246</v>
+        <v>18.59510545543162</v>
       </c>
       <c r="E202" t="n">
-        <v>19.17872539586063</v>
+        <v>19.17872918571811</v>
       </c>
       <c r="F202" t="n">
         <v>1463900</v>
@@ -4492,16 +4492,16 @@
         <v>44049</v>
       </c>
       <c r="B204" t="n">
-        <v>20.3280143737793</v>
+        <v>20.32801628112793</v>
       </c>
       <c r="C204" t="n">
-        <v>20.44473980012632</v>
+        <v>20.44474171842714</v>
       </c>
       <c r="D204" t="n">
-        <v>19.49298521826279</v>
+        <v>19.49298704726182</v>
       </c>
       <c r="E204" t="n">
-        <v>19.67256200684075</v>
+        <v>19.67256385268922</v>
       </c>
       <c r="F204" t="n">
         <v>1309100</v>
@@ -4512,16 +4512,16 @@
         <v>44050</v>
       </c>
       <c r="B205" t="n">
-        <v>20.40882301330566</v>
+        <v>20.40882110595703</v>
       </c>
       <c r="C205" t="n">
-        <v>20.68716719671059</v>
+        <v>20.68716526334872</v>
       </c>
       <c r="D205" t="n">
-        <v>19.99579881223428</v>
+        <v>19.99579694348568</v>
       </c>
       <c r="E205" t="n">
-        <v>20.3100573245027</v>
+        <v>20.31005542638442</v>
       </c>
       <c r="F205" t="n">
         <v>1932500</v>
@@ -4572,16 +4572,16 @@
         <v>44055</v>
       </c>
       <c r="B208" t="n">
-        <v>19.88805198669434</v>
+        <v>19.8880558013916</v>
       </c>
       <c r="C208" t="n">
-        <v>20.20231049242404</v>
+        <v>20.20231436739875</v>
       </c>
       <c r="D208" t="n">
-        <v>19.67256088028368</v>
+        <v>19.67256465364792</v>
       </c>
       <c r="E208" t="n">
-        <v>20.02273371412961</v>
+        <v>20.02273755465998</v>
       </c>
       <c r="F208" t="n">
         <v>857000</v>
@@ -4632,16 +4632,16 @@
         <v>44060</v>
       </c>
       <c r="B211" t="n">
-        <v>18.96323585510254</v>
+        <v>18.96323776245117</v>
       </c>
       <c r="C211" t="n">
-        <v>19.85213729498017</v>
+        <v>19.85213929173574</v>
       </c>
       <c r="D211" t="n">
-        <v>18.07433270265386</v>
+        <v>18.07433452059538</v>
       </c>
       <c r="E211" t="n">
-        <v>19.72643286744795</v>
+        <v>19.72643485156</v>
       </c>
       <c r="F211" t="n">
         <v>1669900</v>
@@ -4652,16 +4652,16 @@
         <v>44061</v>
       </c>
       <c r="B212" t="n">
-        <v>19.59174919128418</v>
+        <v>19.59175300598145</v>
       </c>
       <c r="C212" t="n">
-        <v>19.60072820039731</v>
+        <v>19.60073201684287</v>
       </c>
       <c r="D212" t="n">
-        <v>18.91833892093718</v>
+        <v>18.91834260451515</v>
       </c>
       <c r="E212" t="n">
-        <v>18.96323396650284</v>
+        <v>18.96323765882229</v>
       </c>
       <c r="F212" t="n">
         <v>1173900</v>
@@ -4672,16 +4672,16 @@
         <v>44062</v>
       </c>
       <c r="B213" t="n">
-        <v>19.34034729003906</v>
+        <v>19.34034538269043</v>
       </c>
       <c r="C213" t="n">
-        <v>19.6725621245536</v>
+        <v>19.67256018444188</v>
       </c>
       <c r="D213" t="n">
-        <v>19.07996111630009</v>
+        <v>19.07995923463079</v>
       </c>
       <c r="E213" t="n">
-        <v>19.49298533490112</v>
+        <v>19.4929834124993</v>
       </c>
       <c r="F213" t="n">
         <v>905000</v>
@@ -4692,16 +4692,16 @@
         <v>44063</v>
       </c>
       <c r="B214" t="n">
-        <v>19.30442810058594</v>
+        <v>19.3044319152832</v>
       </c>
       <c r="C214" t="n">
-        <v>19.45706783313992</v>
+        <v>19.45707167799992</v>
       </c>
       <c r="D214" t="n">
-        <v>18.68489016109379</v>
+        <v>18.68489385336579</v>
       </c>
       <c r="E214" t="n">
-        <v>18.99016962620175</v>
+        <v>18.99017337879923</v>
       </c>
       <c r="F214" t="n">
         <v>1836100</v>
@@ -4752,16 +4752,16 @@
         <v>44068</v>
       </c>
       <c r="B217" t="n">
-        <v>20.85776329040527</v>
+        <v>20.85776138305664</v>
       </c>
       <c r="C217" t="n">
-        <v>20.85776329040527</v>
+        <v>20.85776138305664</v>
       </c>
       <c r="D217" t="n">
-        <v>19.82520107344314</v>
+        <v>19.82519926051768</v>
       </c>
       <c r="E217" t="n">
-        <v>19.9598828039041</v>
+        <v>19.9598809786626</v>
       </c>
       <c r="F217" t="n">
         <v>1628100</v>
@@ -4792,16 +4792,16 @@
         <v>44070</v>
       </c>
       <c r="B219" t="n">
-        <v>20.68716621398926</v>
+        <v>20.68716812133789</v>
       </c>
       <c r="C219" t="n">
-        <v>21.45934222986984</v>
+        <v>21.45934420841279</v>
       </c>
       <c r="D219" t="n">
-        <v>20.28311932989922</v>
+        <v>20.28312119999489</v>
       </c>
       <c r="E219" t="n">
-        <v>21.05529705835083</v>
+        <v>21.05529899964099</v>
       </c>
       <c r="F219" t="n">
         <v>2350400</v>
@@ -4812,16 +4812,16 @@
         <v>44071</v>
       </c>
       <c r="B220" t="n">
-        <v>20.8308277130127</v>
+        <v>20.83082389831543</v>
       </c>
       <c r="C220" t="n">
-        <v>20.89367907227541</v>
+        <v>20.89367524606833</v>
       </c>
       <c r="D220" t="n">
-        <v>20.43575982434136</v>
+        <v>20.43575608199189</v>
       </c>
       <c r="E220" t="n">
-        <v>20.68716697396332</v>
+        <v>20.68716318557428</v>
       </c>
       <c r="F220" t="n">
         <v>1545000</v>
@@ -4832,16 +4832,16 @@
         <v>44074</v>
       </c>
       <c r="B221" t="n">
-        <v>21.16304397583008</v>
+        <v>21.16304206848145</v>
       </c>
       <c r="C221" t="n">
-        <v>21.28874670294423</v>
+        <v>21.28874478426647</v>
       </c>
       <c r="D221" t="n">
-        <v>20.10354466852157</v>
+        <v>20.10354285666178</v>
       </c>
       <c r="E221" t="n">
-        <v>20.20231207558053</v>
+        <v>20.20231025481919</v>
       </c>
       <c r="F221" t="n">
         <v>2917000</v>
@@ -4852,16 +4852,16 @@
         <v>44075</v>
       </c>
       <c r="B222" t="n">
-        <v>23.21919059753418</v>
+        <v>23.21918678283691</v>
       </c>
       <c r="C222" t="n">
-        <v>23.58732147059421</v>
+        <v>23.58731759541647</v>
       </c>
       <c r="D222" t="n">
-        <v>21.27976882785214</v>
+        <v>21.27976533178386</v>
       </c>
       <c r="E222" t="n">
-        <v>21.71973007339777</v>
+        <v>21.71972650504793</v>
       </c>
       <c r="F222" t="n">
         <v>5707300</v>
@@ -4872,16 +4872,16 @@
         <v>44076</v>
       </c>
       <c r="B223" t="n">
-        <v>23.50650978088379</v>
+        <v>23.50651168823242</v>
       </c>
       <c r="C223" t="n">
-        <v>23.74893790644841</v>
+        <v>23.74893983346797</v>
       </c>
       <c r="D223" t="n">
-        <v>22.94084415456635</v>
+        <v>22.94084601601614</v>
       </c>
       <c r="E223" t="n">
-        <v>23.40774238619354</v>
+        <v>23.40774428552806</v>
       </c>
       <c r="F223" t="n">
         <v>2065500</v>
@@ -4892,16 +4892,16 @@
         <v>44077</v>
       </c>
       <c r="B224" t="n">
-        <v>23.34489440917969</v>
+        <v>23.34489250183105</v>
       </c>
       <c r="C224" t="n">
-        <v>23.74894134359783</v>
+        <v>23.74893940323734</v>
       </c>
       <c r="D224" t="n">
-        <v>22.81514474519645</v>
+        <v>22.81514288112997</v>
       </c>
       <c r="E224" t="n">
-        <v>23.52447120504803</v>
+        <v>23.52446928302743</v>
       </c>
       <c r="F224" t="n">
         <v>1703200</v>
@@ -4912,16 +4912,16 @@
         <v>44078</v>
       </c>
       <c r="B225" t="n">
-        <v>22.91390991210938</v>
+        <v>22.91390800476074</v>
       </c>
       <c r="C225" t="n">
-        <v>23.52446890323449</v>
+        <v>23.52446694506307</v>
       </c>
       <c r="D225" t="n">
-        <v>22.50986301722626</v>
+        <v>22.5098611435104</v>
       </c>
       <c r="E225" t="n">
-        <v>23.37182915545321</v>
+        <v>23.37182720998749</v>
       </c>
       <c r="F225" t="n">
         <v>1795000</v>
@@ -4932,16 +4932,16 @@
         <v>44082</v>
       </c>
       <c r="B226" t="n">
-        <v>23.01267623901367</v>
+        <v>23.01267242431641</v>
       </c>
       <c r="C226" t="n">
-        <v>23.34489277433356</v>
+        <v>23.34488890456641</v>
       </c>
       <c r="D226" t="n">
-        <v>22.60863104546211</v>
+        <v>22.60862729774142</v>
       </c>
       <c r="E226" t="n">
-        <v>23.33591376391182</v>
+        <v>23.33590989563307</v>
       </c>
       <c r="F226" t="n">
         <v>1248900</v>
@@ -4972,16 +4972,16 @@
         <v>44084</v>
       </c>
       <c r="B228" t="n">
-        <v>22.56373596191406</v>
+        <v>22.5637378692627</v>
       </c>
       <c r="C228" t="n">
-        <v>23.73996063695625</v>
+        <v>23.73996264373304</v>
       </c>
       <c r="D228" t="n">
-        <v>22.31233052074014</v>
+        <v>22.31233240683706</v>
       </c>
       <c r="E228" t="n">
-        <v>23.27306237110307</v>
+        <v>23.2730643384122</v>
       </c>
       <c r="F228" t="n">
         <v>1912900</v>
@@ -4992,16 +4992,16 @@
         <v>44085</v>
       </c>
       <c r="B229" t="n">
-        <v>22.67148017883301</v>
+        <v>22.67148208618164</v>
       </c>
       <c r="C229" t="n">
-        <v>22.95880163382072</v>
+        <v>22.95880356534168</v>
       </c>
       <c r="D229" t="n">
-        <v>21.98011185741196</v>
+        <v>21.98011370659587</v>
       </c>
       <c r="E229" t="n">
-        <v>22.69841720745222</v>
+        <v>22.69841911706706</v>
       </c>
       <c r="F229" t="n">
         <v>1240800</v>
@@ -5052,16 +5052,16 @@
         <v>44090</v>
       </c>
       <c r="B232" t="n">
-        <v>22.37518119812012</v>
+        <v>22.37517929077148</v>
       </c>
       <c r="C232" t="n">
-        <v>22.99471919687902</v>
+        <v>22.99471723671853</v>
       </c>
       <c r="D232" t="n">
-        <v>22.37518119812012</v>
+        <v>22.37517929077148</v>
       </c>
       <c r="E232" t="n">
-        <v>22.98574018674384</v>
+        <v>22.98573822734875</v>
       </c>
       <c r="F232" t="n">
         <v>850700</v>
@@ -5092,16 +5092,16 @@
         <v>44092</v>
       </c>
       <c r="B234" t="n">
-        <v>21.11814880371094</v>
+        <v>21.1181468963623</v>
       </c>
       <c r="C234" t="n">
-        <v>21.92624087418246</v>
+        <v>21.92623889384858</v>
       </c>
       <c r="D234" t="n">
-        <v>20.83980462840913</v>
+        <v>20.83980274619998</v>
       </c>
       <c r="E234" t="n">
-        <v>21.7017707594642</v>
+        <v>21.70176879940401</v>
       </c>
       <c r="F234" t="n">
         <v>1460500</v>
@@ -5112,16 +5112,16 @@
         <v>44095</v>
       </c>
       <c r="B235" t="n">
-        <v>20.29210090637207</v>
+        <v>20.29209899902344</v>
       </c>
       <c r="C235" t="n">
-        <v>20.9475533011787</v>
+        <v>20.94755133222105</v>
       </c>
       <c r="D235" t="n">
-        <v>20.11252411015899</v>
+        <v>20.11252221968961</v>
       </c>
       <c r="E235" t="n">
-        <v>20.74104118433353</v>
+        <v>20.74103923478691</v>
       </c>
       <c r="F235" t="n">
         <v>1918600</v>
@@ -5132,16 +5132,16 @@
         <v>44096</v>
       </c>
       <c r="B236" t="n">
-        <v>21.54913330078125</v>
+        <v>21.54912948608398</v>
       </c>
       <c r="C236" t="n">
-        <v>21.64790070976596</v>
+        <v>21.64789687758457</v>
       </c>
       <c r="D236" t="n">
-        <v>20.12150308259879</v>
+        <v>20.12149952062525</v>
       </c>
       <c r="E236" t="n">
-        <v>20.39086656383006</v>
+        <v>20.39086295417292</v>
       </c>
       <c r="F236" t="n">
         <v>1607900</v>
@@ -5152,16 +5152,16 @@
         <v>44097</v>
       </c>
       <c r="B237" t="n">
-        <v>20.5704402923584</v>
+        <v>20.57044219970703</v>
       </c>
       <c r="C237" t="n">
-        <v>21.50423675151769</v>
+        <v>21.50423874545054</v>
       </c>
       <c r="D237" t="n">
-        <v>20.5704402923584</v>
+        <v>20.57044219970703</v>
       </c>
       <c r="E237" t="n">
-        <v>21.45934170295946</v>
+        <v>21.45934369272951</v>
       </c>
       <c r="F237" t="n">
         <v>2087300</v>
@@ -5172,16 +5172,16 @@
         <v>44098</v>
       </c>
       <c r="B238" t="n">
-        <v>21.30670166015625</v>
+        <v>21.30670356750488</v>
       </c>
       <c r="C238" t="n">
-        <v>21.45036238835865</v>
+        <v>21.45036430856761</v>
       </c>
       <c r="D238" t="n">
-        <v>20.33699088850455</v>
+        <v>20.33699270904592</v>
       </c>
       <c r="E238" t="n">
-        <v>20.5704399999762</v>
+        <v>20.57044184141563</v>
       </c>
       <c r="F238" t="n">
         <v>1454500</v>
@@ -5192,16 +5192,16 @@
         <v>44099</v>
       </c>
       <c r="B239" t="n">
-        <v>21.44138526916504</v>
+        <v>21.44138336181641</v>
       </c>
       <c r="C239" t="n">
-        <v>21.44138526916504</v>
+        <v>21.44138336181641</v>
       </c>
       <c r="D239" t="n">
-        <v>20.75899760632607</v>
+        <v>20.75899575968019</v>
       </c>
       <c r="E239" t="n">
-        <v>21.18997982893103</v>
+        <v>21.18997794394653</v>
       </c>
       <c r="F239" t="n">
         <v>1659900</v>
@@ -5212,16 +5212,16 @@
         <v>44102</v>
       </c>
       <c r="B240" t="n">
-        <v>21.40547180175781</v>
+        <v>21.40546989440918</v>
       </c>
       <c r="C240" t="n">
-        <v>22.21356392980888</v>
+        <v>22.21356195045467</v>
       </c>
       <c r="D240" t="n">
-        <v>21.34262043916968</v>
+        <v>21.34261853742146</v>
       </c>
       <c r="E240" t="n">
-        <v>21.80951872206894</v>
+        <v>21.80951677871744</v>
       </c>
       <c r="F240" t="n">
         <v>1593300</v>
@@ -5232,16 +5232,16 @@
         <v>44103</v>
       </c>
       <c r="B241" t="n">
-        <v>21.54913330078125</v>
+        <v>21.54912948608398</v>
       </c>
       <c r="C241" t="n">
-        <v>21.92624320204777</v>
+        <v>21.92623932059329</v>
       </c>
       <c r="D241" t="n">
-        <v>21.01938363679801</v>
+        <v>21.01937991587874</v>
       </c>
       <c r="E241" t="n">
-        <v>21.45036589179654</v>
+        <v>21.4503620945834</v>
       </c>
       <c r="F241" t="n">
         <v>2063000</v>
@@ -5252,16 +5252,16 @@
         <v>44104</v>
       </c>
       <c r="B242" t="n">
-        <v>21.27976989746094</v>
+        <v>21.27976608276367</v>
       </c>
       <c r="C242" t="n">
-        <v>21.80054055230032</v>
+        <v>21.8005366442476</v>
       </c>
       <c r="D242" t="n">
-        <v>20.90265999481371</v>
+        <v>20.90265624771869</v>
       </c>
       <c r="E242" t="n">
-        <v>21.54913337967842</v>
+        <v>21.54912951669397</v>
       </c>
       <c r="F242" t="n">
         <v>1374800</v>
@@ -5272,16 +5272,16 @@
         <v>44105</v>
       </c>
       <c r="B243" t="n">
-        <v>21.63891792297363</v>
+        <v>21.63891983032227</v>
       </c>
       <c r="C243" t="n">
-        <v>21.63891792297363</v>
+        <v>21.63891983032227</v>
       </c>
       <c r="D243" t="n">
-        <v>20.99244294070703</v>
+        <v>20.99244479107254</v>
       </c>
       <c r="E243" t="n">
-        <v>21.38751079513985</v>
+        <v>21.38751268032836</v>
       </c>
       <c r="F243" t="n">
         <v>1048600</v>
@@ -5292,16 +5292,16 @@
         <v>44106</v>
       </c>
       <c r="B244" t="n">
-        <v>21.48627853393555</v>
+        <v>21.48628234863281</v>
       </c>
       <c r="C244" t="n">
-        <v>21.48627853393555</v>
+        <v>21.48628234863281</v>
       </c>
       <c r="D244" t="n">
-        <v>21.10018968275046</v>
+        <v>21.10019342890109</v>
       </c>
       <c r="E244" t="n">
-        <v>21.4503624954202</v>
+        <v>21.45036630374089</v>
       </c>
       <c r="F244" t="n">
         <v>795300</v>
@@ -5332,16 +5332,16 @@
         <v>44110</v>
       </c>
       <c r="B246" t="n">
-        <v>21.39649200439453</v>
+        <v>21.3964900970459</v>
       </c>
       <c r="C246" t="n">
-        <v>21.77360187863036</v>
+        <v>21.773599937665</v>
       </c>
       <c r="D246" t="n">
-        <v>21.28874559208239</v>
+        <v>21.2887436943386</v>
       </c>
       <c r="E246" t="n">
-        <v>21.54015274576331</v>
+        <v>21.54015082560832</v>
       </c>
       <c r="F246" t="n">
         <v>753200</v>
@@ -5352,16 +5352,16 @@
         <v>44111</v>
       </c>
       <c r="B247" t="n">
-        <v>21.24385261535645</v>
+        <v>21.24385070800781</v>
       </c>
       <c r="C247" t="n">
-        <v>21.6209624960314</v>
+        <v>21.6209605548245</v>
       </c>
       <c r="D247" t="n">
-        <v>21.03734051018403</v>
+        <v>21.03733862137679</v>
       </c>
       <c r="E247" t="n">
-        <v>21.52219509243974</v>
+        <v>21.52219316010054</v>
       </c>
       <c r="F247" t="n">
         <v>911200</v>
@@ -5372,16 +5372,16 @@
         <v>44112</v>
       </c>
       <c r="B248" t="n">
-        <v>21.47730445861816</v>
+        <v>21.4773006439209</v>
       </c>
       <c r="C248" t="n">
-        <v>21.61198620885127</v>
+        <v>21.61198237023247</v>
       </c>
       <c r="D248" t="n">
-        <v>21.14508787630989</v>
+        <v>21.14508412061937</v>
       </c>
       <c r="E248" t="n">
-        <v>21.34262270838506</v>
+        <v>21.34261891760933</v>
       </c>
       <c r="F248" t="n">
         <v>406500</v>
@@ -5392,16 +5392,16 @@
         <v>44113</v>
       </c>
       <c r="B249" t="n">
-        <v>21.22589492797852</v>
+        <v>21.22589302062988</v>
       </c>
       <c r="C249" t="n">
-        <v>21.75564457136495</v>
+        <v>21.75564261641327</v>
       </c>
       <c r="D249" t="n">
-        <v>21.19895960844539</v>
+        <v>21.19895770351715</v>
       </c>
       <c r="E249" t="n">
-        <v>21.47730208990517</v>
+        <v>21.47730015996521</v>
       </c>
       <c r="F249" t="n">
         <v>541000</v>
@@ -5452,16 +5452,16 @@
         <v>44119</v>
       </c>
       <c r="B252" t="n">
-        <v>22.33926391601562</v>
+        <v>22.33926582336426</v>
       </c>
       <c r="C252" t="n">
-        <v>22.44701031907843</v>
+        <v>22.44701223562656</v>
       </c>
       <c r="D252" t="n">
-        <v>21.60300225156121</v>
+        <v>21.60300409604709</v>
       </c>
       <c r="E252" t="n">
-        <v>21.92623974817865</v>
+        <v>21.92624162026287</v>
       </c>
       <c r="F252" t="n">
         <v>1147000</v>
@@ -5472,16 +5472,16 @@
         <v>44120</v>
       </c>
       <c r="B253" t="n">
-        <v>22.4649715423584</v>
+        <v>22.46496772766113</v>
       </c>
       <c r="C253" t="n">
-        <v>22.4649715423584</v>
+        <v>22.46496772766113</v>
       </c>
       <c r="D253" t="n">
-        <v>22.10581966854425</v>
+        <v>22.10581591483329</v>
       </c>
       <c r="E253" t="n">
-        <v>22.38416215667881</v>
+        <v>22.3841583557035</v>
       </c>
       <c r="F253" t="n">
         <v>716800</v>
@@ -5492,16 +5492,16 @@
         <v>44123</v>
       </c>
       <c r="B254" t="n">
-        <v>22.43803405761719</v>
+        <v>22.43803215026855</v>
       </c>
       <c r="C254" t="n">
-        <v>22.44701306835307</v>
+        <v>22.44701116024117</v>
       </c>
       <c r="D254" t="n">
-        <v>22.17764959656131</v>
+        <v>22.1776477113467</v>
       </c>
       <c r="E254" t="n">
-        <v>22.44701306835307</v>
+        <v>22.44701116024117</v>
       </c>
       <c r="F254" t="n">
         <v>1116900</v>
@@ -5512,16 +5512,16 @@
         <v>44124</v>
       </c>
       <c r="B255" t="n">
-        <v>22.2225399017334</v>
+        <v>22.22254180908203</v>
       </c>
       <c r="C255" t="n">
-        <v>22.57271270973801</v>
+        <v>22.57271464714178</v>
       </c>
       <c r="D255" t="n">
-        <v>22.04296313669101</v>
+        <v>22.04296502862666</v>
       </c>
       <c r="E255" t="n">
-        <v>22.43803099224169</v>
+        <v>22.43803291808581</v>
       </c>
       <c r="F255" t="n">
         <v>1239700</v>
@@ -5552,16 +5552,16 @@
         <v>44126</v>
       </c>
       <c r="B257" t="n">
-        <v>22.2853946685791</v>
+        <v>22.2853889465332</v>
       </c>
       <c r="C257" t="n">
-        <v>22.43803442846956</v>
+        <v>22.43802866723155</v>
       </c>
       <c r="D257" t="n">
-        <v>22.20458528319173</v>
+        <v>22.20457958189462</v>
       </c>
       <c r="E257" t="n">
-        <v>22.38416207573505</v>
+        <v>22.38415632832942</v>
       </c>
       <c r="F257" t="n">
         <v>792800</v>
@@ -5572,16 +5572,16 @@
         <v>44127</v>
       </c>
       <c r="B258" t="n">
-        <v>22.33926391601562</v>
+        <v>22.33926582336426</v>
       </c>
       <c r="C258" t="n">
-        <v>22.67148042226922</v>
+        <v>22.67148235798282</v>
       </c>
       <c r="D258" t="n">
-        <v>21.80053703841453</v>
+        <v>21.80053889976612</v>
       </c>
       <c r="E258" t="n">
-        <v>22.29437058040586</v>
+        <v>22.29437248392145</v>
       </c>
       <c r="F258" t="n">
         <v>1048300</v>
@@ -5612,16 +5612,16 @@
         <v>44131</v>
       </c>
       <c r="B260" t="n">
-        <v>22.27641677856445</v>
+        <v>22.27641296386719</v>
       </c>
       <c r="C260" t="n">
-        <v>22.59965433637809</v>
+        <v>22.59965046632842</v>
       </c>
       <c r="D260" t="n">
-        <v>22.23152343445536</v>
+        <v>22.2315196274458</v>
       </c>
       <c r="E260" t="n">
-        <v>22.37518419069002</v>
+        <v>22.37518035907945</v>
       </c>
       <c r="F260" t="n">
         <v>1111200</v>
@@ -5632,16 +5632,16 @@
         <v>44132</v>
       </c>
       <c r="B261" t="n">
-        <v>21.22589492797852</v>
+        <v>21.22589302062988</v>
       </c>
       <c r="C261" t="n">
-        <v>21.63892085738865</v>
+        <v>21.63891891292571</v>
       </c>
       <c r="D261" t="n">
-        <v>20.74104033809926</v>
+        <v>20.74103847431942</v>
       </c>
       <c r="E261" t="n">
-        <v>21.63892085738865</v>
+        <v>21.63891891292571</v>
       </c>
       <c r="F261" t="n">
         <v>1795600</v>
@@ -5672,16 +5672,16 @@
         <v>44134</v>
       </c>
       <c r="B263" t="n">
-        <v>19.57379531860352</v>
+        <v>19.57379341125488</v>
       </c>
       <c r="C263" t="n">
-        <v>21.04632058617749</v>
+        <v>21.04631853534012</v>
       </c>
       <c r="D263" t="n">
-        <v>19.32238986047402</v>
+        <v>19.32238797762334</v>
       </c>
       <c r="E263" t="n">
-        <v>20.87572280203873</v>
+        <v>20.87572076782509</v>
       </c>
       <c r="F263" t="n">
         <v>2020100</v>
@@ -5692,16 +5692,16 @@
         <v>44138</v>
       </c>
       <c r="B264" t="n">
-        <v>19.69949722290039</v>
+        <v>19.69950103759766</v>
       </c>
       <c r="C264" t="n">
-        <v>20.10354239109712</v>
+        <v>20.10354628403547</v>
       </c>
       <c r="D264" t="n">
-        <v>19.16076861940039</v>
+        <v>19.16077232977588</v>
       </c>
       <c r="E264" t="n">
-        <v>19.43911107472317</v>
+        <v>19.43911483899812</v>
       </c>
       <c r="F264" t="n">
         <v>3577600</v>
@@ -5732,16 +5732,16 @@
         <v>44140</v>
       </c>
       <c r="B266" t="n">
-        <v>21.11814880371094</v>
+        <v>21.1181468963623</v>
       </c>
       <c r="C266" t="n">
-        <v>21.32466089823468</v>
+        <v>21.32465897223429</v>
       </c>
       <c r="D266" t="n">
-        <v>20.61533451369087</v>
+        <v>20.61533265175541</v>
       </c>
       <c r="E266" t="n">
-        <v>20.90265769908994</v>
+        <v>20.90265581120403</v>
       </c>
       <c r="F266" t="n">
         <v>1197100</v>
@@ -5752,16 +5752,16 @@
         <v>44141</v>
       </c>
       <c r="B267" t="n">
-        <v>21.31568336486816</v>
+        <v>21.31568145751953</v>
       </c>
       <c r="C267" t="n">
-        <v>21.50423916483143</v>
+        <v>21.50423724061064</v>
       </c>
       <c r="D267" t="n">
-        <v>20.48963321697414</v>
+        <v>20.4896313835413</v>
       </c>
       <c r="E267" t="n">
-        <v>20.78593372042682</v>
+        <v>20.78593186048072</v>
       </c>
       <c r="F267" t="n">
         <v>615700</v>
@@ -5772,16 +5772,16 @@
         <v>44144</v>
       </c>
       <c r="B268" t="n">
-        <v>21.93522071838379</v>
+        <v>21.93521881103516</v>
       </c>
       <c r="C268" t="n">
-        <v>22.53680071720712</v>
+        <v>22.53679875754888</v>
       </c>
       <c r="D268" t="n">
-        <v>21.59402517199801</v>
+        <v>21.59402329431759</v>
       </c>
       <c r="E268" t="n">
-        <v>21.8364533161293</v>
+        <v>21.83645141736886</v>
       </c>
       <c r="F268" t="n">
         <v>2657700</v>
@@ -5792,16 +5792,16 @@
         <v>44145</v>
       </c>
       <c r="B269" t="n">
-        <v>22.74331283569336</v>
+        <v>22.74331092834473</v>
       </c>
       <c r="C269" t="n">
-        <v>23.10246469063979</v>
+        <v>23.1024627531712</v>
       </c>
       <c r="D269" t="n">
-        <v>21.99807209446534</v>
+        <v>21.99807024961569</v>
       </c>
       <c r="E269" t="n">
-        <v>21.99807209446534</v>
+        <v>21.99807024961569</v>
       </c>
       <c r="F269" t="n">
         <v>2468800</v>
@@ -5812,16 +5812,16 @@
         <v>44146</v>
       </c>
       <c r="B270" t="n">
-        <v>22.9318675994873</v>
+        <v>22.93186569213867</v>
       </c>
       <c r="C270" t="n">
-        <v>23.29101943829578</v>
+        <v>23.29101750107484</v>
       </c>
       <c r="D270" t="n">
-        <v>22.37518096490589</v>
+        <v>22.37517910385943</v>
       </c>
       <c r="E270" t="n">
-        <v>22.62658810835734</v>
+        <v>22.62658622640021</v>
       </c>
       <c r="F270" t="n">
         <v>1813400</v>
@@ -5852,16 +5852,16 @@
         <v>44148</v>
       </c>
       <c r="B272" t="n">
-        <v>23.18327331542969</v>
+        <v>23.18327140808105</v>
       </c>
       <c r="C272" t="n">
-        <v>23.28204071453061</v>
+        <v>23.28203879905612</v>
       </c>
       <c r="D272" t="n">
-        <v>21.8274736087571</v>
+        <v>21.82747181295366</v>
       </c>
       <c r="E272" t="n">
-        <v>21.8274736087571</v>
+        <v>21.82747181295366</v>
       </c>
       <c r="F272" t="n">
         <v>3187800</v>
@@ -5912,16 +5912,16 @@
         <v>44153</v>
       </c>
       <c r="B275" t="n">
-        <v>23.56936264038086</v>
+        <v>23.56936454772949</v>
       </c>
       <c r="C275" t="n">
-        <v>23.85668412046174</v>
+        <v>23.85668605106184</v>
       </c>
       <c r="D275" t="n">
-        <v>22.99471968021909</v>
+        <v>22.99472154106479</v>
       </c>
       <c r="E275" t="n">
-        <v>23.43468091066433</v>
+        <v>23.43468280711386</v>
       </c>
       <c r="F275" t="n">
         <v>2279100</v>
@@ -5932,16 +5932,16 @@
         <v>44154</v>
       </c>
       <c r="B276" t="n">
-        <v>23.60527992248535</v>
+        <v>23.60528182983398</v>
       </c>
       <c r="C276" t="n">
-        <v>23.74894067007731</v>
+        <v>23.74894258903398</v>
       </c>
       <c r="D276" t="n">
-        <v>23.10246559334232</v>
+        <v>23.10246746006266</v>
       </c>
       <c r="E276" t="n">
-        <v>23.4616174623222</v>
+        <v>23.46161935806265</v>
       </c>
       <c r="F276" t="n">
         <v>781800</v>
@@ -5972,16 +5972,16 @@
         <v>44159</v>
       </c>
       <c r="B278" t="n">
-        <v>23.38080596923828</v>
+        <v>23.38080787658691</v>
       </c>
       <c r="C278" t="n">
-        <v>23.668127417466</v>
+        <v>23.66812934825361</v>
       </c>
       <c r="D278" t="n">
-        <v>22.92288676891125</v>
+        <v>22.92288863890396</v>
       </c>
       <c r="E278" t="n">
-        <v>23.2371435325535</v>
+        <v>23.2371454281825</v>
       </c>
       <c r="F278" t="n">
         <v>509000</v>
@@ -5992,16 +5992,16 @@
         <v>44160</v>
       </c>
       <c r="B279" t="n">
-        <v>24.23379325866699</v>
+        <v>24.23379516601562</v>
       </c>
       <c r="C279" t="n">
-        <v>24.24277226871949</v>
+        <v>24.24277417677482</v>
       </c>
       <c r="D279" t="n">
-        <v>23.38080785453246</v>
+        <v>23.38080969474589</v>
       </c>
       <c r="E279" t="n">
-        <v>23.38080785453246</v>
+        <v>23.38080969474589</v>
       </c>
       <c r="F279" t="n">
         <v>1238000</v>
@@ -6012,16 +6012,16 @@
         <v>44161</v>
       </c>
       <c r="B280" t="n">
-        <v>24.0991096496582</v>
+        <v>24.09911155700684</v>
       </c>
       <c r="C280" t="n">
-        <v>24.23379136477807</v>
+        <v>24.23379328278622</v>
       </c>
       <c r="D280" t="n">
-        <v>23.83872351619833</v>
+        <v>23.83872540293844</v>
       </c>
       <c r="E280" t="n">
-        <v>24.17991902124431</v>
+        <v>24.17992093498868</v>
       </c>
       <c r="F280" t="n">
         <v>547400</v>
@@ -6032,16 +6032,16 @@
         <v>44162</v>
       </c>
       <c r="B281" t="n">
-        <v>23.80281257629395</v>
+        <v>23.80281066894531</v>
       </c>
       <c r="C281" t="n">
-        <v>24.20685777911162</v>
+        <v>24.20685583938635</v>
       </c>
       <c r="D281" t="n">
-        <v>23.5693634376883</v>
+        <v>23.56936154904624</v>
       </c>
       <c r="E281" t="n">
-        <v>24.17094344917215</v>
+        <v>24.17094151232473</v>
       </c>
       <c r="F281" t="n">
         <v>418000</v>
@@ -6052,16 +6052,16 @@
         <v>44165</v>
       </c>
       <c r="B282" t="n">
-        <v>22.44700813293457</v>
+        <v>22.4470100402832</v>
       </c>
       <c r="C282" t="n">
-        <v>24.11706608604756</v>
+        <v>24.11706813530298</v>
       </c>
       <c r="D282" t="n">
-        <v>22.36619876665034</v>
+        <v>22.36620066713251</v>
       </c>
       <c r="E282" t="n">
-        <v>23.80280762967232</v>
+        <v>23.80280965222482</v>
       </c>
       <c r="F282" t="n">
         <v>1366700</v>
@@ -6072,16 +6072,16 @@
         <v>44166</v>
       </c>
       <c r="B283" t="n">
-        <v>22.86003303527832</v>
+        <v>22.86003684997559</v>
       </c>
       <c r="C283" t="n">
-        <v>23.08450312421501</v>
+        <v>23.08450697637003</v>
       </c>
       <c r="D283" t="n">
-        <v>22.44700889366883</v>
+        <v>22.44701263944397</v>
       </c>
       <c r="E283" t="n">
-        <v>22.68045799167149</v>
+        <v>22.68046177640273</v>
       </c>
       <c r="F283" t="n">
         <v>2100900</v>
@@ -6112,16 +6112,16 @@
         <v>44168</v>
       </c>
       <c r="B285" t="n">
-        <v>23.68608474731445</v>
+        <v>23.68608856201172</v>
       </c>
       <c r="C285" t="n">
-        <v>23.74893781533046</v>
+        <v>23.74894164015036</v>
       </c>
       <c r="D285" t="n">
-        <v>23.1922512008999</v>
+        <v>23.19225493606416</v>
       </c>
       <c r="E285" t="n">
-        <v>23.52446771012912</v>
+        <v>23.5244714987976</v>
       </c>
       <c r="F285" t="n">
         <v>865200</v>
@@ -6132,16 +6132,16 @@
         <v>44169</v>
       </c>
       <c r="B286" t="n">
-        <v>23.70404434204102</v>
+        <v>23.70404624938965</v>
       </c>
       <c r="C286" t="n">
-        <v>23.88362112316457</v>
+        <v>23.88362304496287</v>
       </c>
       <c r="D286" t="n">
-        <v>23.29999915336967</v>
+        <v>23.30000102820676</v>
       </c>
       <c r="E286" t="n">
-        <v>23.83872607159813</v>
+        <v>23.83872798978394</v>
       </c>
       <c r="F286" t="n">
         <v>518000</v>
@@ -6152,16 +6152,16 @@
         <v>44172</v>
       </c>
       <c r="B287" t="n">
-        <v>23.70404434204102</v>
+        <v>23.70404624938965</v>
       </c>
       <c r="C287" t="n">
-        <v>23.81179075322937</v>
+        <v>23.81179266924783</v>
       </c>
       <c r="D287" t="n">
-        <v>22.985740642689</v>
+        <v>22.98574249223924</v>
       </c>
       <c r="E287" t="n">
-        <v>23.70404434204102</v>
+        <v>23.70404624938965</v>
       </c>
       <c r="F287" t="n">
         <v>838600</v>
@@ -6172,16 +6172,16 @@
         <v>44173</v>
       </c>
       <c r="B288" t="n">
-        <v>23.70404434204102</v>
+        <v>23.70404624938965</v>
       </c>
       <c r="C288" t="n">
-        <v>23.7848537222895</v>
+        <v>23.78485563614047</v>
       </c>
       <c r="D288" t="n">
-        <v>23.39876484167363</v>
+        <v>23.39876672445791</v>
       </c>
       <c r="E288" t="n">
-        <v>23.69506533172773</v>
+        <v>23.69506723835386</v>
       </c>
       <c r="F288" t="n">
         <v>592200</v>
@@ -6192,16 +6192,16 @@
         <v>44174</v>
       </c>
       <c r="B289" t="n">
-        <v>23.03961372375488</v>
+        <v>23.03961181640625</v>
       </c>
       <c r="C289" t="n">
-        <v>23.74894014789352</v>
+        <v>23.74893818182286</v>
       </c>
       <c r="D289" t="n">
-        <v>22.98574137273523</v>
+        <v>22.98573946984645</v>
       </c>
       <c r="E289" t="n">
-        <v>23.74894014789352</v>
+        <v>23.74893818182286</v>
       </c>
       <c r="F289" t="n">
         <v>683100</v>
@@ -6212,16 +6212,16 @@
         <v>44175</v>
       </c>
       <c r="B290" t="n">
-        <v>23.03063201904297</v>
+        <v>23.03063011169434</v>
       </c>
       <c r="C290" t="n">
-        <v>23.14735743059742</v>
+        <v>23.14735551358184</v>
       </c>
       <c r="D290" t="n">
-        <v>22.23151900754186</v>
+        <v>22.23151716637409</v>
       </c>
       <c r="E290" t="n">
-        <v>23.04859003813919</v>
+        <v>23.04858812930331</v>
       </c>
       <c r="F290" t="n">
         <v>501000</v>
@@ -6232,16 +6232,16 @@
         <v>44176</v>
       </c>
       <c r="B291" t="n">
-        <v>23.2102108001709</v>
+        <v>23.21020889282227</v>
       </c>
       <c r="C291" t="n">
-        <v>23.28204117022173</v>
+        <v>23.28203925697028</v>
       </c>
       <c r="D291" t="n">
-        <v>22.50986340774696</v>
+        <v>22.50986155795086</v>
       </c>
       <c r="E291" t="n">
-        <v>22.71637550757171</v>
+        <v>22.71637364080505</v>
       </c>
       <c r="F291" t="n">
         <v>261200</v>
@@ -6252,16 +6252,16 @@
         <v>44179</v>
       </c>
       <c r="B292" t="n">
-        <v>23.8566837310791</v>
+        <v>23.85668563842773</v>
       </c>
       <c r="C292" t="n">
-        <v>24.00932347895211</v>
+        <v>24.00932539850434</v>
       </c>
       <c r="D292" t="n">
-        <v>22.83310054685483</v>
+        <v>22.8331023723677</v>
       </c>
       <c r="E292" t="n">
-        <v>23.29999880065123</v>
+        <v>23.30000066349275</v>
       </c>
       <c r="F292" t="n">
         <v>720600</v>
@@ -6272,16 +6272,16 @@
         <v>44180</v>
       </c>
       <c r="B293" t="n">
-        <v>23.66812896728516</v>
+        <v>23.66813087463379</v>
       </c>
       <c r="C293" t="n">
-        <v>24.01830179117109</v>
+        <v>24.01830372673917</v>
       </c>
       <c r="D293" t="n">
-        <v>23.48855219409846</v>
+        <v>23.48855408697549</v>
       </c>
       <c r="E293" t="n">
-        <v>23.85668303781727</v>
+        <v>23.85668496036094</v>
       </c>
       <c r="F293" t="n">
         <v>453700</v>
@@ -6292,16 +6292,16 @@
         <v>44181</v>
       </c>
       <c r="B294" t="n">
-        <v>23.96442794799805</v>
+        <v>23.96442985534668</v>
       </c>
       <c r="C294" t="n">
-        <v>24.15298200675758</v>
+        <v>24.15298392911338</v>
       </c>
       <c r="D294" t="n">
-        <v>23.50650874627658</v>
+        <v>23.50651061717904</v>
       </c>
       <c r="E294" t="n">
-        <v>23.69506280503611</v>
+        <v>23.69506469094574</v>
       </c>
       <c r="F294" t="n">
         <v>646700</v>
@@ -6312,16 +6312,16 @@
         <v>44182</v>
       </c>
       <c r="B295" t="n">
-        <v>25.07779884338379</v>
+        <v>25.07780265808105</v>
       </c>
       <c r="C295" t="n">
-        <v>25.07779884338379</v>
+        <v>25.07780265808105</v>
       </c>
       <c r="D295" t="n">
-        <v>23.92851136080755</v>
+        <v>23.9285150006815</v>
       </c>
       <c r="E295" t="n">
-        <v>23.95544838825613</v>
+        <v>23.9554520322276</v>
       </c>
       <c r="F295" t="n">
         <v>842600</v>
@@ -6332,16 +6332,16 @@
         <v>44183</v>
       </c>
       <c r="B296" t="n">
-        <v>24.80843734741211</v>
+        <v>24.80843353271484</v>
       </c>
       <c r="C296" t="n">
-        <v>25.42797536908371</v>
+        <v>25.42797145912248</v>
       </c>
       <c r="D296" t="n">
-        <v>24.53009487321171</v>
+        <v>24.53009110131408</v>
       </c>
       <c r="E296" t="n">
-        <v>25.00597215254948</v>
+        <v>25.00596830747805</v>
       </c>
       <c r="F296" t="n">
         <v>1105900</v>
@@ -6352,16 +6352,16 @@
         <v>44186</v>
       </c>
       <c r="B297" t="n">
-        <v>24.10809326171875</v>
+        <v>24.10809135437012</v>
       </c>
       <c r="C297" t="n">
-        <v>24.682736269312</v>
+        <v>24.68273431649961</v>
       </c>
       <c r="D297" t="n">
-        <v>23.56936458581445</v>
+        <v>23.56936272108817</v>
       </c>
       <c r="E297" t="n">
-        <v>24.45826613039948</v>
+        <v>24.45826419534638</v>
       </c>
       <c r="F297" t="n">
         <v>562500</v>
@@ -6392,16 +6392,16 @@
         <v>44188</v>
       </c>
       <c r="B299" t="n">
-        <v>24.82639503479004</v>
+        <v>24.82639312744141</v>
       </c>
       <c r="C299" t="n">
-        <v>25.16759057767708</v>
+        <v>25.16758864411527</v>
       </c>
       <c r="D299" t="n">
-        <v>24.15298467193368</v>
+        <v>24.15298281632145</v>
       </c>
       <c r="E299" t="n">
-        <v>24.92516243603173</v>
+        <v>24.92516052109505</v>
       </c>
       <c r="F299" t="n">
         <v>742900</v>
@@ -6412,16 +6412,16 @@
         <v>44193</v>
       </c>
       <c r="B300" t="n">
-        <v>25.03290748596191</v>
+        <v>25.03290557861328</v>
       </c>
       <c r="C300" t="n">
-        <v>25.22146328074186</v>
+        <v>25.22146135902647</v>
       </c>
       <c r="D300" t="n">
-        <v>24.41337117650056</v>
+        <v>24.41336931635667</v>
       </c>
       <c r="E300" t="n">
-        <v>25.03290748596191</v>
+        <v>25.03290557861328</v>
       </c>
       <c r="F300" t="n">
         <v>654000</v>
@@ -6452,16 +6452,16 @@
         <v>44195</v>
       </c>
       <c r="B302" t="n">
-        <v>26.55075263977051</v>
+        <v>26.55075454711914</v>
       </c>
       <c r="C302" t="n">
-        <v>26.55075263977051</v>
+        <v>26.55075454711914</v>
       </c>
       <c r="D302" t="n">
-        <v>25.1898703190841</v>
+        <v>25.18987212866989</v>
       </c>
       <c r="E302" t="n">
-        <v>25.47826926701746</v>
+        <v>25.47827109732121</v>
       </c>
       <c r="F302" t="n">
         <v>872600</v>
@@ -6472,16 +6472,16 @@
         <v>44200</v>
       </c>
       <c r="B303" t="n">
-        <v>25.62246704101562</v>
+        <v>25.62246894836426</v>
       </c>
       <c r="C303" t="n">
-        <v>26.55075087821333</v>
+        <v>26.55075285466386</v>
       </c>
       <c r="D303" t="n">
-        <v>24.97356773222461</v>
+        <v>24.97356959126887</v>
       </c>
       <c r="E303" t="n">
-        <v>26.55075087821333</v>
+        <v>26.55075285466386</v>
       </c>
       <c r="F303" t="n">
         <v>1053500</v>
@@ -6552,16 +6552,16 @@
         <v>44204</v>
       </c>
       <c r="B307" t="n">
-        <v>23.88306045532227</v>
+        <v>23.88305854797363</v>
       </c>
       <c r="C307" t="n">
-        <v>24.25257181918703</v>
+        <v>24.25256988232849</v>
       </c>
       <c r="D307" t="n">
-        <v>23.53157445530293</v>
+        <v>23.53157257602467</v>
       </c>
       <c r="E307" t="n">
-        <v>23.774909991243</v>
+        <v>23.77490809253147</v>
       </c>
       <c r="F307" t="n">
         <v>884000</v>
@@ -6572,16 +6572,16 @@
         <v>44207</v>
       </c>
       <c r="B308" t="n">
-        <v>23.15304946899414</v>
+        <v>23.15305137634277</v>
       </c>
       <c r="C308" t="n">
-        <v>24.32467056746064</v>
+        <v>24.32467257132744</v>
       </c>
       <c r="D308" t="n">
-        <v>23.02687364619494</v>
+        <v>23.02687554314921</v>
       </c>
       <c r="E308" t="n">
-        <v>23.65774760321121</v>
+        <v>23.65774955213688</v>
       </c>
       <c r="F308" t="n">
         <v>792900</v>
@@ -6612,16 +6612,16 @@
         <v>44209</v>
       </c>
       <c r="B310" t="n">
-        <v>23.88306045532227</v>
+        <v>23.88305854797363</v>
       </c>
       <c r="C310" t="n">
-        <v>24.50492175604312</v>
+        <v>24.50491979903141</v>
       </c>
       <c r="D310" t="n">
-        <v>23.65774856423432</v>
+        <v>23.65774667487954</v>
       </c>
       <c r="E310" t="n">
-        <v>24.45084566450683</v>
+        <v>24.45084371181375</v>
       </c>
       <c r="F310" t="n">
         <v>550500</v>
@@ -6632,16 +6632,16 @@
         <v>44210</v>
       </c>
       <c r="B311" t="n">
-        <v>24.31565856933594</v>
+        <v>24.31566047668457</v>
       </c>
       <c r="C311" t="n">
-        <v>24.51393413116758</v>
+        <v>24.51393605406918</v>
       </c>
       <c r="D311" t="n">
-        <v>23.93713452828578</v>
+        <v>23.93713640594255</v>
       </c>
       <c r="E311" t="n">
-        <v>24.00022158196193</v>
+        <v>24.00022346456732</v>
       </c>
       <c r="F311" t="n">
         <v>755300</v>
@@ -6652,16 +6652,16 @@
         <v>44211</v>
       </c>
       <c r="B312" t="n">
-        <v>23.97318267822266</v>
+        <v>23.97318458557129</v>
       </c>
       <c r="C312" t="n">
-        <v>24.31565595521461</v>
+        <v>24.31565788981102</v>
       </c>
       <c r="D312" t="n">
-        <v>23.54058431181395</v>
+        <v>23.5405861847443</v>
       </c>
       <c r="E312" t="n">
-        <v>24.31565595521461</v>
+        <v>24.31565788981102</v>
       </c>
       <c r="F312" t="n">
         <v>1146400</v>
@@ -6692,16 +6692,16 @@
         <v>44215</v>
       </c>
       <c r="B314" t="n">
-        <v>24.06331062316895</v>
+        <v>24.06331253051758</v>
       </c>
       <c r="C314" t="n">
-        <v>24.51393440473396</v>
+        <v>24.51393634780073</v>
       </c>
       <c r="D314" t="n">
-        <v>23.84700969530363</v>
+        <v>23.84701158550743</v>
       </c>
       <c r="E314" t="n">
-        <v>24.42380930462229</v>
+        <v>24.42381124054541</v>
       </c>
       <c r="F314" t="n">
         <v>512700</v>
@@ -6712,16 +6712,16 @@
         <v>44216</v>
       </c>
       <c r="B315" t="n">
-        <v>23.84700965881348</v>
+        <v>23.84701156616211</v>
       </c>
       <c r="C315" t="n">
-        <v>24.2075100587085</v>
+        <v>24.20751199489094</v>
       </c>
       <c r="D315" t="n">
-        <v>23.59466144167892</v>
+        <v>23.59466332884406</v>
       </c>
       <c r="E315" t="n">
-        <v>24.10837227683804</v>
+        <v>24.10837420509116</v>
       </c>
       <c r="F315" t="n">
         <v>312700</v>
@@ -6752,16 +6752,16 @@
         <v>44218</v>
       </c>
       <c r="B317" t="n">
-        <v>23.36934852600098</v>
+        <v>23.36935043334961</v>
       </c>
       <c r="C317" t="n">
-        <v>23.56762236205009</v>
+        <v>23.56762428558135</v>
       </c>
       <c r="D317" t="n">
-        <v>22.63933851432721</v>
+        <v>22.63934036209422</v>
       </c>
       <c r="E317" t="n">
-        <v>22.90069940189226</v>
+        <v>22.90070127099091</v>
       </c>
       <c r="F317" t="n">
         <v>530800</v>
@@ -6772,16 +6772,16 @@
         <v>44222</v>
       </c>
       <c r="B318" t="n">
-        <v>22.90971183776855</v>
+        <v>22.90971374511719</v>
       </c>
       <c r="C318" t="n">
-        <v>23.47749701431774</v>
+        <v>23.47749896893734</v>
       </c>
       <c r="D318" t="n">
-        <v>22.69341264103586</v>
+        <v>22.69341453037649</v>
       </c>
       <c r="E318" t="n">
-        <v>23.36033559404331</v>
+        <v>23.36033753890864</v>
       </c>
       <c r="F318" t="n">
         <v>474300</v>
@@ -6792,16 +6792,16 @@
         <v>44223</v>
       </c>
       <c r="B319" t="n">
-        <v>22.9818115234375</v>
+        <v>22.98181343078613</v>
       </c>
       <c r="C319" t="n">
-        <v>23.11699830624731</v>
+        <v>23.11700022481562</v>
       </c>
       <c r="D319" t="n">
-        <v>22.71143795781787</v>
+        <v>22.71143984272717</v>
       </c>
       <c r="E319" t="n">
-        <v>22.83761205924127</v>
+        <v>22.83761395462223</v>
       </c>
       <c r="F319" t="n">
         <v>836700</v>
@@ -6812,16 +6812,16 @@
         <v>44224</v>
       </c>
       <c r="B320" t="n">
-        <v>23.7298469543457</v>
+        <v>23.72984886169434</v>
       </c>
       <c r="C320" t="n">
-        <v>23.92812078841674</v>
+        <v>23.92812271170215</v>
       </c>
       <c r="D320" t="n">
-        <v>22.55822587475586</v>
+        <v>22.55822768793238</v>
       </c>
       <c r="E320" t="n">
-        <v>22.95477354289793</v>
+        <v>22.954775387948</v>
       </c>
       <c r="F320" t="n">
         <v>1744800</v>
@@ -6832,16 +6832,16 @@
         <v>44225</v>
       </c>
       <c r="B321" t="n">
-        <v>22.96378898620605</v>
+        <v>22.96378707885742</v>
       </c>
       <c r="C321" t="n">
-        <v>23.96417439627722</v>
+        <v>23.96417240583761</v>
       </c>
       <c r="D321" t="n">
-        <v>22.90070192773191</v>
+        <v>22.90070002562323</v>
       </c>
       <c r="E321" t="n">
-        <v>23.59466300893432</v>
+        <v>23.59466104918594</v>
       </c>
       <c r="F321" t="n">
         <v>872100</v>
@@ -6852,16 +6852,16 @@
         <v>44228</v>
       </c>
       <c r="B322" t="n">
-        <v>23.20712471008301</v>
+        <v>23.20712852478027</v>
       </c>
       <c r="C322" t="n">
-        <v>23.67577385465085</v>
+        <v>23.67577774638284</v>
       </c>
       <c r="D322" t="n">
-        <v>23.09897424633916</v>
+        <v>23.09897804325907</v>
       </c>
       <c r="E322" t="n">
-        <v>23.3062624919321</v>
+        <v>23.30626632292525</v>
       </c>
       <c r="F322" t="n">
         <v>1044300</v>
@@ -6892,16 +6892,16 @@
         <v>44230</v>
       </c>
       <c r="B324" t="n">
-        <v>23.61268997192383</v>
+        <v>23.61268615722656</v>
       </c>
       <c r="C324" t="n">
-        <v>24.10837550976074</v>
+        <v>24.10837161498407</v>
       </c>
       <c r="D324" t="n">
-        <v>23.18910246094226</v>
+        <v>23.18909871467677</v>
       </c>
       <c r="E324" t="n">
-        <v>23.41441438159423</v>
+        <v>23.41441059892895</v>
       </c>
       <c r="F324" t="n">
         <v>1369600</v>
@@ -6952,16 +6952,16 @@
         <v>44235</v>
       </c>
       <c r="B327" t="n">
-        <v>24.06331062316895</v>
+        <v>24.06331253051758</v>
       </c>
       <c r="C327" t="n">
-        <v>24.45985831327097</v>
+        <v>24.45986025205147</v>
       </c>
       <c r="D327" t="n">
-        <v>23.77490995901296</v>
+        <v>23.77491184350187</v>
       </c>
       <c r="E327" t="n">
-        <v>24.37874589506981</v>
+        <v>24.37874782742103</v>
       </c>
       <c r="F327" t="n">
         <v>1394400</v>
@@ -6972,16 +6972,16 @@
         <v>44236</v>
       </c>
       <c r="B328" t="n">
-        <v>24.36072540283203</v>
+        <v>24.3607234954834</v>
       </c>
       <c r="C328" t="n">
-        <v>24.47788684484407</v>
+        <v>24.47788492832216</v>
       </c>
       <c r="D328" t="n">
-        <v>23.4955267363829</v>
+        <v>23.4955248967759</v>
       </c>
       <c r="E328" t="n">
-        <v>24.04528837111627</v>
+        <v>24.04528648846511</v>
       </c>
       <c r="F328" t="n">
         <v>957300</v>
@@ -7012,16 +7012,16 @@
         <v>44238</v>
       </c>
       <c r="B330" t="n">
-        <v>23.1350212097168</v>
+        <v>23.13502311706543</v>
       </c>
       <c r="C330" t="n">
-        <v>24.04528130506361</v>
+        <v>24.04528328745792</v>
       </c>
       <c r="D330" t="n">
-        <v>23.01785980213432</v>
+        <v>23.01786169982368</v>
       </c>
       <c r="E330" t="n">
-        <v>23.79293141004895</v>
+        <v>23.79293337163847</v>
       </c>
       <c r="F330" t="n">
         <v>859100</v>
@@ -7032,16 +7032,16 @@
         <v>44239</v>
       </c>
       <c r="B331" t="n">
-        <v>23.45046043395996</v>
+        <v>23.45046234130859</v>
       </c>
       <c r="C331" t="n">
-        <v>23.68478499095261</v>
+        <v>23.68478691736009</v>
       </c>
       <c r="D331" t="n">
-        <v>22.63933802528891</v>
+        <v>22.63933986666471</v>
       </c>
       <c r="E331" t="n">
-        <v>23.13502346420089</v>
+        <v>23.13502534589338</v>
       </c>
       <c r="F331" t="n">
         <v>808300</v>
@@ -7052,16 +7052,16 @@
         <v>44244</v>
       </c>
       <c r="B332" t="n">
-        <v>23.27021408081055</v>
+        <v>23.27021217346191</v>
       </c>
       <c r="C332" t="n">
-        <v>23.65775084589657</v>
+        <v>23.65774890678339</v>
       </c>
       <c r="D332" t="n">
-        <v>23.23416506863626</v>
+        <v>23.2341631642424</v>
       </c>
       <c r="E332" t="n">
-        <v>23.65775084589657</v>
+        <v>23.65774890678339</v>
       </c>
       <c r="F332" t="n">
         <v>300200</v>
@@ -7072,16 +7072,16 @@
         <v>44245</v>
       </c>
       <c r="B333" t="n">
-        <v>23.10798645019531</v>
+        <v>23.10798835754395</v>
       </c>
       <c r="C333" t="n">
-        <v>23.63070995632475</v>
+        <v>23.63071190681934</v>
       </c>
       <c r="D333" t="n">
-        <v>22.98181234426542</v>
+        <v>22.98181424119957</v>
       </c>
       <c r="E333" t="n">
-        <v>23.35132369934004</v>
+        <v>23.35132562677389</v>
       </c>
       <c r="F333" t="n">
         <v>590700</v>
@@ -7092,16 +7092,16 @@
         <v>44246</v>
       </c>
       <c r="B334" t="n">
-        <v>23.32428550720215</v>
+        <v>23.32428741455078</v>
       </c>
       <c r="C334" t="n">
-        <v>23.4955230205943</v>
+        <v>23.49552494194592</v>
       </c>
       <c r="D334" t="n">
-        <v>22.99983756271411</v>
+        <v>22.99983944353095</v>
       </c>
       <c r="E334" t="n">
-        <v>22.99983756271411</v>
+        <v>22.99983944353095</v>
       </c>
       <c r="F334" t="n">
         <v>553600</v>
@@ -7152,16 +7152,16 @@
         <v>44251</v>
       </c>
       <c r="B337" t="n">
-        <v>23.035888671875</v>
+        <v>23.03589057922363</v>
       </c>
       <c r="C337" t="n">
-        <v>23.50453784654846</v>
+        <v>23.50453979270078</v>
       </c>
       <c r="D337" t="n">
-        <v>22.97280161355231</v>
+        <v>22.97280351567739</v>
       </c>
       <c r="E337" t="n">
-        <v>23.27922594168546</v>
+        <v>23.27922786918218</v>
       </c>
       <c r="F337" t="n">
         <v>586700</v>
@@ -7192,16 +7192,16 @@
         <v>44253</v>
       </c>
       <c r="B339" t="n">
-        <v>21.40463066101074</v>
+        <v>21.40462875366211</v>
       </c>
       <c r="C339" t="n">
-        <v>22.61230259161461</v>
+        <v>22.61230057665135</v>
       </c>
       <c r="D339" t="n">
-        <v>21.09820633718627</v>
+        <v>21.09820445714286</v>
       </c>
       <c r="E339" t="n">
-        <v>22.07155368374829</v>
+        <v>22.07155171697071</v>
       </c>
       <c r="F339" t="n">
         <v>1022900</v>
@@ -7212,16 +7212,16 @@
         <v>44256</v>
       </c>
       <c r="B340" t="n">
-        <v>21.4947566986084</v>
+        <v>21.49475479125977</v>
       </c>
       <c r="C340" t="n">
-        <v>21.84624273043304</v>
+        <v>21.84624079189511</v>
       </c>
       <c r="D340" t="n">
-        <v>20.89993338983125</v>
+        <v>20.89993153526459</v>
       </c>
       <c r="E340" t="n">
-        <v>21.3595698955215</v>
+        <v>21.35956800016874</v>
       </c>
       <c r="F340" t="n">
         <v>1168300</v>
@@ -7232,16 +7232,16 @@
         <v>44257</v>
       </c>
       <c r="B341" t="n">
-        <v>21.41364288330078</v>
+        <v>21.41364097595215</v>
       </c>
       <c r="C341" t="n">
-        <v>21.87327935916252</v>
+        <v>21.8732774108733</v>
       </c>
       <c r="D341" t="n">
-        <v>20.54844430550417</v>
+        <v>20.54844247522021</v>
       </c>
       <c r="E341" t="n">
-        <v>21.36857947253393</v>
+        <v>21.36857756919917</v>
       </c>
       <c r="F341" t="n">
         <v>1430800</v>
@@ -7312,16 +7312,16 @@
         <v>44263</v>
       </c>
       <c r="B345" t="n">
-        <v>20.72869300842285</v>
+        <v>20.72869682312012</v>
       </c>
       <c r="C345" t="n">
-        <v>21.58487884202022</v>
+        <v>21.58488281428119</v>
       </c>
       <c r="D345" t="n">
-        <v>20.61153158690618</v>
+        <v>20.61153538004225</v>
       </c>
       <c r="E345" t="n">
-        <v>21.13425508096755</v>
+        <v>21.13425897030032</v>
       </c>
       <c r="F345" t="n">
         <v>1680600</v>
@@ -7372,16 +7372,16 @@
         <v>44266</v>
       </c>
       <c r="B348" t="n">
-        <v>21.4947566986084</v>
+        <v>21.49475479125977</v>
       </c>
       <c r="C348" t="n">
-        <v>21.67500519639311</v>
+        <v>21.67500327305003</v>
       </c>
       <c r="D348" t="n">
-        <v>20.66560879561701</v>
+        <v>20.66560696184325</v>
       </c>
       <c r="E348" t="n">
-        <v>21.07116920487772</v>
+        <v>21.07116733511634</v>
       </c>
       <c r="F348" t="n">
         <v>2008400</v>
@@ -7392,16 +7392,16 @@
         <v>44267</v>
       </c>
       <c r="B349" t="n">
-        <v>21.33252906799316</v>
+        <v>21.3325309753418</v>
       </c>
       <c r="C349" t="n">
-        <v>21.89130329201072</v>
+        <v>21.89130524931954</v>
       </c>
       <c r="D349" t="n">
-        <v>20.97203040039792</v>
+        <v>20.97203227551425</v>
       </c>
       <c r="E349" t="n">
-        <v>21.53080290542224</v>
+        <v>21.5308048304986</v>
       </c>
       <c r="F349" t="n">
         <v>748600</v>
@@ -7412,16 +7412,16 @@
         <v>44270</v>
       </c>
       <c r="B350" t="n">
-        <v>21.85525321960449</v>
+        <v>21.85525512695312</v>
       </c>
       <c r="C350" t="n">
-        <v>22.05352706296538</v>
+        <v>22.05352898761774</v>
       </c>
       <c r="D350" t="n">
-        <v>21.2063555985198</v>
+        <v>21.20635744923793</v>
       </c>
       <c r="E350" t="n">
-        <v>21.34154238803828</v>
+        <v>21.34154425055442</v>
       </c>
       <c r="F350" t="n">
         <v>500800</v>
@@ -7432,16 +7432,16 @@
         <v>44271</v>
       </c>
       <c r="B351" t="n">
-        <v>21.17030715942383</v>
+        <v>21.1703052520752</v>
       </c>
       <c r="C351" t="n">
-        <v>21.99044238600779</v>
+        <v>21.99044040476869</v>
       </c>
       <c r="D351" t="n">
-        <v>20.75573406422467</v>
+        <v>20.7557321942272</v>
       </c>
       <c r="E351" t="n">
-        <v>21.93636800815431</v>
+        <v>21.93636603178707</v>
       </c>
       <c r="F351" t="n">
         <v>624200</v>
@@ -7452,16 +7452,16 @@
         <v>44272</v>
       </c>
       <c r="B352" t="n">
-        <v>21.31450843811035</v>
+        <v>21.31450462341309</v>
       </c>
       <c r="C352" t="n">
-        <v>21.45870793717037</v>
+        <v>21.45870409666546</v>
       </c>
       <c r="D352" t="n">
-        <v>20.61153630994115</v>
+        <v>20.61153262105612</v>
       </c>
       <c r="E352" t="n">
-        <v>21.15228357191942</v>
+        <v>21.15227978625584</v>
       </c>
       <c r="F352" t="n">
         <v>714100</v>
@@ -7472,16 +7472,16 @@
         <v>44273</v>
       </c>
       <c r="B353" t="n">
-        <v>20.99005889892578</v>
+        <v>20.99005699157715</v>
       </c>
       <c r="C353" t="n">
-        <v>21.94538094050315</v>
+        <v>21.94537894634523</v>
       </c>
       <c r="D353" t="n">
-        <v>20.81882136161689</v>
+        <v>20.81881946982847</v>
       </c>
       <c r="E353" t="n">
-        <v>21.66599464625754</v>
+        <v>21.66599267748721</v>
       </c>
       <c r="F353" t="n">
         <v>1527100</v>
@@ -7492,16 +7492,16 @@
         <v>44274</v>
       </c>
       <c r="B354" t="n">
-        <v>21.125244140625</v>
+        <v>21.12524223327637</v>
       </c>
       <c r="C354" t="n">
-        <v>21.48574283538105</v>
+        <v>21.48574089548384</v>
       </c>
       <c r="D354" t="n">
-        <v>20.70165667016744</v>
+        <v>20.70165480106353</v>
       </c>
       <c r="E354" t="n">
-        <v>21.03511903718764</v>
+        <v>21.0351171379762</v>
       </c>
       <c r="F354" t="n">
         <v>1593400</v>
@@ -7512,16 +7512,16 @@
         <v>44277</v>
       </c>
       <c r="B355" t="n">
-        <v>22.20673942565918</v>
+        <v>22.20674324035645</v>
       </c>
       <c r="C355" t="n">
-        <v>22.25180283525269</v>
+        <v>22.25180665769099</v>
       </c>
       <c r="D355" t="n">
-        <v>20.99906755244622</v>
+        <v>20.99907115968833</v>
       </c>
       <c r="E355" t="n">
-        <v>21.02610559820233</v>
+        <v>21.02610921008906</v>
       </c>
       <c r="F355" t="n">
         <v>2913300</v>
@@ -7552,16 +7552,16 @@
         <v>44279</v>
       </c>
       <c r="B357" t="n">
-        <v>21.54883003234863</v>
+        <v>21.54883193969727</v>
       </c>
       <c r="C357" t="n">
-        <v>22.40501594208629</v>
+        <v>22.40501792521839</v>
       </c>
       <c r="D357" t="n">
-        <v>21.4947556575316</v>
+        <v>21.49475756009396</v>
       </c>
       <c r="E357" t="n">
-        <v>22.12562794771264</v>
+        <v>22.12562990611531</v>
       </c>
       <c r="F357" t="n">
         <v>1550100</v>
@@ -7572,16 +7572,16 @@
         <v>44280</v>
       </c>
       <c r="B358" t="n">
-        <v>21.90932846069336</v>
+        <v>21.90933036804199</v>
       </c>
       <c r="C358" t="n">
-        <v>22.41402834943919</v>
+        <v>22.41403030072521</v>
       </c>
       <c r="D358" t="n">
-        <v>20.91795576657742</v>
+        <v>20.91795758762066</v>
       </c>
       <c r="E358" t="n">
-        <v>21.57586781458656</v>
+        <v>21.57586969290529</v>
       </c>
       <c r="F358" t="n">
         <v>1774000</v>
@@ -7592,16 +7592,16 @@
         <v>44281</v>
       </c>
       <c r="B359" t="n">
-        <v>21.35956764221191</v>
+        <v>21.35956573486328</v>
       </c>
       <c r="C359" t="n">
-        <v>22.11661572242658</v>
+        <v>22.1166137474757</v>
       </c>
       <c r="D359" t="n">
-        <v>21.01709261026118</v>
+        <v>21.01709073349459</v>
       </c>
       <c r="E359" t="n">
-        <v>21.94537820645121</v>
+        <v>21.94537624679136</v>
       </c>
       <c r="F359" t="n">
         <v>1291300</v>
@@ -7612,16 +7612,16 @@
         <v>44284</v>
       </c>
       <c r="B360" t="n">
-        <v>20.36819458007812</v>
+        <v>20.36819839477539</v>
       </c>
       <c r="C360" t="n">
-        <v>21.26042943105189</v>
+        <v>21.2604334128531</v>
       </c>
       <c r="D360" t="n">
-        <v>20.15189537853842</v>
+        <v>20.15189915272566</v>
       </c>
       <c r="E360" t="n">
-        <v>21.26042943105189</v>
+        <v>21.2604334128531</v>
       </c>
       <c r="F360" t="n">
         <v>2284900</v>
@@ -7632,16 +7632,16 @@
         <v>44285</v>
       </c>
       <c r="B361" t="n">
-        <v>22.2337760925293</v>
+        <v>22.23377799987793</v>
       </c>
       <c r="C361" t="n">
-        <v>22.2337760925293</v>
+        <v>22.23377799987793</v>
       </c>
       <c r="D361" t="n">
-        <v>20.28708161264534</v>
+        <v>20.28708335299467</v>
       </c>
       <c r="E361" t="n">
-        <v>20.33214330045091</v>
+        <v>20.33214504466591</v>
       </c>
       <c r="F361" t="n">
         <v>1408700</v>
@@ -7652,16 +7652,16 @@
         <v>44286</v>
       </c>
       <c r="B362" t="n">
-        <v>22.20673942565918</v>
+        <v>22.20674324035645</v>
       </c>
       <c r="C362" t="n">
-        <v>22.63032688087157</v>
+        <v>22.63033076833314</v>
       </c>
       <c r="D362" t="n">
-        <v>21.82821538004029</v>
+        <v>21.8282191297143</v>
       </c>
       <c r="E362" t="n">
-        <v>21.99945289850899</v>
+        <v>21.99945667759835</v>
       </c>
       <c r="F362" t="n">
         <v>1238700</v>
@@ -7672,16 +7672,16 @@
         <v>44287</v>
       </c>
       <c r="B363" t="n">
-        <v>21.69302749633789</v>
+        <v>21.69302940368652</v>
       </c>
       <c r="C363" t="n">
-        <v>22.5311879636236</v>
+        <v>22.53118994466708</v>
       </c>
       <c r="D363" t="n">
-        <v>21.57586607528407</v>
+        <v>21.57586797233134</v>
       </c>
       <c r="E363" t="n">
-        <v>22.35093777231733</v>
+        <v>22.35093973751239</v>
       </c>
       <c r="F363" t="n">
         <v>809500</v>
@@ -7772,16 +7772,16 @@
         <v>44295</v>
       </c>
       <c r="B368" t="n">
-        <v>23.18910026550293</v>
+        <v>23.1890983581543</v>
       </c>
       <c r="C368" t="n">
-        <v>23.18910026550293</v>
+        <v>23.1890983581543</v>
       </c>
       <c r="D368" t="n">
-        <v>22.7024274568473</v>
+        <v>22.70242558952845</v>
       </c>
       <c r="E368" t="n">
-        <v>22.8015635236328</v>
+        <v>22.80156164815982</v>
       </c>
       <c r="F368" t="n">
         <v>389400</v>
@@ -7812,16 +7812,16 @@
         <v>44299</v>
       </c>
       <c r="B370" t="n">
-        <v>22.90971183776855</v>
+        <v>22.90971374511719</v>
       </c>
       <c r="C370" t="n">
-        <v>23.02687325804298</v>
+        <v>23.02687517514589</v>
       </c>
       <c r="D370" t="n">
-        <v>22.68439995963118</v>
+        <v>22.68440184822146</v>
       </c>
       <c r="E370" t="n">
-        <v>22.89168647495919</v>
+        <v>22.89168838080712</v>
       </c>
       <c r="F370" t="n">
         <v>313000</v>
@@ -7832,16 +7832,16 @@
         <v>44300</v>
       </c>
       <c r="B371" t="n">
-        <v>22.71143913269043</v>
+        <v>22.7114372253418</v>
       </c>
       <c r="C371" t="n">
-        <v>23.0809504936824</v>
+        <v>23.08094855530152</v>
       </c>
       <c r="D371" t="n">
-        <v>22.41402750752632</v>
+        <v>22.41402562515487</v>
       </c>
       <c r="E371" t="n">
-        <v>22.97280003044396</v>
+        <v>22.97279810114575</v>
       </c>
       <c r="F371" t="n">
         <v>698900</v>
@@ -7872,16 +7872,16 @@
         <v>44302</v>
       </c>
       <c r="B373" t="n">
-        <v>23.12601089477539</v>
+        <v>23.12601470947266</v>
       </c>
       <c r="C373" t="n">
-        <v>23.12601089477539</v>
+        <v>23.12601470947266</v>
       </c>
       <c r="D373" t="n">
-        <v>22.53118767760605</v>
+        <v>22.53119139418563</v>
       </c>
       <c r="E373" t="n">
-        <v>22.5492130403065</v>
+        <v>22.54921675985942</v>
       </c>
       <c r="F373" t="n">
         <v>598500</v>
@@ -7892,16 +7892,16 @@
         <v>44305</v>
       </c>
       <c r="B374" t="n">
-        <v>23.1350212097168</v>
+        <v>23.13502311706543</v>
       </c>
       <c r="C374" t="n">
-        <v>23.49551983188558</v>
+        <v>23.49552176895524</v>
       </c>
       <c r="D374" t="n">
-        <v>22.56723609467509</v>
+        <v>22.56723795521313</v>
       </c>
       <c r="E374" t="n">
-        <v>23.16205925100184</v>
+        <v>23.1620611605796</v>
       </c>
       <c r="F374" t="n">
         <v>998400</v>
@@ -7912,16 +7912,16 @@
         <v>44306</v>
       </c>
       <c r="B375" t="n">
-        <v>22.36896705627441</v>
+        <v>22.36896514892578</v>
       </c>
       <c r="C375" t="n">
-        <v>23.14404060816256</v>
+        <v>23.14403863472524</v>
       </c>
       <c r="D375" t="n">
-        <v>22.18871855236583</v>
+        <v>22.18871666038655</v>
       </c>
       <c r="E375" t="n">
-        <v>23.1350279251181</v>
+        <v>23.13502595244928</v>
       </c>
       <c r="F375" t="n">
         <v>666400</v>
@@ -7952,16 +7952,16 @@
         <v>44309</v>
       </c>
       <c r="B377" t="n">
-        <v>22.01747512817383</v>
+        <v>22.01748085021973</v>
       </c>
       <c r="C377" t="n">
-        <v>22.54921125273173</v>
+        <v>22.54921711296871</v>
       </c>
       <c r="D377" t="n">
-        <v>21.91833736017362</v>
+        <v>21.91834305645495</v>
       </c>
       <c r="E377" t="n">
-        <v>22.08056217363103</v>
+        <v>22.0805679120724</v>
       </c>
       <c r="F377" t="n">
         <v>1091100</v>
@@ -7972,16 +7972,16 @@
         <v>44312</v>
       </c>
       <c r="B378" t="n">
-        <v>22.3509407043457</v>
+        <v>22.35093879699707</v>
       </c>
       <c r="C378" t="n">
-        <v>22.35995338699264</v>
+        <v>22.35995147887489</v>
       </c>
       <c r="D378" t="n">
-        <v>21.97241662814177</v>
+        <v>21.97241475309501</v>
       </c>
       <c r="E378" t="n">
-        <v>21.97241662814177</v>
+        <v>21.97241475309501</v>
       </c>
       <c r="F378" t="n">
         <v>422300</v>
@@ -7992,16 +7992,16 @@
         <v>44313</v>
       </c>
       <c r="B379" t="n">
-        <v>22.30587768554688</v>
+        <v>22.30587577819824</v>
       </c>
       <c r="C379" t="n">
-        <v>22.38699010555924</v>
+        <v>22.38698819127478</v>
       </c>
       <c r="D379" t="n">
-        <v>21.96340436026727</v>
+        <v>21.96340248220312</v>
       </c>
       <c r="E379" t="n">
-        <v>22.35093937711226</v>
+        <v>22.35093746591046</v>
       </c>
       <c r="F379" t="n">
         <v>435600</v>
@@ -8032,16 +8032,16 @@
         <v>44315</v>
       </c>
       <c r="B381" t="n">
-        <v>22.81057548522949</v>
+        <v>22.81057739257812</v>
       </c>
       <c r="C381" t="n">
-        <v>22.89168790394174</v>
+        <v>22.89168981807274</v>
       </c>
       <c r="D381" t="n">
-        <v>21.99044033513306</v>
+        <v>21.99044217390457</v>
       </c>
       <c r="E381" t="n">
-        <v>22.47711484740654</v>
+        <v>22.47711672687224</v>
       </c>
       <c r="F381" t="n">
         <v>1108700</v>
@@ -8072,16 +8072,16 @@
         <v>44319</v>
       </c>
       <c r="B383" t="n">
-        <v>22.43420028686523</v>
+        <v>22.43420219421387</v>
       </c>
       <c r="C383" t="n">
-        <v>22.96705783562249</v>
+        <v>22.9670597882745</v>
       </c>
       <c r="D383" t="n">
-        <v>22.19938156007234</v>
+        <v>22.19938344745676</v>
       </c>
       <c r="E383" t="n">
-        <v>22.80449089225676</v>
+        <v>22.80449283108739</v>
       </c>
       <c r="F383" t="n">
         <v>1760300</v>
@@ -8092,16 +8092,16 @@
         <v>44320</v>
       </c>
       <c r="B384" t="n">
-        <v>23.26510047912598</v>
+        <v>23.26509666442871</v>
       </c>
       <c r="C384" t="n">
-        <v>23.39154069023806</v>
+        <v>23.39153685480884</v>
       </c>
       <c r="D384" t="n">
-        <v>22.05488161596587</v>
+        <v>22.05487799970397</v>
       </c>
       <c r="E384" t="n">
-        <v>22.244541932634</v>
+        <v>22.24453828527416</v>
       </c>
       <c r="F384" t="n">
         <v>1769300</v>
@@ -8112,16 +8112,16 @@
         <v>44321</v>
       </c>
       <c r="B385" t="n">
-        <v>22.66901969909668</v>
+        <v>22.66902160644531</v>
       </c>
       <c r="C385" t="n">
-        <v>23.66248304322317</v>
+        <v>23.66248503416082</v>
       </c>
       <c r="D385" t="n">
-        <v>22.61483129054242</v>
+        <v>22.61483319333169</v>
       </c>
       <c r="E385" t="n">
-        <v>23.27412904957767</v>
+        <v>23.2741310078396</v>
       </c>
       <c r="F385" t="n">
         <v>867500</v>
@@ -8232,16 +8232,16 @@
         <v>44329</v>
       </c>
       <c r="B391" t="n">
-        <v>23.36444473266602</v>
+        <v>23.36444664001465</v>
       </c>
       <c r="C391" t="n">
-        <v>23.48185324091847</v>
+        <v>23.48185515785171</v>
       </c>
       <c r="D391" t="n">
-        <v>22.75933536870684</v>
+        <v>22.75933722665757</v>
       </c>
       <c r="E391" t="n">
-        <v>23.1115626160827</v>
+        <v>23.11156450278738</v>
       </c>
       <c r="F391" t="n">
         <v>1130900</v>
@@ -8312,16 +8312,16 @@
         <v>44335</v>
       </c>
       <c r="B395" t="n">
-        <v>24.06890106201172</v>
+        <v>24.06889915466309</v>
       </c>
       <c r="C395" t="n">
-        <v>24.38500330118037</v>
+        <v>24.38500136878211</v>
       </c>
       <c r="D395" t="n">
-        <v>23.71667378778818</v>
+        <v>23.71667190835193</v>
       </c>
       <c r="E395" t="n">
-        <v>23.95149254481008</v>
+        <v>23.95149064676553</v>
       </c>
       <c r="F395" t="n">
         <v>795000</v>
@@ -8372,16 +8372,16 @@
         <v>44340</v>
       </c>
       <c r="B398" t="n">
-        <v>25.19783592224121</v>
+        <v>25.19783782958984</v>
       </c>
       <c r="C398" t="n">
-        <v>25.19783592224121</v>
+        <v>25.19783782958984</v>
       </c>
       <c r="D398" t="n">
-        <v>24.60175821287991</v>
+        <v>24.60176007510848</v>
       </c>
       <c r="E398" t="n">
-        <v>24.89979706756056</v>
+        <v>24.89979895234917</v>
       </c>
       <c r="F398" t="n">
         <v>853600</v>
@@ -8392,16 +8392,16 @@
         <v>44341</v>
       </c>
       <c r="B399" t="n">
-        <v>25.0804271697998</v>
+        <v>25.08042907714844</v>
       </c>
       <c r="C399" t="n">
-        <v>25.39652939998178</v>
+        <v>25.39653133136976</v>
       </c>
       <c r="D399" t="n">
-        <v>24.83657673029212</v>
+        <v>24.83657861909609</v>
       </c>
       <c r="E399" t="n">
-        <v>25.20686737282517</v>
+        <v>25.20686928978949</v>
       </c>
       <c r="F399" t="n">
         <v>711500</v>
@@ -8432,16 +8432,16 @@
         <v>44343</v>
       </c>
       <c r="B401" t="n">
-        <v>26.63384056091309</v>
+        <v>26.63383865356445</v>
       </c>
       <c r="C401" t="n">
-        <v>26.81447089233165</v>
+        <v>26.8144689720474</v>
       </c>
       <c r="D401" t="n">
-        <v>25.5229686737589</v>
+        <v>25.52296684596395</v>
       </c>
       <c r="E401" t="n">
-        <v>25.61328383946818</v>
+        <v>25.61328200520542</v>
       </c>
       <c r="F401" t="n">
         <v>1666700</v>
@@ -8492,16 +8492,16 @@
         <v>44348</v>
       </c>
       <c r="B404" t="n">
-        <v>28.08790969848633</v>
+        <v>28.08791160583496</v>
       </c>
       <c r="C404" t="n">
-        <v>29.0723396633821</v>
+        <v>29.07234163757982</v>
       </c>
       <c r="D404" t="n">
-        <v>27.39248516278936</v>
+        <v>27.39248702291422</v>
       </c>
       <c r="E404" t="n">
-        <v>27.93437443375607</v>
+        <v>27.93437633067867</v>
       </c>
       <c r="F404" t="n">
         <v>4051600</v>
@@ -8512,16 +8512,16 @@
         <v>44349</v>
       </c>
       <c r="B405" t="n">
-        <v>28.81042861938477</v>
+        <v>28.81042671203613</v>
       </c>
       <c r="C405" t="n">
-        <v>29.0181540245529</v>
+        <v>29.01815210345214</v>
       </c>
       <c r="D405" t="n">
-        <v>28.27757101797948</v>
+        <v>28.27756914590784</v>
       </c>
       <c r="E405" t="n">
-        <v>28.27757101797948</v>
+        <v>28.27756914590784</v>
       </c>
       <c r="F405" t="n">
         <v>2374700</v>
@@ -8532,16 +8532,16 @@
         <v>44351</v>
       </c>
       <c r="B406" t="n">
-        <v>28.7743034362793</v>
+        <v>28.77430152893066</v>
       </c>
       <c r="C406" t="n">
-        <v>29.03621725235974</v>
+        <v>29.03621532764976</v>
       </c>
       <c r="D406" t="n">
-        <v>28.20531908123073</v>
+        <v>28.2053172115981</v>
       </c>
       <c r="E406" t="n">
-        <v>28.72011330167182</v>
+        <v>28.72011139791527</v>
       </c>
       <c r="F406" t="n">
         <v>1004000</v>
@@ -8552,16 +8552,16 @@
         <v>44354</v>
       </c>
       <c r="B407" t="n">
-        <v>28.39497947692871</v>
+        <v>28.39498138427734</v>
       </c>
       <c r="C407" t="n">
-        <v>28.80139512744059</v>
+        <v>28.80139706208899</v>
       </c>
       <c r="D407" t="n">
-        <v>28.10597233275534</v>
+        <v>28.10597422069078</v>
       </c>
       <c r="E407" t="n">
-        <v>28.63882817818845</v>
+        <v>28.6388301019169</v>
       </c>
       <c r="F407" t="n">
         <v>1005300</v>
@@ -8572,16 +8572,16 @@
         <v>44355</v>
       </c>
       <c r="B408" t="n">
-        <v>28.32272720336914</v>
+        <v>28.32272911071777</v>
       </c>
       <c r="C408" t="n">
-        <v>28.39497898816882</v>
+        <v>28.39498090038313</v>
       </c>
       <c r="D408" t="n">
-        <v>27.91630983723443</v>
+        <v>27.91631171721354</v>
       </c>
       <c r="E408" t="n">
-        <v>28.17822363376978</v>
+        <v>28.17822553138705</v>
       </c>
       <c r="F408" t="n">
         <v>1212600</v>
@@ -8652,16 +8652,16 @@
         <v>44361</v>
       </c>
       <c r="B412" t="n">
-        <v>29.60519790649414</v>
+        <v>29.60519599914551</v>
       </c>
       <c r="C412" t="n">
-        <v>29.6955147967266</v>
+        <v>29.6955128835592</v>
       </c>
       <c r="D412" t="n">
-        <v>28.08791032557823</v>
+        <v>28.08790851598258</v>
       </c>
       <c r="E412" t="n">
-        <v>28.08791032557823</v>
+        <v>28.08790851598258</v>
       </c>
       <c r="F412" t="n">
         <v>1333100</v>
@@ -8692,16 +8692,16 @@
         <v>44363</v>
       </c>
       <c r="B414" t="n">
-        <v>29.09943771362305</v>
+        <v>29.09943580627441</v>
       </c>
       <c r="C414" t="n">
-        <v>29.79486227945943</v>
+        <v>29.79486032652857</v>
       </c>
       <c r="D414" t="n">
-        <v>28.83752389430081</v>
+        <v>28.83752200411955</v>
       </c>
       <c r="E414" t="n">
-        <v>29.46069494643292</v>
+        <v>29.46069301540536</v>
       </c>
       <c r="F414" t="n">
         <v>758400</v>
@@ -8732,16 +8732,16 @@
         <v>44365</v>
       </c>
       <c r="B416" t="n">
-        <v>31.21280479431152</v>
+        <v>31.21280670166016</v>
       </c>
       <c r="C416" t="n">
-        <v>31.21280479431152</v>
+        <v>31.21280670166016</v>
       </c>
       <c r="D416" t="n">
-        <v>29.81292224909573</v>
+        <v>29.8129240709005</v>
       </c>
       <c r="E416" t="n">
-        <v>29.97548920989193</v>
+        <v>29.97549104163082</v>
       </c>
       <c r="F416" t="n">
         <v>1597800</v>
@@ -8792,16 +8792,16 @@
         <v>44370</v>
       </c>
       <c r="B419" t="n">
-        <v>30.36384391784668</v>
+        <v>30.36384201049805</v>
       </c>
       <c r="C419" t="n">
-        <v>30.93282829345847</v>
+        <v>30.93282635036827</v>
       </c>
       <c r="D419" t="n">
-        <v>30.05677336778096</v>
+        <v>30.05677147972141</v>
       </c>
       <c r="E419" t="n">
-        <v>30.75219795014266</v>
+        <v>30.752196018399</v>
       </c>
       <c r="F419" t="n">
         <v>798300</v>
@@ -8812,16 +8812,16 @@
         <v>44371</v>
       </c>
       <c r="B420" t="n">
-        <v>30.29159355163574</v>
+        <v>30.29159164428711</v>
       </c>
       <c r="C420" t="n">
-        <v>30.69801095881528</v>
+        <v>30.69800902587606</v>
       </c>
       <c r="D420" t="n">
-        <v>30.07483645272759</v>
+        <v>30.07483455902734</v>
       </c>
       <c r="E420" t="n">
-        <v>30.49028382662791</v>
+        <v>30.49028190676849</v>
       </c>
       <c r="F420" t="n">
         <v>917300</v>
@@ -8872,16 +8872,16 @@
         <v>44376</v>
       </c>
       <c r="B423" t="n">
-        <v>29.72260856628418</v>
+        <v>29.72260665893555</v>
       </c>
       <c r="C423" t="n">
-        <v>29.77679870119871</v>
+        <v>29.7767967903726</v>
       </c>
       <c r="D423" t="n">
-        <v>28.8646170456084</v>
+        <v>28.86461519331849</v>
       </c>
       <c r="E423" t="n">
-        <v>29.60519832992127</v>
+        <v>29.60519643010704</v>
       </c>
       <c r="F423" t="n">
         <v>1611300</v>
@@ -8952,16 +8952,16 @@
         <v>44382</v>
       </c>
       <c r="B427" t="n">
-        <v>28.8284912109375</v>
+        <v>28.82849311828613</v>
       </c>
       <c r="C427" t="n">
-        <v>29.65938764107877</v>
+        <v>29.65938960340112</v>
       </c>
       <c r="D427" t="n">
-        <v>28.8284912109375</v>
+        <v>28.82849311828613</v>
       </c>
       <c r="E427" t="n">
-        <v>29.39747383078863</v>
+        <v>29.39747577578225</v>
       </c>
       <c r="F427" t="n">
         <v>1101800</v>
@@ -9052,16 +9052,16 @@
         <v>44390</v>
       </c>
       <c r="B432" t="n">
-        <v>28.90977478027344</v>
+        <v>28.90977668762207</v>
       </c>
       <c r="C432" t="n">
-        <v>29.09943853649185</v>
+        <v>29.09944045635372</v>
       </c>
       <c r="D432" t="n">
-        <v>28.51239077937428</v>
+        <v>28.51239266050514</v>
       </c>
       <c r="E432" t="n">
-        <v>28.90074481342364</v>
+        <v>28.90074672017651</v>
       </c>
       <c r="F432" t="n">
         <v>734700</v>
@@ -9092,16 +9092,16 @@
         <v>44392</v>
       </c>
       <c r="B434" t="n">
-        <v>28.7743034362793</v>
+        <v>28.77430152893066</v>
       </c>
       <c r="C434" t="n">
-        <v>29.21684414391042</v>
+        <v>29.21684220722731</v>
       </c>
       <c r="D434" t="n">
-        <v>28.6839882678854</v>
+        <v>28.68398636652345</v>
       </c>
       <c r="E434" t="n">
-        <v>28.81042847006572</v>
+        <v>28.81042656032249</v>
       </c>
       <c r="F434" t="n">
         <v>728800</v>
@@ -9112,16 +9112,16 @@
         <v>44393</v>
       </c>
       <c r="B435" t="n">
-        <v>28.90074157714844</v>
+        <v>28.90074348449707</v>
       </c>
       <c r="C435" t="n">
-        <v>29.21684206005375</v>
+        <v>29.21684398826392</v>
       </c>
       <c r="D435" t="n">
-        <v>28.72011125324389</v>
+        <v>28.72011314867154</v>
       </c>
       <c r="E435" t="n">
-        <v>28.8826782002343</v>
+        <v>28.88268010639081</v>
       </c>
       <c r="F435" t="n">
         <v>731700</v>
@@ -9152,16 +9152,16 @@
         <v>44397</v>
       </c>
       <c r="B437" t="n">
-        <v>28.23241424560547</v>
+        <v>28.23241233825684</v>
       </c>
       <c r="C437" t="n">
-        <v>28.8194602582564</v>
+        <v>28.81945831124763</v>
       </c>
       <c r="D437" t="n">
-        <v>28.18725579994398</v>
+        <v>28.18725389564619</v>
       </c>
       <c r="E437" t="n">
-        <v>28.56657813040772</v>
+        <v>28.56657620048336</v>
       </c>
       <c r="F437" t="n">
         <v>691100</v>
@@ -9172,16 +9172,16 @@
         <v>44398</v>
       </c>
       <c r="B438" t="n">
-        <v>28.75624084472656</v>
+        <v>28.75623893737793</v>
       </c>
       <c r="C438" t="n">
-        <v>28.91880780775901</v>
+        <v>28.91880588962761</v>
       </c>
       <c r="D438" t="n">
-        <v>28.16016312868664</v>
+        <v>28.16016126087474</v>
       </c>
       <c r="E438" t="n">
-        <v>28.17822650738327</v>
+        <v>28.17822463837327</v>
       </c>
       <c r="F438" t="n">
         <v>876300</v>
@@ -9232,16 +9232,16 @@
         <v>44403</v>
       </c>
       <c r="B441" t="n">
-        <v>28.22338104248047</v>
+        <v>28.2233829498291</v>
       </c>
       <c r="C441" t="n">
-        <v>28.70205020510359</v>
+        <v>28.70205214480089</v>
       </c>
       <c r="D441" t="n">
-        <v>28.19628597653704</v>
+        <v>28.19628788205457</v>
       </c>
       <c r="E441" t="n">
-        <v>28.70205020510359</v>
+        <v>28.70205214480089</v>
       </c>
       <c r="F441" t="n">
         <v>447900</v>
@@ -9252,16 +9252,16 @@
         <v>44404</v>
       </c>
       <c r="B442" t="n">
-        <v>27.53698921203613</v>
+        <v>27.5369873046875</v>
       </c>
       <c r="C442" t="n">
-        <v>28.24144544866373</v>
+        <v>28.24144349252096</v>
       </c>
       <c r="D442" t="n">
-        <v>27.1666985770779</v>
+        <v>27.16669669537744</v>
       </c>
       <c r="E442" t="n">
-        <v>28.08791018129433</v>
+        <v>28.08790823578617</v>
       </c>
       <c r="F442" t="n">
         <v>742400</v>
@@ -9272,16 +9272,16 @@
         <v>44405</v>
       </c>
       <c r="B443" t="n">
-        <v>28.17822265625</v>
+        <v>28.17822456359863</v>
       </c>
       <c r="C443" t="n">
-        <v>28.33175790895039</v>
+        <v>28.33175982669163</v>
       </c>
       <c r="D443" t="n">
-        <v>27.59117498717191</v>
+        <v>27.59117685478402</v>
       </c>
       <c r="E443" t="n">
-        <v>27.63633342774166</v>
+        <v>27.63633529841049</v>
       </c>
       <c r="F443" t="n">
         <v>805700</v>
@@ -9292,16 +9292,16 @@
         <v>44406</v>
       </c>
       <c r="B444" t="n">
-        <v>28.17822265625</v>
+        <v>28.17822456359863</v>
       </c>
       <c r="C444" t="n">
-        <v>28.39497800312966</v>
+        <v>28.39497992515019</v>
       </c>
       <c r="D444" t="n">
-        <v>27.89824549257269</v>
+        <v>27.89824738097002</v>
       </c>
       <c r="E444" t="n">
-        <v>28.22337937420138</v>
+        <v>28.22338128460661</v>
       </c>
       <c r="F444" t="n">
         <v>553900</v>
@@ -9312,16 +9312,16 @@
         <v>44407</v>
       </c>
       <c r="B445" t="n">
-        <v>28.17822265625</v>
+        <v>28.17822456359863</v>
       </c>
       <c r="C445" t="n">
-        <v>29.54197483170725</v>
+        <v>29.54197683136655</v>
       </c>
       <c r="D445" t="n">
-        <v>27.75374192798625</v>
+        <v>27.75374380660232</v>
       </c>
       <c r="E445" t="n">
-        <v>27.82599371027948</v>
+        <v>27.82599559378617</v>
       </c>
       <c r="F445" t="n">
         <v>1996900</v>
@@ -9392,16 +9392,16 @@
         <v>44413</v>
       </c>
       <c r="B449" t="n">
-        <v>27.44667625427246</v>
+        <v>27.44667434692383</v>
       </c>
       <c r="C449" t="n">
-        <v>28.0788807525946</v>
+        <v>28.07887880131226</v>
       </c>
       <c r="D449" t="n">
-        <v>27.21185748982763</v>
+        <v>27.21185559879723</v>
       </c>
       <c r="E449" t="n">
-        <v>27.99759726787837</v>
+        <v>27.99759532224465</v>
       </c>
       <c r="F449" t="n">
         <v>966400</v>
@@ -9432,16 +9432,16 @@
         <v>44417</v>
       </c>
       <c r="B451" t="n">
-        <v>27.92534446716309</v>
+        <v>27.92534255981445</v>
       </c>
       <c r="C451" t="n">
-        <v>27.9343761565417</v>
+        <v>27.93437424857619</v>
       </c>
       <c r="D451" t="n">
-        <v>27.27507833547053</v>
+        <v>27.27507647253619</v>
       </c>
       <c r="E451" t="n">
-        <v>27.77180919296391</v>
+        <v>27.771807296102</v>
       </c>
       <c r="F451" t="n">
         <v>1314300</v>
@@ -9472,16 +9472,16 @@
         <v>44419</v>
       </c>
       <c r="B453" t="n">
-        <v>27.5460205078125</v>
+        <v>27.54601860046387</v>
       </c>
       <c r="C453" t="n">
-        <v>27.87115441586395</v>
+        <v>27.87115248600231</v>
       </c>
       <c r="D453" t="n">
-        <v>27.03122630181005</v>
+        <v>27.03122443010693</v>
       </c>
       <c r="E453" t="n">
-        <v>27.36539017609092</v>
+        <v>27.36538828124953</v>
       </c>
       <c r="F453" t="n">
         <v>1902000</v>
@@ -9492,16 +9492,16 @@
         <v>44420</v>
       </c>
       <c r="B454" t="n">
-        <v>27.18476295471191</v>
+        <v>27.18476104736328</v>
       </c>
       <c r="C454" t="n">
-        <v>27.76277728953776</v>
+        <v>27.76277534163425</v>
       </c>
       <c r="D454" t="n">
-        <v>27.02219599238749</v>
+        <v>27.02219409644495</v>
       </c>
       <c r="E454" t="n">
-        <v>27.52795853536011</v>
+        <v>27.52795660393205</v>
       </c>
       <c r="F454" t="n">
         <v>489800</v>
@@ -9552,16 +9552,16 @@
         <v>44425</v>
       </c>
       <c r="B457" t="n">
-        <v>26.92284965515137</v>
+        <v>26.92284774780273</v>
       </c>
       <c r="C457" t="n">
-        <v>27.36539210416901</v>
+        <v>27.36539016546847</v>
       </c>
       <c r="D457" t="n">
-        <v>25.78488261941229</v>
+        <v>25.7848807926829</v>
       </c>
       <c r="E457" t="n">
-        <v>27.36539210416901</v>
+        <v>27.36539016546847</v>
       </c>
       <c r="F457" t="n">
         <v>2325200</v>
@@ -9652,16 +9652,16 @@
         <v>44432</v>
       </c>
       <c r="B462" t="n">
-        <v>28.98202705383301</v>
+        <v>28.98202514648438</v>
       </c>
       <c r="C462" t="n">
-        <v>29.31619093674931</v>
+        <v>29.31618900740888</v>
       </c>
       <c r="D462" t="n">
-        <v>28.61173641459139</v>
+        <v>28.61173453161212</v>
       </c>
       <c r="E462" t="n">
-        <v>28.88268019655697</v>
+        <v>28.8826782957465</v>
       </c>
       <c r="F462" t="n">
         <v>1724500</v>
@@ -9712,16 +9712,16 @@
         <v>44435</v>
       </c>
       <c r="B465" t="n">
-        <v>29.72260856628418</v>
+        <v>29.72260665893555</v>
       </c>
       <c r="C465" t="n">
-        <v>29.74067194458902</v>
+        <v>29.74067003608123</v>
       </c>
       <c r="D465" t="n">
-        <v>28.74720853186406</v>
+        <v>28.74720668710845</v>
       </c>
       <c r="E465" t="n">
-        <v>28.93687055882777</v>
+        <v>28.93686870190124</v>
       </c>
       <c r="F465" t="n">
         <v>1133700</v>
@@ -9792,16 +9792,16 @@
         <v>44441</v>
       </c>
       <c r="B469" t="n">
-        <v>29.25296783447266</v>
+        <v>29.25296974182129</v>
       </c>
       <c r="C469" t="n">
-        <v>29.91226556619919</v>
+        <v>29.91226751653528</v>
       </c>
       <c r="D469" t="n">
-        <v>29.25296783447265</v>
+        <v>29.25296974182129</v>
       </c>
       <c r="E469" t="n">
-        <v>29.91226556619919</v>
+        <v>29.91226751653528</v>
       </c>
       <c r="F469" t="n">
         <v>600700</v>
@@ -9832,16 +9832,16 @@
         <v>44445</v>
       </c>
       <c r="B471" t="n">
-        <v>29.10846710205078</v>
+        <v>29.10846519470215</v>
       </c>
       <c r="C471" t="n">
-        <v>29.3252241936211</v>
+        <v>29.32522227206933</v>
       </c>
       <c r="D471" t="n">
-        <v>28.72914477573055</v>
+        <v>28.72914289323722</v>
       </c>
       <c r="E471" t="n">
-        <v>29.0813737575684</v>
+        <v>29.08137185199507</v>
       </c>
       <c r="F471" t="n">
         <v>544100</v>
@@ -9892,16 +9892,16 @@
         <v>44449</v>
       </c>
       <c r="B474" t="n">
-        <v>28.17822265625</v>
+        <v>28.17822456359863</v>
       </c>
       <c r="C474" t="n">
-        <v>28.60270166189538</v>
+        <v>28.60270359797646</v>
       </c>
       <c r="D474" t="n">
-        <v>27.62730173962771</v>
+        <v>27.6273036096852</v>
       </c>
       <c r="E474" t="n">
-        <v>27.98856065109381</v>
+        <v>27.98856254560446</v>
       </c>
       <c r="F474" t="n">
         <v>1603100</v>
@@ -9912,16 +9912,16 @@
         <v>44452</v>
       </c>
       <c r="B475" t="n">
-        <v>28.94589805603027</v>
+        <v>28.94589996337891</v>
       </c>
       <c r="C475" t="n">
-        <v>29.32522207759813</v>
+        <v>29.32522400994178</v>
       </c>
       <c r="D475" t="n">
-        <v>28.15112842722206</v>
+        <v>28.15113028220048</v>
       </c>
       <c r="E475" t="n">
-        <v>28.53045072617149</v>
+        <v>28.53045260614482</v>
       </c>
       <c r="F475" t="n">
         <v>1109800</v>
@@ -9932,16 +9932,16 @@
         <v>44453</v>
       </c>
       <c r="B476" t="n">
-        <v>28.8646183013916</v>
+        <v>28.86461639404297</v>
       </c>
       <c r="C476" t="n">
-        <v>29.66841972212301</v>
+        <v>29.66841776165989</v>
       </c>
       <c r="D476" t="n">
-        <v>28.76527316163</v>
+        <v>28.765271260846</v>
       </c>
       <c r="E476" t="n">
-        <v>28.95493519684514</v>
+        <v>28.95493328352844</v>
       </c>
       <c r="F476" t="n">
         <v>571800</v>
@@ -9952,16 +9952,16 @@
         <v>44454</v>
       </c>
       <c r="B477" t="n">
-        <v>28.49432754516602</v>
+        <v>28.49432563781738</v>
       </c>
       <c r="C477" t="n">
-        <v>28.98202844322661</v>
+        <v>28.98202650323234</v>
       </c>
       <c r="D477" t="n">
-        <v>27.88018816176107</v>
+        <v>27.8801862955216</v>
       </c>
       <c r="E477" t="n">
-        <v>28.8646182021593</v>
+        <v>28.86461627002421</v>
       </c>
       <c r="F477" t="n">
         <v>994400</v>
@@ -10012,16 +10012,16 @@
         <v>44459</v>
       </c>
       <c r="B480" t="n">
-        <v>26.90478515625</v>
+        <v>26.90478706359863</v>
       </c>
       <c r="C480" t="n">
-        <v>26.96800525334194</v>
+        <v>26.96800716517241</v>
       </c>
       <c r="D480" t="n">
-        <v>26.16420220035146</v>
+        <v>26.16420405519829</v>
       </c>
       <c r="E480" t="n">
-        <v>26.82350168209795</v>
+        <v>26.82350358368419</v>
       </c>
       <c r="F480" t="n">
         <v>812900</v>
@@ -10052,16 +10052,16 @@
         <v>44461</v>
       </c>
       <c r="B482" t="n">
-        <v>28.44916915893555</v>
+        <v>28.44916725158691</v>
       </c>
       <c r="C482" t="n">
-        <v>29.03621688475444</v>
+        <v>29.03621493804773</v>
       </c>
       <c r="D482" t="n">
-        <v>27.74471292152399</v>
+        <v>27.74471106140499</v>
       </c>
       <c r="E482" t="n">
-        <v>28.07887852356523</v>
+        <v>28.0788766410424</v>
       </c>
       <c r="F482" t="n">
         <v>1369400</v>
@@ -10072,16 +10072,16 @@
         <v>44462</v>
       </c>
       <c r="B483" t="n">
-        <v>28.70205116271973</v>
+        <v>28.70205307006836</v>
       </c>
       <c r="C483" t="n">
-        <v>29.22587706344037</v>
+        <v>29.22587900559901</v>
       </c>
       <c r="D483" t="n">
-        <v>27.99759492825326</v>
+        <v>27.99759678878839</v>
       </c>
       <c r="E483" t="n">
-        <v>27.99759492825326</v>
+        <v>27.99759678878839</v>
       </c>
       <c r="F483" t="n">
         <v>1197400</v>
@@ -10152,16 +10152,16 @@
         <v>44468</v>
       </c>
       <c r="B487" t="n">
-        <v>27.09444808959961</v>
+        <v>27.09444618225098</v>
       </c>
       <c r="C487" t="n">
-        <v>27.86212446332866</v>
+        <v>27.86212250193845</v>
       </c>
       <c r="D487" t="n">
-        <v>27.09444808959961</v>
+        <v>27.09444618225098</v>
       </c>
       <c r="E487" t="n">
-        <v>27.61827401709379</v>
+        <v>27.61827207286975</v>
       </c>
       <c r="F487" t="n">
         <v>1039400</v>
@@ -10192,16 +10192,16 @@
         <v>44470</v>
       </c>
       <c r="B489" t="n">
-        <v>27.01316452026367</v>
+        <v>27.01316261291504</v>
       </c>
       <c r="C489" t="n">
-        <v>27.11251138084258</v>
+        <v>27.11250946647926</v>
       </c>
       <c r="D489" t="n">
-        <v>26.20033142472501</v>
+        <v>26.20032957476899</v>
       </c>
       <c r="E489" t="n">
-        <v>26.48030690507995</v>
+        <v>26.48030503535539</v>
       </c>
       <c r="F489" t="n">
         <v>1027100</v>
@@ -10232,16 +10232,16 @@
         <v>44474</v>
       </c>
       <c r="B491" t="n">
-        <v>25.37846374511719</v>
+        <v>25.37846565246582</v>
       </c>
       <c r="C491" t="n">
-        <v>25.74875435443381</v>
+        <v>25.74875628961207</v>
       </c>
       <c r="D491" t="n">
-        <v>25.15267670418664</v>
+        <v>25.15267859456598</v>
       </c>
       <c r="E491" t="n">
-        <v>25.55006237855756</v>
+        <v>25.55006429880289</v>
       </c>
       <c r="F491" t="n">
         <v>653500</v>
@@ -10252,16 +10252,16 @@
         <v>44475</v>
       </c>
       <c r="B492" t="n">
-        <v>25.30621337890625</v>
+        <v>25.30621528625488</v>
       </c>
       <c r="C492" t="n">
-        <v>25.30621337890625</v>
+        <v>25.30621528625488</v>
       </c>
       <c r="D492" t="n">
-        <v>24.00567946794038</v>
+        <v>24.00568127726677</v>
       </c>
       <c r="E492" t="n">
-        <v>25.10751966927819</v>
+        <v>25.10752156165112</v>
       </c>
       <c r="F492" t="n">
         <v>2490200</v>
@@ -10272,16 +10272,16 @@
         <v>44476</v>
       </c>
       <c r="B493" t="n">
-        <v>25.82100868225098</v>
+        <v>25.82101058959961</v>
       </c>
       <c r="C493" t="n">
-        <v>26.00163902183665</v>
+        <v>26.0016409425281</v>
       </c>
       <c r="D493" t="n">
-        <v>25.36943455590538</v>
+        <v>25.36943642989709</v>
       </c>
       <c r="E493" t="n">
-        <v>25.6403783426653</v>
+        <v>25.64038023667112</v>
       </c>
       <c r="F493" t="n">
         <v>1261800</v>
@@ -10292,16 +10292,16 @@
         <v>44477</v>
       </c>
       <c r="B494" t="n">
-        <v>26.56158638000488</v>
+        <v>26.56159019470215</v>
       </c>
       <c r="C494" t="n">
-        <v>26.75124838317006</v>
+        <v>26.75125222510603</v>
       </c>
       <c r="D494" t="n">
-        <v>25.95647706366949</v>
+        <v>25.95648079146273</v>
       </c>
       <c r="E494" t="n">
-        <v>26.04679222124251</v>
+        <v>26.04679596200655</v>
       </c>
       <c r="F494" t="n">
         <v>1400600</v>
@@ -10312,16 +10312,16 @@
         <v>44480</v>
       </c>
       <c r="B495" t="n">
-        <v>26.11001396179199</v>
+        <v>26.11001586914062</v>
       </c>
       <c r="C495" t="n">
-        <v>26.74221838206459</v>
+        <v>26.74222033559605</v>
       </c>
       <c r="D495" t="n">
-        <v>26.01969879852184</v>
+        <v>26.01970069927291</v>
       </c>
       <c r="E495" t="n">
-        <v>26.46224120366528</v>
+        <v>26.46224313674427</v>
       </c>
       <c r="F495" t="n">
         <v>791300</v>
@@ -10372,16 +10372,16 @@
         <v>44484</v>
       </c>
       <c r="B498" t="n">
-        <v>27.09444808959961</v>
+        <v>27.09444618225098</v>
       </c>
       <c r="C498" t="n">
-        <v>27.27507843257772</v>
+        <v>27.27507651251338</v>
       </c>
       <c r="D498" t="n">
-        <v>26.65190564418372</v>
+        <v>26.65190376798843</v>
       </c>
       <c r="E498" t="n">
-        <v>26.72415743685124</v>
+        <v>26.72415555556969</v>
       </c>
       <c r="F498" t="n">
         <v>489400</v>
@@ -10392,16 +10392,16 @@
         <v>44487</v>
       </c>
       <c r="B499" t="n">
-        <v>27.25701332092285</v>
+        <v>27.25701522827148</v>
       </c>
       <c r="C499" t="n">
-        <v>27.88018606969936</v>
+        <v>27.8801880206554</v>
       </c>
       <c r="D499" t="n">
-        <v>26.88672269171528</v>
+        <v>26.8867245731523</v>
       </c>
       <c r="E499" t="n">
-        <v>27.02219457902709</v>
+        <v>27.02219646994394</v>
       </c>
       <c r="F499" t="n">
         <v>764500</v>
@@ -10412,16 +10412,16 @@
         <v>44488</v>
       </c>
       <c r="B500" t="n">
-        <v>26.26355171203613</v>
+        <v>26.26355361938477</v>
       </c>
       <c r="C500" t="n">
-        <v>27.22992008860446</v>
+        <v>27.22992206613405</v>
       </c>
       <c r="D500" t="n">
-        <v>26.08292136837423</v>
+        <v>26.08292326260488</v>
       </c>
       <c r="E500" t="n">
-        <v>27.02219639922631</v>
+        <v>27.0221983616703</v>
       </c>
       <c r="F500" t="n">
         <v>1116800</v>
@@ -10512,16 +10512,16 @@
         <v>44495</v>
       </c>
       <c r="B505" t="n">
-        <v>24.45725440979004</v>
+        <v>24.45725250244141</v>
       </c>
       <c r="C505" t="n">
-        <v>24.99914370140448</v>
+        <v>24.99914175179551</v>
       </c>
       <c r="D505" t="n">
-        <v>23.92439680734134</v>
+        <v>23.92439494154869</v>
       </c>
       <c r="E505" t="n">
-        <v>24.99914370140448</v>
+        <v>24.99914175179551</v>
       </c>
       <c r="F505" t="n">
         <v>1077600</v>
@@ -10552,16 +10552,16 @@
         <v>44497</v>
       </c>
       <c r="B507" t="n">
-        <v>23.84311676025391</v>
+        <v>23.84311485290527</v>
       </c>
       <c r="C507" t="n">
-        <v>24.59272984274936</v>
+        <v>24.59272787543485</v>
       </c>
       <c r="D507" t="n">
-        <v>23.662488118789</v>
+        <v>23.6624862258899</v>
       </c>
       <c r="E507" t="n">
-        <v>24.27662756691226</v>
+        <v>24.27662562488459</v>
       </c>
       <c r="F507" t="n">
         <v>604100</v>
@@ -10572,16 +10572,16 @@
         <v>44498</v>
       </c>
       <c r="B508" t="n">
-        <v>23.42766761779785</v>
+        <v>23.42766571044922</v>
       </c>
       <c r="C508" t="n">
-        <v>24.20437399215729</v>
+        <v>24.2043720215736</v>
       </c>
       <c r="D508" t="n">
-        <v>23.42766761779785</v>
+        <v>23.42766571044922</v>
       </c>
       <c r="E508" t="n">
-        <v>23.94246187830896</v>
+        <v>23.94245992904868</v>
       </c>
       <c r="F508" t="n">
         <v>1297100</v>
@@ -10612,16 +10612,16 @@
         <v>44503</v>
       </c>
       <c r="B510" t="n">
-        <v>24.81851196289062</v>
+        <v>24.81851387023926</v>
       </c>
       <c r="C510" t="n">
-        <v>25.09848914337458</v>
+        <v>25.09849107223997</v>
       </c>
       <c r="D510" t="n">
-        <v>23.80698695006507</v>
+        <v>23.80698877967614</v>
       </c>
       <c r="E510" t="n">
-        <v>23.82504860475882</v>
+        <v>23.82505043575795</v>
       </c>
       <c r="F510" t="n">
         <v>1013100</v>
@@ -10692,16 +10692,16 @@
         <v>44509</v>
       </c>
       <c r="B514" t="n">
-        <v>24.98108100891113</v>
+        <v>24.9810791015625</v>
       </c>
       <c r="C514" t="n">
-        <v>25.84810424382147</v>
+        <v>25.84810227027411</v>
       </c>
       <c r="D514" t="n">
-        <v>24.41209835679702</v>
+        <v>24.41209649289119</v>
       </c>
       <c r="E514" t="n">
-        <v>24.4933818389017</v>
+        <v>24.49337996878974</v>
       </c>
       <c r="F514" t="n">
         <v>781000</v>
@@ -10712,16 +10712,16 @@
         <v>44510</v>
       </c>
       <c r="B515" t="n">
-        <v>26.32677268981934</v>
+        <v>26.3267707824707</v>
       </c>
       <c r="C515" t="n">
-        <v>26.76028346186202</v>
+        <v>26.76028152310596</v>
       </c>
       <c r="D515" t="n">
-        <v>24.89076675013658</v>
+        <v>24.89076494682516</v>
       </c>
       <c r="E515" t="n">
-        <v>24.89076675013658</v>
+        <v>24.89076494682516</v>
       </c>
       <c r="F515" t="n">
         <v>970400</v>
@@ -10752,16 +10752,16 @@
         <v>44512</v>
       </c>
       <c r="B517" t="n">
-        <v>26.26355171203613</v>
+        <v>26.26355361938477</v>
       </c>
       <c r="C517" t="n">
-        <v>27.31120357099045</v>
+        <v>27.31120555442313</v>
       </c>
       <c r="D517" t="n">
-        <v>26.1912999190951</v>
+        <v>26.19130182119656</v>
       </c>
       <c r="E517" t="n">
-        <v>26.371930262757</v>
+        <v>26.37193217797645</v>
       </c>
       <c r="F517" t="n">
         <v>964700</v>
@@ -10792,16 +10792,16 @@
         <v>44517</v>
       </c>
       <c r="B519" t="n">
-        <v>24.25856018066406</v>
+        <v>24.2585620880127</v>
       </c>
       <c r="C519" t="n">
-        <v>25.41458872545803</v>
+        <v>25.41459072370033</v>
       </c>
       <c r="D519" t="n">
-        <v>23.90633122613104</v>
+        <v>23.90633310578539</v>
       </c>
       <c r="E519" t="n">
-        <v>25.17976999664215</v>
+        <v>25.17977197642164</v>
       </c>
       <c r="F519" t="n">
         <v>889600</v>
@@ -10952,16 +10952,16 @@
         <v>44529</v>
       </c>
       <c r="B527" t="n">
-        <v>22.89480781555176</v>
+        <v>22.89480972290039</v>
       </c>
       <c r="C527" t="n">
-        <v>23.5450739164797</v>
+        <v>23.5450758780015</v>
       </c>
       <c r="D527" t="n">
-        <v>22.84061940446239</v>
+        <v>22.84062130729663</v>
       </c>
       <c r="E527" t="n">
-        <v>23.5450739164797</v>
+        <v>23.5450758780015</v>
       </c>
       <c r="F527" t="n">
         <v>477300</v>
@@ -11012,16 +11012,16 @@
         <v>44532</v>
       </c>
       <c r="B530" t="n">
-        <v>21.49492645263672</v>
+        <v>21.49492454528809</v>
       </c>
       <c r="C530" t="n">
-        <v>22.25357107779976</v>
+        <v>22.25356910313292</v>
       </c>
       <c r="D530" t="n">
-        <v>21.17882596100086</v>
+        <v>21.17882408170135</v>
       </c>
       <c r="E530" t="n">
-        <v>22.1632576359715</v>
+        <v>22.16325566931861</v>
       </c>
       <c r="F530" t="n">
         <v>1427300</v>
@@ -11072,16 +11072,16 @@
         <v>44537</v>
       </c>
       <c r="B533" t="n">
-        <v>22.57870674133301</v>
+        <v>22.57870483398438</v>
       </c>
       <c r="C533" t="n">
-        <v>23.3825081500865</v>
+        <v>23.38250617483631</v>
       </c>
       <c r="D533" t="n">
-        <v>22.55161167310071</v>
+        <v>22.55160976804094</v>
       </c>
       <c r="E533" t="n">
-        <v>23.03931256557043</v>
+        <v>23.03931061931187</v>
       </c>
       <c r="F533" t="n">
         <v>550100</v>
@@ -11092,16 +11092,16 @@
         <v>44538</v>
       </c>
       <c r="B534" t="n">
-        <v>23.66248512268066</v>
+        <v>23.66248321533203</v>
       </c>
       <c r="C534" t="n">
-        <v>23.66248512268066</v>
+        <v>23.66248321533203</v>
       </c>
       <c r="D534" t="n">
-        <v>22.44323462604225</v>
+        <v>22.44323281697306</v>
       </c>
       <c r="E534" t="n">
-        <v>22.58773820996488</v>
+        <v>22.58773638924777</v>
       </c>
       <c r="F534" t="n">
         <v>822800</v>
@@ -11152,16 +11152,16 @@
         <v>44543</v>
       </c>
       <c r="B537" t="n">
-        <v>23.27412986755371</v>
+        <v>23.27412796020508</v>
       </c>
       <c r="C537" t="n">
-        <v>23.57216870900448</v>
+        <v>23.57216677723113</v>
       </c>
       <c r="D537" t="n">
-        <v>23.03027943656167</v>
+        <v>23.03027754919694</v>
       </c>
       <c r="E537" t="n">
-        <v>23.34638165570485</v>
+        <v>23.34637974243508</v>
       </c>
       <c r="F537" t="n">
         <v>776500</v>
@@ -11292,16 +11292,16 @@
         <v>44552</v>
       </c>
       <c r="B544" t="n">
-        <v>22.25357246398926</v>
+        <v>22.25357437133789</v>
       </c>
       <c r="C544" t="n">
-        <v>22.67805324654457</v>
+        <v>22.67805519027536</v>
       </c>
       <c r="D544" t="n">
-        <v>21.81103002551431</v>
+        <v>21.81103189493273</v>
       </c>
       <c r="E544" t="n">
-        <v>22.54257963012648</v>
+        <v>22.54258156224585</v>
       </c>
       <c r="F544" t="n">
         <v>962700</v>
@@ -11352,16 +11352,16 @@
         <v>44558</v>
       </c>
       <c r="B547" t="n">
-        <v>22.60456275939941</v>
+        <v>22.60456085205078</v>
       </c>
       <c r="C547" t="n">
-        <v>22.87855676270879</v>
+        <v>22.87855483224084</v>
       </c>
       <c r="D547" t="n">
-        <v>22.35796711121414</v>
+        <v>22.35796522467298</v>
       </c>
       <c r="E547" t="n">
-        <v>22.35796711121414</v>
+        <v>22.35796522467298</v>
       </c>
       <c r="F547" t="n">
         <v>521700</v>
@@ -11432,16 +11432,16 @@
         <v>44565</v>
       </c>
       <c r="B551" t="n">
-        <v>21.21632194519043</v>
+        <v>21.2163200378418</v>
       </c>
       <c r="C551" t="n">
-        <v>22.4675651411926</v>
+        <v>22.46756312135713</v>
       </c>
       <c r="D551" t="n">
-        <v>21.1615234944346</v>
+        <v>21.16152159201236</v>
       </c>
       <c r="E551" t="n">
-        <v>22.36709986313081</v>
+        <v>22.36709785232717</v>
       </c>
       <c r="F551" t="n">
         <v>946700</v>
@@ -11472,16 +11472,16 @@
         <v>44567</v>
       </c>
       <c r="B553" t="n">
-        <v>20.2208080291748</v>
+        <v>20.22080612182617</v>
       </c>
       <c r="C553" t="n">
-        <v>20.62266740483826</v>
+        <v>20.62266545958383</v>
       </c>
       <c r="D553" t="n">
-        <v>19.95594739526826</v>
+        <v>19.95594551290288</v>
       </c>
       <c r="E553" t="n">
-        <v>20.09294439501381</v>
+        <v>20.09294249972604</v>
       </c>
       <c r="F553" t="n">
         <v>2456700</v>
@@ -11492,16 +11492,16 @@
         <v>44568</v>
       </c>
       <c r="B554" t="n">
-        <v>20.18427848815918</v>
+        <v>20.18427658081055</v>
       </c>
       <c r="C554" t="n">
-        <v>20.28474203641364</v>
+        <v>20.28474011957153</v>
       </c>
       <c r="D554" t="n">
-        <v>19.75501896939461</v>
+        <v>19.7550171026096</v>
       </c>
       <c r="E554" t="n">
-        <v>20.11121329760523</v>
+        <v>20.11121139716102</v>
       </c>
       <c r="F554" t="n">
         <v>922900</v>
@@ -11552,16 +11552,16 @@
         <v>44573</v>
       </c>
       <c r="B557" t="n">
-        <v>20.68659973144531</v>
+        <v>20.68659782409668</v>
       </c>
       <c r="C557" t="n">
-        <v>20.88753029523179</v>
+        <v>20.88752836935694</v>
       </c>
       <c r="D557" t="n">
-        <v>19.71848560178518</v>
+        <v>19.71848378369873</v>
       </c>
       <c r="E557" t="n">
-        <v>19.93768115517928</v>
+        <v>19.93767931688253</v>
       </c>
       <c r="F557" t="n">
         <v>936900</v>
@@ -11592,16 +11592,16 @@
         <v>44575</v>
       </c>
       <c r="B559" t="n">
-        <v>20.18427848815918</v>
+        <v>20.18427658081055</v>
       </c>
       <c r="C559" t="n">
-        <v>20.66833472232478</v>
+        <v>20.66833276923441</v>
       </c>
       <c r="D559" t="n">
-        <v>19.97421628306801</v>
+        <v>19.97421439556958</v>
       </c>
       <c r="E559" t="n">
-        <v>20.54047107435825</v>
+        <v>20.54046913335058</v>
       </c>
       <c r="F559" t="n">
         <v>463400</v>
@@ -11652,16 +11652,16 @@
         <v>44580</v>
       </c>
       <c r="B562" t="n">
-        <v>20.23907661437988</v>
+        <v>20.23907470703125</v>
       </c>
       <c r="C562" t="n">
-        <v>20.64093602685637</v>
+        <v>20.64093408163615</v>
       </c>
       <c r="D562" t="n">
-        <v>19.78241874538753</v>
+        <v>19.78241688107475</v>
       </c>
       <c r="E562" t="n">
-        <v>19.80981884465123</v>
+        <v>19.80981697775623</v>
       </c>
       <c r="F562" t="n">
         <v>747400</v>
@@ -11672,16 +11672,16 @@
         <v>44581</v>
       </c>
       <c r="B563" t="n">
-        <v>21.14325714111328</v>
+        <v>21.14325904846191</v>
       </c>
       <c r="C563" t="n">
-        <v>21.80997715358547</v>
+        <v>21.8099791210794</v>
       </c>
       <c r="D563" t="n">
-        <v>20.13860956858716</v>
+        <v>20.1386113853058</v>
       </c>
       <c r="E563" t="n">
-        <v>20.22080811719456</v>
+        <v>20.2208099413284</v>
       </c>
       <c r="F563" t="n">
         <v>1850100</v>
@@ -11732,16 +11732,16 @@
         <v>44586</v>
       </c>
       <c r="B566" t="n">
-        <v>21.18892288208008</v>
+        <v>21.18892478942871</v>
       </c>
       <c r="C566" t="n">
-        <v>21.56338214340724</v>
+        <v>21.56338408446331</v>
       </c>
       <c r="D566" t="n">
-        <v>20.50393617350436</v>
+        <v>20.50393801919301</v>
       </c>
       <c r="E566" t="n">
-        <v>20.69573161574015</v>
+        <v>20.69573347869352</v>
       </c>
       <c r="F566" t="n">
         <v>1204000</v>
@@ -11772,16 +11772,16 @@
         <v>44588</v>
       </c>
       <c r="B568" t="n">
-        <v>22.9333553314209</v>
+        <v>22.93335723876953</v>
       </c>
       <c r="C568" t="n">
-        <v>23.54527685464833</v>
+        <v>23.54527881288999</v>
       </c>
       <c r="D568" t="n">
-        <v>22.50409588344849</v>
+        <v>22.50409775509596</v>
       </c>
       <c r="E568" t="n">
-        <v>22.90595523622757</v>
+        <v>22.90595714129736</v>
       </c>
       <c r="F568" t="n">
         <v>1423700</v>
@@ -11832,16 +11832,16 @@
         <v>44593</v>
       </c>
       <c r="B571" t="n">
-        <v>23.93800163269043</v>
+        <v>23.9379997253418</v>
       </c>
       <c r="C571" t="n">
-        <v>24.2941959100797</v>
+        <v>24.29419397434998</v>
       </c>
       <c r="D571" t="n">
-        <v>23.39914701799535</v>
+        <v>23.39914515358195</v>
       </c>
       <c r="E571" t="n">
-        <v>23.83753809876998</v>
+        <v>23.83753619942615</v>
       </c>
       <c r="F571" t="n">
         <v>1150300</v>
@@ -11872,16 +11872,16 @@
         <v>44595</v>
       </c>
       <c r="B573" t="n">
-        <v>23.39001274108887</v>
+        <v>23.3900146484375</v>
       </c>
       <c r="C573" t="n">
-        <v>24.20286305609526</v>
+        <v>24.20286502972813</v>
       </c>
       <c r="D573" t="n">
-        <v>23.22561565670302</v>
+        <v>23.22561755064583</v>
       </c>
       <c r="E573" t="n">
-        <v>23.78273872223032</v>
+        <v>23.78274066160397</v>
       </c>
       <c r="F573" t="n">
         <v>844100</v>
@@ -11892,16 +11892,16 @@
         <v>44596</v>
       </c>
       <c r="B574" t="n">
-        <v>22.55889892578125</v>
+        <v>22.55889701843262</v>
       </c>
       <c r="C574" t="n">
-        <v>23.25301733831812</v>
+        <v>23.25301537228196</v>
       </c>
       <c r="D574" t="n">
-        <v>22.19357124506313</v>
+        <v>22.19356936860285</v>
       </c>
       <c r="E574" t="n">
-        <v>23.2256189816723</v>
+        <v>23.22561701795267</v>
       </c>
       <c r="F574" t="n">
         <v>1145700</v>
@@ -11932,16 +11932,16 @@
         <v>44600</v>
       </c>
       <c r="B576" t="n">
-        <v>22.11137008666992</v>
+        <v>22.11137199401855</v>
       </c>
       <c r="C576" t="n">
-        <v>22.37623244979206</v>
+        <v>22.37623437998798</v>
       </c>
       <c r="D576" t="n">
-        <v>21.75517755613725</v>
+        <v>21.75517943276036</v>
       </c>
       <c r="E576" t="n">
-        <v>22.01090655411608</v>
+        <v>22.01090845279862</v>
       </c>
       <c r="F576" t="n">
         <v>873400</v>
@@ -11972,16 +11972,16 @@
         <v>44602</v>
       </c>
       <c r="B578" t="n">
-        <v>22.45842933654785</v>
+        <v>22.45843124389648</v>
       </c>
       <c r="C578" t="n">
-        <v>23.03381736202015</v>
+        <v>23.03381931823532</v>
       </c>
       <c r="D578" t="n">
-        <v>21.91957302694132</v>
+        <v>21.91957488852598</v>
       </c>
       <c r="E578" t="n">
-        <v>22.60455968403323</v>
+        <v>22.60456160379242</v>
       </c>
       <c r="F578" t="n">
         <v>703500</v>
@@ -11992,16 +11992,16 @@
         <v>44603</v>
       </c>
       <c r="B579" t="n">
-        <v>22.60456275939941</v>
+        <v>22.60456085205078</v>
       </c>
       <c r="C579" t="n">
-        <v>23.49961169502219</v>
+        <v>23.4996097121503</v>
       </c>
       <c r="D579" t="n">
-        <v>22.27576856181905</v>
+        <v>22.27576668221372</v>
       </c>
       <c r="E579" t="n">
-        <v>22.46756575774473</v>
+        <v>22.46756386195575</v>
       </c>
       <c r="F579" t="n">
         <v>1581300</v>
@@ -12012,16 +12012,16 @@
         <v>44606</v>
       </c>
       <c r="B580" t="n">
-        <v>23.39001274108887</v>
+        <v>23.3900146484375</v>
       </c>
       <c r="C580" t="n">
-        <v>23.55440982547471</v>
+        <v>23.55441174622917</v>
       </c>
       <c r="D580" t="n">
-        <v>22.18443644494101</v>
+        <v>22.18443825398041</v>
       </c>
       <c r="E580" t="n">
-        <v>22.19356806784135</v>
+        <v>22.19356987762539</v>
       </c>
       <c r="F580" t="n">
         <v>1108200</v>
@@ -12072,16 +12072,16 @@
         <v>44609</v>
       </c>
       <c r="B583" t="n">
-        <v>23.81013870239258</v>
+        <v>23.81013679504395</v>
       </c>
       <c r="C583" t="n">
-        <v>24.76912117951999</v>
+        <v>24.76911919535056</v>
       </c>
       <c r="D583" t="n">
-        <v>23.62747661770975</v>
+        <v>23.62747472499355</v>
       </c>
       <c r="E583" t="n">
-        <v>24.56819062175412</v>
+        <v>24.56818865368055</v>
       </c>
       <c r="F583" t="n">
         <v>1278800</v>
@@ -12112,16 +12112,16 @@
         <v>44613</v>
       </c>
       <c r="B585" t="n">
-        <v>23.66400909423828</v>
+        <v>23.66400718688965</v>
       </c>
       <c r="C585" t="n">
-        <v>24.31246413191962</v>
+        <v>24.31246217230471</v>
       </c>
       <c r="D585" t="n">
-        <v>23.48134526170543</v>
+        <v>23.48134336907973</v>
       </c>
       <c r="E585" t="n">
-        <v>24.07500184643148</v>
+        <v>24.07499990595632</v>
       </c>
       <c r="F585" t="n">
         <v>913100</v>
@@ -12272,16 +12272,16 @@
         <v>44627</v>
       </c>
       <c r="B593" t="n">
-        <v>21.92870712280273</v>
+        <v>21.92870903015137</v>
       </c>
       <c r="C593" t="n">
-        <v>23.70053982267321</v>
+        <v>23.70054188413502</v>
       </c>
       <c r="D593" t="n">
-        <v>21.92870712280273</v>
+        <v>21.92870903015137</v>
       </c>
       <c r="E593" t="n">
-        <v>23.70053982267321</v>
+        <v>23.70054188413502</v>
       </c>
       <c r="F593" t="n">
         <v>1568800</v>
@@ -12312,16 +12312,16 @@
         <v>44629</v>
       </c>
       <c r="B595" t="n">
-        <v>23.65487289428711</v>
+        <v>23.65487480163574</v>
       </c>
       <c r="C595" t="n">
-        <v>23.85580343440176</v>
+        <v>23.85580535795189</v>
       </c>
       <c r="D595" t="n">
-        <v>22.52236179750086</v>
+        <v>22.52236361353243</v>
       </c>
       <c r="E595" t="n">
-        <v>22.56802687915717</v>
+        <v>22.56802869887082</v>
       </c>
       <c r="F595" t="n">
         <v>1193700</v>
@@ -12392,16 +12392,16 @@
         <v>44635</v>
       </c>
       <c r="B599" t="n">
-        <v>21.83737754821777</v>
+        <v>21.83737945556641</v>
       </c>
       <c r="C599" t="n">
-        <v>22.04743973440702</v>
+        <v>22.04744166010318</v>
       </c>
       <c r="D599" t="n">
-        <v>21.1797908924035</v>
+        <v>21.17979274231634</v>
       </c>
       <c r="E599" t="n">
-        <v>22.01090801342303</v>
+        <v>22.0109099359284</v>
       </c>
       <c r="F599" t="n">
         <v>1768200</v>
@@ -12412,16 +12412,16 @@
         <v>44636</v>
       </c>
       <c r="B600" t="n">
-        <v>21.89217567443848</v>
+        <v>21.89217758178711</v>
       </c>
       <c r="C600" t="n">
-        <v>22.5040972344004</v>
+        <v>22.5040991950625</v>
       </c>
       <c r="D600" t="n">
-        <v>21.39898612543066</v>
+        <v>21.39898798981032</v>
       </c>
       <c r="E600" t="n">
-        <v>22.25750333090219</v>
+        <v>22.25750527007987</v>
       </c>
       <c r="F600" t="n">
         <v>1335900</v>
@@ -12452,16 +12452,16 @@
         <v>44638</v>
       </c>
       <c r="B602" t="n">
-        <v>23.75534057617188</v>
+        <v>23.75533866882324</v>
       </c>
       <c r="C602" t="n">
-        <v>24.03846794361094</v>
+        <v>24.03846601352962</v>
       </c>
       <c r="D602" t="n">
-        <v>21.66384687415755</v>
+        <v>21.6638451347378</v>
       </c>
       <c r="E602" t="n">
-        <v>22.43103216955036</v>
+        <v>22.43103036853225</v>
       </c>
       <c r="F602" t="n">
         <v>2359200</v>
@@ -12492,16 +12492,16 @@
         <v>44642</v>
       </c>
       <c r="B604" t="n">
-        <v>23.56354331970215</v>
+        <v>23.56354522705078</v>
       </c>
       <c r="C604" t="n">
-        <v>23.6092101478867</v>
+        <v>23.60921205893183</v>
       </c>
       <c r="D604" t="n">
-        <v>22.90595667194699</v>
+        <v>22.90595852606733</v>
       </c>
       <c r="E604" t="n">
-        <v>22.95162175812017</v>
+        <v>22.95162361593687</v>
       </c>
       <c r="F604" t="n">
         <v>1289700</v>
@@ -12532,16 +12532,16 @@
         <v>44644</v>
       </c>
       <c r="B606" t="n">
-        <v>24.77825164794922</v>
+        <v>24.77825355529785</v>
       </c>
       <c r="C606" t="n">
-        <v>24.95178210101803</v>
+        <v>24.95178402172447</v>
       </c>
       <c r="D606" t="n">
-        <v>23.91060286662769</v>
+        <v>23.91060470718757</v>
       </c>
       <c r="E606" t="n">
-        <v>24.20286358210489</v>
+        <v>24.20286544516204</v>
       </c>
       <c r="F606" t="n">
         <v>1668300</v>
@@ -12552,16 +12552,16 @@
         <v>44645</v>
       </c>
       <c r="B607" t="n">
-        <v>25.39017677307129</v>
+        <v>25.39017486572266</v>
       </c>
       <c r="C607" t="n">
-        <v>25.57284061714119</v>
+        <v>25.57283869607057</v>
       </c>
       <c r="D607" t="n">
-        <v>24.75085680284967</v>
+        <v>24.75085494352772</v>
       </c>
       <c r="E607" t="n">
-        <v>24.82392199207533</v>
+        <v>24.82392012726461</v>
       </c>
       <c r="F607" t="n">
         <v>1605600</v>
@@ -12652,16 +12652,16 @@
         <v>44652</v>
       </c>
       <c r="B612" t="n">
-        <v>25.81029891967773</v>
+        <v>25.81030082702637</v>
       </c>
       <c r="C612" t="n">
-        <v>26.02036108841196</v>
+        <v>26.02036301128392</v>
       </c>
       <c r="D612" t="n">
-        <v>25.42670630015768</v>
+        <v>25.4267081791593</v>
       </c>
       <c r="E612" t="n">
-        <v>25.55456992599395</v>
+        <v>25.55457181444453</v>
       </c>
       <c r="F612" t="n">
         <v>858600</v>
@@ -12692,16 +12692,16 @@
         <v>44656</v>
       </c>
       <c r="B614" t="n">
-        <v>25.3627758026123</v>
+        <v>25.36277770996094</v>
       </c>
       <c r="C614" t="n">
-        <v>26.39482171183918</v>
+        <v>26.39482369680043</v>
       </c>
       <c r="D614" t="n">
-        <v>25.33537570622154</v>
+        <v>25.33537761150961</v>
       </c>
       <c r="E614" t="n">
-        <v>26.25782471390801</v>
+        <v>26.25782668856672</v>
       </c>
       <c r="F614" t="n">
         <v>767600</v>
@@ -12712,16 +12712,16 @@
         <v>44657</v>
       </c>
       <c r="B615" t="n">
-        <v>25.10704612731934</v>
+        <v>25.10704803466797</v>
       </c>
       <c r="C615" t="n">
-        <v>25.32624166657651</v>
+        <v>25.32624359057713</v>
       </c>
       <c r="D615" t="n">
-        <v>24.50425795885928</v>
+        <v>24.50425982041491</v>
       </c>
       <c r="E615" t="n">
-        <v>25.32624166657651</v>
+        <v>25.32624359057713</v>
       </c>
       <c r="F615" t="n">
         <v>1144600</v>
@@ -12872,16 +12872,16 @@
         <v>44670</v>
       </c>
       <c r="B623" t="n">
-        <v>25.30797576904297</v>
+        <v>25.3079776763916</v>
       </c>
       <c r="C623" t="n">
-        <v>25.38104269321135</v>
+        <v>25.38104460606671</v>
       </c>
       <c r="D623" t="n">
-        <v>24.78738612842271</v>
+        <v>24.78738799653684</v>
       </c>
       <c r="E623" t="n">
-        <v>24.88785140714289</v>
+        <v>24.88785328282863</v>
       </c>
       <c r="F623" t="n">
         <v>997600</v>
@@ -12932,16 +12932,16 @@
         <v>44676</v>
       </c>
       <c r="B626" t="n">
-        <v>24.06587028503418</v>
+        <v>24.06586837768555</v>
       </c>
       <c r="C626" t="n">
-        <v>24.27593248878918</v>
+        <v>24.275930564792</v>
       </c>
       <c r="D626" t="n">
-        <v>23.26215145204145</v>
+        <v>23.26214960839183</v>
       </c>
       <c r="E626" t="n">
-        <v>23.95627162889461</v>
+        <v>23.95626973023226</v>
       </c>
       <c r="F626" t="n">
         <v>529900</v>
@@ -12972,16 +12972,16 @@
         <v>44678</v>
       </c>
       <c r="B628" t="n">
-        <v>23.43567848205566</v>
+        <v>23.4356803894043</v>
       </c>
       <c r="C628" t="n">
-        <v>24.20286373606933</v>
+        <v>24.20286570585651</v>
       </c>
       <c r="D628" t="n">
-        <v>23.18908284854885</v>
+        <v>23.18908473582792</v>
       </c>
       <c r="E628" t="n">
-        <v>23.65487402005796</v>
+        <v>23.65487594524615</v>
       </c>
       <c r="F628" t="n">
         <v>920800</v>
@@ -34652,19 +34652,39 @@
         <v>46261</v>
       </c>
       <c r="B1712" t="n">
-        <v>22.6</v>
+        <v>22.60000038146973</v>
       </c>
       <c r="C1712" t="n">
-        <v>22.74</v>
+        <v>22.73999977111816</v>
       </c>
       <c r="D1712" t="n">
-        <v>22.38</v>
+        <v>22.3799991607666</v>
       </c>
       <c r="E1712" t="n">
-        <v>22.7</v>
+        <v>22.70000076293945</v>
       </c>
       <c r="F1712" t="n">
         <v>2650300</v>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B1713" t="n">
+        <v>22.08</v>
+      </c>
+      <c r="C1713" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="D1713" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="E1713" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="F1713" t="n">
+        <v>2075900</v>
       </c>
     </row>
   </sheetData>

--- a/database/VIVA3.xlsx
+++ b/database/VIVA3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1720"/>
+  <dimension ref="A1:F1721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>43749</v>
       </c>
       <c r="B2" t="n">
-        <v>21.18223571777344</v>
+        <v>21.18223762512207</v>
       </c>
       <c r="C2" t="n">
-        <v>21.75352347985466</v>
+        <v>21.75352543864475</v>
       </c>
       <c r="D2" t="n">
-        <v>21.17330916027268</v>
+        <v>21.17331106681752</v>
       </c>
       <c r="E2" t="n">
-        <v>21.69103757734936</v>
+        <v>21.69103953051291</v>
       </c>
       <c r="F2" t="n">
         <v>7077400</v>
@@ -492,16 +492,16 @@
         <v>43753</v>
       </c>
       <c r="B4" t="n">
-        <v>21.02156448364258</v>
+        <v>21.02156257629395</v>
       </c>
       <c r="C4" t="n">
-        <v>21.10190181156005</v>
+        <v>21.10189989692218</v>
       </c>
       <c r="D4" t="n">
-        <v>20.75377452562902</v>
+        <v>20.75377264257776</v>
       </c>
       <c r="E4" t="n">
-        <v>21.06619727835619</v>
+        <v>21.0661953669579</v>
       </c>
       <c r="F4" t="n">
         <v>1133500</v>
@@ -552,16 +552,16 @@
         <v>43756</v>
       </c>
       <c r="B7" t="n">
-        <v>21.55714416503906</v>
+        <v>21.5571460723877</v>
       </c>
       <c r="C7" t="n">
-        <v>21.55714416503906</v>
+        <v>21.5571460723877</v>
       </c>
       <c r="D7" t="n">
-        <v>21.2536479985278</v>
+        <v>21.25364987902348</v>
       </c>
       <c r="E7" t="n">
-        <v>21.52143963504373</v>
+        <v>21.52144153923327</v>
       </c>
       <c r="F7" t="n">
         <v>1051300</v>
@@ -572,16 +572,16 @@
         <v>43759</v>
       </c>
       <c r="B8" t="n">
-        <v>21.43217468261719</v>
+        <v>21.43217658996582</v>
       </c>
       <c r="C8" t="n">
-        <v>21.63748040186501</v>
+        <v>21.63748232748475</v>
       </c>
       <c r="D8" t="n">
-        <v>21.39646845184359</v>
+        <v>21.39647035601456</v>
       </c>
       <c r="E8" t="n">
-        <v>21.5571430851912</v>
+        <v>21.55714500366135</v>
       </c>
       <c r="F8" t="n">
         <v>3309600</v>
@@ -592,16 +592,16 @@
         <v>43760</v>
       </c>
       <c r="B9" t="n">
-        <v>21.28935241699219</v>
+        <v>21.28935432434082</v>
       </c>
       <c r="C9" t="n">
-        <v>21.51251124378966</v>
+        <v>21.51251317113147</v>
       </c>
       <c r="D9" t="n">
-        <v>21.16438231624022</v>
+        <v>21.16438421239258</v>
       </c>
       <c r="E9" t="n">
-        <v>21.45002704469704</v>
+        <v>21.45002896644079</v>
       </c>
       <c r="F9" t="n">
         <v>928900</v>
@@ -612,16 +612,16 @@
         <v>43761</v>
       </c>
       <c r="B10" t="n">
-        <v>20.99478721618652</v>
+        <v>20.99478340148926</v>
       </c>
       <c r="C10" t="n">
-        <v>21.34291451383752</v>
+        <v>21.34291063588645</v>
       </c>
       <c r="D10" t="n">
-        <v>20.80733287721262</v>
+        <v>20.80732909657531</v>
       </c>
       <c r="E10" t="n">
-        <v>21.34291451383752</v>
+        <v>21.34291063588645</v>
       </c>
       <c r="F10" t="n">
         <v>1482200</v>
@@ -672,16 +672,16 @@
         <v>43766</v>
       </c>
       <c r="B13" t="n">
-        <v>20.87874031066895</v>
+        <v>20.87873840332031</v>
       </c>
       <c r="C13" t="n">
-        <v>20.87874031066895</v>
+        <v>20.87873840332031</v>
       </c>
       <c r="D13" t="n">
-        <v>20.53061306867368</v>
+        <v>20.53061119312774</v>
       </c>
       <c r="E13" t="n">
-        <v>20.66450803078211</v>
+        <v>20.66450614300437</v>
       </c>
       <c r="F13" t="n">
         <v>1950600</v>
@@ -732,16 +732,16 @@
         <v>43769</v>
       </c>
       <c r="B16" t="n">
-        <v>21.63748359680176</v>
+        <v>21.63747978210449</v>
       </c>
       <c r="C16" t="n">
-        <v>21.63748359680176</v>
+        <v>21.63747978210449</v>
       </c>
       <c r="D16" t="n">
-        <v>20.81625889598369</v>
+        <v>20.81625522606868</v>
       </c>
       <c r="E16" t="n">
-        <v>21.1554613281515</v>
+        <v>21.15545759843496</v>
       </c>
       <c r="F16" t="n">
         <v>554600</v>
@@ -752,16 +752,16 @@
         <v>43770</v>
       </c>
       <c r="B17" t="n">
-        <v>21.37862014770508</v>
+        <v>21.37861824035645</v>
       </c>
       <c r="C17" t="n">
-        <v>21.53929310184948</v>
+        <v>21.53929118016599</v>
       </c>
       <c r="D17" t="n">
-        <v>21.34291391173941</v>
+        <v>21.3429120075764</v>
       </c>
       <c r="E17" t="n">
-        <v>21.5303682454251</v>
+        <v>21.53036632453787</v>
       </c>
       <c r="F17" t="n">
         <v>740500</v>
@@ -792,16 +792,16 @@
         <v>43774</v>
       </c>
       <c r="B19" t="n">
-        <v>21.69104194641113</v>
+        <v>21.6910400390625</v>
       </c>
       <c r="C19" t="n">
-        <v>21.69104194641113</v>
+        <v>21.6910400390625</v>
       </c>
       <c r="D19" t="n">
-        <v>21.2090196622474</v>
+        <v>21.20901779728422</v>
       </c>
       <c r="E19" t="n">
-        <v>21.51251586813709</v>
+        <v>21.51251397648671</v>
       </c>
       <c r="F19" t="n">
         <v>2102900</v>
@@ -832,16 +832,16 @@
         <v>43776</v>
       </c>
       <c r="B21" t="n">
-        <v>21.28935241699219</v>
+        <v>21.28935432434082</v>
       </c>
       <c r="C21" t="n">
-        <v>21.49465812902984</v>
+        <v>21.49466005477216</v>
       </c>
       <c r="D21" t="n">
-        <v>21.22686821789957</v>
+        <v>21.22687011965014</v>
       </c>
       <c r="E21" t="n">
-        <v>21.47680501427003</v>
+        <v>21.47680693841286</v>
       </c>
       <c r="F21" t="n">
         <v>641700</v>
@@ -892,16 +892,16 @@
         <v>43781</v>
       </c>
       <c r="B24" t="n">
-        <v>20.89659690856934</v>
+        <v>20.89659118652344</v>
       </c>
       <c r="C24" t="n">
-        <v>21.39647231160594</v>
+        <v>21.39646645268082</v>
       </c>
       <c r="D24" t="n">
-        <v>20.5216899306501</v>
+        <v>20.52168431126374</v>
       </c>
       <c r="E24" t="n">
-        <v>21.39647231160594</v>
+        <v>21.39646645268082</v>
       </c>
       <c r="F24" t="n">
         <v>1578700</v>
@@ -912,16 +912,16 @@
         <v>43782</v>
       </c>
       <c r="B25" t="n">
-        <v>20.42349815368652</v>
+        <v>20.42349624633789</v>
       </c>
       <c r="C25" t="n">
-        <v>20.87874243318845</v>
+        <v>20.8787404833246</v>
       </c>
       <c r="D25" t="n">
-        <v>20.20033929329736</v>
+        <v>20.20033740678952</v>
       </c>
       <c r="E25" t="n">
-        <v>20.87874243318845</v>
+        <v>20.8787404833246</v>
       </c>
       <c r="F25" t="n">
         <v>1400300</v>
@@ -952,16 +952,16 @@
         <v>43787</v>
       </c>
       <c r="B27" t="n">
-        <v>21.36076354980469</v>
+        <v>21.36076545715332</v>
       </c>
       <c r="C27" t="n">
-        <v>21.40539463492381</v>
+        <v>21.40539654625765</v>
       </c>
       <c r="D27" t="n">
-        <v>20.89659277327204</v>
+        <v>20.89659463917386</v>
       </c>
       <c r="E27" t="n">
-        <v>21.2090154768062</v>
+        <v>21.20901737060492</v>
       </c>
       <c r="F27" t="n">
         <v>523400</v>
@@ -972,16 +972,16 @@
         <v>43788</v>
       </c>
       <c r="B28" t="n">
-        <v>21.2715015411377</v>
+        <v>21.27149772644043</v>
       </c>
       <c r="C28" t="n">
-        <v>21.51251350806239</v>
+        <v>21.51250965014356</v>
       </c>
       <c r="D28" t="n">
-        <v>21.06619580749084</v>
+        <v>21.06619202961181</v>
       </c>
       <c r="E28" t="n">
-        <v>21.40539651079578</v>
+        <v>21.40539267208663</v>
       </c>
       <c r="F28" t="n">
         <v>1162900</v>
@@ -992,16 +992,16 @@
         <v>43790</v>
       </c>
       <c r="B29" t="n">
-        <v>21.11082458496094</v>
+        <v>21.1108283996582</v>
       </c>
       <c r="C29" t="n">
-        <v>21.45895351103337</v>
+        <v>21.45895738863706</v>
       </c>
       <c r="D29" t="n">
-        <v>20.97692962996388</v>
+        <v>20.9769334204665</v>
       </c>
       <c r="E29" t="n">
-        <v>21.3875410522971</v>
+        <v>21.38754491699665</v>
       </c>
       <c r="F29" t="n">
         <v>1121600</v>
@@ -1012,16 +1012,16 @@
         <v>43791</v>
       </c>
       <c r="B30" t="n">
-        <v>20.79840278625488</v>
+        <v>20.79840469360352</v>
       </c>
       <c r="C30" t="n">
-        <v>21.33398433193429</v>
+        <v>21.33398628839923</v>
       </c>
       <c r="D30" t="n">
-        <v>20.68236094093163</v>
+        <v>20.68236283763847</v>
       </c>
       <c r="E30" t="n">
-        <v>21.27150013040894</v>
+        <v>21.27150208114367</v>
       </c>
       <c r="F30" t="n">
         <v>1810700</v>
@@ -1032,16 +1032,16 @@
         <v>43794</v>
       </c>
       <c r="B31" t="n">
-        <v>21.22686767578125</v>
+        <v>21.22686958312988</v>
       </c>
       <c r="C31" t="n">
-        <v>21.22686767578125</v>
+        <v>21.22686958312988</v>
       </c>
       <c r="D31" t="n">
-        <v>20.60202229567972</v>
+        <v>20.60202414688262</v>
       </c>
       <c r="E31" t="n">
-        <v>20.87873875712277</v>
+        <v>20.87874063319014</v>
       </c>
       <c r="F31" t="n">
         <v>2173000</v>
@@ -1112,16 +1112,16 @@
         <v>43798</v>
       </c>
       <c r="B35" t="n">
-        <v>21.22686767578125</v>
+        <v>21.22686958312988</v>
       </c>
       <c r="C35" t="n">
-        <v>21.22686767578125</v>
+        <v>21.22686958312988</v>
       </c>
       <c r="D35" t="n">
-        <v>20.76269691928107</v>
+        <v>20.76269878492145</v>
       </c>
       <c r="E35" t="n">
-        <v>20.8608873453856</v>
+        <v>20.86088921984892</v>
       </c>
       <c r="F35" t="n">
         <v>599200</v>
@@ -1132,16 +1132,16 @@
         <v>43801</v>
       </c>
       <c r="B36" t="n">
-        <v>20.96800422668457</v>
+        <v>20.9680061340332</v>
       </c>
       <c r="C36" t="n">
-        <v>21.22686929615112</v>
+        <v>21.22687122704734</v>
       </c>
       <c r="D36" t="n">
-        <v>20.94122455318453</v>
+        <v>20.94122645809716</v>
       </c>
       <c r="E36" t="n">
-        <v>21.22686929615112</v>
+        <v>21.22687122704734</v>
       </c>
       <c r="F36" t="n">
         <v>516500</v>
@@ -1192,16 +1192,16 @@
         <v>43804</v>
       </c>
       <c r="B39" t="n">
-        <v>21.36076354980469</v>
+        <v>21.36076545715332</v>
       </c>
       <c r="C39" t="n">
-        <v>21.37861666487904</v>
+        <v>21.37861857382182</v>
       </c>
       <c r="D39" t="n">
-        <v>20.67343394254289</v>
+        <v>20.67343578851838</v>
       </c>
       <c r="E39" t="n">
-        <v>21.01263631868858</v>
+        <v>21.01263819495218</v>
       </c>
       <c r="F39" t="n">
         <v>1835400</v>
@@ -1232,16 +1232,16 @@
         <v>43808</v>
       </c>
       <c r="B41" t="n">
-        <v>24.18149566650391</v>
+        <v>24.18149375915527</v>
       </c>
       <c r="C41" t="n">
-        <v>24.23505331942033</v>
+        <v>24.23505140784727</v>
       </c>
       <c r="D41" t="n">
-        <v>22.61045699289629</v>
+        <v>22.61045520946548</v>
       </c>
       <c r="E41" t="n">
-        <v>23.08355441759815</v>
+        <v>23.08355259685113</v>
       </c>
       <c r="F41" t="n">
         <v>2077700</v>
@@ -1272,16 +1272,16 @@
         <v>43810</v>
       </c>
       <c r="B43" t="n">
-        <v>23.74410057067871</v>
+        <v>23.74410247802734</v>
       </c>
       <c r="C43" t="n">
-        <v>24.41357708092773</v>
+        <v>24.41357904205499</v>
       </c>
       <c r="D43" t="n">
-        <v>23.66376325324348</v>
+        <v>23.66376515413867</v>
       </c>
       <c r="E43" t="n">
-        <v>24.12793404229884</v>
+        <v>24.12793598048058</v>
       </c>
       <c r="F43" t="n">
         <v>1527800</v>
@@ -1312,16 +1312,16 @@
         <v>43812</v>
       </c>
       <c r="B45" t="n">
-        <v>25.26158142089844</v>
+        <v>25.26158332824707</v>
       </c>
       <c r="C45" t="n">
-        <v>25.26158142089844</v>
+        <v>25.26158332824707</v>
       </c>
       <c r="D45" t="n">
-        <v>24.51176754032499</v>
+        <v>24.51176939105973</v>
       </c>
       <c r="E45" t="n">
-        <v>24.98486492052895</v>
+        <v>24.9848668069844</v>
       </c>
       <c r="F45" t="n">
         <v>1395200</v>
@@ -1352,16 +1352,16 @@
         <v>43816</v>
       </c>
       <c r="B47" t="n">
-        <v>24.72600173950195</v>
+        <v>24.72599983215332</v>
       </c>
       <c r="C47" t="n">
-        <v>25.41332971685165</v>
+        <v>25.41332775648296</v>
       </c>
       <c r="D47" t="n">
-        <v>24.63673785726122</v>
+        <v>24.63673595679835</v>
       </c>
       <c r="E47" t="n">
-        <v>25.12768665573485</v>
+        <v>25.12768471740049</v>
       </c>
       <c r="F47" t="n">
         <v>1300800</v>
@@ -1432,16 +1432,16 @@
         <v>43822</v>
       </c>
       <c r="B51" t="n">
-        <v>26.03817558288574</v>
+        <v>26.03817176818848</v>
       </c>
       <c r="C51" t="n">
-        <v>26.48449329825741</v>
+        <v>26.48448941817281</v>
       </c>
       <c r="D51" t="n">
-        <v>25.75253251745859</v>
+        <v>25.75252874460918</v>
       </c>
       <c r="E51" t="n">
-        <v>25.75253251745859</v>
+        <v>25.75252874460918</v>
       </c>
       <c r="F51" t="n">
         <v>893300</v>
@@ -1452,16 +1452,16 @@
         <v>43825</v>
       </c>
       <c r="B52" t="n">
-        <v>26.22562789916992</v>
+        <v>26.22562599182129</v>
       </c>
       <c r="C52" t="n">
-        <v>26.70765184336195</v>
+        <v>26.70764990095647</v>
       </c>
       <c r="D52" t="n">
-        <v>26.06495495367286</v>
+        <v>26.06495305800972</v>
       </c>
       <c r="E52" t="n">
-        <v>26.2702606917249</v>
+        <v>26.27025878113019</v>
       </c>
       <c r="F52" t="n">
         <v>955400</v>
@@ -1532,16 +1532,16 @@
         <v>43833</v>
       </c>
       <c r="B56" t="n">
-        <v>26.03853416442871</v>
+        <v>26.03853607177734</v>
       </c>
       <c r="C56" t="n">
-        <v>26.26300428653586</v>
+        <v>26.26300621032715</v>
       </c>
       <c r="D56" t="n">
-        <v>25.25737738596456</v>
+        <v>25.25737923609267</v>
       </c>
       <c r="E56" t="n">
-        <v>26.03853416442871</v>
+        <v>26.03853607177734</v>
       </c>
       <c r="F56" t="n">
         <v>1128400</v>
@@ -1552,16 +1552,16 @@
         <v>43836</v>
       </c>
       <c r="B57" t="n">
-        <v>25.58061218261719</v>
+        <v>25.58061408996582</v>
       </c>
       <c r="C57" t="n">
-        <v>26.00261535066234</v>
+        <v>26.00261728947649</v>
       </c>
       <c r="D57" t="n">
-        <v>25.46388848509693</v>
+        <v>25.46389038374238</v>
       </c>
       <c r="E57" t="n">
-        <v>26.00261535066234</v>
+        <v>26.00261728947649</v>
       </c>
       <c r="F57" t="n">
         <v>445400</v>
@@ -1572,16 +1572,16 @@
         <v>43837</v>
       </c>
       <c r="B58" t="n">
-        <v>25.05086326599121</v>
+        <v>25.05086517333984</v>
       </c>
       <c r="C58" t="n">
-        <v>25.85895529794493</v>
+        <v>25.85895726682091</v>
       </c>
       <c r="D58" t="n">
-        <v>24.76354180685842</v>
+        <v>24.76354369233067</v>
       </c>
       <c r="E58" t="n">
-        <v>25.64346420359534</v>
+        <v>25.64346615606404</v>
       </c>
       <c r="F58" t="n">
         <v>1259500</v>
@@ -1592,16 +1592,16 @@
         <v>43838</v>
       </c>
       <c r="B59" t="n">
-        <v>25.09576034545898</v>
+        <v>25.09575653076172</v>
       </c>
       <c r="C59" t="n">
-        <v>25.40103984863807</v>
+        <v>25.40103598753659</v>
       </c>
       <c r="D59" t="n">
-        <v>24.47622232870483</v>
+        <v>24.47621860818084</v>
       </c>
       <c r="E59" t="n">
-        <v>25.05086529347905</v>
+        <v>25.05086148560608</v>
       </c>
       <c r="F59" t="n">
         <v>1739100</v>
@@ -1612,16 +1612,16 @@
         <v>43839</v>
       </c>
       <c r="B60" t="n">
-        <v>25.49980354309082</v>
+        <v>25.49980163574219</v>
       </c>
       <c r="C60" t="n">
-        <v>25.93078573295725</v>
+        <v>25.93078379337177</v>
       </c>
       <c r="D60" t="n">
-        <v>25.12269369881495</v>
+        <v>25.12269181967359</v>
       </c>
       <c r="E60" t="n">
-        <v>25.12269369881495</v>
+        <v>25.12269181967359</v>
       </c>
       <c r="F60" t="n">
         <v>1769000</v>
@@ -1632,16 +1632,16 @@
         <v>43840</v>
       </c>
       <c r="B61" t="n">
-        <v>25.99363899230957</v>
+        <v>25.9936408996582</v>
       </c>
       <c r="C61" t="n">
-        <v>25.99363899230957</v>
+        <v>25.9936408996582</v>
       </c>
       <c r="D61" t="n">
-        <v>25.51776175046936</v>
+        <v>25.51776362289931</v>
       </c>
       <c r="E61" t="n">
-        <v>25.51776175046936</v>
+        <v>25.51776362289931</v>
       </c>
       <c r="F61" t="n">
         <v>1402200</v>
@@ -1652,16 +1652,16 @@
         <v>43843</v>
       </c>
       <c r="B62" t="n">
-        <v>26.93641662597656</v>
+        <v>26.9364128112793</v>
       </c>
       <c r="C62" t="n">
-        <v>27.37637789202563</v>
+        <v>27.37637401502167</v>
       </c>
       <c r="D62" t="n">
-        <v>26.05649409387843</v>
+        <v>26.05649040379455</v>
       </c>
       <c r="E62" t="n">
-        <v>26.11934545866097</v>
+        <v>26.11934175967617</v>
       </c>
       <c r="F62" t="n">
         <v>2538500</v>
@@ -1692,16 +1692,16 @@
         <v>43845</v>
       </c>
       <c r="B64" t="n">
-        <v>28.41791915893555</v>
+        <v>28.41791725158691</v>
       </c>
       <c r="C64" t="n">
-        <v>28.43587718101201</v>
+        <v>28.43587527245808</v>
       </c>
       <c r="D64" t="n">
-        <v>26.89152324643202</v>
+        <v>26.89152144153174</v>
       </c>
       <c r="E64" t="n">
-        <v>27.14292870521757</v>
+        <v>27.14292688344351</v>
       </c>
       <c r="F64" t="n">
         <v>1889600</v>
@@ -1712,16 +1712,16 @@
         <v>43846</v>
       </c>
       <c r="B65" t="n">
-        <v>28.79502487182617</v>
+        <v>28.7950267791748</v>
       </c>
       <c r="C65" t="n">
-        <v>29.23498778585654</v>
+        <v>29.23498972234781</v>
       </c>
       <c r="D65" t="n">
-        <v>28.24731726614954</v>
+        <v>28.24731913721867</v>
       </c>
       <c r="E65" t="n">
-        <v>28.39097970929621</v>
+        <v>28.39098158988137</v>
       </c>
       <c r="F65" t="n">
         <v>1262700</v>
@@ -1732,16 +1732,16 @@
         <v>43847</v>
       </c>
       <c r="B66" t="n">
-        <v>29.10030555725098</v>
+        <v>29.10030364990234</v>
       </c>
       <c r="C66" t="n">
-        <v>29.41456234803923</v>
+        <v>29.41456042009297</v>
       </c>
       <c r="D66" t="n">
-        <v>28.47178855053234</v>
+        <v>28.47178668437919</v>
       </c>
       <c r="E66" t="n">
-        <v>29.00153815867692</v>
+        <v>29.00153625780189</v>
       </c>
       <c r="F66" t="n">
         <v>1385800</v>
@@ -1752,16 +1752,16 @@
         <v>43850</v>
       </c>
       <c r="B67" t="n">
-        <v>28.80400657653809</v>
+        <v>28.80400848388672</v>
       </c>
       <c r="C67" t="n">
-        <v>29.18111472273289</v>
+        <v>29.18111665505293</v>
       </c>
       <c r="D67" t="n">
-        <v>28.69625845607491</v>
+        <v>28.69626035628866</v>
       </c>
       <c r="E67" t="n">
-        <v>29.18111472273289</v>
+        <v>29.18111665505293</v>
       </c>
       <c r="F67" t="n">
         <v>528200</v>
@@ -1772,16 +1772,16 @@
         <v>43851</v>
       </c>
       <c r="B68" t="n">
-        <v>27.93305969238281</v>
+        <v>27.93306159973145</v>
       </c>
       <c r="C68" t="n">
-        <v>28.93868477775592</v>
+        <v>28.93868675377149</v>
       </c>
       <c r="D68" t="n">
-        <v>27.78939896590094</v>
+        <v>27.78940086344001</v>
       </c>
       <c r="E68" t="n">
-        <v>28.82195936713255</v>
+        <v>28.82196133517778</v>
       </c>
       <c r="F68" t="n">
         <v>1246300</v>
@@ -1792,16 +1792,16 @@
         <v>43852</v>
       </c>
       <c r="B69" t="n">
-        <v>27.60982322692871</v>
+        <v>27.60982513427734</v>
       </c>
       <c r="C69" t="n">
-        <v>28.39097995468525</v>
+        <v>28.39098191599795</v>
       </c>
       <c r="D69" t="n">
-        <v>27.2506713973853</v>
+        <v>27.25067327992292</v>
       </c>
       <c r="E69" t="n">
-        <v>28.02284740276087</v>
+        <v>28.02284933864215</v>
       </c>
       <c r="F69" t="n">
         <v>1068100</v>
@@ -1812,16 +1812,16 @@
         <v>43853</v>
       </c>
       <c r="B70" t="n">
-        <v>28.0856990814209</v>
+        <v>28.08570098876953</v>
       </c>
       <c r="C70" t="n">
-        <v>28.0856990814209</v>
+        <v>28.08570098876953</v>
       </c>
       <c r="D70" t="n">
-        <v>27.14292364888665</v>
+        <v>27.14292549220977</v>
       </c>
       <c r="E70" t="n">
-        <v>27.47514014512921</v>
+        <v>27.47514201101373</v>
       </c>
       <c r="F70" t="n">
         <v>1247300</v>
@@ -1832,16 +1832,16 @@
         <v>43854</v>
       </c>
       <c r="B71" t="n">
-        <v>28.19344520568848</v>
+        <v>28.19344329833984</v>
       </c>
       <c r="C71" t="n">
-        <v>28.65136443124743</v>
+        <v>28.65136249291955</v>
       </c>
       <c r="D71" t="n">
-        <v>27.70859066323084</v>
+        <v>27.70858878868368</v>
       </c>
       <c r="E71" t="n">
-        <v>28.41791531355633</v>
+        <v>28.4179133910218</v>
       </c>
       <c r="F71" t="n">
         <v>978300</v>
@@ -1852,16 +1852,16 @@
         <v>43857</v>
       </c>
       <c r="B72" t="n">
-        <v>27.38535308837891</v>
+        <v>27.38535499572754</v>
       </c>
       <c r="C72" t="n">
-        <v>27.69961158108762</v>
+        <v>27.69961351032389</v>
       </c>
       <c r="D72" t="n">
-        <v>26.48747265925173</v>
+        <v>26.48747450406434</v>
       </c>
       <c r="E72" t="n">
-        <v>27.38535308837891</v>
+        <v>27.38535499572754</v>
       </c>
       <c r="F72" t="n">
         <v>1743500</v>
@@ -1972,16 +1972,16 @@
         <v>43865</v>
       </c>
       <c r="B78" t="n">
-        <v>29.36967086791992</v>
+        <v>29.36966896057129</v>
       </c>
       <c r="C78" t="n">
-        <v>29.98921061629559</v>
+        <v>29.98920866871232</v>
       </c>
       <c r="D78" t="n">
-        <v>28.92971133298596</v>
+        <v>28.92970945420953</v>
       </c>
       <c r="E78" t="n">
-        <v>29.62107974159596</v>
+        <v>29.62107781792014</v>
       </c>
       <c r="F78" t="n">
         <v>2096800</v>
@@ -1992,16 +1992,16 @@
         <v>43866</v>
       </c>
       <c r="B79" t="n">
-        <v>28.36404418945312</v>
+        <v>28.36404609680176</v>
       </c>
       <c r="C79" t="n">
-        <v>29.82759031485853</v>
+        <v>29.82759232062376</v>
       </c>
       <c r="D79" t="n">
-        <v>28.14855308212255</v>
+        <v>28.14855497498042</v>
       </c>
       <c r="E79" t="n">
-        <v>29.56720415647716</v>
+        <v>29.56720614473264</v>
       </c>
       <c r="F79" t="n">
         <v>2205100</v>
@@ -2012,16 +2012,16 @@
         <v>43867</v>
       </c>
       <c r="B80" t="n">
-        <v>27.38535308837891</v>
+        <v>27.38535499572754</v>
       </c>
       <c r="C80" t="n">
-        <v>28.65136435644255</v>
+        <v>28.65136635196696</v>
       </c>
       <c r="D80" t="n">
-        <v>26.99028522004307</v>
+        <v>26.99028709987582</v>
       </c>
       <c r="E80" t="n">
-        <v>28.36404289313321</v>
+        <v>28.36404486864612</v>
       </c>
       <c r="F80" t="n">
         <v>4008000</v>
@@ -2132,16 +2132,16 @@
         <v>43875</v>
       </c>
       <c r="B86" t="n">
-        <v>27.38535308837891</v>
+        <v>27.38535499572754</v>
       </c>
       <c r="C86" t="n">
-        <v>27.78939996651454</v>
+        <v>27.78940190200443</v>
       </c>
       <c r="D86" t="n">
-        <v>26.67602672733435</v>
+        <v>26.67602858527947</v>
       </c>
       <c r="E86" t="n">
-        <v>27.46616246400603</v>
+        <v>27.46616437698292</v>
       </c>
       <c r="F86" t="n">
         <v>912400</v>
@@ -2152,16 +2152,16 @@
         <v>43878</v>
       </c>
       <c r="B87" t="n">
-        <v>28.19344520568848</v>
+        <v>28.19344329833984</v>
       </c>
       <c r="C87" t="n">
-        <v>28.23834025480466</v>
+        <v>28.23833834441877</v>
       </c>
       <c r="D87" t="n">
-        <v>27.00824331015756</v>
+        <v>27.00824148299045</v>
       </c>
       <c r="E87" t="n">
-        <v>27.29556477421706</v>
+        <v>27.29556292761201</v>
       </c>
       <c r="F87" t="n">
         <v>467300</v>
@@ -2212,16 +2212,16 @@
         <v>43881</v>
       </c>
       <c r="B90" t="n">
-        <v>27.83429718017578</v>
+        <v>27.83429336547852</v>
       </c>
       <c r="C90" t="n">
-        <v>28.08570435187721</v>
+        <v>28.08570050272453</v>
       </c>
       <c r="D90" t="n">
-        <v>27.56493369894451</v>
+        <v>27.56492992116358</v>
       </c>
       <c r="E90" t="n">
-        <v>27.93306458916049</v>
+        <v>27.93306076092713</v>
       </c>
       <c r="F90" t="n">
         <v>884200</v>
@@ -2232,16 +2232,16 @@
         <v>43882</v>
       </c>
       <c r="B91" t="n">
-        <v>27.83429718017578</v>
+        <v>27.83429336547852</v>
       </c>
       <c r="C91" t="n">
-        <v>28.13957670560922</v>
+        <v>28.13957284907332</v>
       </c>
       <c r="D91" t="n">
-        <v>26.91845860387548</v>
+        <v>26.91845491469412</v>
       </c>
       <c r="E91" t="n">
-        <v>27.38535690307617</v>
+        <v>27.38535314990628</v>
       </c>
       <c r="F91" t="n">
         <v>843900</v>
@@ -2272,16 +2272,16 @@
         <v>43888</v>
       </c>
       <c r="B93" t="n">
-        <v>25.85895729064941</v>
+        <v>25.85895919799805</v>
       </c>
       <c r="C93" t="n">
-        <v>26.01159704164758</v>
+        <v>26.01159896025487</v>
       </c>
       <c r="D93" t="n">
-        <v>24.79945975659457</v>
+        <v>24.799461585795</v>
       </c>
       <c r="E93" t="n">
-        <v>25.64346617969397</v>
+        <v>25.64346807114804</v>
       </c>
       <c r="F93" t="n">
         <v>1043900</v>
@@ -2312,16 +2312,16 @@
         <v>43892</v>
       </c>
       <c r="B95" t="n">
-        <v>24.9251651763916</v>
+        <v>24.92516326904297</v>
       </c>
       <c r="C95" t="n">
-        <v>25.27533805555338</v>
+        <v>25.27533612140846</v>
       </c>
       <c r="D95" t="n">
-        <v>24.61090662999373</v>
+        <v>24.61090474669311</v>
       </c>
       <c r="E95" t="n">
-        <v>24.87129282096009</v>
+        <v>24.87129091773393</v>
       </c>
       <c r="F95" t="n">
         <v>2727300</v>
@@ -2332,16 +2332,16 @@
         <v>43893</v>
       </c>
       <c r="B96" t="n">
-        <v>24.64682006835938</v>
+        <v>24.64681816101074</v>
       </c>
       <c r="C96" t="n">
-        <v>25.64346624499489</v>
+        <v>25.64346426051859</v>
       </c>
       <c r="D96" t="n">
-        <v>24.47622229620438</v>
+        <v>24.47622040205784</v>
       </c>
       <c r="E96" t="n">
-        <v>25.36512377337336</v>
+        <v>25.36512181043721</v>
       </c>
       <c r="F96" t="n">
         <v>1967700</v>
@@ -2372,16 +2372,16 @@
         <v>43895</v>
       </c>
       <c r="B98" t="n">
-        <v>23.74894142150879</v>
+        <v>23.74893760681152</v>
       </c>
       <c r="C98" t="n">
-        <v>25.96670578113082</v>
+        <v>25.96670161020296</v>
       </c>
       <c r="D98" t="n">
-        <v>23.56038561397133</v>
+        <v>23.56038182956102</v>
       </c>
       <c r="E98" t="n">
-        <v>25.85895936074209</v>
+        <v>25.85895520712111</v>
       </c>
       <c r="F98" t="n">
         <v>2079800</v>
@@ -2392,16 +2392,16 @@
         <v>43896</v>
       </c>
       <c r="B99" t="n">
-        <v>22.40211868286133</v>
+        <v>22.4021167755127</v>
       </c>
       <c r="C99" t="n">
-        <v>23.01267597129664</v>
+        <v>23.01267401196428</v>
       </c>
       <c r="D99" t="n">
-        <v>21.49525919166898</v>
+        <v>21.49525736153167</v>
       </c>
       <c r="E99" t="n">
-        <v>22.80616387171244</v>
+        <v>22.80616192996282</v>
       </c>
       <c r="F99" t="n">
         <v>5887000</v>
@@ -2452,16 +2452,16 @@
         <v>43901</v>
       </c>
       <c r="B102" t="n">
-        <v>19.57378959655762</v>
+        <v>19.57379150390625</v>
       </c>
       <c r="C102" t="n">
-        <v>20.79490733645901</v>
+        <v>20.79490936279825</v>
       </c>
       <c r="D102" t="n">
-        <v>18.5232695909238</v>
+        <v>18.52327139590555</v>
       </c>
       <c r="E102" t="n">
-        <v>20.77694931967911</v>
+        <v>20.77695134426845</v>
       </c>
       <c r="F102" t="n">
         <v>1408200</v>
@@ -2472,16 +2472,16 @@
         <v>43902</v>
       </c>
       <c r="B103" t="n">
-        <v>17.14951705932617</v>
+        <v>17.1495189666748</v>
       </c>
       <c r="C103" t="n">
-        <v>18.2090162718631</v>
+        <v>18.20901829704796</v>
       </c>
       <c r="D103" t="n">
-        <v>13.95306225785632</v>
+        <v>13.9530638096991</v>
       </c>
       <c r="E103" t="n">
-        <v>14.4558756901934</v>
+        <v>14.45587729795849</v>
       </c>
       <c r="F103" t="n">
         <v>3374500</v>
@@ -2492,16 +2492,16 @@
         <v>43903</v>
       </c>
       <c r="B104" t="n">
-        <v>19.3044319152832</v>
+        <v>19.30443000793457</v>
       </c>
       <c r="C104" t="n">
-        <v>19.43911365589884</v>
+        <v>19.43911173524315</v>
       </c>
       <c r="D104" t="n">
-        <v>16.17082898663648</v>
+        <v>16.1708273888993</v>
       </c>
       <c r="E104" t="n">
-        <v>18.5053187700687</v>
+        <v>18.50531694167537</v>
       </c>
       <c r="F104" t="n">
         <v>7039400</v>
@@ -2512,16 +2512,16 @@
         <v>43906</v>
       </c>
       <c r="B105" t="n">
-        <v>14.09672260284424</v>
+        <v>14.09672164916992</v>
       </c>
       <c r="C105" t="n">
-        <v>16.74546970442783</v>
+        <v>16.74546857155995</v>
       </c>
       <c r="D105" t="n">
-        <v>14.04285025647584</v>
+        <v>14.0428493064461</v>
       </c>
       <c r="E105" t="n">
-        <v>15.82065395605772</v>
+        <v>15.82065288575565</v>
       </c>
       <c r="F105" t="n">
         <v>3420300</v>
@@ -2592,16 +2592,16 @@
         <v>43910</v>
       </c>
       <c r="B109" t="n">
-        <v>14.35710716247559</v>
+        <v>14.3571081161499</v>
       </c>
       <c r="C109" t="n">
-        <v>14.35710716247559</v>
+        <v>14.3571081161499</v>
       </c>
       <c r="D109" t="n">
-        <v>12.39074949447038</v>
+        <v>12.39075031752892</v>
       </c>
       <c r="E109" t="n">
-        <v>12.57032540036131</v>
+        <v>12.57032623534822</v>
       </c>
       <c r="F109" t="n">
         <v>4777400</v>
@@ -2612,16 +2612,16 @@
         <v>43913</v>
       </c>
       <c r="B110" t="n">
-        <v>12.57032585144043</v>
+        <v>12.57032489776611</v>
       </c>
       <c r="C110" t="n">
-        <v>13.91714647838048</v>
+        <v>13.91714542252677</v>
       </c>
       <c r="D110" t="n">
-        <v>11.51980569392435</v>
+        <v>11.51980481994997</v>
       </c>
       <c r="E110" t="n">
-        <v>13.86327327653726</v>
+        <v>13.86327222477075</v>
       </c>
       <c r="F110" t="n">
         <v>1044300</v>
@@ -2652,16 +2652,16 @@
         <v>43915</v>
       </c>
       <c r="B112" t="n">
-        <v>17.23032760620117</v>
+        <v>17.23032569885254</v>
       </c>
       <c r="C112" t="n">
-        <v>17.86782195143869</v>
+        <v>17.86781997352124</v>
       </c>
       <c r="D112" t="n">
-        <v>12.74990317417663</v>
+        <v>12.74990176279834</v>
       </c>
       <c r="E112" t="n">
-        <v>12.97437330349765</v>
+        <v>12.97437186727114</v>
       </c>
       <c r="F112" t="n">
         <v>1209000</v>
@@ -2672,16 +2672,16 @@
         <v>43916</v>
       </c>
       <c r="B113" t="n">
-        <v>17.41888046264648</v>
+        <v>17.41888236999512</v>
       </c>
       <c r="C113" t="n">
-        <v>17.77803230168198</v>
+        <v>17.77803424835735</v>
       </c>
       <c r="D113" t="n">
-        <v>16.25163655763836</v>
+        <v>16.25163833717505</v>
       </c>
       <c r="E113" t="n">
-        <v>16.61078839667386</v>
+        <v>16.61079021553728</v>
       </c>
       <c r="F113" t="n">
         <v>2254600</v>
@@ -2712,16 +2712,16 @@
         <v>43920</v>
       </c>
       <c r="B115" t="n">
-        <v>15.35375499725342</v>
+        <v>15.35375308990479</v>
       </c>
       <c r="C115" t="n">
-        <v>16.70057558100248</v>
+        <v>16.70057350634256</v>
       </c>
       <c r="D115" t="n">
-        <v>15.2729456252228</v>
+        <v>15.27294372791286</v>
       </c>
       <c r="E115" t="n">
-        <v>15.70392780100547</v>
+        <v>15.70392585015598</v>
       </c>
       <c r="F115" t="n">
         <v>1181300</v>
@@ -2732,16 +2732,16 @@
         <v>43921</v>
       </c>
       <c r="B116" t="n">
-        <v>14.15957546234131</v>
+        <v>14.15957450866699</v>
       </c>
       <c r="C116" t="n">
-        <v>15.61414086875142</v>
+        <v>15.61413981710936</v>
       </c>
       <c r="D116" t="n">
-        <v>13.93510534421632</v>
+        <v>13.93510440566049</v>
       </c>
       <c r="E116" t="n">
-        <v>15.47945914039065</v>
+        <v>15.47945809781966</v>
       </c>
       <c r="F116" t="n">
         <v>1259600</v>
@@ -2752,16 +2752,16 @@
         <v>43922</v>
       </c>
       <c r="B117" t="n">
-        <v>12.06751346588135</v>
+        <v>12.06751251220703</v>
       </c>
       <c r="C117" t="n">
-        <v>13.93510568169277</v>
+        <v>13.93510458042593</v>
       </c>
       <c r="D117" t="n">
-        <v>11.86100136322217</v>
+        <v>11.86100042586814</v>
       </c>
       <c r="E117" t="n">
-        <v>13.85429630020507</v>
+        <v>13.85429520532445</v>
       </c>
       <c r="F117" t="n">
         <v>2267400</v>
@@ -2772,16 +2772,16 @@
         <v>43923</v>
       </c>
       <c r="B118" t="n">
-        <v>12.74092292785645</v>
+        <v>12.74092197418213</v>
       </c>
       <c r="C118" t="n">
-        <v>12.74990193766703</v>
+        <v>12.74990098332062</v>
       </c>
       <c r="D118" t="n">
-        <v>11.76223397821181</v>
+        <v>11.76223309779361</v>
       </c>
       <c r="E118" t="n">
-        <v>12.57032602288294</v>
+        <v>12.57032508197802</v>
       </c>
       <c r="F118" t="n">
         <v>2636100</v>
@@ -2792,16 +2792,16 @@
         <v>43924</v>
       </c>
       <c r="B119" t="n">
-        <v>12.52543163299561</v>
+        <v>12.52543258666992</v>
       </c>
       <c r="C119" t="n">
-        <v>13.01028702342494</v>
+        <v>13.01028801401567</v>
       </c>
       <c r="D119" t="n">
-        <v>11.61857220725087</v>
+        <v>11.61857309187778</v>
       </c>
       <c r="E119" t="n">
-        <v>12.68705038190055</v>
+        <v>12.68705134788036</v>
       </c>
       <c r="F119" t="n">
         <v>2075200</v>
@@ -2832,16 +2832,16 @@
         <v>43928</v>
       </c>
       <c r="B121" t="n">
-        <v>14.09672260284424</v>
+        <v>14.09672164916992</v>
       </c>
       <c r="C121" t="n">
-        <v>14.70728071397066</v>
+        <v>14.70727971899074</v>
       </c>
       <c r="D121" t="n">
-        <v>13.665740406755</v>
+        <v>13.66573948223758</v>
       </c>
       <c r="E121" t="n">
-        <v>14.18651098850558</v>
+        <v>14.18651002875689</v>
       </c>
       <c r="F121" t="n">
         <v>1305600</v>
@@ -2892,16 +2892,16 @@
         <v>43934</v>
       </c>
       <c r="B124" t="n">
-        <v>13.82735824584961</v>
+        <v>13.82735919952393</v>
       </c>
       <c r="C124" t="n">
-        <v>14.50974757649816</v>
+        <v>14.50974857723694</v>
       </c>
       <c r="D124" t="n">
-        <v>13.82735824584961</v>
+        <v>13.82735919952393</v>
       </c>
       <c r="E124" t="n">
-        <v>14.4109801814157</v>
+        <v>14.41098117534248</v>
       </c>
       <c r="F124" t="n">
         <v>1287900</v>
@@ -2912,16 +2912,16 @@
         <v>43935</v>
       </c>
       <c r="B125" t="n">
-        <v>14.79707050323486</v>
+        <v>14.79706859588623</v>
       </c>
       <c r="C125" t="n">
-        <v>15.05745667509506</v>
+        <v>15.05745473418254</v>
       </c>
       <c r="D125" t="n">
-        <v>13.83633862443985</v>
+        <v>13.83633684092996</v>
       </c>
       <c r="E125" t="n">
-        <v>14.40200430896385</v>
+        <v>14.40200245253942</v>
       </c>
       <c r="F125" t="n">
         <v>5420700</v>
@@ -2952,16 +2952,16 @@
         <v>43937</v>
       </c>
       <c r="B127" t="n">
-        <v>13.9620418548584</v>
+        <v>13.96204280853271</v>
       </c>
       <c r="C127" t="n">
-        <v>14.77013481333978</v>
+        <v>14.77013582221072</v>
       </c>
       <c r="D127" t="n">
-        <v>13.49514358689775</v>
+        <v>13.49514450868068</v>
       </c>
       <c r="E127" t="n">
-        <v>14.77013481333978</v>
+        <v>14.77013582221072</v>
       </c>
       <c r="F127" t="n">
         <v>3178600</v>
@@ -2972,16 +2972,16 @@
         <v>43938</v>
       </c>
       <c r="B128" t="n">
-        <v>13.82735824584961</v>
+        <v>13.82735919952393</v>
       </c>
       <c r="C128" t="n">
-        <v>14.57259893243391</v>
+        <v>14.57259993750755</v>
       </c>
       <c r="D128" t="n">
-        <v>13.5400367829599</v>
+        <v>13.54003771681763</v>
       </c>
       <c r="E128" t="n">
-        <v>14.33915067197878</v>
+        <v>14.33915166095147</v>
       </c>
       <c r="F128" t="n">
         <v>3708800</v>
@@ -2992,16 +2992,16 @@
         <v>43941</v>
       </c>
       <c r="B129" t="n">
-        <v>14.18651103973389</v>
+        <v>14.1865119934082</v>
       </c>
       <c r="C129" t="n">
-        <v>14.3301717722824</v>
+        <v>14.33017273561417</v>
       </c>
       <c r="D129" t="n">
-        <v>13.28863060502017</v>
+        <v>13.28863149833535</v>
       </c>
       <c r="E129" t="n">
-        <v>13.58493107997285</v>
+        <v>13.58493199320655</v>
       </c>
       <c r="F129" t="n">
         <v>1191200</v>
@@ -3012,16 +3012,16 @@
         <v>43943</v>
       </c>
       <c r="B130" t="n">
-        <v>15.26396751403809</v>
+        <v>15.26396656036377</v>
       </c>
       <c r="C130" t="n">
-        <v>15.71290773503921</v>
+        <v>15.71290675331565</v>
       </c>
       <c r="D130" t="n">
-        <v>14.16855313503541</v>
+        <v>14.16855224980126</v>
       </c>
       <c r="E130" t="n">
-        <v>14.25834152174984</v>
+        <v>14.25834063090582</v>
       </c>
       <c r="F130" t="n">
         <v>2916000</v>
@@ -3052,16 +3052,16 @@
         <v>43945</v>
       </c>
       <c r="B132" t="n">
-        <v>14.09672260284424</v>
+        <v>14.09672164916992</v>
       </c>
       <c r="C132" t="n">
-        <v>14.44689627938088</v>
+        <v>14.44689530201654</v>
       </c>
       <c r="D132" t="n">
-        <v>13.11803279553471</v>
+        <v>13.11803190807091</v>
       </c>
       <c r="E132" t="n">
-        <v>14.36608690354277</v>
+        <v>14.36608593164536</v>
       </c>
       <c r="F132" t="n">
         <v>905700</v>
@@ -3072,16 +3072,16 @@
         <v>43948</v>
       </c>
       <c r="B133" t="n">
-        <v>15.69494915008545</v>
+        <v>15.69495105743408</v>
       </c>
       <c r="C133" t="n">
-        <v>15.69494915008545</v>
+        <v>15.69495105743408</v>
       </c>
       <c r="D133" t="n">
-        <v>13.97999770461368</v>
+        <v>13.97999940355066</v>
       </c>
       <c r="E133" t="n">
-        <v>14.49178926411654</v>
+        <v>14.49179102524964</v>
       </c>
       <c r="F133" t="n">
         <v>1099600</v>
@@ -3092,16 +3092,16 @@
         <v>43949</v>
       </c>
       <c r="B134" t="n">
-        <v>17.05972862243652</v>
+        <v>17.05972671508789</v>
       </c>
       <c r="C134" t="n">
-        <v>17.23032638818079</v>
+        <v>17.23032446175861</v>
       </c>
       <c r="D134" t="n">
-        <v>15.61414054377574</v>
+        <v>15.61413879804987</v>
       </c>
       <c r="E134" t="n">
-        <v>15.98227139283316</v>
+        <v>15.98226960594873</v>
       </c>
       <c r="F134" t="n">
         <v>2159200</v>
@@ -3112,16 +3112,16 @@
         <v>43950</v>
       </c>
       <c r="B135" t="n">
-        <v>16.87117576599121</v>
+        <v>16.87117385864258</v>
       </c>
       <c r="C135" t="n">
-        <v>17.47275406936573</v>
+        <v>17.47275209400646</v>
       </c>
       <c r="D135" t="n">
-        <v>16.61976860426559</v>
+        <v>16.61976672533946</v>
       </c>
       <c r="E135" t="n">
-        <v>17.3290933234</v>
+        <v>17.3290913642821</v>
       </c>
       <c r="F135" t="n">
         <v>1921700</v>
@@ -3132,16 +3132,16 @@
         <v>43951</v>
       </c>
       <c r="B136" t="n">
-        <v>16.63772583007812</v>
+        <v>16.63772392272949</v>
       </c>
       <c r="C136" t="n">
-        <v>17.14951742717981</v>
+        <v>17.14951546115939</v>
       </c>
       <c r="D136" t="n">
-        <v>16.23367893101306</v>
+        <v>16.23367706998436</v>
       </c>
       <c r="E136" t="n">
-        <v>16.73649151784984</v>
+        <v>16.73648959917871</v>
       </c>
       <c r="F136" t="n">
         <v>3051000</v>
@@ -3152,16 +3152,16 @@
         <v>43955</v>
       </c>
       <c r="B137" t="n">
-        <v>15.82065296173096</v>
+        <v>15.82065391540527</v>
       </c>
       <c r="C137" t="n">
-        <v>16.47610522449293</v>
+        <v>16.47610621767813</v>
       </c>
       <c r="D137" t="n">
-        <v>15.30885970939876</v>
+        <v>15.308860632222</v>
       </c>
       <c r="E137" t="n">
-        <v>16.15286774145594</v>
+        <v>16.15286871515628</v>
       </c>
       <c r="F137" t="n">
         <v>1661100</v>
@@ -3172,16 +3172,16 @@
         <v>43956</v>
       </c>
       <c r="B138" t="n">
-        <v>16.04512214660645</v>
+        <v>16.04512596130371</v>
       </c>
       <c r="C138" t="n">
-        <v>16.67363734598912</v>
+        <v>16.67364131011468</v>
       </c>
       <c r="D138" t="n">
-        <v>15.60515928069652</v>
+        <v>15.60516299079345</v>
       </c>
       <c r="E138" t="n">
-        <v>16.17082484396882</v>
+        <v>16.17082868855166</v>
       </c>
       <c r="F138" t="n">
         <v>1180300</v>
@@ -3192,16 +3192,16 @@
         <v>43957</v>
       </c>
       <c r="B139" t="n">
-        <v>15.71290969848633</v>
+        <v>15.7129077911377</v>
       </c>
       <c r="C139" t="n">
-        <v>16.34142677145428</v>
+        <v>16.34142478781162</v>
       </c>
       <c r="D139" t="n">
-        <v>15.52435560413869</v>
+        <v>15.52435371967814</v>
       </c>
       <c r="E139" t="n">
-        <v>16.17980799768702</v>
+        <v>16.17980603366284</v>
       </c>
       <c r="F139" t="n">
         <v>872400</v>
@@ -3232,16 +3232,16 @@
         <v>43959</v>
       </c>
       <c r="B141" t="n">
-        <v>15.61414051055908</v>
+        <v>15.6141414642334</v>
       </c>
       <c r="C141" t="n">
-        <v>15.70392889826353</v>
+        <v>15.7039298574219</v>
       </c>
       <c r="D141" t="n">
-        <v>14.60851536346824</v>
+        <v>14.60851625572138</v>
       </c>
       <c r="E141" t="n">
-        <v>15.33579804998925</v>
+        <v>15.33579898666308</v>
       </c>
       <c r="F141" t="n">
         <v>1248800</v>
@@ -3272,16 +3272,16 @@
         <v>43963</v>
       </c>
       <c r="B143" t="n">
-        <v>13.91714859008789</v>
+        <v>13.91714668273926</v>
       </c>
       <c r="C143" t="n">
-        <v>14.94971088490274</v>
+        <v>14.94970883604119</v>
       </c>
       <c r="D143" t="n">
-        <v>13.91714859008789</v>
+        <v>13.91714668273926</v>
       </c>
       <c r="E143" t="n">
-        <v>14.84196617743874</v>
+        <v>14.84196414334362</v>
       </c>
       <c r="F143" t="n">
         <v>2058100</v>
@@ -3312,16 +3312,16 @@
         <v>43965</v>
       </c>
       <c r="B145" t="n">
-        <v>13.9620418548584</v>
+        <v>13.96204280853271</v>
       </c>
       <c r="C145" t="n">
-        <v>14.00693605082162</v>
+        <v>14.00693700756243</v>
       </c>
       <c r="D145" t="n">
-        <v>12.94743679374597</v>
+        <v>12.9474376781179</v>
       </c>
       <c r="E145" t="n">
-        <v>13.27067346336718</v>
+        <v>13.27067436981772</v>
       </c>
       <c r="F145" t="n">
         <v>1612600</v>
@@ -3332,16 +3332,16 @@
         <v>43966</v>
       </c>
       <c r="B146" t="n">
-        <v>13.4771842956543</v>
+        <v>13.47718524932861</v>
       </c>
       <c r="C146" t="n">
-        <v>14.42893698972237</v>
+        <v>14.42893801074473</v>
       </c>
       <c r="D146" t="n">
-        <v>13.20782001866478</v>
+        <v>13.20782095327831</v>
       </c>
       <c r="E146" t="n">
-        <v>13.91714546284209</v>
+        <v>13.917146447649</v>
       </c>
       <c r="F146" t="n">
         <v>1353400</v>
@@ -3352,16 +3352,16 @@
         <v>43969</v>
       </c>
       <c r="B147" t="n">
-        <v>15.4166088104248</v>
+        <v>15.41660976409912</v>
       </c>
       <c r="C147" t="n">
-        <v>15.60516290020214</v>
+        <v>15.60516386554044</v>
       </c>
       <c r="D147" t="n">
-        <v>13.72859330669131</v>
+        <v>13.72859415594467</v>
       </c>
       <c r="E147" t="n">
-        <v>13.82735985699642</v>
+        <v>13.8273607123595</v>
       </c>
       <c r="F147" t="n">
         <v>3866000</v>
@@ -3372,16 +3372,16 @@
         <v>43970</v>
       </c>
       <c r="B148" t="n">
-        <v>15.4166088104248</v>
+        <v>15.41660976409912</v>
       </c>
       <c r="C148" t="n">
-        <v>15.70393030679285</v>
+        <v>15.70393127824093</v>
       </c>
       <c r="D148" t="n">
-        <v>14.90481718094782</v>
+        <v>14.90481810296261</v>
       </c>
       <c r="E148" t="n">
-        <v>15.35375744716569</v>
+        <v>15.35375839695201</v>
       </c>
       <c r="F148" t="n">
         <v>1836500</v>
@@ -3432,16 +3432,16 @@
         <v>43973</v>
       </c>
       <c r="B151" t="n">
-        <v>16.32346725463867</v>
+        <v>16.32346534729004</v>
       </c>
       <c r="C151" t="n">
-        <v>16.64670477257483</v>
+        <v>16.64670282745686</v>
       </c>
       <c r="D151" t="n">
-        <v>15.89248503910452</v>
+        <v>15.89248318211488</v>
       </c>
       <c r="E151" t="n">
-        <v>16.16184849567059</v>
+        <v>16.16184660720663</v>
       </c>
       <c r="F151" t="n">
         <v>2123900</v>
@@ -3492,16 +3492,16 @@
         <v>43978</v>
       </c>
       <c r="B154" t="n">
-        <v>17.95761299133301</v>
+        <v>17.95760917663574</v>
       </c>
       <c r="C154" t="n">
-        <v>17.95761299133301</v>
+        <v>17.95760917663574</v>
       </c>
       <c r="D154" t="n">
-        <v>16.40427987859984</v>
+        <v>16.40427639387381</v>
       </c>
       <c r="E154" t="n">
-        <v>16.87117822739165</v>
+        <v>16.87117464348339</v>
       </c>
       <c r="F154" t="n">
         <v>2199800</v>
@@ -3512,16 +3512,16 @@
         <v>43979</v>
       </c>
       <c r="B155" t="n">
-        <v>17.41888046264648</v>
+        <v>17.41888236999512</v>
       </c>
       <c r="C155" t="n">
-        <v>17.87679969963088</v>
+        <v>17.87680165712118</v>
       </c>
       <c r="D155" t="n">
-        <v>17.26624071698502</v>
+        <v>17.26624260761976</v>
       </c>
       <c r="E155" t="n">
-        <v>17.86782068958361</v>
+        <v>17.86782264609072</v>
       </c>
       <c r="F155" t="n">
         <v>2182800</v>
@@ -3532,16 +3532,16 @@
         <v>43980</v>
       </c>
       <c r="B156" t="n">
-        <v>17.22134590148926</v>
+        <v>17.22134780883789</v>
       </c>
       <c r="C156" t="n">
-        <v>17.61641374681152</v>
+        <v>17.61641569791586</v>
       </c>
       <c r="D156" t="n">
-        <v>16.84423607472048</v>
+        <v>16.84423794030235</v>
       </c>
       <c r="E156" t="n">
-        <v>17.28419725385557</v>
+        <v>17.2841991681653</v>
       </c>
       <c r="F156" t="n">
         <v>3327500</v>
@@ -3552,16 +3552,16 @@
         <v>43983</v>
       </c>
       <c r="B157" t="n">
-        <v>17.77803230285645</v>
+        <v>17.77803421020508</v>
       </c>
       <c r="C157" t="n">
-        <v>18.21799523234643</v>
+        <v>18.21799718689729</v>
       </c>
       <c r="D157" t="n">
-        <v>17.2841987382214</v>
+        <v>17.2842005925882</v>
       </c>
       <c r="E157" t="n">
-        <v>17.2841987382214</v>
+        <v>17.2842005925882</v>
       </c>
       <c r="F157" t="n">
         <v>2465800</v>
@@ -3572,16 +3572,16 @@
         <v>43984</v>
       </c>
       <c r="B158" t="n">
-        <v>18.02046012878418</v>
+        <v>18.02046203613281</v>
       </c>
       <c r="C158" t="n">
-        <v>18.39756998150098</v>
+        <v>18.39757192876424</v>
       </c>
       <c r="D158" t="n">
-        <v>17.84986236592941</v>
+        <v>17.84986425522138</v>
       </c>
       <c r="E158" t="n">
-        <v>18.04739715846789</v>
+        <v>18.04739906866763</v>
       </c>
       <c r="F158" t="n">
         <v>1898600</v>
@@ -3592,16 +3592,16 @@
         <v>43985</v>
       </c>
       <c r="B159" t="n">
-        <v>18.72080612182617</v>
+        <v>18.7208080291748</v>
       </c>
       <c r="C159" t="n">
-        <v>19.27749099411373</v>
+        <v>19.27749295817959</v>
       </c>
       <c r="D159" t="n">
-        <v>18.15514052772812</v>
+        <v>18.15514237744454</v>
       </c>
       <c r="E159" t="n">
-        <v>18.40654764872402</v>
+        <v>18.40654952405477</v>
       </c>
       <c r="F159" t="n">
         <v>3291000</v>
@@ -3612,16 +3612,16 @@
         <v>43986</v>
       </c>
       <c r="B160" t="n">
-        <v>18.22697067260742</v>
+        <v>18.22697257995605</v>
       </c>
       <c r="C160" t="n">
-        <v>18.82855058394848</v>
+        <v>18.82855255424903</v>
       </c>
       <c r="D160" t="n">
-        <v>18.04739562766093</v>
+        <v>18.04739751621806</v>
       </c>
       <c r="E160" t="n">
-        <v>18.72080589949476</v>
+        <v>18.72080785852044</v>
       </c>
       <c r="F160" t="n">
         <v>1670100</v>
@@ -3632,16 +3632,16 @@
         <v>43987</v>
       </c>
       <c r="B161" t="n">
-        <v>19.70847702026367</v>
+        <v>19.7084789276123</v>
       </c>
       <c r="C161" t="n">
-        <v>19.94192443562303</v>
+        <v>19.94192636556426</v>
       </c>
       <c r="D161" t="n">
-        <v>18.7657014983248</v>
+        <v>18.76570331443342</v>
       </c>
       <c r="E161" t="n">
-        <v>18.85548988792437</v>
+        <v>18.85549171272254</v>
       </c>
       <c r="F161" t="n">
         <v>3626500</v>
@@ -3652,16 +3652,16 @@
         <v>43990</v>
       </c>
       <c r="B162" t="n">
-        <v>19.66358375549316</v>
+        <v>19.6635799407959</v>
       </c>
       <c r="C162" t="n">
-        <v>20.44474058963029</v>
+        <v>20.4447366233901</v>
       </c>
       <c r="D162" t="n">
-        <v>19.4301346063553</v>
+        <v>19.43013083694672</v>
       </c>
       <c r="E162" t="n">
-        <v>20.02273563394709</v>
+        <v>20.02273174957505</v>
       </c>
       <c r="F162" t="n">
         <v>2478400</v>
@@ -3712,16 +3712,16 @@
         <v>43994</v>
       </c>
       <c r="B165" t="n">
-        <v>17.62538909912109</v>
+        <v>17.62539291381836</v>
       </c>
       <c r="C165" t="n">
-        <v>18.0473939257189</v>
+        <v>18.04739783175149</v>
       </c>
       <c r="D165" t="n">
-        <v>16.74546683792211</v>
+        <v>16.74547046217609</v>
       </c>
       <c r="E165" t="n">
-        <v>17.06870428594244</v>
+        <v>17.06870798015533</v>
       </c>
       <c r="F165" t="n">
         <v>2432500</v>
@@ -3732,16 +3732,16 @@
         <v>43997</v>
       </c>
       <c r="B166" t="n">
-        <v>17.95761299133301</v>
+        <v>17.95760917663574</v>
       </c>
       <c r="C166" t="n">
-        <v>18.18208315372467</v>
+        <v>18.18207929134369</v>
       </c>
       <c r="D166" t="n">
-        <v>16.63772905299574</v>
+        <v>16.6377255186786</v>
       </c>
       <c r="E166" t="n">
-        <v>17.32011855217497</v>
+        <v>17.32011487289929</v>
       </c>
       <c r="F166" t="n">
         <v>1760900</v>
@@ -3812,16 +3812,16 @@
         <v>44001</v>
       </c>
       <c r="B170" t="n">
-        <v>19.37626266479492</v>
+        <v>19.37625885009766</v>
       </c>
       <c r="C170" t="n">
-        <v>19.75337257333415</v>
+        <v>19.75336868439346</v>
       </c>
       <c r="D170" t="n">
-        <v>19.13383449946871</v>
+        <v>19.13383073249944</v>
       </c>
       <c r="E170" t="n">
-        <v>19.13383449946871</v>
+        <v>19.13383073249944</v>
       </c>
       <c r="F170" t="n">
         <v>5416500</v>
@@ -3852,16 +3852,16 @@
         <v>44005</v>
       </c>
       <c r="B172" t="n">
-        <v>19.07098197937012</v>
+        <v>19.07098007202148</v>
       </c>
       <c r="C172" t="n">
-        <v>19.43911285440775</v>
+        <v>19.43911091024119</v>
       </c>
       <c r="D172" t="n">
-        <v>18.86446987143606</v>
+        <v>18.86446798474135</v>
       </c>
       <c r="E172" t="n">
-        <v>19.04404494732913</v>
+        <v>19.04404304267455</v>
       </c>
       <c r="F172" t="n">
         <v>949500</v>
@@ -3932,16 +3932,16 @@
         <v>44011</v>
       </c>
       <c r="B176" t="n">
-        <v>18.25390815734863</v>
+        <v>18.25391006469727</v>
       </c>
       <c r="C176" t="n">
-        <v>18.40654789129145</v>
+        <v>18.40654981458939</v>
       </c>
       <c r="D176" t="n">
-        <v>17.52662552506624</v>
+        <v>17.5266273564212</v>
       </c>
       <c r="E176" t="n">
-        <v>18.1461617576245</v>
+        <v>18.14616365371473</v>
       </c>
       <c r="F176" t="n">
         <v>1645900</v>
@@ -3952,16 +3952,16 @@
         <v>44012</v>
       </c>
       <c r="B177" t="n">
-        <v>18.90936088562012</v>
+        <v>18.90936279296875</v>
       </c>
       <c r="C177" t="n">
-        <v>19.07995864241333</v>
+        <v>19.07996056696981</v>
       </c>
       <c r="D177" t="n">
-        <v>17.99352417233821</v>
+        <v>17.99352598730826</v>
       </c>
       <c r="E177" t="n">
-        <v>18.21799427401366</v>
+        <v>18.21799611162556</v>
       </c>
       <c r="F177" t="n">
         <v>1260700</v>
@@ -3972,16 +3972,16 @@
         <v>44013</v>
       </c>
       <c r="B178" t="n">
-        <v>18.90038299560547</v>
+        <v>18.90038108825684</v>
       </c>
       <c r="C178" t="n">
-        <v>19.20566248897294</v>
+        <v>19.20566055081676</v>
       </c>
       <c r="D178" t="n">
-        <v>18.74774324892174</v>
+        <v>18.74774135697687</v>
       </c>
       <c r="E178" t="n">
-        <v>18.74774324892174</v>
+        <v>18.74774135697687</v>
       </c>
       <c r="F178" t="n">
         <v>691200</v>
@@ -3992,16 +3992,16 @@
         <v>44014</v>
       </c>
       <c r="B179" t="n">
-        <v>19.01711082458496</v>
+        <v>19.01710891723633</v>
       </c>
       <c r="C179" t="n">
-        <v>19.51094445508126</v>
+        <v>19.51094249820287</v>
       </c>
       <c r="D179" t="n">
-        <v>18.89140809229237</v>
+        <v>18.89140619755127</v>
       </c>
       <c r="E179" t="n">
-        <v>19.12485553438682</v>
+        <v>19.12485361623177</v>
       </c>
       <c r="F179" t="n">
         <v>1184800</v>
@@ -4012,16 +4012,16 @@
         <v>44015</v>
       </c>
       <c r="B180" t="n">
-        <v>18.72080612182617</v>
+        <v>18.7208080291748</v>
       </c>
       <c r="C180" t="n">
-        <v>19.19668162352829</v>
+        <v>19.19668357936098</v>
       </c>
       <c r="D180" t="n">
-        <v>18.60408071428236</v>
+        <v>18.60408260973855</v>
       </c>
       <c r="E180" t="n">
-        <v>18.99016954873036</v>
+        <v>18.99017148352279</v>
       </c>
       <c r="F180" t="n">
         <v>998600</v>
@@ -4072,16 +4072,16 @@
         <v>44020</v>
       </c>
       <c r="B183" t="n">
-        <v>20.1484375</v>
+        <v>20.14843940734863</v>
       </c>
       <c r="C183" t="n">
-        <v>20.47167329299951</v>
+        <v>20.47167523094721</v>
       </c>
       <c r="D183" t="n">
-        <v>18.93629856668151</v>
+        <v>18.93630035928321</v>
       </c>
       <c r="E183" t="n">
-        <v>19.02608695295899</v>
+        <v>19.02608875406049</v>
       </c>
       <c r="F183" t="n">
         <v>3489400</v>
@@ -4092,16 +4092,16 @@
         <v>44021</v>
       </c>
       <c r="B184" t="n">
-        <v>19.96886444091797</v>
+        <v>19.9688606262207</v>
       </c>
       <c r="C184" t="n">
-        <v>20.4626998009938</v>
+        <v>20.46269589195806</v>
       </c>
       <c r="D184" t="n">
-        <v>19.5917545184808</v>
+        <v>19.59175077582369</v>
       </c>
       <c r="E184" t="n">
-        <v>20.23822964984243</v>
+        <v>20.23822578368772</v>
       </c>
       <c r="F184" t="n">
         <v>1601400</v>
@@ -4112,16 +4112,16 @@
         <v>44022</v>
       </c>
       <c r="B185" t="n">
-        <v>19.95090103149414</v>
+        <v>19.95090675354004</v>
       </c>
       <c r="C185" t="n">
-        <v>19.97783805888557</v>
+        <v>19.97784378865718</v>
       </c>
       <c r="D185" t="n">
-        <v>19.51093985952607</v>
+        <v>19.51094545538829</v>
       </c>
       <c r="E185" t="n">
-        <v>19.96885904975509</v>
+        <v>19.96886477695147</v>
       </c>
       <c r="F185" t="n">
         <v>1037600</v>
@@ -4132,16 +4132,16 @@
         <v>44025</v>
       </c>
       <c r="B186" t="n">
-        <v>19.45706939697266</v>
+        <v>19.45707130432129</v>
       </c>
       <c r="C186" t="n">
-        <v>20.33699182591409</v>
+        <v>20.33699381952026</v>
       </c>
       <c r="D186" t="n">
-        <v>19.40319704955632</v>
+        <v>19.40319895162392</v>
       </c>
       <c r="E186" t="n">
-        <v>20.02273332627185</v>
+        <v>20.02273528907171</v>
       </c>
       <c r="F186" t="n">
         <v>1075500</v>
@@ -4152,16 +4152,16 @@
         <v>44026</v>
       </c>
       <c r="B187" t="n">
-        <v>19.57378959655762</v>
+        <v>19.57379150390625</v>
       </c>
       <c r="C187" t="n">
-        <v>19.71745030565534</v>
+        <v>19.71745222700285</v>
       </c>
       <c r="D187" t="n">
-        <v>19.1338284608745</v>
+        <v>19.13383032535155</v>
       </c>
       <c r="E187" t="n">
-        <v>19.45706591262974</v>
+        <v>19.45706780860435</v>
       </c>
       <c r="F187" t="n">
         <v>582100</v>
@@ -4192,16 +4192,16 @@
         <v>44028</v>
       </c>
       <c r="B189" t="n">
-        <v>19.80724334716797</v>
+        <v>19.8072452545166</v>
       </c>
       <c r="C189" t="n">
-        <v>20.03171347213043</v>
+        <v>20.03171540109453</v>
       </c>
       <c r="D189" t="n">
-        <v>19.2505583963009</v>
+        <v>19.25056025004327</v>
       </c>
       <c r="E189" t="n">
-        <v>19.89703173966718</v>
+        <v>19.89703365566204</v>
       </c>
       <c r="F189" t="n">
         <v>1051500</v>
@@ -4232,16 +4232,16 @@
         <v>44032</v>
       </c>
       <c r="B191" t="n">
-        <v>21.4773006439209</v>
+        <v>21.47730255126953</v>
       </c>
       <c r="C191" t="n">
-        <v>21.51321497173749</v>
+        <v>21.51321688227559</v>
       </c>
       <c r="D191" t="n">
-        <v>20.48065278658737</v>
+        <v>20.48065460542605</v>
       </c>
       <c r="E191" t="n">
-        <v>20.4986108067812</v>
+        <v>20.49861262721468</v>
       </c>
       <c r="F191" t="n">
         <v>2793600</v>
@@ -4252,16 +4252,16 @@
         <v>44033</v>
       </c>
       <c r="B192" t="n">
-        <v>21.56708717346191</v>
+        <v>21.56709098815918</v>
       </c>
       <c r="C192" t="n">
-        <v>21.98011132689518</v>
+        <v>21.98011521464645</v>
       </c>
       <c r="D192" t="n">
-        <v>21.0732519361215</v>
+        <v>21.07325566347123</v>
       </c>
       <c r="E192" t="n">
-        <v>21.53117113616985</v>
+        <v>21.53117494451443</v>
       </c>
       <c r="F192" t="n">
         <v>1828100</v>
@@ -4272,16 +4272,16 @@
         <v>44034</v>
       </c>
       <c r="B193" t="n">
-        <v>20.81286811828613</v>
+        <v>20.81287002563477</v>
       </c>
       <c r="C193" t="n">
-        <v>21.60300212329511</v>
+        <v>21.6030041030538</v>
       </c>
       <c r="D193" t="n">
-        <v>20.59737702601096</v>
+        <v>20.59737891361139</v>
       </c>
       <c r="E193" t="n">
-        <v>21.45036238552882</v>
+        <v>21.45036435129919</v>
       </c>
       <c r="F193" t="n">
         <v>1944500</v>
@@ -4292,16 +4292,16 @@
         <v>44035</v>
       </c>
       <c r="B194" t="n">
-        <v>20.11252212524414</v>
+        <v>20.11252403259277</v>
       </c>
       <c r="C194" t="n">
-        <v>21.57606824600029</v>
+        <v>21.57607029214269</v>
       </c>
       <c r="D194" t="n">
-        <v>19.82520064971611</v>
+        <v>19.82520252981693</v>
       </c>
       <c r="E194" t="n">
-        <v>20.88469987515404</v>
+        <v>20.88470185573129</v>
       </c>
       <c r="F194" t="n">
         <v>4004200</v>
@@ -4312,16 +4312,16 @@
         <v>44036</v>
       </c>
       <c r="B195" t="n">
-        <v>20.72308349609375</v>
+        <v>20.72308158874512</v>
       </c>
       <c r="C195" t="n">
-        <v>20.82185090685944</v>
+        <v>20.82184899042027</v>
       </c>
       <c r="D195" t="n">
-        <v>19.03506877729229</v>
+        <v>19.03506702530821</v>
       </c>
       <c r="E195" t="n">
-        <v>20.07661010193875</v>
+        <v>20.07660825409141</v>
       </c>
       <c r="F195" t="n">
         <v>2630900</v>
@@ -4352,16 +4352,16 @@
         <v>44040</v>
       </c>
       <c r="B197" t="n">
-        <v>20.05865097045898</v>
+        <v>20.05864906311035</v>
       </c>
       <c r="C197" t="n">
-        <v>20.5165702415477</v>
+        <v>20.51656829065618</v>
       </c>
       <c r="D197" t="n">
-        <v>19.88805319199742</v>
+        <v>19.88805130087069</v>
       </c>
       <c r="E197" t="n">
-        <v>20.47167518796772</v>
+        <v>20.4716732413452</v>
       </c>
       <c r="F197" t="n">
         <v>1193800</v>
@@ -4372,16 +4372,16 @@
         <v>44041</v>
       </c>
       <c r="B198" t="n">
-        <v>20.18435096740723</v>
+        <v>20.18435287475586</v>
       </c>
       <c r="C198" t="n">
-        <v>20.47167242120263</v>
+        <v>20.4716743557021</v>
       </c>
       <c r="D198" t="n">
-        <v>19.94192284855325</v>
+        <v>19.9419247329933</v>
       </c>
       <c r="E198" t="n">
-        <v>20.049669250012</v>
+        <v>20.0496711446337</v>
       </c>
       <c r="F198" t="n">
         <v>977000</v>
@@ -4392,16 +4392,16 @@
         <v>44042</v>
       </c>
       <c r="B199" t="n">
-        <v>20.31903266906738</v>
+        <v>20.31903457641602</v>
       </c>
       <c r="C199" t="n">
-        <v>20.46269510842478</v>
+        <v>20.46269702925902</v>
       </c>
       <c r="D199" t="n">
-        <v>19.84315715380138</v>
+        <v>19.84315901647955</v>
       </c>
       <c r="E199" t="n">
-        <v>20.02273220599896</v>
+        <v>20.02273408553386</v>
       </c>
       <c r="F199" t="n">
         <v>1101900</v>
@@ -4412,16 +4412,16 @@
         <v>44043</v>
       </c>
       <c r="B200" t="n">
-        <v>19.90600967407227</v>
+        <v>19.90601348876953</v>
       </c>
       <c r="C200" t="n">
-        <v>20.63329236011445</v>
+        <v>20.63329631418486</v>
       </c>
       <c r="D200" t="n">
-        <v>19.7264328987816</v>
+        <v>19.72643667906559</v>
       </c>
       <c r="E200" t="n">
-        <v>20.35494989972787</v>
+        <v>20.354953800458</v>
       </c>
       <c r="F200" t="n">
         <v>1082200</v>
@@ -4432,16 +4432,16 @@
         <v>44046</v>
       </c>
       <c r="B201" t="n">
-        <v>19.26851272583008</v>
+        <v>19.26851654052734</v>
       </c>
       <c r="C201" t="n">
-        <v>20.19333016222049</v>
+        <v>20.19333416000914</v>
       </c>
       <c r="D201" t="n">
-        <v>19.26851272583008</v>
+        <v>19.26851654052734</v>
       </c>
       <c r="E201" t="n">
-        <v>20.10354177894272</v>
+        <v>20.10354575895545</v>
       </c>
       <c r="F201" t="n">
         <v>1387700</v>
@@ -4452,16 +4452,16 @@
         <v>44047</v>
       </c>
       <c r="B202" t="n">
-        <v>19.3044319152832</v>
+        <v>19.30443000793457</v>
       </c>
       <c r="C202" t="n">
-        <v>19.46605068905046</v>
+        <v>19.4660487657333</v>
       </c>
       <c r="D202" t="n">
-        <v>18.59510545543162</v>
+        <v>18.59510361816704</v>
       </c>
       <c r="E202" t="n">
-        <v>19.17872918571811</v>
+        <v>19.17872729078937</v>
       </c>
       <c r="F202" t="n">
         <v>1463900</v>
@@ -4512,16 +4512,16 @@
         <v>44050</v>
       </c>
       <c r="B205" t="n">
-        <v>20.40882110595703</v>
+        <v>20.40882301330566</v>
       </c>
       <c r="C205" t="n">
-        <v>20.68716526334872</v>
+        <v>20.68716719671059</v>
       </c>
       <c r="D205" t="n">
-        <v>19.99579694348568</v>
+        <v>19.99579881223428</v>
       </c>
       <c r="E205" t="n">
-        <v>20.31005542638442</v>
+        <v>20.3100573245027</v>
       </c>
       <c r="F205" t="n">
         <v>1932500</v>
@@ -4532,16 +4532,16 @@
         <v>44053</v>
       </c>
       <c r="B206" t="n">
-        <v>20.08558654785156</v>
+        <v>20.0855884552002</v>
       </c>
       <c r="C206" t="n">
-        <v>20.40882234736025</v>
+        <v>20.4088242854037</v>
       </c>
       <c r="D206" t="n">
-        <v>19.68153965775188</v>
+        <v>19.68154152673179</v>
       </c>
       <c r="E206" t="n">
-        <v>20.40882234736025</v>
+        <v>20.4088242854037</v>
       </c>
       <c r="F206" t="n">
         <v>855900</v>
@@ -4652,16 +4652,16 @@
         <v>44061</v>
       </c>
       <c r="B212" t="n">
-        <v>19.59174919128418</v>
+        <v>19.59175109863281</v>
       </c>
       <c r="C212" t="n">
-        <v>19.60072820039731</v>
+        <v>19.60073010862009</v>
       </c>
       <c r="D212" t="n">
-        <v>18.91833892093718</v>
+        <v>18.91834076272616</v>
       </c>
       <c r="E212" t="n">
-        <v>18.96323396650284</v>
+        <v>18.96323581266256</v>
       </c>
       <c r="F212" t="n">
         <v>1173900</v>
@@ -4672,16 +4672,16 @@
         <v>44062</v>
       </c>
       <c r="B213" t="n">
-        <v>19.34034729003906</v>
+        <v>19.34034538269043</v>
       </c>
       <c r="C213" t="n">
-        <v>19.6725621245536</v>
+        <v>19.67256018444188</v>
       </c>
       <c r="D213" t="n">
-        <v>19.07996111630009</v>
+        <v>19.07995923463079</v>
       </c>
       <c r="E213" t="n">
-        <v>19.49298533490112</v>
+        <v>19.4929834124993</v>
       </c>
       <c r="F213" t="n">
         <v>905000</v>
@@ -4692,16 +4692,16 @@
         <v>44063</v>
       </c>
       <c r="B214" t="n">
-        <v>19.3044319152832</v>
+        <v>19.30443000793457</v>
       </c>
       <c r="C214" t="n">
-        <v>19.45707167799992</v>
+        <v>19.45706975556992</v>
       </c>
       <c r="D214" t="n">
-        <v>18.68489385336579</v>
+        <v>18.68489200722979</v>
       </c>
       <c r="E214" t="n">
-        <v>18.99017337879923</v>
+        <v>18.99017150250049</v>
       </c>
       <c r="F214" t="n">
         <v>1836100</v>
@@ -4712,16 +4712,16 @@
         <v>44064</v>
       </c>
       <c r="B215" t="n">
-        <v>19.84315872192383</v>
+        <v>19.84316062927246</v>
       </c>
       <c r="C215" t="n">
-        <v>20.11252217779236</v>
+        <v>20.11252411103253</v>
       </c>
       <c r="D215" t="n">
-        <v>19.17872737988652</v>
+        <v>19.1787292233692</v>
       </c>
       <c r="E215" t="n">
-        <v>19.30443009761568</v>
+        <v>19.30443195318107</v>
       </c>
       <c r="F215" t="n">
         <v>1309100</v>
@@ -4772,16 +4772,16 @@
         <v>44069</v>
       </c>
       <c r="B218" t="n">
-        <v>20.49861145019531</v>
+        <v>20.49860954284668</v>
       </c>
       <c r="C218" t="n">
-        <v>21.1450847843251</v>
+        <v>21.14508281682362</v>
       </c>
       <c r="D218" t="n">
-        <v>19.95988281546826</v>
+        <v>19.95988095824709</v>
       </c>
       <c r="E218" t="n">
-        <v>21.01040305378612</v>
+        <v>21.01040109881646</v>
       </c>
       <c r="F218" t="n">
         <v>2129900</v>
@@ -4792,16 +4792,16 @@
         <v>44070</v>
       </c>
       <c r="B219" t="n">
-        <v>20.68716621398926</v>
+        <v>20.68716812133789</v>
       </c>
       <c r="C219" t="n">
-        <v>21.45934222986984</v>
+        <v>21.45934420841279</v>
       </c>
       <c r="D219" t="n">
-        <v>20.28311932989922</v>
+        <v>20.28312119999489</v>
       </c>
       <c r="E219" t="n">
-        <v>21.05529705835083</v>
+        <v>21.05529899964099</v>
       </c>
       <c r="F219" t="n">
         <v>2350400</v>
@@ -4812,16 +4812,16 @@
         <v>44071</v>
       </c>
       <c r="B220" t="n">
-        <v>20.8308277130127</v>
+        <v>20.83082580566406</v>
       </c>
       <c r="C220" t="n">
-        <v>20.89367907227541</v>
+        <v>20.89367715917187</v>
       </c>
       <c r="D220" t="n">
-        <v>20.43575982434136</v>
+        <v>20.43575795316663</v>
       </c>
       <c r="E220" t="n">
-        <v>20.68716697396332</v>
+        <v>20.6871650797688</v>
       </c>
       <c r="F220" t="n">
         <v>1545000</v>
@@ -4832,16 +4832,16 @@
         <v>44074</v>
       </c>
       <c r="B221" t="n">
-        <v>21.16304206848145</v>
+        <v>21.16304016113281</v>
       </c>
       <c r="C221" t="n">
-        <v>21.28874478426647</v>
+        <v>21.28874286558871</v>
       </c>
       <c r="D221" t="n">
-        <v>20.10354285666178</v>
+        <v>20.10354104480199</v>
       </c>
       <c r="E221" t="n">
-        <v>20.20231025481919</v>
+        <v>20.20230843405785</v>
       </c>
       <c r="F221" t="n">
         <v>2917000</v>
@@ -4852,16 +4852,16 @@
         <v>44075</v>
       </c>
       <c r="B222" t="n">
-        <v>23.21919059753418</v>
+        <v>23.21918869018555</v>
       </c>
       <c r="C222" t="n">
-        <v>23.58732147059421</v>
+        <v>23.58731953300534</v>
       </c>
       <c r="D222" t="n">
-        <v>21.27976882785214</v>
+        <v>21.279767079818</v>
       </c>
       <c r="E222" t="n">
-        <v>21.71973007339777</v>
+        <v>21.71972828922285</v>
       </c>
       <c r="F222" t="n">
         <v>5707300</v>
@@ -4912,16 +4912,16 @@
         <v>44078</v>
       </c>
       <c r="B225" t="n">
-        <v>22.91391181945801</v>
+        <v>22.91390991210938</v>
       </c>
       <c r="C225" t="n">
-        <v>23.52447086140592</v>
+        <v>23.52446890323449</v>
       </c>
       <c r="D225" t="n">
-        <v>22.50986489094212</v>
+        <v>22.50986301722626</v>
       </c>
       <c r="E225" t="n">
-        <v>23.37183110091894</v>
+        <v>23.37182915545321</v>
       </c>
       <c r="F225" t="n">
         <v>1795000</v>
@@ -4972,16 +4972,16 @@
         <v>44084</v>
       </c>
       <c r="B228" t="n">
-        <v>22.56373596191406</v>
+        <v>22.56373405456543</v>
       </c>
       <c r="C228" t="n">
-        <v>23.73996063695625</v>
+        <v>23.73995863017947</v>
       </c>
       <c r="D228" t="n">
-        <v>22.31233052074014</v>
+        <v>22.3123286346432</v>
       </c>
       <c r="E228" t="n">
-        <v>23.27306237110307</v>
+        <v>23.27306040379395</v>
       </c>
       <c r="F228" t="n">
         <v>1912900</v>
@@ -5012,16 +5012,16 @@
         <v>44088</v>
       </c>
       <c r="B230" t="n">
-        <v>22.97676277160645</v>
+        <v>22.97676086425781</v>
       </c>
       <c r="C230" t="n">
-        <v>23.20123290285499</v>
+        <v>23.20123097687262</v>
       </c>
       <c r="D230" t="n">
-        <v>22.59965288260605</v>
+        <v>22.59965100656209</v>
       </c>
       <c r="E230" t="n">
-        <v>22.80616499233762</v>
+        <v>22.80616309915066</v>
       </c>
       <c r="F230" t="n">
         <v>1136200</v>
@@ -5032,16 +5032,16 @@
         <v>44089</v>
       </c>
       <c r="B231" t="n">
-        <v>22.88697242736816</v>
+        <v>22.8869743347168</v>
       </c>
       <c r="C231" t="n">
-        <v>23.11144253949917</v>
+        <v>23.11144446555463</v>
       </c>
       <c r="D231" t="n">
-        <v>22.54577861046031</v>
+        <v>22.54578048937461</v>
       </c>
       <c r="E231" t="n">
-        <v>22.95880279474724</v>
+        <v>22.95880470808206</v>
       </c>
       <c r="F231" t="n">
         <v>961400</v>
@@ -5052,16 +5052,16 @@
         <v>44090</v>
       </c>
       <c r="B232" t="n">
-        <v>22.37518119812012</v>
+        <v>22.37517929077148</v>
       </c>
       <c r="C232" t="n">
-        <v>22.99471919687902</v>
+        <v>22.99471723671853</v>
       </c>
       <c r="D232" t="n">
-        <v>22.37518119812012</v>
+        <v>22.37517929077148</v>
       </c>
       <c r="E232" t="n">
-        <v>22.98574018674384</v>
+        <v>22.98573822734875</v>
       </c>
       <c r="F232" t="n">
         <v>850700</v>
@@ -5072,16 +5072,16 @@
         <v>44091</v>
       </c>
       <c r="B233" t="n">
-        <v>21.70177268981934</v>
+        <v>21.7017707824707</v>
       </c>
       <c r="C233" t="n">
-        <v>22.38416210476936</v>
+        <v>22.38416013744616</v>
       </c>
       <c r="D233" t="n">
-        <v>21.45934453334277</v>
+        <v>21.45934264730093</v>
       </c>
       <c r="E233" t="n">
-        <v>22.28539469748531</v>
+        <v>22.28539273884268</v>
       </c>
       <c r="F233" t="n">
         <v>1677100</v>
@@ -5092,16 +5092,16 @@
         <v>44092</v>
       </c>
       <c r="B234" t="n">
-        <v>21.11814880371094</v>
+        <v>21.1181468963623</v>
       </c>
       <c r="C234" t="n">
-        <v>21.92624087418246</v>
+        <v>21.92623889384858</v>
       </c>
       <c r="D234" t="n">
-        <v>20.83980462840913</v>
+        <v>20.83980274619998</v>
       </c>
       <c r="E234" t="n">
-        <v>21.7017707594642</v>
+        <v>21.70176879940401</v>
       </c>
       <c r="F234" t="n">
         <v>1460500</v>
@@ -5172,16 +5172,16 @@
         <v>44098</v>
       </c>
       <c r="B238" t="n">
-        <v>21.30670166015625</v>
+        <v>21.30670356750488</v>
       </c>
       <c r="C238" t="n">
-        <v>21.45036238835865</v>
+        <v>21.45036430856761</v>
       </c>
       <c r="D238" t="n">
-        <v>20.33699088850455</v>
+        <v>20.33699270904592</v>
       </c>
       <c r="E238" t="n">
-        <v>20.5704399999762</v>
+        <v>20.57044184141563</v>
       </c>
       <c r="F238" t="n">
         <v>1454500</v>
@@ -5212,16 +5212,16 @@
         <v>44102</v>
       </c>
       <c r="B240" t="n">
-        <v>21.40546798706055</v>
+        <v>21.40547180175781</v>
       </c>
       <c r="C240" t="n">
-        <v>22.21355997110046</v>
+        <v>22.21356392980888</v>
       </c>
       <c r="D240" t="n">
-        <v>21.34261663567324</v>
+        <v>21.34262043916968</v>
       </c>
       <c r="E240" t="n">
-        <v>21.80951483536594</v>
+        <v>21.80951872206894</v>
       </c>
       <c r="F240" t="n">
         <v>1593300</v>
@@ -5252,16 +5252,16 @@
         <v>44104</v>
       </c>
       <c r="B242" t="n">
-        <v>21.27976417541504</v>
+        <v>21.2797679901123</v>
       </c>
       <c r="C242" t="n">
-        <v>21.80053469022125</v>
+        <v>21.80053859827396</v>
       </c>
       <c r="D242" t="n">
-        <v>20.90265437417118</v>
+        <v>20.9026581212662</v>
       </c>
       <c r="E242" t="n">
-        <v>21.54912758520175</v>
+        <v>21.54913144818619</v>
       </c>
       <c r="F242" t="n">
         <v>1374800</v>
@@ -5292,16 +5292,16 @@
         <v>44106</v>
       </c>
       <c r="B244" t="n">
-        <v>21.48627853393555</v>
+        <v>21.48628234863281</v>
       </c>
       <c r="C244" t="n">
-        <v>21.48627853393555</v>
+        <v>21.48628234863281</v>
       </c>
       <c r="D244" t="n">
-        <v>21.10018968275046</v>
+        <v>21.10019342890109</v>
       </c>
       <c r="E244" t="n">
-        <v>21.4503624954202</v>
+        <v>21.45036630374089</v>
       </c>
       <c r="F244" t="n">
         <v>795300</v>
@@ -5332,16 +5332,16 @@
         <v>44110</v>
       </c>
       <c r="B246" t="n">
-        <v>21.39649391174316</v>
+        <v>21.3964900970459</v>
       </c>
       <c r="C246" t="n">
-        <v>21.77360381959571</v>
+        <v>21.773599937665</v>
       </c>
       <c r="D246" t="n">
-        <v>21.28874748982618</v>
+        <v>21.2887436943386</v>
       </c>
       <c r="E246" t="n">
-        <v>21.5401546659183</v>
+        <v>21.54015082560832</v>
       </c>
       <c r="F246" t="n">
         <v>753200</v>
@@ -5372,16 +5372,16 @@
         <v>44112</v>
       </c>
       <c r="B248" t="n">
-        <v>21.4773006439209</v>
+        <v>21.47730255126953</v>
       </c>
       <c r="C248" t="n">
-        <v>21.61198237023247</v>
+        <v>21.61198428954187</v>
       </c>
       <c r="D248" t="n">
-        <v>21.14508412061937</v>
+        <v>21.14508599846463</v>
       </c>
       <c r="E248" t="n">
-        <v>21.34261891760933</v>
+        <v>21.34262081299719</v>
       </c>
       <c r="F248" t="n">
         <v>406500</v>
@@ -5412,16 +5412,16 @@
         <v>44117</v>
       </c>
       <c r="B250" t="n">
-        <v>22.31232833862305</v>
+        <v>22.31233024597168</v>
       </c>
       <c r="C250" t="n">
-        <v>22.40211672136303</v>
+        <v>22.40211863638714</v>
       </c>
       <c r="D250" t="n">
-        <v>21.23487117088518</v>
+        <v>21.23487298612839</v>
       </c>
       <c r="E250" t="n">
-        <v>21.37853189824077</v>
+        <v>21.37853372576468</v>
       </c>
       <c r="F250" t="n">
         <v>1004000</v>
@@ -5452,16 +5452,16 @@
         <v>44119</v>
       </c>
       <c r="B252" t="n">
-        <v>22.33926200866699</v>
+        <v>22.33926391601562</v>
       </c>
       <c r="C252" t="n">
-        <v>22.4470084025303</v>
+        <v>22.44701031907843</v>
       </c>
       <c r="D252" t="n">
-        <v>21.60300040707533</v>
+        <v>21.60300225156121</v>
       </c>
       <c r="E252" t="n">
-        <v>21.92623787609443</v>
+        <v>21.92623974817865</v>
       </c>
       <c r="F252" t="n">
         <v>1147000</v>
@@ -5472,16 +5472,16 @@
         <v>44120</v>
       </c>
       <c r="B253" t="n">
-        <v>22.46496963500977</v>
+        <v>22.4649715423584</v>
       </c>
       <c r="C253" t="n">
-        <v>22.46496963500977</v>
+        <v>22.4649715423584</v>
       </c>
       <c r="D253" t="n">
-        <v>22.10581779168876</v>
+        <v>22.10581966854425</v>
       </c>
       <c r="E253" t="n">
-        <v>22.38416025619116</v>
+        <v>22.38416215667881</v>
       </c>
       <c r="F253" t="n">
         <v>716800</v>
@@ -5512,16 +5512,16 @@
         <v>44124</v>
       </c>
       <c r="B255" t="n">
-        <v>22.22254371643066</v>
+        <v>22.2225399017334</v>
       </c>
       <c r="C255" t="n">
-        <v>22.57271658454556</v>
+        <v>22.57271270973801</v>
       </c>
       <c r="D255" t="n">
-        <v>22.04296692056232</v>
+        <v>22.04296313669101</v>
       </c>
       <c r="E255" t="n">
-        <v>22.43803484392993</v>
+        <v>22.43803099224169</v>
       </c>
       <c r="F255" t="n">
         <v>1239700</v>
@@ -5532,16 +5532,16 @@
         <v>44125</v>
       </c>
       <c r="B256" t="n">
-        <v>22.29437255859375</v>
+        <v>22.29437065124512</v>
       </c>
       <c r="C256" t="n">
-        <v>22.53680070256757</v>
+        <v>22.5367987744785</v>
       </c>
       <c r="D256" t="n">
-        <v>21.95317872500074</v>
+        <v>21.95317684684223</v>
       </c>
       <c r="E256" t="n">
-        <v>22.26743552729517</v>
+        <v>22.26743362225108</v>
       </c>
       <c r="F256" t="n">
         <v>621200</v>
@@ -5572,16 +5572,16 @@
         <v>44127</v>
       </c>
       <c r="B258" t="n">
-        <v>22.33926200866699</v>
+        <v>22.33926391601562</v>
       </c>
       <c r="C258" t="n">
-        <v>22.67147848655561</v>
+        <v>22.67148042226922</v>
       </c>
       <c r="D258" t="n">
-        <v>21.80053517706293</v>
+        <v>21.80053703841453</v>
       </c>
       <c r="E258" t="n">
-        <v>22.29436867689026</v>
+        <v>22.29437058040586</v>
       </c>
       <c r="F258" t="n">
         <v>1048300</v>
@@ -5612,16 +5612,16 @@
         <v>44131</v>
       </c>
       <c r="B260" t="n">
-        <v>22.27641296386719</v>
+        <v>22.27641105651855</v>
       </c>
       <c r="C260" t="n">
-        <v>22.59965046632842</v>
+        <v>22.59964853130358</v>
       </c>
       <c r="D260" t="n">
-        <v>22.2315196274458</v>
+        <v>22.23151772394102</v>
       </c>
       <c r="E260" t="n">
-        <v>22.37518035907945</v>
+        <v>22.37517844327417</v>
       </c>
       <c r="F260" t="n">
         <v>1111200</v>
@@ -5652,16 +5652,16 @@
         <v>44133</v>
       </c>
       <c r="B262" t="n">
-        <v>21.0552978515625</v>
+        <v>21.05529594421387</v>
       </c>
       <c r="C262" t="n">
-        <v>21.46832204857339</v>
+        <v>21.46832010380989</v>
       </c>
       <c r="D262" t="n">
-        <v>20.21128972442886</v>
+        <v>20.21128789353689</v>
       </c>
       <c r="E262" t="n">
-        <v>21.00142378994022</v>
+        <v>21.00142188747191</v>
       </c>
       <c r="F262" t="n">
         <v>1457000</v>
@@ -5672,16 +5672,16 @@
         <v>44134</v>
       </c>
       <c r="B263" t="n">
-        <v>19.57378959655762</v>
+        <v>19.57379150390625</v>
       </c>
       <c r="C263" t="n">
-        <v>21.04631443366539</v>
+        <v>21.04631648450276</v>
       </c>
       <c r="D263" t="n">
-        <v>19.32238421192197</v>
+        <v>19.32238609477265</v>
       </c>
       <c r="E263" t="n">
-        <v>20.87571669939782</v>
+        <v>20.87571873361146</v>
       </c>
       <c r="F263" t="n">
         <v>2020100</v>
@@ -5692,16 +5692,16 @@
         <v>44138</v>
       </c>
       <c r="B264" t="n">
-        <v>19.69949531555176</v>
+        <v>19.69949913024902</v>
       </c>
       <c r="C264" t="n">
-        <v>20.10354044462795</v>
+        <v>20.1035443375663</v>
       </c>
       <c r="D264" t="n">
-        <v>19.16076676421265</v>
+        <v>19.16077047458814</v>
       </c>
       <c r="E264" t="n">
-        <v>19.43910919258569</v>
+        <v>19.43911295686064</v>
       </c>
       <c r="F264" t="n">
         <v>3577600</v>
@@ -5732,16 +5732,16 @@
         <v>44140</v>
       </c>
       <c r="B266" t="n">
-        <v>21.11814880371094</v>
+        <v>21.1181468963623</v>
       </c>
       <c r="C266" t="n">
-        <v>21.32466089823468</v>
+        <v>21.32465897223429</v>
       </c>
       <c r="D266" t="n">
-        <v>20.61533451369087</v>
+        <v>20.61533265175541</v>
       </c>
       <c r="E266" t="n">
-        <v>20.90265769908994</v>
+        <v>20.90265581120403</v>
       </c>
       <c r="F266" t="n">
         <v>1197100</v>
@@ -5832,16 +5832,16 @@
         <v>44147</v>
       </c>
       <c r="B271" t="n">
-        <v>21.76462173461914</v>
+        <v>21.76462364196777</v>
       </c>
       <c r="C271" t="n">
-        <v>22.94084463552694</v>
+        <v>22.9408466459542</v>
       </c>
       <c r="D271" t="n">
-        <v>21.50423729666445</v>
+        <v>21.50423918119422</v>
       </c>
       <c r="E271" t="n">
-        <v>22.78820489170142</v>
+        <v>22.78820688875205</v>
       </c>
       <c r="F271" t="n">
         <v>934300</v>
@@ -5852,16 +5852,16 @@
         <v>44148</v>
       </c>
       <c r="B272" t="n">
-        <v>23.18327331542969</v>
+        <v>23.18327140808105</v>
       </c>
       <c r="C272" t="n">
-        <v>23.28204071453061</v>
+        <v>23.28203879905612</v>
       </c>
       <c r="D272" t="n">
-        <v>21.8274736087571</v>
+        <v>21.82747181295366</v>
       </c>
       <c r="E272" t="n">
-        <v>21.8274736087571</v>
+        <v>21.82747181295366</v>
       </c>
       <c r="F272" t="n">
         <v>3187800</v>
@@ -5892,16 +5892,16 @@
         <v>44152</v>
       </c>
       <c r="B274" t="n">
-        <v>23.4346809387207</v>
+        <v>23.43467903137207</v>
       </c>
       <c r="C274" t="n">
-        <v>23.51549031916159</v>
+        <v>23.51548840523588</v>
       </c>
       <c r="D274" t="n">
-        <v>22.6714821859852</v>
+        <v>22.67148034075331</v>
       </c>
       <c r="E274" t="n">
-        <v>22.9498246560754</v>
+        <v>22.94982278818922</v>
       </c>
       <c r="F274" t="n">
         <v>1311700</v>
@@ -5912,16 +5912,16 @@
         <v>44153</v>
       </c>
       <c r="B275" t="n">
-        <v>23.56936264038086</v>
+        <v>23.56936073303223</v>
       </c>
       <c r="C275" t="n">
-        <v>23.85668412046174</v>
+        <v>23.85668218986164</v>
       </c>
       <c r="D275" t="n">
-        <v>22.99471968021909</v>
+        <v>22.99471781937339</v>
       </c>
       <c r="E275" t="n">
-        <v>23.43468091066433</v>
+        <v>23.43467901421481</v>
       </c>
       <c r="F275" t="n">
         <v>2279100</v>
@@ -5992,16 +5992,16 @@
         <v>44160</v>
       </c>
       <c r="B279" t="n">
-        <v>24.23379516601562</v>
+        <v>24.23379707336426</v>
       </c>
       <c r="C279" t="n">
-        <v>24.24277417677482</v>
+        <v>24.24277608483016</v>
       </c>
       <c r="D279" t="n">
-        <v>23.38080969474589</v>
+        <v>23.38081153495933</v>
       </c>
       <c r="E279" t="n">
-        <v>23.38080969474589</v>
+        <v>23.38081153495933</v>
       </c>
       <c r="F279" t="n">
         <v>1238000</v>
@@ -6012,16 +6012,16 @@
         <v>44161</v>
       </c>
       <c r="B280" t="n">
-        <v>24.09911155700684</v>
+        <v>24.0991096496582</v>
       </c>
       <c r="C280" t="n">
-        <v>24.23379328278622</v>
+        <v>24.23379136477807</v>
       </c>
       <c r="D280" t="n">
-        <v>23.83872540293844</v>
+        <v>23.83872351619833</v>
       </c>
       <c r="E280" t="n">
-        <v>24.17992093498868</v>
+        <v>24.17991902124431</v>
       </c>
       <c r="F280" t="n">
         <v>547400</v>
@@ -6072,16 +6072,16 @@
         <v>44166</v>
       </c>
       <c r="B283" t="n">
-        <v>22.86003303527832</v>
+        <v>22.86003684997559</v>
       </c>
       <c r="C283" t="n">
-        <v>23.08450312421501</v>
+        <v>23.08450697637003</v>
       </c>
       <c r="D283" t="n">
-        <v>22.44700889366883</v>
+        <v>22.44701263944397</v>
       </c>
       <c r="E283" t="n">
-        <v>22.68045799167149</v>
+        <v>22.68046177640273</v>
       </c>
       <c r="F283" t="n">
         <v>2100900</v>
@@ -6132,16 +6132,16 @@
         <v>44169</v>
       </c>
       <c r="B286" t="n">
-        <v>23.70404434204102</v>
+        <v>23.70404624938965</v>
       </c>
       <c r="C286" t="n">
-        <v>23.88362112316457</v>
+        <v>23.88362304496287</v>
       </c>
       <c r="D286" t="n">
-        <v>23.29999915336967</v>
+        <v>23.30000102820676</v>
       </c>
       <c r="E286" t="n">
-        <v>23.83872607159813</v>
+        <v>23.83872798978394</v>
       </c>
       <c r="F286" t="n">
         <v>518000</v>
@@ -6152,16 +6152,16 @@
         <v>44172</v>
       </c>
       <c r="B287" t="n">
-        <v>23.70404434204102</v>
+        <v>23.70404624938965</v>
       </c>
       <c r="C287" t="n">
-        <v>23.81179075322937</v>
+        <v>23.81179266924783</v>
       </c>
       <c r="D287" t="n">
-        <v>22.985740642689</v>
+        <v>22.98574249223924</v>
       </c>
       <c r="E287" t="n">
-        <v>23.70404434204102</v>
+        <v>23.70404624938965</v>
       </c>
       <c r="F287" t="n">
         <v>838600</v>
@@ -6172,16 +6172,16 @@
         <v>44173</v>
       </c>
       <c r="B288" t="n">
-        <v>23.70404434204102</v>
+        <v>23.70404624938965</v>
       </c>
       <c r="C288" t="n">
-        <v>23.7848537222895</v>
+        <v>23.78485563614047</v>
       </c>
       <c r="D288" t="n">
-        <v>23.39876484167363</v>
+        <v>23.39876672445791</v>
       </c>
       <c r="E288" t="n">
-        <v>23.69506533172773</v>
+        <v>23.69506723835386</v>
       </c>
       <c r="F288" t="n">
         <v>592200</v>
@@ -6192,16 +6192,16 @@
         <v>44174</v>
       </c>
       <c r="B289" t="n">
-        <v>23.03961372375488</v>
+        <v>23.03961181640625</v>
       </c>
       <c r="C289" t="n">
-        <v>23.74894014789352</v>
+        <v>23.74893818182286</v>
       </c>
       <c r="D289" t="n">
-        <v>22.98574137273523</v>
+        <v>22.98573946984645</v>
       </c>
       <c r="E289" t="n">
-        <v>23.74894014789352</v>
+        <v>23.74893818182286</v>
       </c>
       <c r="F289" t="n">
         <v>683100</v>
@@ -6212,16 +6212,16 @@
         <v>44175</v>
       </c>
       <c r="B290" t="n">
-        <v>23.0306339263916</v>
+        <v>23.03063201904297</v>
       </c>
       <c r="C290" t="n">
-        <v>23.14735934761301</v>
+        <v>23.14735743059742</v>
       </c>
       <c r="D290" t="n">
-        <v>22.23152084870963</v>
+        <v>22.23151900754186</v>
       </c>
       <c r="E290" t="n">
-        <v>23.04859194697507</v>
+        <v>23.04859003813919</v>
       </c>
       <c r="F290" t="n">
         <v>501000</v>
@@ -6232,16 +6232,16 @@
         <v>44176</v>
       </c>
       <c r="B291" t="n">
-        <v>23.2102108001709</v>
+        <v>23.21020889282227</v>
       </c>
       <c r="C291" t="n">
-        <v>23.28204117022173</v>
+        <v>23.28203925697028</v>
       </c>
       <c r="D291" t="n">
-        <v>22.50986340774696</v>
+        <v>22.50986155795086</v>
       </c>
       <c r="E291" t="n">
-        <v>22.71637550757171</v>
+        <v>22.71637364080505</v>
       </c>
       <c r="F291" t="n">
         <v>261200</v>
@@ -6252,16 +6252,16 @@
         <v>44179</v>
       </c>
       <c r="B292" t="n">
-        <v>23.8566837310791</v>
+        <v>23.85668182373047</v>
       </c>
       <c r="C292" t="n">
-        <v>24.00932347895211</v>
+        <v>24.00932155939989</v>
       </c>
       <c r="D292" t="n">
-        <v>22.83310054685483</v>
+        <v>22.83309872134197</v>
       </c>
       <c r="E292" t="n">
-        <v>23.29999880065123</v>
+        <v>23.29999693780972</v>
       </c>
       <c r="F292" t="n">
         <v>720600</v>
@@ -6272,16 +6272,16 @@
         <v>44180</v>
       </c>
       <c r="B293" t="n">
-        <v>23.66812896728516</v>
+        <v>23.66813087463379</v>
       </c>
       <c r="C293" t="n">
-        <v>24.01830179117109</v>
+        <v>24.01830372673917</v>
       </c>
       <c r="D293" t="n">
-        <v>23.48855219409846</v>
+        <v>23.48855408697549</v>
       </c>
       <c r="E293" t="n">
-        <v>23.85668303781727</v>
+        <v>23.85668496036094</v>
       </c>
       <c r="F293" t="n">
         <v>453700</v>
@@ -6312,16 +6312,16 @@
         <v>44182</v>
       </c>
       <c r="B295" t="n">
-        <v>25.07780265808105</v>
+        <v>25.07780075073242</v>
       </c>
       <c r="C295" t="n">
-        <v>25.07780265808105</v>
+        <v>25.07780075073242</v>
       </c>
       <c r="D295" t="n">
-        <v>23.9285150006815</v>
+        <v>23.92851318074452</v>
       </c>
       <c r="E295" t="n">
-        <v>23.9554520322276</v>
+        <v>23.95545021024186</v>
       </c>
       <c r="F295" t="n">
         <v>842600</v>
@@ -6392,16 +6392,16 @@
         <v>44188</v>
       </c>
       <c r="B299" t="n">
-        <v>24.82639312744141</v>
+        <v>24.82639503479004</v>
       </c>
       <c r="C299" t="n">
-        <v>25.16758864411527</v>
+        <v>25.16759057767708</v>
       </c>
       <c r="D299" t="n">
-        <v>24.15298281632145</v>
+        <v>24.15298467193368</v>
       </c>
       <c r="E299" t="n">
-        <v>24.92516052109505</v>
+        <v>24.92516243603173</v>
       </c>
       <c r="F299" t="n">
         <v>742900</v>
@@ -6412,16 +6412,16 @@
         <v>44193</v>
       </c>
       <c r="B300" t="n">
-        <v>25.03290748596191</v>
+        <v>25.03290557861328</v>
       </c>
       <c r="C300" t="n">
-        <v>25.22146328074186</v>
+        <v>25.22146135902647</v>
       </c>
       <c r="D300" t="n">
-        <v>24.41337117650056</v>
+        <v>24.41336931635667</v>
       </c>
       <c r="E300" t="n">
-        <v>25.03290748596191</v>
+        <v>25.03290557861328</v>
       </c>
       <c r="F300" t="n">
         <v>654000</v>
@@ -6432,16 +6432,16 @@
         <v>44194</v>
       </c>
       <c r="B301" t="n">
-        <v>25.43695449829102</v>
+        <v>25.43695259094238</v>
       </c>
       <c r="C301" t="n">
-        <v>25.60755227282297</v>
+        <v>25.60755035268234</v>
       </c>
       <c r="D301" t="n">
-        <v>24.7725231337527</v>
+        <v>24.77252127622537</v>
       </c>
       <c r="E301" t="n">
-        <v>25.03290758823406</v>
+        <v>25.03290571118223</v>
       </c>
       <c r="F301" t="n">
         <v>1076100</v>
@@ -6452,16 +6452,16 @@
         <v>44195</v>
       </c>
       <c r="B302" t="n">
-        <v>26.55075454711914</v>
+        <v>26.55075263977051</v>
       </c>
       <c r="C302" t="n">
-        <v>26.55075454711914</v>
+        <v>26.55075263977051</v>
       </c>
       <c r="D302" t="n">
-        <v>25.18987212866989</v>
+        <v>25.1898703190841</v>
       </c>
       <c r="E302" t="n">
-        <v>25.47827109732121</v>
+        <v>25.47826926701746</v>
       </c>
       <c r="F302" t="n">
         <v>872600</v>
@@ -6472,16 +6472,16 @@
         <v>44200</v>
       </c>
       <c r="B303" t="n">
-        <v>25.62246894836426</v>
+        <v>25.62247085571289</v>
       </c>
       <c r="C303" t="n">
-        <v>26.55075285466386</v>
+        <v>26.55075483111438</v>
       </c>
       <c r="D303" t="n">
-        <v>24.97356959126887</v>
+        <v>24.97357145031313</v>
       </c>
       <c r="E303" t="n">
-        <v>26.55075285466386</v>
+        <v>26.55075483111438</v>
       </c>
       <c r="F303" t="n">
         <v>1053500</v>
@@ -6492,16 +6492,16 @@
         <v>44201</v>
       </c>
       <c r="B304" t="n">
-        <v>24.4238109588623</v>
+        <v>24.42380905151367</v>
       </c>
       <c r="C304" t="n">
-        <v>25.66753192386268</v>
+        <v>25.66752991938713</v>
       </c>
       <c r="D304" t="n">
-        <v>24.29763512256268</v>
+        <v>24.2976332250676</v>
       </c>
       <c r="E304" t="n">
-        <v>25.59543218268865</v>
+        <v>25.59543018384365</v>
       </c>
       <c r="F304" t="n">
         <v>1266200</v>
@@ -6512,16 +6512,16 @@
         <v>44202</v>
       </c>
       <c r="B305" t="n">
-        <v>23.68478584289551</v>
+        <v>23.68478775024414</v>
       </c>
       <c r="C305" t="n">
-        <v>24.20750934452975</v>
+        <v>24.20751129397359</v>
       </c>
       <c r="D305" t="n">
-        <v>22.97279946500075</v>
+        <v>22.97280131501273</v>
       </c>
       <c r="E305" t="n">
-        <v>24.18948398126813</v>
+        <v>24.18948592926038</v>
       </c>
       <c r="F305" t="n">
         <v>2011600</v>
@@ -6572,16 +6572,16 @@
         <v>44207</v>
       </c>
       <c r="B308" t="n">
-        <v>23.15305137634277</v>
+        <v>23.15304946899414</v>
       </c>
       <c r="C308" t="n">
-        <v>24.32467257132744</v>
+        <v>24.32467056746064</v>
       </c>
       <c r="D308" t="n">
-        <v>23.02687554314921</v>
+        <v>23.02687364619494</v>
       </c>
       <c r="E308" t="n">
-        <v>23.65774955213688</v>
+        <v>23.65774760321121</v>
       </c>
       <c r="F308" t="n">
         <v>792900</v>
@@ -6592,16 +6592,16 @@
         <v>44208</v>
       </c>
       <c r="B309" t="n">
-        <v>24.54096984863281</v>
+        <v>24.54097175598145</v>
       </c>
       <c r="C309" t="n">
-        <v>24.87443219135197</v>
+        <v>24.87443412461763</v>
       </c>
       <c r="D309" t="n">
-        <v>23.07193712993506</v>
+        <v>23.07193892310901</v>
       </c>
       <c r="E309" t="n">
-        <v>23.30626169419845</v>
+        <v>23.30626350558433</v>
       </c>
       <c r="F309" t="n">
         <v>1731300</v>
@@ -6632,16 +6632,16 @@
         <v>44210</v>
       </c>
       <c r="B311" t="n">
-        <v>24.31565856933594</v>
+        <v>24.31566047668457</v>
       </c>
       <c r="C311" t="n">
-        <v>24.51393413116758</v>
+        <v>24.51393605406918</v>
       </c>
       <c r="D311" t="n">
-        <v>23.93713452828578</v>
+        <v>23.93713640594255</v>
       </c>
       <c r="E311" t="n">
-        <v>24.00022158196193</v>
+        <v>24.00022346456732</v>
       </c>
       <c r="F311" t="n">
         <v>755300</v>
@@ -6672,16 +6672,16 @@
         <v>44214</v>
       </c>
       <c r="B313" t="n">
-        <v>24.24355888366699</v>
+        <v>24.24355697631836</v>
       </c>
       <c r="C313" t="n">
-        <v>24.43282176407762</v>
+        <v>24.43281984183884</v>
       </c>
       <c r="D313" t="n">
-        <v>23.76589877971278</v>
+        <v>23.76589690994379</v>
       </c>
       <c r="E313" t="n">
-        <v>23.97318530478699</v>
+        <v>23.97318341870985</v>
       </c>
       <c r="F313" t="n">
         <v>558300</v>
@@ -6692,16 +6692,16 @@
         <v>44215</v>
       </c>
       <c r="B314" t="n">
-        <v>24.06331062316895</v>
+        <v>24.06330871582031</v>
       </c>
       <c r="C314" t="n">
-        <v>24.51393440473396</v>
+        <v>24.51393246166718</v>
       </c>
       <c r="D314" t="n">
-        <v>23.84700969530363</v>
+        <v>23.84700780509982</v>
       </c>
       <c r="E314" t="n">
-        <v>24.42380930462229</v>
+        <v>24.42380736869918</v>
       </c>
       <c r="F314" t="n">
         <v>512700</v>
@@ -6732,16 +6732,16 @@
         <v>44217</v>
       </c>
       <c r="B316" t="n">
-        <v>23.36033821105957</v>
+        <v>23.36033630371094</v>
       </c>
       <c r="C316" t="n">
-        <v>23.91911248779575</v>
+        <v>23.91911053482375</v>
       </c>
       <c r="D316" t="n">
-        <v>22.85564002880952</v>
+        <v>22.855638162669</v>
       </c>
       <c r="E316" t="n">
-        <v>23.64873717234531</v>
+        <v>23.64873524144919</v>
       </c>
       <c r="F316" t="n">
         <v>915600</v>
@@ -6752,16 +6752,16 @@
         <v>44218</v>
       </c>
       <c r="B317" t="n">
-        <v>23.36935234069824</v>
+        <v>23.36935043334961</v>
       </c>
       <c r="C317" t="n">
-        <v>23.5676262091126</v>
+        <v>23.56762428558135</v>
       </c>
       <c r="D317" t="n">
-        <v>22.63934220986124</v>
+        <v>22.63934036209422</v>
       </c>
       <c r="E317" t="n">
-        <v>22.90070314008955</v>
+        <v>22.90070127099091</v>
       </c>
       <c r="F317" t="n">
         <v>530800</v>
@@ -6772,16 +6772,16 @@
         <v>44222</v>
       </c>
       <c r="B318" t="n">
-        <v>22.90971183776855</v>
+        <v>22.90971374511719</v>
       </c>
       <c r="C318" t="n">
-        <v>23.47749701431774</v>
+        <v>23.47749896893734</v>
       </c>
       <c r="D318" t="n">
-        <v>22.69341264103586</v>
+        <v>22.69341453037649</v>
       </c>
       <c r="E318" t="n">
-        <v>23.36033559404331</v>
+        <v>23.36033753890864</v>
       </c>
       <c r="F318" t="n">
         <v>474300</v>
@@ -6832,16 +6832,16 @@
         <v>44225</v>
       </c>
       <c r="B321" t="n">
-        <v>22.96378898620605</v>
+        <v>22.96379089355469</v>
       </c>
       <c r="C321" t="n">
-        <v>23.96417439627722</v>
+        <v>23.96417638671683</v>
       </c>
       <c r="D321" t="n">
-        <v>22.90070192773191</v>
+        <v>22.9007038298406</v>
       </c>
       <c r="E321" t="n">
-        <v>23.59466300893432</v>
+        <v>23.59466496868269</v>
       </c>
       <c r="F321" t="n">
         <v>872100</v>
@@ -6872,16 +6872,16 @@
         <v>44229</v>
       </c>
       <c r="B323" t="n">
-        <v>23.28823852539062</v>
+        <v>23.28824043273926</v>
       </c>
       <c r="C323" t="n">
-        <v>23.92812350737087</v>
+        <v>23.92812546712723</v>
       </c>
       <c r="D323" t="n">
-        <v>22.80156398783376</v>
+        <v>22.80156585532287</v>
       </c>
       <c r="E323" t="n">
-        <v>23.32428753613924</v>
+        <v>23.32428944644035</v>
       </c>
       <c r="F323" t="n">
         <v>1408300</v>
@@ -6892,16 +6892,16 @@
         <v>44230</v>
       </c>
       <c r="B324" t="n">
-        <v>23.61268997192383</v>
+        <v>23.6126880645752</v>
       </c>
       <c r="C324" t="n">
-        <v>24.10837550976074</v>
+        <v>24.10837356237241</v>
       </c>
       <c r="D324" t="n">
-        <v>23.18910246094226</v>
+        <v>23.18910058780952</v>
       </c>
       <c r="E324" t="n">
-        <v>23.41441438159423</v>
+        <v>23.41441249026159</v>
       </c>
       <c r="F324" t="n">
         <v>1369600</v>
@@ -6932,16 +6932,16 @@
         <v>44232</v>
       </c>
       <c r="B326" t="n">
-        <v>24.38776016235352</v>
+        <v>24.38775825500488</v>
       </c>
       <c r="C326" t="n">
-        <v>24.48689795082032</v>
+        <v>24.48689603571819</v>
       </c>
       <c r="D326" t="n">
-        <v>23.91911270549549</v>
+        <v>23.91911083479943</v>
       </c>
       <c r="E326" t="n">
-        <v>24.28862409288013</v>
+        <v>24.28862219328486</v>
       </c>
       <c r="F326" t="n">
         <v>693800</v>
@@ -6952,16 +6952,16 @@
         <v>44235</v>
       </c>
       <c r="B327" t="n">
-        <v>24.06331062316895</v>
+        <v>24.06330871582031</v>
       </c>
       <c r="C327" t="n">
-        <v>24.45985831327097</v>
+        <v>24.45985637449048</v>
       </c>
       <c r="D327" t="n">
-        <v>23.77490995901296</v>
+        <v>23.77490807452405</v>
       </c>
       <c r="E327" t="n">
-        <v>24.37874589506981</v>
+        <v>24.37874396271859</v>
       </c>
       <c r="F327" t="n">
         <v>1394400</v>
@@ -7012,16 +7012,16 @@
         <v>44238</v>
       </c>
       <c r="B330" t="n">
-        <v>23.13502311706543</v>
+        <v>23.13502502441406</v>
       </c>
       <c r="C330" t="n">
-        <v>24.04528328745792</v>
+        <v>24.04528526985223</v>
       </c>
       <c r="D330" t="n">
-        <v>23.01786169982368</v>
+        <v>23.01786359751303</v>
       </c>
       <c r="E330" t="n">
-        <v>23.79293337163847</v>
+        <v>23.79293533322799</v>
       </c>
       <c r="F330" t="n">
         <v>859100</v>
@@ -7052,16 +7052,16 @@
         <v>44244</v>
       </c>
       <c r="B332" t="n">
-        <v>23.27021217346191</v>
+        <v>23.27021026611328</v>
       </c>
       <c r="C332" t="n">
-        <v>23.65774890678339</v>
+        <v>23.65774696767022</v>
       </c>
       <c r="D332" t="n">
-        <v>23.2341631642424</v>
+        <v>23.23416125984853</v>
       </c>
       <c r="E332" t="n">
-        <v>23.65774890678339</v>
+        <v>23.65774696767022</v>
       </c>
       <c r="F332" t="n">
         <v>300200</v>
@@ -7072,16 +7072,16 @@
         <v>44245</v>
       </c>
       <c r="B333" t="n">
-        <v>23.10798645019531</v>
+        <v>23.10799026489258</v>
       </c>
       <c r="C333" t="n">
-        <v>23.63070995632475</v>
+        <v>23.63071385731392</v>
       </c>
       <c r="D333" t="n">
-        <v>22.98181234426542</v>
+        <v>22.9818161381337</v>
       </c>
       <c r="E333" t="n">
-        <v>23.35132369934004</v>
+        <v>23.35132755420774</v>
       </c>
       <c r="F333" t="n">
         <v>590700</v>
@@ -7132,16 +7132,16 @@
         <v>44250</v>
       </c>
       <c r="B336" t="n">
-        <v>23.31527519226074</v>
+        <v>23.31527709960938</v>
       </c>
       <c r="C336" t="n">
-        <v>23.84700967252572</v>
+        <v>23.84701162337386</v>
       </c>
       <c r="D336" t="n">
-        <v>23.03588721028212</v>
+        <v>23.03588909477491</v>
       </c>
       <c r="E336" t="n">
-        <v>23.59466145524606</v>
+        <v>23.5946633854504</v>
       </c>
       <c r="F336" t="n">
         <v>758800</v>
@@ -7172,16 +7172,16 @@
         <v>44252</v>
       </c>
       <c r="B338" t="n">
-        <v>21.94537925720215</v>
+        <v>21.94537734985352</v>
       </c>
       <c r="C338" t="n">
-        <v>23.08996411411466</v>
+        <v>23.0899621072862</v>
       </c>
       <c r="D338" t="n">
-        <v>21.71105467648825</v>
+        <v>21.71105278950557</v>
       </c>
       <c r="E338" t="n">
-        <v>22.99983901091803</v>
+        <v>22.99983701192265</v>
       </c>
       <c r="F338" t="n">
         <v>838500</v>
@@ -7232,16 +7232,16 @@
         <v>44257</v>
       </c>
       <c r="B341" t="n">
-        <v>21.41364479064941</v>
+        <v>21.41364288330078</v>
       </c>
       <c r="C341" t="n">
-        <v>21.87328130745173</v>
+        <v>21.87327935916252</v>
       </c>
       <c r="D341" t="n">
-        <v>20.54844613578814</v>
+        <v>20.54844430550417</v>
       </c>
       <c r="E341" t="n">
-        <v>21.36858137586869</v>
+        <v>21.36857947253393</v>
       </c>
       <c r="F341" t="n">
         <v>1430800</v>
@@ -7312,16 +7312,16 @@
         <v>44263</v>
       </c>
       <c r="B345" t="n">
-        <v>20.72869682312012</v>
+        <v>20.72869300842285</v>
       </c>
       <c r="C345" t="n">
-        <v>21.58488281428119</v>
+        <v>21.58487884202022</v>
       </c>
       <c r="D345" t="n">
-        <v>20.61153538004225</v>
+        <v>20.61153158690618</v>
       </c>
       <c r="E345" t="n">
-        <v>21.13425897030032</v>
+        <v>21.13425508096755</v>
       </c>
       <c r="F345" t="n">
         <v>1680600</v>
@@ -7332,16 +7332,16 @@
         <v>44264</v>
       </c>
       <c r="B346" t="n">
-        <v>20.64758110046387</v>
+        <v>20.6475830078125</v>
       </c>
       <c r="C346" t="n">
-        <v>21.17931728907064</v>
+        <v>21.17931924553913</v>
       </c>
       <c r="D346" t="n">
-        <v>20.44029457785263</v>
+        <v>20.44029646605288</v>
       </c>
       <c r="E346" t="n">
-        <v>20.62054305529982</v>
+        <v>20.62054496015077</v>
       </c>
       <c r="F346" t="n">
         <v>1265700</v>
@@ -7392,16 +7392,16 @@
         <v>44267</v>
       </c>
       <c r="B349" t="n">
-        <v>21.3325309753418</v>
+        <v>21.33253288269043</v>
       </c>
       <c r="C349" t="n">
-        <v>21.89130524931954</v>
+        <v>21.89130720662837</v>
       </c>
       <c r="D349" t="n">
-        <v>20.97203227551425</v>
+        <v>20.97203415063057</v>
       </c>
       <c r="E349" t="n">
-        <v>21.5308048304986</v>
+        <v>21.53080675557496</v>
       </c>
       <c r="F349" t="n">
         <v>748600</v>
@@ -7412,16 +7412,16 @@
         <v>44270</v>
       </c>
       <c r="B350" t="n">
-        <v>21.85525131225586</v>
+        <v>21.85525512695312</v>
       </c>
       <c r="C350" t="n">
-        <v>22.05352513831302</v>
+        <v>22.05352898761774</v>
       </c>
       <c r="D350" t="n">
-        <v>21.20635374780167</v>
+        <v>21.20635744923793</v>
       </c>
       <c r="E350" t="n">
-        <v>21.34154052552215</v>
+        <v>21.34154425055442</v>
       </c>
       <c r="F350" t="n">
         <v>500800</v>
@@ -7452,16 +7452,16 @@
         <v>44272</v>
       </c>
       <c r="B352" t="n">
-        <v>21.31450653076172</v>
+        <v>21.31450271606445</v>
       </c>
       <c r="C352" t="n">
-        <v>21.45870601691791</v>
+        <v>21.458702176413</v>
       </c>
       <c r="D352" t="n">
-        <v>20.61153446549863</v>
+        <v>20.6115307766136</v>
       </c>
       <c r="E352" t="n">
-        <v>21.15228167908763</v>
+        <v>21.15227789342405</v>
       </c>
       <c r="F352" t="n">
         <v>714100</v>
@@ -7472,16 +7472,16 @@
         <v>44273</v>
       </c>
       <c r="B353" t="n">
-        <v>20.99005699157715</v>
+        <v>20.99005508422852</v>
       </c>
       <c r="C353" t="n">
-        <v>21.94537894634523</v>
+        <v>21.9453769521873</v>
       </c>
       <c r="D353" t="n">
-        <v>20.81881946982847</v>
+        <v>20.81881757804004</v>
       </c>
       <c r="E353" t="n">
-        <v>21.66599267748721</v>
+        <v>21.66599070871687</v>
       </c>
       <c r="F353" t="n">
         <v>1527100</v>
@@ -7492,16 +7492,16 @@
         <v>44274</v>
       </c>
       <c r="B354" t="n">
-        <v>21.125244140625</v>
+        <v>21.12524032592773</v>
       </c>
       <c r="C354" t="n">
-        <v>21.48574283538105</v>
+        <v>21.48573895558663</v>
       </c>
       <c r="D354" t="n">
-        <v>20.70165667016744</v>
+        <v>20.70165293195961</v>
       </c>
       <c r="E354" t="n">
-        <v>21.03511903718764</v>
+        <v>21.03511523876475</v>
       </c>
       <c r="F354" t="n">
         <v>1593400</v>
@@ -7512,16 +7512,16 @@
         <v>44277</v>
       </c>
       <c r="B355" t="n">
-        <v>22.20674324035645</v>
+        <v>22.20673942565918</v>
       </c>
       <c r="C355" t="n">
-        <v>22.25180665769099</v>
+        <v>22.25180283525269</v>
       </c>
       <c r="D355" t="n">
-        <v>20.99907115968833</v>
+        <v>20.99906755244622</v>
       </c>
       <c r="E355" t="n">
-        <v>21.02610921008906</v>
+        <v>21.02610559820233</v>
       </c>
       <c r="F355" t="n">
         <v>2913300</v>
@@ -7572,16 +7572,16 @@
         <v>44280</v>
       </c>
       <c r="B358" t="n">
-        <v>21.90932655334473</v>
+        <v>21.90932846069336</v>
       </c>
       <c r="C358" t="n">
-        <v>22.41402639815317</v>
+        <v>22.41402834943919</v>
       </c>
       <c r="D358" t="n">
-        <v>20.91795394553419</v>
+        <v>20.91795576657742</v>
       </c>
       <c r="E358" t="n">
-        <v>21.57586593626783</v>
+        <v>21.57586781458656</v>
       </c>
       <c r="F358" t="n">
         <v>1774000</v>
@@ -7592,16 +7592,16 @@
         <v>44281</v>
       </c>
       <c r="B359" t="n">
-        <v>21.35956573486328</v>
+        <v>21.35956764221191</v>
       </c>
       <c r="C359" t="n">
-        <v>22.1166137474757</v>
+        <v>22.11661572242658</v>
       </c>
       <c r="D359" t="n">
-        <v>21.01709073349459</v>
+        <v>21.01709261026118</v>
       </c>
       <c r="E359" t="n">
-        <v>21.94537624679136</v>
+        <v>21.94537820645121</v>
       </c>
       <c r="F359" t="n">
         <v>1291300</v>
@@ -7632,16 +7632,16 @@
         <v>44285</v>
       </c>
       <c r="B361" t="n">
-        <v>22.2337760925293</v>
+        <v>22.23377799987793</v>
       </c>
       <c r="C361" t="n">
-        <v>22.2337760925293</v>
+        <v>22.23377799987793</v>
       </c>
       <c r="D361" t="n">
-        <v>20.28708161264534</v>
+        <v>20.28708335299467</v>
       </c>
       <c r="E361" t="n">
-        <v>20.33214330045091</v>
+        <v>20.33214504466591</v>
       </c>
       <c r="F361" t="n">
         <v>1408700</v>
@@ -7652,16 +7652,16 @@
         <v>44286</v>
       </c>
       <c r="B362" t="n">
-        <v>22.20674324035645</v>
+        <v>22.20673942565918</v>
       </c>
       <c r="C362" t="n">
-        <v>22.63033076833314</v>
+        <v>22.63032688087157</v>
       </c>
       <c r="D362" t="n">
-        <v>21.8282191297143</v>
+        <v>21.82821538004029</v>
       </c>
       <c r="E362" t="n">
-        <v>21.99945667759835</v>
+        <v>21.99945289850899</v>
       </c>
       <c r="F362" t="n">
         <v>1238700</v>
@@ -7672,16 +7672,16 @@
         <v>44287</v>
       </c>
       <c r="B363" t="n">
-        <v>21.69303131103516</v>
+        <v>21.69302749633789</v>
       </c>
       <c r="C363" t="n">
-        <v>22.53119192571055</v>
+        <v>22.5311879636236</v>
       </c>
       <c r="D363" t="n">
-        <v>21.57586986937861</v>
+        <v>21.57586607528407</v>
       </c>
       <c r="E363" t="n">
-        <v>22.35094170270746</v>
+        <v>22.35093777231733</v>
       </c>
       <c r="F363" t="n">
         <v>809500</v>
@@ -7692,16 +7692,16 @@
         <v>44291</v>
       </c>
       <c r="B364" t="n">
-        <v>22.61230278015137</v>
+        <v>22.61230087280273</v>
       </c>
       <c r="C364" t="n">
-        <v>22.64835179084655</v>
+        <v>22.64834988045718</v>
       </c>
       <c r="D364" t="n">
-        <v>21.63895542547378</v>
+        <v>21.63895360022704</v>
       </c>
       <c r="E364" t="n">
-        <v>21.84624196420294</v>
+        <v>21.84624012147157</v>
       </c>
       <c r="F364" t="n">
         <v>851700</v>
@@ -7712,16 +7712,16 @@
         <v>44292</v>
       </c>
       <c r="B365" t="n">
-        <v>23.00885200500488</v>
+        <v>23.00885009765625</v>
       </c>
       <c r="C365" t="n">
-        <v>23.07193906239961</v>
+        <v>23.0719371498213</v>
       </c>
       <c r="D365" t="n">
-        <v>22.3509399460473</v>
+        <v>22.35093809323714</v>
       </c>
       <c r="E365" t="n">
-        <v>22.44106505046551</v>
+        <v>22.44106319018432</v>
       </c>
       <c r="F365" t="n">
         <v>734100</v>
@@ -7752,16 +7752,16 @@
         <v>44294</v>
       </c>
       <c r="B367" t="n">
-        <v>22.9908275604248</v>
+        <v>22.99082946777344</v>
       </c>
       <c r="C367" t="n">
-        <v>23.34231359082972</v>
+        <v>23.34231552733809</v>
       </c>
       <c r="D367" t="n">
-        <v>22.81959002707654</v>
+        <v>22.81959192021909</v>
       </c>
       <c r="E367" t="n">
-        <v>22.98181487772295</v>
+        <v>22.98181678432388</v>
       </c>
       <c r="F367" t="n">
         <v>602300</v>
@@ -7812,16 +7812,16 @@
         <v>44299</v>
       </c>
       <c r="B370" t="n">
-        <v>22.90971183776855</v>
+        <v>22.90971374511719</v>
       </c>
       <c r="C370" t="n">
-        <v>23.02687325804298</v>
+        <v>23.02687517514589</v>
       </c>
       <c r="D370" t="n">
-        <v>22.68439995963118</v>
+        <v>22.68440184822146</v>
       </c>
       <c r="E370" t="n">
-        <v>22.89168647495919</v>
+        <v>22.89168838080712</v>
       </c>
       <c r="F370" t="n">
         <v>313000</v>
@@ -7852,16 +7852,16 @@
         <v>44301</v>
       </c>
       <c r="B372" t="n">
-        <v>22.61230278015137</v>
+        <v>22.61230087280273</v>
       </c>
       <c r="C372" t="n">
-        <v>23.32428750156691</v>
+        <v>23.32428553416234</v>
       </c>
       <c r="D372" t="n">
-        <v>22.56724108703404</v>
+        <v>22.56723918348636</v>
       </c>
       <c r="E372" t="n">
-        <v>22.71144056780158</v>
+        <v>22.71143865209067</v>
       </c>
       <c r="F372" t="n">
         <v>1122600</v>
@@ -7872,16 +7872,16 @@
         <v>44302</v>
       </c>
       <c r="B373" t="n">
-        <v>23.12601470947266</v>
+        <v>23.12601089477539</v>
       </c>
       <c r="C373" t="n">
-        <v>23.12601470947266</v>
+        <v>23.12601089477539</v>
       </c>
       <c r="D373" t="n">
-        <v>22.53119139418563</v>
+        <v>22.53118767760605</v>
       </c>
       <c r="E373" t="n">
-        <v>22.54921675985942</v>
+        <v>22.5492130403065</v>
       </c>
       <c r="F373" t="n">
         <v>598500</v>
@@ -7892,16 +7892,16 @@
         <v>44305</v>
       </c>
       <c r="B374" t="n">
-        <v>23.13502311706543</v>
+        <v>23.13502502441406</v>
       </c>
       <c r="C374" t="n">
-        <v>23.49552176895524</v>
+        <v>23.49552370602489</v>
       </c>
       <c r="D374" t="n">
-        <v>22.56723795521313</v>
+        <v>22.56723981575116</v>
       </c>
       <c r="E374" t="n">
-        <v>23.1620611605796</v>
+        <v>23.16206307015737</v>
       </c>
       <c r="F374" t="n">
         <v>998400</v>
@@ -7932,16 +7932,16 @@
         <v>44308</v>
       </c>
       <c r="B376" t="n">
-        <v>21.94537925720215</v>
+        <v>21.94537734985352</v>
       </c>
       <c r="C376" t="n">
-        <v>22.55822789614722</v>
+        <v>22.5582259355338</v>
       </c>
       <c r="D376" t="n">
-        <v>21.92735389276415</v>
+        <v>21.92735198698216</v>
       </c>
       <c r="E376" t="n">
-        <v>22.42303938185559</v>
+        <v>22.42303743299186</v>
       </c>
       <c r="F376" t="n">
         <v>1422400</v>
@@ -7992,16 +7992,16 @@
         <v>44313</v>
       </c>
       <c r="B379" t="n">
-        <v>22.30587959289551</v>
+        <v>22.30587768554688</v>
       </c>
       <c r="C379" t="n">
-        <v>22.3869920198437</v>
+        <v>22.38699010555924</v>
       </c>
       <c r="D379" t="n">
-        <v>21.96340623833142</v>
+        <v>21.96340436026727</v>
       </c>
       <c r="E379" t="n">
-        <v>22.35094128831406</v>
+        <v>22.35093937711226</v>
       </c>
       <c r="F379" t="n">
         <v>435600</v>
@@ -8052,16 +8052,16 @@
         <v>44316</v>
       </c>
       <c r="B382" t="n">
-        <v>22.63032913208008</v>
+        <v>22.63032722473145</v>
       </c>
       <c r="C382" t="n">
-        <v>23.01786589816885</v>
+        <v>23.01786395815752</v>
       </c>
       <c r="D382" t="n">
-        <v>22.01748045259025</v>
+        <v>22.01747859689425</v>
       </c>
       <c r="E382" t="n">
-        <v>22.81057763140484</v>
+        <v>22.81057570886435</v>
       </c>
       <c r="F382" t="n">
         <v>889000</v>
@@ -8092,16 +8092,16 @@
         <v>44320</v>
       </c>
       <c r="B384" t="n">
-        <v>23.26509857177734</v>
+        <v>23.26509666442871</v>
       </c>
       <c r="C384" t="n">
-        <v>23.39153877252345</v>
+        <v>23.39153685480884</v>
       </c>
       <c r="D384" t="n">
-        <v>22.05487980783492</v>
+        <v>22.05487799970397</v>
       </c>
       <c r="E384" t="n">
-        <v>22.24454010895408</v>
+        <v>22.24453828527416</v>
       </c>
       <c r="F384" t="n">
         <v>1769300</v>
@@ -8152,16 +8152,16 @@
         <v>44323</v>
       </c>
       <c r="B387" t="n">
-        <v>23.72570610046387</v>
+        <v>23.72570419311523</v>
       </c>
       <c r="C387" t="n">
-        <v>23.72570610046387</v>
+        <v>23.72570419311523</v>
       </c>
       <c r="D387" t="n">
-        <v>22.89480960095111</v>
+        <v>22.89480776039961</v>
       </c>
       <c r="E387" t="n">
-        <v>23.03028150054825</v>
+        <v>23.03027964910594</v>
       </c>
       <c r="F387" t="n">
         <v>712600</v>
@@ -8172,16 +8172,16 @@
         <v>44326</v>
       </c>
       <c r="B388" t="n">
-        <v>23.59023284912109</v>
+        <v>23.59023094177246</v>
       </c>
       <c r="C388" t="n">
-        <v>23.99664852462446</v>
+        <v>23.99664658441577</v>
       </c>
       <c r="D388" t="n">
-        <v>23.21091051841348</v>
+        <v>23.21090864173432</v>
       </c>
       <c r="E388" t="n">
-        <v>23.90633335586196</v>
+        <v>23.90633142295556</v>
       </c>
       <c r="F388" t="n">
         <v>1342100</v>
@@ -8232,16 +8232,16 @@
         <v>44329</v>
       </c>
       <c r="B391" t="n">
-        <v>23.36444473266602</v>
+        <v>23.36444664001465</v>
       </c>
       <c r="C391" t="n">
-        <v>23.48185324091847</v>
+        <v>23.48185515785171</v>
       </c>
       <c r="D391" t="n">
-        <v>22.75933536870684</v>
+        <v>22.75933722665757</v>
       </c>
       <c r="E391" t="n">
-        <v>23.1115626160827</v>
+        <v>23.11156450278738</v>
       </c>
       <c r="F391" t="n">
         <v>1130900</v>
@@ -8352,16 +8352,16 @@
         <v>44337</v>
       </c>
       <c r="B397" t="n">
-        <v>24.89979362487793</v>
+        <v>24.89979553222656</v>
       </c>
       <c r="C397" t="n">
-        <v>25.12558065698255</v>
+        <v>25.12558258162668</v>
       </c>
       <c r="D397" t="n">
-        <v>24.18630749918889</v>
+        <v>24.18630935188379</v>
       </c>
       <c r="E397" t="n">
-        <v>24.56562978202938</v>
+        <v>24.56563166378073</v>
       </c>
       <c r="F397" t="n">
         <v>1408900</v>
@@ -8372,16 +8372,16 @@
         <v>44340</v>
       </c>
       <c r="B398" t="n">
-        <v>25.19783401489258</v>
+        <v>25.19783592224121</v>
       </c>
       <c r="C398" t="n">
-        <v>25.19783401489258</v>
+        <v>25.19783592224121</v>
       </c>
       <c r="D398" t="n">
-        <v>24.60175635065135</v>
+        <v>24.60175821287991</v>
       </c>
       <c r="E398" t="n">
-        <v>24.89979518277196</v>
+        <v>24.89979706756056</v>
       </c>
       <c r="F398" t="n">
         <v>853600</v>
@@ -8392,16 +8392,16 @@
         <v>44341</v>
       </c>
       <c r="B399" t="n">
-        <v>25.08042526245117</v>
+        <v>25.0804271697998</v>
       </c>
       <c r="C399" t="n">
-        <v>25.3965274685938</v>
+        <v>25.39652939998178</v>
       </c>
       <c r="D399" t="n">
-        <v>24.83657484148814</v>
+        <v>24.83657673029212</v>
       </c>
       <c r="E399" t="n">
-        <v>25.20686545586085</v>
+        <v>25.20686737282517</v>
       </c>
       <c r="F399" t="n">
         <v>711500</v>
@@ -8412,16 +8412,16 @@
         <v>44342</v>
       </c>
       <c r="B400" t="n">
-        <v>25.6042537689209</v>
+        <v>25.60425186157227</v>
       </c>
       <c r="C400" t="n">
-        <v>25.77585242235237</v>
+        <v>25.77585050222076</v>
       </c>
       <c r="D400" t="n">
-        <v>24.99011267042397</v>
+        <v>24.99011080882481</v>
       </c>
       <c r="E400" t="n">
-        <v>25.19783635885128</v>
+        <v>25.19783448177807</v>
       </c>
       <c r="F400" t="n">
         <v>1467200</v>
@@ -8472,16 +8472,16 @@
         <v>44347</v>
       </c>
       <c r="B403" t="n">
-        <v>27.19379615783691</v>
+        <v>27.19379234313965</v>
       </c>
       <c r="C403" t="n">
-        <v>27.65440200252411</v>
+        <v>27.65439812321387</v>
       </c>
       <c r="D403" t="n">
-        <v>26.78737872940154</v>
+        <v>26.78737497171579</v>
       </c>
       <c r="E403" t="n">
-        <v>27.64537031271236</v>
+        <v>27.64536643466907</v>
       </c>
       <c r="F403" t="n">
         <v>1084300</v>
@@ -8492,16 +8492,16 @@
         <v>44348</v>
       </c>
       <c r="B404" t="n">
-        <v>28.08790969848633</v>
+        <v>28.08791160583496</v>
       </c>
       <c r="C404" t="n">
-        <v>29.0723396633821</v>
+        <v>29.07234163757982</v>
       </c>
       <c r="D404" t="n">
-        <v>27.39248516278936</v>
+        <v>27.39248702291422</v>
       </c>
       <c r="E404" t="n">
-        <v>27.93437443375607</v>
+        <v>27.93437633067867</v>
       </c>
       <c r="F404" t="n">
         <v>4051600</v>
@@ -8512,16 +8512,16 @@
         <v>44349</v>
       </c>
       <c r="B405" t="n">
-        <v>28.81042861938477</v>
+        <v>28.81042671203613</v>
       </c>
       <c r="C405" t="n">
-        <v>29.0181540245529</v>
+        <v>29.01815210345214</v>
       </c>
       <c r="D405" t="n">
-        <v>28.27757101797948</v>
+        <v>28.27756914590784</v>
       </c>
       <c r="E405" t="n">
-        <v>28.27757101797948</v>
+        <v>28.27756914590784</v>
       </c>
       <c r="F405" t="n">
         <v>2374700</v>
@@ -8532,16 +8532,16 @@
         <v>44351</v>
       </c>
       <c r="B406" t="n">
-        <v>28.77430152893066</v>
+        <v>28.7743034362793</v>
       </c>
       <c r="C406" t="n">
-        <v>29.03621532764976</v>
+        <v>29.03621725235974</v>
       </c>
       <c r="D406" t="n">
-        <v>28.2053172115981</v>
+        <v>28.20531908123073</v>
       </c>
       <c r="E406" t="n">
-        <v>28.72011139791527</v>
+        <v>28.72011330167182</v>
       </c>
       <c r="F406" t="n">
         <v>1004000</v>
@@ -8572,16 +8572,16 @@
         <v>44355</v>
       </c>
       <c r="B408" t="n">
-        <v>28.32272720336914</v>
+        <v>28.32272911071777</v>
       </c>
       <c r="C408" t="n">
-        <v>28.39497898816882</v>
+        <v>28.39498090038313</v>
       </c>
       <c r="D408" t="n">
-        <v>27.91630983723443</v>
+        <v>27.91631171721354</v>
       </c>
       <c r="E408" t="n">
-        <v>28.17822363376978</v>
+        <v>28.17822553138705</v>
       </c>
       <c r="F408" t="n">
         <v>1212600</v>
@@ -8592,16 +8592,16 @@
         <v>44356</v>
       </c>
       <c r="B409" t="n">
-        <v>28.59367179870605</v>
+        <v>28.59367370605469</v>
       </c>
       <c r="C409" t="n">
-        <v>29.0994360296562</v>
+        <v>29.09943797074197</v>
       </c>
       <c r="D409" t="n">
-        <v>28.24144455287382</v>
+        <v>28.24144643672703</v>
       </c>
       <c r="E409" t="n">
-        <v>28.33175971715909</v>
+        <v>28.33176160703681</v>
       </c>
       <c r="F409" t="n">
         <v>997100</v>
@@ -8612,16 +8612,16 @@
         <v>44357</v>
       </c>
       <c r="B410" t="n">
-        <v>28.71108436584473</v>
+        <v>28.71108627319336</v>
       </c>
       <c r="C410" t="n">
-        <v>29.09040498600235</v>
+        <v>29.09040691855019</v>
       </c>
       <c r="D410" t="n">
-        <v>28.15113167979651</v>
+        <v>28.1511335499461</v>
       </c>
       <c r="E410" t="n">
-        <v>28.59367412593236</v>
+        <v>28.59367602548114</v>
       </c>
       <c r="F410" t="n">
         <v>708800</v>
@@ -8632,16 +8632,16 @@
         <v>44358</v>
       </c>
       <c r="B411" t="n">
-        <v>28.01565742492676</v>
+        <v>28.01565933227539</v>
       </c>
       <c r="C411" t="n">
-        <v>28.86461548802019</v>
+        <v>28.86461745316718</v>
       </c>
       <c r="D411" t="n">
-        <v>27.63633511408684</v>
+        <v>27.63633699561063</v>
       </c>
       <c r="E411" t="n">
-        <v>28.78333373527165</v>
+        <v>28.78333569488485</v>
       </c>
       <c r="F411" t="n">
         <v>853800</v>
@@ -8652,16 +8652,16 @@
         <v>44361</v>
       </c>
       <c r="B412" t="n">
-        <v>29.60519790649414</v>
+        <v>29.60519599914551</v>
       </c>
       <c r="C412" t="n">
-        <v>29.6955147967266</v>
+        <v>29.6955128835592</v>
       </c>
       <c r="D412" t="n">
-        <v>28.08791032557823</v>
+        <v>28.08790851598258</v>
       </c>
       <c r="E412" t="n">
-        <v>28.08791032557823</v>
+        <v>28.08790851598258</v>
       </c>
       <c r="F412" t="n">
         <v>1333100</v>
@@ -8672,16 +8672,16 @@
         <v>44362</v>
       </c>
       <c r="B413" t="n">
-        <v>29.39747619628906</v>
+        <v>29.3974723815918</v>
       </c>
       <c r="C413" t="n">
-        <v>29.6864833739207</v>
+        <v>29.68647952172106</v>
       </c>
       <c r="D413" t="n">
-        <v>29.12653239791407</v>
+        <v>29.12652861837521</v>
       </c>
       <c r="E413" t="n">
-        <v>29.61423330213145</v>
+        <v>29.61422945930718</v>
       </c>
       <c r="F413" t="n">
         <v>824500</v>
@@ -8732,16 +8732,16 @@
         <v>44365</v>
       </c>
       <c r="B416" t="n">
-        <v>31.21280479431152</v>
+        <v>31.21280670166016</v>
       </c>
       <c r="C416" t="n">
-        <v>31.21280479431152</v>
+        <v>31.21280670166016</v>
       </c>
       <c r="D416" t="n">
-        <v>29.81292224909573</v>
+        <v>29.8129240709005</v>
       </c>
       <c r="E416" t="n">
-        <v>29.97548920989193</v>
+        <v>29.97549104163082</v>
       </c>
       <c r="F416" t="n">
         <v>1597800</v>
@@ -8752,16 +8752,16 @@
         <v>44368</v>
       </c>
       <c r="B417" t="n">
-        <v>30.67994499206543</v>
+        <v>30.67994689941406</v>
       </c>
       <c r="C417" t="n">
-        <v>31.68244003012831</v>
+        <v>31.68244199980129</v>
       </c>
       <c r="D417" t="n">
-        <v>30.34577768255319</v>
+        <v>30.3457795691269</v>
       </c>
       <c r="E417" t="n">
-        <v>31.68244003012831</v>
+        <v>31.68244199980129</v>
       </c>
       <c r="F417" t="n">
         <v>1410300</v>
@@ -8832,16 +8832,16 @@
         <v>44372</v>
       </c>
       <c r="B421" t="n">
-        <v>29.34328842163086</v>
+        <v>29.34328651428223</v>
       </c>
       <c r="C421" t="n">
-        <v>30.32772016077128</v>
+        <v>30.32771818943341</v>
       </c>
       <c r="D421" t="n">
-        <v>29.00009111888577</v>
+        <v>29.00008923384538</v>
       </c>
       <c r="E421" t="n">
-        <v>30.29159340359028</v>
+        <v>30.2915914346007</v>
       </c>
       <c r="F421" t="n">
         <v>1155100</v>
@@ -8852,16 +8852,16 @@
         <v>44375</v>
       </c>
       <c r="B422" t="n">
-        <v>29.61423110961914</v>
+        <v>29.61423301696777</v>
       </c>
       <c r="C422" t="n">
-        <v>29.93936502169252</v>
+        <v>29.93936694998189</v>
       </c>
       <c r="D422" t="n">
-        <v>29.28909719754576</v>
+        <v>29.28909908395366</v>
       </c>
       <c r="E422" t="n">
-        <v>29.3703806755641</v>
+        <v>29.37038256720719</v>
       </c>
       <c r="F422" t="n">
         <v>1163900</v>
@@ -8872,16 +8872,16 @@
         <v>44376</v>
       </c>
       <c r="B423" t="n">
-        <v>29.72260856628418</v>
+        <v>29.72260665893555</v>
       </c>
       <c r="C423" t="n">
-        <v>29.77679870119871</v>
+        <v>29.7767967903726</v>
       </c>
       <c r="D423" t="n">
-        <v>28.8646170456084</v>
+        <v>28.86461519331849</v>
       </c>
       <c r="E423" t="n">
-        <v>29.60519832992127</v>
+        <v>29.60519643010704</v>
       </c>
       <c r="F423" t="n">
         <v>1611300</v>
@@ -8912,16 +8912,16 @@
         <v>44378</v>
       </c>
       <c r="B425" t="n">
-        <v>28.88267707824707</v>
+        <v>28.88268089294434</v>
       </c>
       <c r="C425" t="n">
-        <v>29.39747124197319</v>
+        <v>29.39747512466221</v>
       </c>
       <c r="D425" t="n">
-        <v>28.66592173155283</v>
+        <v>28.665925517622</v>
       </c>
       <c r="E425" t="n">
-        <v>28.76526857810291</v>
+        <v>28.76527237729338</v>
       </c>
       <c r="F425" t="n">
         <v>1124300</v>
@@ -8932,16 +8932,16 @@
         <v>44379</v>
       </c>
       <c r="B426" t="n">
-        <v>29.39747619628906</v>
+        <v>29.3974723815918</v>
       </c>
       <c r="C426" t="n">
-        <v>29.50585302659159</v>
+        <v>29.50584919783105</v>
       </c>
       <c r="D426" t="n">
-        <v>28.72011497773292</v>
+        <v>28.72011125093191</v>
       </c>
       <c r="E426" t="n">
-        <v>28.79236677214083</v>
+        <v>28.79236303596423</v>
       </c>
       <c r="F426" t="n">
         <v>880200</v>
@@ -8952,16 +8952,16 @@
         <v>44382</v>
       </c>
       <c r="B427" t="n">
-        <v>28.82849311828613</v>
+        <v>28.8284912109375</v>
       </c>
       <c r="C427" t="n">
-        <v>29.65938960340112</v>
+        <v>29.65938764107877</v>
       </c>
       <c r="D427" t="n">
-        <v>28.82849311828613</v>
+        <v>28.8284912109375</v>
       </c>
       <c r="E427" t="n">
-        <v>29.39747577578225</v>
+        <v>29.39747383078863</v>
       </c>
       <c r="F427" t="n">
         <v>1101800</v>
@@ -8972,16 +8972,16 @@
         <v>44383</v>
       </c>
       <c r="B428" t="n">
-        <v>28.71108436584473</v>
+        <v>28.71108627319336</v>
       </c>
       <c r="C428" t="n">
-        <v>28.9910581249409</v>
+        <v>28.99106005088889</v>
       </c>
       <c r="D428" t="n">
-        <v>28.49432726487091</v>
+        <v>28.49432915781984</v>
       </c>
       <c r="E428" t="n">
-        <v>28.61173750478328</v>
+        <v>28.61173940553206</v>
       </c>
       <c r="F428" t="n">
         <v>1125800</v>
@@ -8992,16 +8992,16 @@
         <v>44384</v>
       </c>
       <c r="B429" t="n">
-        <v>28.57560729980469</v>
+        <v>28.57560920715332</v>
       </c>
       <c r="C429" t="n">
-        <v>29.08137151090486</v>
+        <v>29.08137345201196</v>
       </c>
       <c r="D429" t="n">
-        <v>28.32272691687302</v>
+        <v>28.32272880734253</v>
       </c>
       <c r="E429" t="n">
-        <v>28.82848940535477</v>
+        <v>28.82849132958264</v>
       </c>
       <c r="F429" t="n">
         <v>1353100</v>
@@ -9032,16 +9032,16 @@
         <v>44389</v>
       </c>
       <c r="B431" t="n">
-        <v>29.01815414428711</v>
+        <v>29.01815223693848</v>
       </c>
       <c r="C431" t="n">
-        <v>29.03621752265775</v>
+        <v>29.03621561412182</v>
       </c>
       <c r="D431" t="n">
-        <v>28.15113093130056</v>
+        <v>28.15112908094092</v>
       </c>
       <c r="E431" t="n">
-        <v>28.16016262048588</v>
+        <v>28.1601607695326</v>
       </c>
       <c r="F431" t="n">
         <v>993700</v>
@@ -9072,16 +9072,16 @@
         <v>44391</v>
       </c>
       <c r="B433" t="n">
-        <v>28.8917121887207</v>
+        <v>28.89171028137207</v>
       </c>
       <c r="C433" t="n">
-        <v>29.22587779776106</v>
+        <v>29.22587586835176</v>
       </c>
       <c r="D433" t="n">
-        <v>28.79236533040249</v>
+        <v>28.79236342961245</v>
       </c>
       <c r="E433" t="n">
-        <v>28.95493401295321</v>
+        <v>28.95493210143085</v>
       </c>
       <c r="F433" t="n">
         <v>880400</v>
@@ -9092,16 +9092,16 @@
         <v>44392</v>
       </c>
       <c r="B434" t="n">
-        <v>28.77430152893066</v>
+        <v>28.7743034362793</v>
       </c>
       <c r="C434" t="n">
-        <v>29.21684220722731</v>
+        <v>29.21684414391042</v>
       </c>
       <c r="D434" t="n">
-        <v>28.68398636652345</v>
+        <v>28.6839882678854</v>
       </c>
       <c r="E434" t="n">
-        <v>28.81042656032249</v>
+        <v>28.81042847006572</v>
       </c>
       <c r="F434" t="n">
         <v>728800</v>
@@ -9132,16 +9132,16 @@
         <v>44396</v>
       </c>
       <c r="B436" t="n">
-        <v>28.57560729980469</v>
+        <v>28.57560920715332</v>
       </c>
       <c r="C436" t="n">
-        <v>28.72011086794233</v>
+        <v>28.72011278493621</v>
       </c>
       <c r="D436" t="n">
-        <v>28.09693987633064</v>
+        <v>28.09694175172945</v>
       </c>
       <c r="E436" t="n">
-        <v>28.53948226907948</v>
+        <v>28.53948417401686</v>
       </c>
       <c r="F436" t="n">
         <v>772000</v>
@@ -9152,16 +9152,16 @@
         <v>44397</v>
       </c>
       <c r="B437" t="n">
-        <v>28.23241424560547</v>
+        <v>28.23241233825684</v>
       </c>
       <c r="C437" t="n">
-        <v>28.8194602582564</v>
+        <v>28.81945831124763</v>
       </c>
       <c r="D437" t="n">
-        <v>28.18725579994398</v>
+        <v>28.18725389564619</v>
       </c>
       <c r="E437" t="n">
-        <v>28.56657813040772</v>
+        <v>28.56657620048336</v>
       </c>
       <c r="F437" t="n">
         <v>691100</v>
@@ -9192,16 +9192,16 @@
         <v>44399</v>
       </c>
       <c r="B439" t="n">
-        <v>29.00912094116211</v>
+        <v>29.00911903381348</v>
       </c>
       <c r="C439" t="n">
-        <v>29.5329485819675</v>
+        <v>29.53294664017722</v>
       </c>
       <c r="D439" t="n">
-        <v>28.73817715412771</v>
+        <v>28.73817526459362</v>
       </c>
       <c r="E439" t="n">
-        <v>28.75624053262829</v>
+        <v>28.75623864190653</v>
       </c>
       <c r="F439" t="n">
         <v>981600</v>
@@ -9212,16 +9212,16 @@
         <v>44400</v>
       </c>
       <c r="B440" t="n">
-        <v>28.71108436584473</v>
+        <v>28.71108627319336</v>
       </c>
       <c r="C440" t="n">
-        <v>29.13556171051103</v>
+        <v>29.13556364605875</v>
       </c>
       <c r="D440" t="n">
-        <v>28.47626560863861</v>
+        <v>28.47626750038765</v>
       </c>
       <c r="E440" t="n">
-        <v>29.13556171051103</v>
+        <v>29.13556364605875</v>
       </c>
       <c r="F440" t="n">
         <v>496100</v>
@@ -9232,16 +9232,16 @@
         <v>44403</v>
       </c>
       <c r="B441" t="n">
-        <v>28.22338104248047</v>
+        <v>28.2233829498291</v>
       </c>
       <c r="C441" t="n">
-        <v>28.70205020510359</v>
+        <v>28.70205214480089</v>
       </c>
       <c r="D441" t="n">
-        <v>28.19628597653704</v>
+        <v>28.19628788205457</v>
       </c>
       <c r="E441" t="n">
-        <v>28.70205020510359</v>
+        <v>28.70205214480089</v>
       </c>
       <c r="F441" t="n">
         <v>447900</v>
@@ -9252,16 +9252,16 @@
         <v>44404</v>
       </c>
       <c r="B442" t="n">
-        <v>27.5369873046875</v>
+        <v>27.53698921203613</v>
       </c>
       <c r="C442" t="n">
-        <v>28.24144349252096</v>
+        <v>28.24144544866373</v>
       </c>
       <c r="D442" t="n">
-        <v>27.16669669537744</v>
+        <v>27.1666985770779</v>
       </c>
       <c r="E442" t="n">
-        <v>28.08790823578617</v>
+        <v>28.08791018129433</v>
       </c>
       <c r="F442" t="n">
         <v>742400</v>
@@ -9272,16 +9272,16 @@
         <v>44405</v>
       </c>
       <c r="B443" t="n">
-        <v>28.17822456359863</v>
+        <v>28.17822647094727</v>
       </c>
       <c r="C443" t="n">
-        <v>28.33175982669163</v>
+        <v>28.33176174443287</v>
       </c>
       <c r="D443" t="n">
-        <v>27.59117685478402</v>
+        <v>27.59117872239614</v>
       </c>
       <c r="E443" t="n">
-        <v>27.63633529841049</v>
+        <v>27.63633716907932</v>
       </c>
       <c r="F443" t="n">
         <v>805700</v>
@@ -9292,16 +9292,16 @@
         <v>44406</v>
       </c>
       <c r="B444" t="n">
-        <v>28.17822456359863</v>
+        <v>28.17822647094727</v>
       </c>
       <c r="C444" t="n">
-        <v>28.39497992515019</v>
+        <v>28.39498184717073</v>
       </c>
       <c r="D444" t="n">
-        <v>27.89824738097002</v>
+        <v>27.89824926936735</v>
       </c>
       <c r="E444" t="n">
-        <v>28.22338128460661</v>
+        <v>28.22338319501185</v>
       </c>
       <c r="F444" t="n">
         <v>553900</v>
@@ -9312,16 +9312,16 @@
         <v>44407</v>
       </c>
       <c r="B445" t="n">
-        <v>28.17822456359863</v>
+        <v>28.17822647094727</v>
       </c>
       <c r="C445" t="n">
-        <v>29.54197683136655</v>
+        <v>29.54197883102587</v>
       </c>
       <c r="D445" t="n">
-        <v>27.75374380660232</v>
+        <v>27.75374568521838</v>
       </c>
       <c r="E445" t="n">
-        <v>27.82599559378617</v>
+        <v>27.82599747729287</v>
       </c>
       <c r="F445" t="n">
         <v>1996900</v>
@@ -9332,16 +9332,16 @@
         <v>44410</v>
       </c>
       <c r="B446" t="n">
-        <v>28.24144744873047</v>
+        <v>28.24144554138184</v>
       </c>
       <c r="C446" t="n">
-        <v>28.84655687208524</v>
+        <v>28.84655492386921</v>
       </c>
       <c r="D446" t="n">
-        <v>27.78987330361851</v>
+        <v>27.78987142676793</v>
       </c>
       <c r="E446" t="n">
-        <v>28.62076979952926</v>
+        <v>28.62076786656225</v>
       </c>
       <c r="F446" t="n">
         <v>1268700</v>
@@ -9352,16 +9352,16 @@
         <v>44411</v>
       </c>
       <c r="B447" t="n">
-        <v>28.48529624938965</v>
+        <v>28.48529434204102</v>
       </c>
       <c r="C447" t="n">
-        <v>28.53948466132887</v>
+        <v>28.53948275035183</v>
       </c>
       <c r="D447" t="n">
-        <v>27.10347882530039</v>
+        <v>27.10347701047695</v>
       </c>
       <c r="E447" t="n">
-        <v>28.27757084548862</v>
+        <v>28.27756895204909</v>
       </c>
       <c r="F447" t="n">
         <v>2457100</v>
@@ -9392,16 +9392,16 @@
         <v>44413</v>
       </c>
       <c r="B449" t="n">
-        <v>27.44667625427246</v>
+        <v>27.44667434692383</v>
       </c>
       <c r="C449" t="n">
-        <v>28.0788807525946</v>
+        <v>28.07887880131226</v>
       </c>
       <c r="D449" t="n">
-        <v>27.21185748982763</v>
+        <v>27.21185559879723</v>
       </c>
       <c r="E449" t="n">
-        <v>27.99759726787837</v>
+        <v>27.99759532224465</v>
       </c>
       <c r="F449" t="n">
         <v>966400</v>
@@ -9412,16 +9412,16 @@
         <v>44414</v>
       </c>
       <c r="B450" t="n">
-        <v>27.79890251159668</v>
+        <v>27.79890632629395</v>
       </c>
       <c r="C450" t="n">
-        <v>27.86212261064964</v>
+        <v>27.86212643402227</v>
       </c>
       <c r="D450" t="n">
-        <v>27.10347797677709</v>
+        <v>27.1034816960449</v>
       </c>
       <c r="E450" t="n">
-        <v>27.46473691609295</v>
+        <v>27.46474068493442</v>
       </c>
       <c r="F450" t="n">
         <v>792400</v>
@@ -9512,16 +9512,16 @@
         <v>44421</v>
       </c>
       <c r="B455" t="n">
-        <v>26.96800804138184</v>
+        <v>26.9680061340332</v>
       </c>
       <c r="C455" t="n">
-        <v>27.50086566141453</v>
+        <v>27.50086371637882</v>
       </c>
       <c r="D455" t="n">
-        <v>26.91381790459915</v>
+        <v>26.91381600108318</v>
       </c>
       <c r="E455" t="n">
-        <v>27.35636207523129</v>
+        <v>27.35636014041579</v>
       </c>
       <c r="F455" t="n">
         <v>1254900</v>
@@ -9552,16 +9552,16 @@
         <v>44425</v>
       </c>
       <c r="B457" t="n">
-        <v>26.92284774780273</v>
+        <v>26.9228458404541</v>
       </c>
       <c r="C457" t="n">
-        <v>27.36539016546847</v>
+        <v>27.36538822676793</v>
       </c>
       <c r="D457" t="n">
-        <v>25.7848807926829</v>
+        <v>25.78487896595352</v>
       </c>
       <c r="E457" t="n">
-        <v>27.36539016546847</v>
+        <v>27.36538822676793</v>
       </c>
       <c r="F457" t="n">
         <v>2325200</v>
@@ -9612,16 +9612,16 @@
         <v>44428</v>
       </c>
       <c r="B460" t="n">
-        <v>28.67495918273926</v>
+        <v>28.67495727539062</v>
       </c>
       <c r="C460" t="n">
-        <v>28.78333773917744</v>
+        <v>28.78333582461988</v>
       </c>
       <c r="D460" t="n">
-        <v>27.90728276560675</v>
+        <v>27.90728090932101</v>
       </c>
       <c r="E460" t="n">
-        <v>28.32273188889793</v>
+        <v>28.32273000497811</v>
       </c>
       <c r="F460" t="n">
         <v>1113100</v>
@@ -9652,16 +9652,16 @@
         <v>44432</v>
       </c>
       <c r="B462" t="n">
-        <v>28.98202705383301</v>
+        <v>28.98202514648438</v>
       </c>
       <c r="C462" t="n">
-        <v>29.31619093674931</v>
+        <v>29.31618900740888</v>
       </c>
       <c r="D462" t="n">
-        <v>28.61173641459139</v>
+        <v>28.61173453161212</v>
       </c>
       <c r="E462" t="n">
-        <v>28.88268019655697</v>
+        <v>28.8826782957465</v>
       </c>
       <c r="F462" t="n">
         <v>1724500</v>
@@ -9692,16 +9692,16 @@
         <v>44434</v>
       </c>
       <c r="B464" t="n">
-        <v>28.96396255493164</v>
+        <v>28.96396446228027</v>
       </c>
       <c r="C464" t="n">
-        <v>29.84001741311792</v>
+        <v>29.84001937815694</v>
       </c>
       <c r="D464" t="n">
-        <v>28.76527057068636</v>
+        <v>28.76527246495063</v>
       </c>
       <c r="E464" t="n">
-        <v>29.7316371483357</v>
+        <v>29.7316391062376</v>
       </c>
       <c r="F464" t="n">
         <v>847800</v>
@@ -9712,16 +9712,16 @@
         <v>44435</v>
       </c>
       <c r="B465" t="n">
-        <v>29.72260856628418</v>
+        <v>29.72260665893555</v>
       </c>
       <c r="C465" t="n">
-        <v>29.74067194458902</v>
+        <v>29.74067003608123</v>
       </c>
       <c r="D465" t="n">
-        <v>28.74720853186406</v>
+        <v>28.74720668710845</v>
       </c>
       <c r="E465" t="n">
-        <v>28.93687055882777</v>
+        <v>28.93686870190124</v>
       </c>
       <c r="F465" t="n">
         <v>1133700</v>
@@ -9772,16 +9772,16 @@
         <v>44440</v>
       </c>
       <c r="B468" t="n">
-        <v>29.91227149963379</v>
+        <v>29.91226959228516</v>
       </c>
       <c r="C468" t="n">
-        <v>30.28256217433525</v>
+        <v>30.28256024337513</v>
       </c>
       <c r="D468" t="n">
-        <v>29.70454779872686</v>
+        <v>29.70454590462368</v>
       </c>
       <c r="E468" t="n">
-        <v>30.28256217433525</v>
+        <v>30.28256024337513</v>
       </c>
       <c r="F468" t="n">
         <v>811700</v>
@@ -9792,16 +9792,16 @@
         <v>44441</v>
       </c>
       <c r="B469" t="n">
-        <v>29.25296783447266</v>
+        <v>29.25296974182129</v>
       </c>
       <c r="C469" t="n">
-        <v>29.91226556619919</v>
+        <v>29.91226751653528</v>
       </c>
       <c r="D469" t="n">
-        <v>29.25296783447265</v>
+        <v>29.25296974182129</v>
       </c>
       <c r="E469" t="n">
-        <v>29.91226556619919</v>
+        <v>29.91226751653528</v>
       </c>
       <c r="F469" t="n">
         <v>600700</v>
@@ -9812,16 +9812,16 @@
         <v>44442</v>
       </c>
       <c r="B470" t="n">
-        <v>29.14459419250488</v>
+        <v>29.14459228515625</v>
       </c>
       <c r="C470" t="n">
-        <v>29.47875807749012</v>
+        <v>29.47875614827236</v>
       </c>
       <c r="D470" t="n">
-        <v>28.75624017269617</v>
+        <v>28.75623829076311</v>
       </c>
       <c r="E470" t="n">
-        <v>29.3884446313548</v>
+        <v>29.38844270804754</v>
       </c>
       <c r="F470" t="n">
         <v>890900</v>
@@ -9872,16 +9872,16 @@
         <v>44448</v>
       </c>
       <c r="B473" t="n">
-        <v>27.5821475982666</v>
+        <v>27.58214569091797</v>
       </c>
       <c r="C473" t="n">
-        <v>27.90727978764918</v>
+        <v>27.90727785781715</v>
       </c>
       <c r="D473" t="n">
-        <v>26.8235029520097</v>
+        <v>26.82350109712253</v>
       </c>
       <c r="E473" t="n">
-        <v>27.10347841922258</v>
+        <v>27.10347654497468</v>
       </c>
       <c r="F473" t="n">
         <v>956300</v>
@@ -9892,16 +9892,16 @@
         <v>44449</v>
       </c>
       <c r="B474" t="n">
-        <v>28.17822456359863</v>
+        <v>28.17822647094727</v>
       </c>
       <c r="C474" t="n">
-        <v>28.60270359797646</v>
+        <v>28.60270553405755</v>
       </c>
       <c r="D474" t="n">
-        <v>27.6273036096852</v>
+        <v>27.62730547974268</v>
       </c>
       <c r="E474" t="n">
-        <v>27.98856254560446</v>
+        <v>27.98856444011511</v>
       </c>
       <c r="F474" t="n">
         <v>1603100</v>
@@ -9912,16 +9912,16 @@
         <v>44452</v>
       </c>
       <c r="B475" t="n">
-        <v>28.94589805603027</v>
+        <v>28.94589996337891</v>
       </c>
       <c r="C475" t="n">
-        <v>29.32522207759813</v>
+        <v>29.32522400994178</v>
       </c>
       <c r="D475" t="n">
-        <v>28.15112842722206</v>
+        <v>28.15113028220048</v>
       </c>
       <c r="E475" t="n">
-        <v>28.53045072617149</v>
+        <v>28.53045260614482</v>
       </c>
       <c r="F475" t="n">
         <v>1109800</v>
@@ -9932,16 +9932,16 @@
         <v>44453</v>
       </c>
       <c r="B476" t="n">
-        <v>28.8646183013916</v>
+        <v>28.86461639404297</v>
       </c>
       <c r="C476" t="n">
-        <v>29.66841972212301</v>
+        <v>29.66841776165989</v>
       </c>
       <c r="D476" t="n">
-        <v>28.76527316163</v>
+        <v>28.765271260846</v>
       </c>
       <c r="E476" t="n">
-        <v>28.95493519684514</v>
+        <v>28.95493328352844</v>
       </c>
       <c r="F476" t="n">
         <v>571800</v>
@@ -9952,16 +9952,16 @@
         <v>44454</v>
       </c>
       <c r="B477" t="n">
-        <v>28.49432754516602</v>
+        <v>28.49432373046875</v>
       </c>
       <c r="C477" t="n">
-        <v>28.98202844322661</v>
+        <v>28.98202456323806</v>
       </c>
       <c r="D477" t="n">
-        <v>27.88018816176107</v>
+        <v>27.88018442928212</v>
       </c>
       <c r="E477" t="n">
-        <v>28.8646182021593</v>
+        <v>28.86461433788912</v>
       </c>
       <c r="F477" t="n">
         <v>994400</v>
@@ -9972,16 +9972,16 @@
         <v>44455</v>
       </c>
       <c r="B478" t="n">
-        <v>28.33175849914551</v>
+        <v>28.33176040649414</v>
       </c>
       <c r="C478" t="n">
-        <v>28.72011076042508</v>
+        <v>28.72011269391833</v>
       </c>
       <c r="D478" t="n">
-        <v>28.04274964133375</v>
+        <v>28.04275152922575</v>
       </c>
       <c r="E478" t="n">
-        <v>28.32272681084341</v>
+        <v>28.32272871758402</v>
       </c>
       <c r="F478" t="n">
         <v>1323100</v>
@@ -10032,16 +10032,16 @@
         <v>44460</v>
       </c>
       <c r="B481" t="n">
-        <v>27.74471473693848</v>
+        <v>27.74471282958984</v>
       </c>
       <c r="C481" t="n">
-        <v>27.93437677283647</v>
+        <v>27.93437485244926</v>
       </c>
       <c r="D481" t="n">
-        <v>26.88672489846451</v>
+        <v>26.88672305009957</v>
       </c>
       <c r="E481" t="n">
-        <v>27.0944485908996</v>
+        <v>27.09444672825441</v>
       </c>
       <c r="F481" t="n">
         <v>916200</v>
@@ -10052,16 +10052,16 @@
         <v>44461</v>
       </c>
       <c r="B482" t="n">
-        <v>28.44916725158691</v>
+        <v>28.44916915893555</v>
       </c>
       <c r="C482" t="n">
-        <v>29.03621493804773</v>
+        <v>29.03621688475444</v>
       </c>
       <c r="D482" t="n">
-        <v>27.74471106140499</v>
+        <v>27.74471292152399</v>
       </c>
       <c r="E482" t="n">
-        <v>28.0788766410424</v>
+        <v>28.07887852356523</v>
       </c>
       <c r="F482" t="n">
         <v>1369400</v>
@@ -10072,16 +10072,16 @@
         <v>44462</v>
       </c>
       <c r="B483" t="n">
-        <v>28.70205116271973</v>
+        <v>28.70205307006836</v>
       </c>
       <c r="C483" t="n">
-        <v>29.22587706344037</v>
+        <v>29.22587900559901</v>
       </c>
       <c r="D483" t="n">
-        <v>27.99759492825326</v>
+        <v>27.99759678878839</v>
       </c>
       <c r="E483" t="n">
-        <v>27.99759492825326</v>
+        <v>27.99759678878839</v>
       </c>
       <c r="F483" t="n">
         <v>1197400</v>
@@ -10092,16 +10092,16 @@
         <v>44463</v>
       </c>
       <c r="B484" t="n">
-        <v>28.67495918273926</v>
+        <v>28.67495727539062</v>
       </c>
       <c r="C484" t="n">
-        <v>29.00912309673777</v>
+        <v>29.00912116716183</v>
       </c>
       <c r="D484" t="n">
-        <v>28.35885692596485</v>
+        <v>28.35885503964213</v>
       </c>
       <c r="E484" t="n">
-        <v>28.37692030580766</v>
+        <v>28.37691841828343</v>
       </c>
       <c r="F484" t="n">
         <v>879100</v>
@@ -10152,16 +10152,16 @@
         <v>44468</v>
       </c>
       <c r="B487" t="n">
-        <v>27.09444808959961</v>
+        <v>27.09444618225098</v>
       </c>
       <c r="C487" t="n">
-        <v>27.86212446332866</v>
+        <v>27.86212250193845</v>
       </c>
       <c r="D487" t="n">
-        <v>27.09444808959961</v>
+        <v>27.09444618225098</v>
       </c>
       <c r="E487" t="n">
-        <v>27.61827401709379</v>
+        <v>27.61827207286975</v>
       </c>
       <c r="F487" t="n">
         <v>1039400</v>
@@ -10172,16 +10172,16 @@
         <v>44469</v>
       </c>
       <c r="B488" t="n">
-        <v>26.66093826293945</v>
+        <v>26.66093635559082</v>
       </c>
       <c r="C488" t="n">
-        <v>28.17822768446557</v>
+        <v>28.17822566856862</v>
       </c>
       <c r="D488" t="n">
-        <v>26.43515118765566</v>
+        <v>26.43514929646004</v>
       </c>
       <c r="E488" t="n">
-        <v>27.29314104016288</v>
+        <v>27.29313908758587</v>
       </c>
       <c r="F488" t="n">
         <v>941700</v>
@@ -10192,16 +10192,16 @@
         <v>44470</v>
       </c>
       <c r="B489" t="n">
-        <v>27.0131664276123</v>
+        <v>27.01316261291504</v>
       </c>
       <c r="C489" t="n">
-        <v>27.11251329520591</v>
+        <v>27.11250946647926</v>
       </c>
       <c r="D489" t="n">
-        <v>26.20033327468103</v>
+        <v>26.20032957476899</v>
       </c>
       <c r="E489" t="n">
-        <v>26.48030877480452</v>
+        <v>26.48030503535539</v>
       </c>
       <c r="F489" t="n">
         <v>1027100</v>
@@ -10212,16 +10212,16 @@
         <v>44473</v>
       </c>
       <c r="B490" t="n">
-        <v>25.51393699645996</v>
+        <v>25.51393890380859</v>
       </c>
       <c r="C490" t="n">
-        <v>26.79640752677968</v>
+        <v>26.79640953000213</v>
       </c>
       <c r="D490" t="n">
-        <v>25.15267805607803</v>
+        <v>25.15267993641999</v>
       </c>
       <c r="E490" t="n">
-        <v>26.49836868563728</v>
+        <v>26.49837066657919</v>
       </c>
       <c r="F490" t="n">
         <v>1176600</v>
@@ -10292,16 +10292,16 @@
         <v>44477</v>
       </c>
       <c r="B494" t="n">
-        <v>26.56158828735352</v>
+        <v>26.56159210205078</v>
       </c>
       <c r="C494" t="n">
-        <v>26.75125030413805</v>
+        <v>26.75125414607401</v>
       </c>
       <c r="D494" t="n">
-        <v>25.95647892756611</v>
+        <v>25.95648265535935</v>
       </c>
       <c r="E494" t="n">
-        <v>26.04679409162453</v>
+        <v>26.04679783238857</v>
       </c>
       <c r="F494" t="n">
         <v>1400600</v>
@@ -10312,16 +10312,16 @@
         <v>44480</v>
       </c>
       <c r="B495" t="n">
-        <v>26.11001586914062</v>
+        <v>26.11001396179199</v>
       </c>
       <c r="C495" t="n">
-        <v>26.74222033559605</v>
+        <v>26.74221838206459</v>
       </c>
       <c r="D495" t="n">
-        <v>26.01970069927291</v>
+        <v>26.01969879852184</v>
       </c>
       <c r="E495" t="n">
-        <v>26.46224313674427</v>
+        <v>26.46224120366528</v>
       </c>
       <c r="F495" t="n">
         <v>791300</v>
@@ -10332,16 +10332,16 @@
         <v>44482</v>
       </c>
       <c r="B496" t="n">
-        <v>26.9409122467041</v>
+        <v>26.94091415405273</v>
       </c>
       <c r="C496" t="n">
-        <v>27.28410782398261</v>
+        <v>27.28410975562863</v>
       </c>
       <c r="D496" t="n">
-        <v>26.17323588916437</v>
+        <v>26.17323774216346</v>
       </c>
       <c r="E496" t="n">
-        <v>26.37192960677382</v>
+        <v>26.37193147383992</v>
       </c>
       <c r="F496" t="n">
         <v>675900</v>
@@ -10372,16 +10372,16 @@
         <v>44484</v>
       </c>
       <c r="B498" t="n">
-        <v>27.09444808959961</v>
+        <v>27.09444618225098</v>
       </c>
       <c r="C498" t="n">
-        <v>27.27507843257772</v>
+        <v>27.27507651251338</v>
       </c>
       <c r="D498" t="n">
-        <v>26.65190564418372</v>
+        <v>26.65190376798843</v>
       </c>
       <c r="E498" t="n">
-        <v>26.72415743685124</v>
+        <v>26.72415555556969</v>
       </c>
       <c r="F498" t="n">
         <v>489400</v>
@@ -10392,16 +10392,16 @@
         <v>44487</v>
       </c>
       <c r="B499" t="n">
-        <v>27.25701332092285</v>
+        <v>27.25701141357422</v>
       </c>
       <c r="C499" t="n">
-        <v>27.88018606969936</v>
+        <v>27.88018411874332</v>
       </c>
       <c r="D499" t="n">
-        <v>26.88672269171528</v>
+        <v>26.88672081027827</v>
       </c>
       <c r="E499" t="n">
-        <v>27.02219457902709</v>
+        <v>27.02219268811023</v>
       </c>
       <c r="F499" t="n">
         <v>764500</v>
@@ -10472,16 +10472,16 @@
         <v>44491</v>
       </c>
       <c r="B503" t="n">
-        <v>24.23147010803223</v>
+        <v>24.23146629333496</v>
       </c>
       <c r="C503" t="n">
-        <v>24.63788755368136</v>
+        <v>24.63788367500285</v>
       </c>
       <c r="D503" t="n">
-        <v>22.69611722737858</v>
+        <v>22.69611365438791</v>
       </c>
       <c r="E503" t="n">
-        <v>24.03277809161419</v>
+        <v>24.03277430819649</v>
       </c>
       <c r="F503" t="n">
         <v>2336000</v>
@@ -10552,16 +10552,16 @@
         <v>44497</v>
       </c>
       <c r="B507" t="n">
-        <v>23.84311676025391</v>
+        <v>23.84311294555664</v>
       </c>
       <c r="C507" t="n">
-        <v>24.59272984274936</v>
+        <v>24.59272590812034</v>
       </c>
       <c r="D507" t="n">
-        <v>23.662488118789</v>
+        <v>23.66248433299079</v>
       </c>
       <c r="E507" t="n">
-        <v>24.27662756691226</v>
+        <v>24.27662368285693</v>
       </c>
       <c r="F507" t="n">
         <v>604100</v>
@@ -10572,16 +10572,16 @@
         <v>44498</v>
       </c>
       <c r="B508" t="n">
-        <v>23.42766380310059</v>
+        <v>23.42766761779785</v>
       </c>
       <c r="C508" t="n">
-        <v>24.20437005098992</v>
+        <v>24.20437399215729</v>
       </c>
       <c r="D508" t="n">
-        <v>23.42766380310059</v>
+        <v>23.42766761779785</v>
       </c>
       <c r="E508" t="n">
-        <v>23.9424579797884</v>
+        <v>23.94246187830896</v>
       </c>
       <c r="F508" t="n">
         <v>1297100</v>
@@ -10592,16 +10592,16 @@
         <v>44501</v>
       </c>
       <c r="B509" t="n">
-        <v>23.82505035400391</v>
+        <v>23.82504844665527</v>
       </c>
       <c r="C509" t="n">
-        <v>24.26759451755265</v>
+        <v>24.2675925747755</v>
       </c>
       <c r="D509" t="n">
-        <v>23.49991815160502</v>
+        <v>23.49991627028531</v>
       </c>
       <c r="E509" t="n">
-        <v>23.49991815160502</v>
+        <v>23.49991627028531</v>
       </c>
       <c r="F509" t="n">
         <v>1313700</v>
@@ -10612,16 +10612,16 @@
         <v>44503</v>
       </c>
       <c r="B510" t="n">
-        <v>24.81851196289062</v>
+        <v>24.81851387023926</v>
       </c>
       <c r="C510" t="n">
-        <v>25.09848914337458</v>
+        <v>25.09849107223997</v>
       </c>
       <c r="D510" t="n">
-        <v>23.80698695006507</v>
+        <v>23.80698877967614</v>
       </c>
       <c r="E510" t="n">
-        <v>23.82504860475882</v>
+        <v>23.82505043575795</v>
       </c>
       <c r="F510" t="n">
         <v>1013100</v>
@@ -10632,16 +10632,16 @@
         <v>44504</v>
       </c>
       <c r="B511" t="n">
-        <v>24.56563377380371</v>
+        <v>24.56563186645508</v>
       </c>
       <c r="C511" t="n">
-        <v>25.5500655315538</v>
+        <v>25.55006354777097</v>
       </c>
       <c r="D511" t="n">
-        <v>24.2404998435028</v>
+        <v>24.24049796139853</v>
       </c>
       <c r="E511" t="n">
-        <v>24.83657756730872</v>
+        <v>24.83657563892321</v>
       </c>
       <c r="F511" t="n">
         <v>728800</v>
@@ -10652,16 +10652,16 @@
         <v>44505</v>
       </c>
       <c r="B512" t="n">
-        <v>24.89076614379883</v>
+        <v>24.8907642364502</v>
       </c>
       <c r="C512" t="n">
-        <v>25.38749873195538</v>
+        <v>25.38749678654274</v>
       </c>
       <c r="D512" t="n">
-        <v>24.69207414210739</v>
+        <v>24.69207224998428</v>
       </c>
       <c r="E512" t="n">
-        <v>24.74626255663803</v>
+        <v>24.74626066036253</v>
       </c>
       <c r="F512" t="n">
         <v>791300</v>
@@ -10672,16 +10672,16 @@
         <v>44508</v>
       </c>
       <c r="B513" t="n">
-        <v>24.61078834533691</v>
+        <v>24.61079025268555</v>
       </c>
       <c r="C513" t="n">
-        <v>24.90882718116469</v>
+        <v>24.90882911161149</v>
       </c>
       <c r="D513" t="n">
-        <v>24.24049772272114</v>
+        <v>24.24049960137206</v>
       </c>
       <c r="E513" t="n">
-        <v>24.90882718116469</v>
+        <v>24.90882911161149</v>
       </c>
       <c r="F513" t="n">
         <v>422400</v>
@@ -10692,16 +10692,16 @@
         <v>44509</v>
       </c>
       <c r="B514" t="n">
-        <v>24.9810791015625</v>
+        <v>24.98108100891113</v>
       </c>
       <c r="C514" t="n">
-        <v>25.84810227027411</v>
+        <v>25.84810424382147</v>
       </c>
       <c r="D514" t="n">
-        <v>24.41209649289119</v>
+        <v>24.41209835679702</v>
       </c>
       <c r="E514" t="n">
-        <v>24.49337996878974</v>
+        <v>24.4933818389017</v>
       </c>
       <c r="F514" t="n">
         <v>781000</v>
@@ -10772,16 +10772,16 @@
         <v>44516</v>
       </c>
       <c r="B518" t="n">
-        <v>25.01720428466797</v>
+        <v>25.01720809936523</v>
       </c>
       <c r="C518" t="n">
-        <v>26.50739837815058</v>
+        <v>26.50740242007704</v>
       </c>
       <c r="D518" t="n">
-        <v>25.01720428466797</v>
+        <v>25.01720809936523</v>
       </c>
       <c r="E518" t="n">
-        <v>26.50739837815058</v>
+        <v>26.50740242007704</v>
       </c>
       <c r="F518" t="n">
         <v>810400</v>
@@ -10792,16 +10792,16 @@
         <v>44517</v>
       </c>
       <c r="B519" t="n">
-        <v>24.25856018066406</v>
+        <v>24.2585620880127</v>
       </c>
       <c r="C519" t="n">
-        <v>25.41458872545803</v>
+        <v>25.41459072370033</v>
       </c>
       <c r="D519" t="n">
-        <v>23.90633122613104</v>
+        <v>23.90633310578539</v>
       </c>
       <c r="E519" t="n">
-        <v>25.17976999664215</v>
+        <v>25.17977197642164</v>
       </c>
       <c r="F519" t="n">
         <v>889600</v>
@@ -10812,16 +10812,16 @@
         <v>44518</v>
       </c>
       <c r="B520" t="n">
-        <v>24.33081245422363</v>
+        <v>24.33081436157227</v>
       </c>
       <c r="C520" t="n">
-        <v>24.7372281016975</v>
+        <v>24.737230040906</v>
       </c>
       <c r="D520" t="n">
-        <v>23.79795489015523</v>
+        <v>23.79795675573193</v>
       </c>
       <c r="E520" t="n">
-        <v>24.33081245422363</v>
+        <v>24.33081436157227</v>
       </c>
       <c r="F520" t="n">
         <v>1163500</v>
@@ -10852,16 +10852,16 @@
         <v>44522</v>
       </c>
       <c r="B522" t="n">
-        <v>23.98761558532715</v>
+        <v>23.98761749267578</v>
       </c>
       <c r="C522" t="n">
-        <v>24.5836932564279</v>
+        <v>24.58369521117299</v>
       </c>
       <c r="D522" t="n">
-        <v>23.44572632361233</v>
+        <v>23.44572818787324</v>
       </c>
       <c r="E522" t="n">
-        <v>24.25856107749379</v>
+        <v>24.25856300638636</v>
       </c>
       <c r="F522" t="n">
         <v>888100</v>
@@ -10892,16 +10892,16 @@
         <v>44524</v>
       </c>
       <c r="B524" t="n">
-        <v>23.29219627380371</v>
+        <v>23.29219245910645</v>
       </c>
       <c r="C524" t="n">
-        <v>23.74377043911869</v>
+        <v>23.74376655046452</v>
       </c>
       <c r="D524" t="n">
-        <v>22.94899894349783</v>
+        <v>22.94899518500798</v>
       </c>
       <c r="E524" t="n">
-        <v>23.30122624120552</v>
+        <v>23.30122242502937</v>
       </c>
       <c r="F524" t="n">
         <v>507500</v>
@@ -10992,16 +10992,16 @@
         <v>44531</v>
       </c>
       <c r="B529" t="n">
-        <v>21.94650268554688</v>
+        <v>21.94650077819824</v>
       </c>
       <c r="C529" t="n">
-        <v>22.79546255767922</v>
+        <v>22.79546057654833</v>
       </c>
       <c r="D529" t="n">
-        <v>21.9194093394122</v>
+        <v>21.91940743441823</v>
       </c>
       <c r="E529" t="n">
-        <v>22.30776337844993</v>
+        <v>22.3077614397045</v>
       </c>
       <c r="F529" t="n">
         <v>843300</v>
@@ -11012,16 +11012,16 @@
         <v>44532</v>
       </c>
       <c r="B530" t="n">
-        <v>21.49492645263672</v>
+        <v>21.49492454528809</v>
       </c>
       <c r="C530" t="n">
-        <v>22.25357107779976</v>
+        <v>22.25356910313292</v>
       </c>
       <c r="D530" t="n">
-        <v>21.17882596100086</v>
+        <v>21.17882408170135</v>
       </c>
       <c r="E530" t="n">
-        <v>22.1632576359715</v>
+        <v>22.16325566931861</v>
       </c>
       <c r="F530" t="n">
         <v>1427300</v>
@@ -11032,16 +11032,16 @@
         <v>44533</v>
       </c>
       <c r="B531" t="n">
-        <v>22.16325759887695</v>
+        <v>22.16325950622559</v>
       </c>
       <c r="C531" t="n">
-        <v>22.4161379917624</v>
+        <v>22.41613992087367</v>
       </c>
       <c r="D531" t="n">
-        <v>21.47686476189643</v>
+        <v>21.47686661017475</v>
       </c>
       <c r="E531" t="n">
-        <v>21.49492641666076</v>
+        <v>21.49492826649345</v>
       </c>
       <c r="F531" t="n">
         <v>1286600</v>
@@ -11072,16 +11072,16 @@
         <v>44537</v>
       </c>
       <c r="B533" t="n">
-        <v>22.57870674133301</v>
+        <v>22.57870483398438</v>
       </c>
       <c r="C533" t="n">
-        <v>23.3825081500865</v>
+        <v>23.38250617483631</v>
       </c>
       <c r="D533" t="n">
-        <v>22.55161167310071</v>
+        <v>22.55160976804094</v>
       </c>
       <c r="E533" t="n">
-        <v>23.03931256557043</v>
+        <v>23.03931061931187</v>
       </c>
       <c r="F533" t="n">
         <v>550100</v>
@@ -11092,16 +11092,16 @@
         <v>44538</v>
       </c>
       <c r="B534" t="n">
-        <v>23.6624870300293</v>
+        <v>23.66248512268066</v>
       </c>
       <c r="C534" t="n">
-        <v>23.6624870300293</v>
+        <v>23.66248512268066</v>
       </c>
       <c r="D534" t="n">
-        <v>22.44323643511145</v>
+        <v>22.44323462604225</v>
       </c>
       <c r="E534" t="n">
-        <v>22.58774003068199</v>
+        <v>22.58773820996488</v>
       </c>
       <c r="F534" t="n">
         <v>822800</v>
@@ -11112,16 +11112,16 @@
         <v>44539</v>
       </c>
       <c r="B535" t="n">
-        <v>23.05737495422363</v>
+        <v>23.057373046875</v>
       </c>
       <c r="C535" t="n">
-        <v>23.53604241410824</v>
+        <v>23.53604046716335</v>
       </c>
       <c r="D535" t="n">
-        <v>22.92190134149848</v>
+        <v>22.92189944535647</v>
       </c>
       <c r="E535" t="n">
-        <v>23.42766559107037</v>
+        <v>23.4276636530906</v>
       </c>
       <c r="F535" t="n">
         <v>778000</v>
@@ -11152,16 +11152,16 @@
         <v>44543</v>
       </c>
       <c r="B537" t="n">
-        <v>23.27412986755371</v>
+        <v>23.27413177490234</v>
       </c>
       <c r="C537" t="n">
-        <v>23.57216870900448</v>
+        <v>23.57217064077782</v>
       </c>
       <c r="D537" t="n">
-        <v>23.03027943656167</v>
+        <v>23.03028132392641</v>
       </c>
       <c r="E537" t="n">
-        <v>23.34638165570485</v>
+        <v>23.34638356897462</v>
       </c>
       <c r="F537" t="n">
         <v>776500</v>
@@ -11172,16 +11172,16 @@
         <v>44544</v>
       </c>
       <c r="B538" t="n">
-        <v>22.24453926086426</v>
+        <v>22.24454116821289</v>
       </c>
       <c r="C538" t="n">
-        <v>23.65345168382733</v>
+        <v>23.65345371198256</v>
       </c>
       <c r="D538" t="n">
-        <v>22.1361624422477</v>
+        <v>22.1361643403036</v>
       </c>
       <c r="E538" t="n">
-        <v>23.17478252085185</v>
+        <v>23.1747845079638</v>
       </c>
       <c r="F538" t="n">
         <v>633600</v>
@@ -11192,16 +11192,16 @@
         <v>44545</v>
       </c>
       <c r="B539" t="n">
-        <v>22.62386322021484</v>
+        <v>22.62386512756348</v>
       </c>
       <c r="C539" t="n">
-        <v>22.62386322021484</v>
+        <v>22.62386512756348</v>
       </c>
       <c r="D539" t="n">
-        <v>21.33236265562784</v>
+        <v>21.33236445409401</v>
       </c>
       <c r="E539" t="n">
-        <v>22.20841584754041</v>
+        <v>22.20841771986395</v>
       </c>
       <c r="F539" t="n">
         <v>1877300</v>
@@ -11212,16 +11212,16 @@
         <v>44546</v>
       </c>
       <c r="B540" t="n">
-        <v>22.36195182800293</v>
+        <v>22.36195373535156</v>
       </c>
       <c r="C540" t="n">
-        <v>23.04834473391666</v>
+        <v>23.04834669981074</v>
       </c>
       <c r="D540" t="n">
-        <v>21.83812588962385</v>
+        <v>21.83812775229308</v>
       </c>
       <c r="E540" t="n">
-        <v>22.72321079884735</v>
+        <v>22.72321273700934</v>
       </c>
       <c r="F540" t="n">
         <v>1678500</v>
@@ -11232,16 +11232,16 @@
         <v>44547</v>
       </c>
       <c r="B541" t="n">
-        <v>22.94899749755859</v>
+        <v>22.94899940490723</v>
       </c>
       <c r="C541" t="n">
-        <v>23.16575287653851</v>
+        <v>23.16575480190222</v>
       </c>
       <c r="D541" t="n">
-        <v>21.85618891320753</v>
+        <v>21.85619072973011</v>
       </c>
       <c r="E541" t="n">
-        <v>22.21744787817405</v>
+        <v>22.21744972472177</v>
       </c>
       <c r="F541" t="n">
         <v>1206000</v>
@@ -11252,16 +11252,16 @@
         <v>44550</v>
       </c>
       <c r="B542" t="n">
-        <v>22.4974250793457</v>
+        <v>22.49742126464844</v>
       </c>
       <c r="C542" t="n">
-        <v>22.92190418028135</v>
+        <v>22.92190029360877</v>
       </c>
       <c r="D542" t="n">
-        <v>22.4342049709743</v>
+        <v>22.43420116699673</v>
       </c>
       <c r="E542" t="n">
-        <v>22.578708568</v>
+        <v>22.57870473952019</v>
       </c>
       <c r="F542" t="n">
         <v>959700</v>
@@ -11272,16 +11272,16 @@
         <v>44551</v>
       </c>
       <c r="B543" t="n">
-        <v>22.4432315826416</v>
+        <v>22.44323348999023</v>
       </c>
       <c r="C543" t="n">
-        <v>22.65998692913256</v>
+        <v>22.65998885490225</v>
       </c>
       <c r="D543" t="n">
-        <v>21.81102719674586</v>
+        <v>21.81102905036631</v>
       </c>
       <c r="E543" t="n">
-        <v>22.47935661241424</v>
+        <v>22.47935852283298</v>
       </c>
       <c r="F543" t="n">
         <v>1333600</v>
@@ -11292,16 +11292,16 @@
         <v>44552</v>
       </c>
       <c r="B544" t="n">
-        <v>22.25357437133789</v>
+        <v>22.25357246398926</v>
       </c>
       <c r="C544" t="n">
-        <v>22.67805519027536</v>
+        <v>22.67805324654457</v>
       </c>
       <c r="D544" t="n">
-        <v>21.81103189493273</v>
+        <v>21.81103002551431</v>
       </c>
       <c r="E544" t="n">
-        <v>22.54258156224585</v>
+        <v>22.54257963012648</v>
       </c>
       <c r="F544" t="n">
         <v>962700</v>
@@ -11432,16 +11432,16 @@
         <v>44565</v>
       </c>
       <c r="B551" t="n">
-        <v>21.21632194519043</v>
+        <v>21.21632385253906</v>
       </c>
       <c r="C551" t="n">
-        <v>22.4675651411926</v>
+        <v>22.46756716102808</v>
       </c>
       <c r="D551" t="n">
-        <v>21.1615234944346</v>
+        <v>21.16152539685685</v>
       </c>
       <c r="E551" t="n">
-        <v>22.36709986313081</v>
+        <v>22.36710187393444</v>
       </c>
       <c r="F551" t="n">
         <v>946700</v>
@@ -11452,16 +11452,16 @@
         <v>44566</v>
       </c>
       <c r="B552" t="n">
-        <v>19.98334693908691</v>
+        <v>19.98334503173828</v>
       </c>
       <c r="C552" t="n">
-        <v>21.30765541345454</v>
+        <v>21.30765337970476</v>
       </c>
       <c r="D552" t="n">
-        <v>19.80981820868898</v>
+        <v>19.80981631790313</v>
       </c>
       <c r="E552" t="n">
-        <v>21.29852204732653</v>
+        <v>21.2985200144485</v>
       </c>
       <c r="F552" t="n">
         <v>2108400</v>
@@ -11532,16 +11532,16 @@
         <v>44572</v>
       </c>
       <c r="B556" t="n">
-        <v>19.97421455383301</v>
+        <v>19.97421646118164</v>
       </c>
       <c r="C556" t="n">
-        <v>19.99247954338157</v>
+        <v>19.99248145247434</v>
       </c>
       <c r="D556" t="n">
-        <v>19.57235516957082</v>
+        <v>19.57235703854568</v>
       </c>
       <c r="E556" t="n">
-        <v>19.64542035379927</v>
+        <v>19.64542222975117</v>
       </c>
       <c r="F556" t="n">
         <v>839400</v>
@@ -11712,16 +11712,16 @@
         <v>44585</v>
       </c>
       <c r="B565" t="n">
-        <v>20.83273124694824</v>
+        <v>20.83272933959961</v>
       </c>
       <c r="C565" t="n">
-        <v>21.21632392200261</v>
+        <v>21.216321979534</v>
       </c>
       <c r="D565" t="n">
-        <v>20.65920251305118</v>
+        <v>20.65920062159004</v>
       </c>
       <c r="E565" t="n">
-        <v>21.21632392200261</v>
+        <v>21.216321979534</v>
       </c>
       <c r="F565" t="n">
         <v>531300</v>
@@ -11752,16 +11752,16 @@
         <v>44587</v>
       </c>
       <c r="B567" t="n">
-        <v>22.85115623474121</v>
+        <v>22.85115814208984</v>
       </c>
       <c r="C567" t="n">
-        <v>23.39914593126476</v>
+        <v>23.3991478843532</v>
       </c>
       <c r="D567" t="n">
-        <v>21.22545387485729</v>
+        <v>21.22545564651121</v>
       </c>
       <c r="E567" t="n">
-        <v>21.39898432285885</v>
+        <v>21.39898610899706</v>
       </c>
       <c r="F567" t="n">
         <v>3079500</v>
@@ -11872,16 +11872,16 @@
         <v>44595</v>
       </c>
       <c r="B573" t="n">
-        <v>23.39001274108887</v>
+        <v>23.3900146484375</v>
       </c>
       <c r="C573" t="n">
-        <v>24.20286305609526</v>
+        <v>24.20286502972813</v>
       </c>
       <c r="D573" t="n">
-        <v>23.22561565670302</v>
+        <v>23.22561755064583</v>
       </c>
       <c r="E573" t="n">
-        <v>23.78273872223032</v>
+        <v>23.78274066160397</v>
       </c>
       <c r="F573" t="n">
         <v>844100</v>
@@ -11972,16 +11972,16 @@
         <v>44602</v>
       </c>
       <c r="B578" t="n">
-        <v>22.45842933654785</v>
+        <v>22.45843124389648</v>
       </c>
       <c r="C578" t="n">
-        <v>23.03381736202015</v>
+        <v>23.03381931823532</v>
       </c>
       <c r="D578" t="n">
-        <v>21.91957302694132</v>
+        <v>21.91957488852598</v>
       </c>
       <c r="E578" t="n">
-        <v>22.60455968403323</v>
+        <v>22.60456160379242</v>
       </c>
       <c r="F578" t="n">
         <v>703500</v>
@@ -12012,16 +12012,16 @@
         <v>44606</v>
       </c>
       <c r="B580" t="n">
-        <v>23.39001274108887</v>
+        <v>23.3900146484375</v>
       </c>
       <c r="C580" t="n">
-        <v>23.55440982547471</v>
+        <v>23.55441174622917</v>
       </c>
       <c r="D580" t="n">
-        <v>22.18443644494101</v>
+        <v>22.18443825398041</v>
       </c>
       <c r="E580" t="n">
-        <v>22.19356806784135</v>
+        <v>22.19356987762539</v>
       </c>
       <c r="F580" t="n">
         <v>1108200</v>
@@ -12052,16 +12052,16 @@
         <v>44608</v>
       </c>
       <c r="B582" t="n">
-        <v>24.4951229095459</v>
+        <v>24.49512481689453</v>
       </c>
       <c r="C582" t="n">
-        <v>24.51338963873094</v>
+        <v>24.51339154750194</v>
       </c>
       <c r="D582" t="n">
-        <v>23.96539995725784</v>
+        <v>23.96540182335882</v>
       </c>
       <c r="E582" t="n">
-        <v>24.29419411454394</v>
+        <v>24.29419600624696</v>
       </c>
       <c r="F582" t="n">
         <v>1381900</v>
@@ -12072,16 +12072,16 @@
         <v>44609</v>
       </c>
       <c r="B583" t="n">
-        <v>23.81013870239258</v>
+        <v>23.81014060974121</v>
       </c>
       <c r="C583" t="n">
-        <v>24.76912117951999</v>
+        <v>24.76912316368943</v>
       </c>
       <c r="D583" t="n">
-        <v>23.62747661770975</v>
+        <v>23.62747851042595</v>
       </c>
       <c r="E583" t="n">
-        <v>24.56819062175412</v>
+        <v>24.5681925898277</v>
       </c>
       <c r="F583" t="n">
         <v>1278800</v>
@@ -12112,16 +12112,16 @@
         <v>44613</v>
       </c>
       <c r="B585" t="n">
-        <v>23.66400909423828</v>
+        <v>23.66400718688965</v>
       </c>
       <c r="C585" t="n">
-        <v>24.31246413191962</v>
+        <v>24.31246217230471</v>
       </c>
       <c r="D585" t="n">
-        <v>23.48134526170543</v>
+        <v>23.48134336907973</v>
       </c>
       <c r="E585" t="n">
-        <v>24.07500184643148</v>
+        <v>24.07499990595632</v>
       </c>
       <c r="F585" t="n">
         <v>913100</v>
@@ -12152,16 +12152,16 @@
         <v>44615</v>
       </c>
       <c r="B587" t="n">
-        <v>24.46772766113281</v>
+        <v>24.46772956848145</v>
       </c>
       <c r="C587" t="n">
-        <v>25.51804033433234</v>
+        <v>25.51804232355668</v>
       </c>
       <c r="D587" t="n">
-        <v>24.08413500964996</v>
+        <v>24.08413688709614</v>
       </c>
       <c r="E587" t="n">
-        <v>24.28506383013664</v>
+        <v>24.28506572324596</v>
       </c>
       <c r="F587" t="n">
         <v>1283000</v>
@@ -12172,16 +12172,16 @@
         <v>44616</v>
       </c>
       <c r="B588" t="n">
-        <v>23.89233779907227</v>
+        <v>23.8923397064209</v>
       </c>
       <c r="C588" t="n">
-        <v>24.30333054757005</v>
+        <v>24.30333248772864</v>
       </c>
       <c r="D588" t="n">
-        <v>22.54063102491948</v>
+        <v>22.54063282436005</v>
       </c>
       <c r="E588" t="n">
-        <v>23.74620743116447</v>
+        <v>23.74620932684737</v>
       </c>
       <c r="F588" t="n">
         <v>1355800</v>
@@ -12252,16 +12252,16 @@
         <v>44624</v>
       </c>
       <c r="B592" t="n">
-        <v>23.80100631713867</v>
+        <v>23.8010082244873</v>
       </c>
       <c r="C592" t="n">
-        <v>23.89233823424741</v>
+        <v>23.89234014891514</v>
       </c>
       <c r="D592" t="n">
-        <v>23.15255301548834</v>
+        <v>23.15255487087166</v>
       </c>
       <c r="E592" t="n">
-        <v>23.52701230782388</v>
+        <v>23.52701419321537</v>
       </c>
       <c r="F592" t="n">
         <v>1181200</v>
@@ -12272,16 +12272,16 @@
         <v>44627</v>
       </c>
       <c r="B593" t="n">
-        <v>21.9287052154541</v>
+        <v>21.92870712280273</v>
       </c>
       <c r="C593" t="n">
-        <v>23.7005377612114</v>
+        <v>23.70053982267321</v>
       </c>
       <c r="D593" t="n">
-        <v>21.9287052154541</v>
+        <v>21.92870712280273</v>
       </c>
       <c r="E593" t="n">
-        <v>23.7005377612114</v>
+        <v>23.70053982267321</v>
       </c>
       <c r="F593" t="n">
         <v>1568800</v>
@@ -12332,16 +12332,16 @@
         <v>44630</v>
       </c>
       <c r="B596" t="n">
-        <v>23.46307945251465</v>
+        <v>23.46307754516602</v>
       </c>
       <c r="C596" t="n">
-        <v>23.88320381384962</v>
+        <v>23.88320187234845</v>
       </c>
       <c r="D596" t="n">
-        <v>23.25301552983581</v>
+        <v>23.25301363956359</v>
       </c>
       <c r="E596" t="n">
-        <v>23.61834318214091</v>
+        <v>23.61834126217066</v>
       </c>
       <c r="F596" t="n">
         <v>1261900</v>
@@ -12372,16 +12372,16 @@
         <v>44634</v>
       </c>
       <c r="B598" t="n">
-        <v>21.80997657775879</v>
+        <v>21.80997848510742</v>
       </c>
       <c r="C598" t="n">
-        <v>22.96075448586829</v>
+        <v>22.96075649385594</v>
       </c>
       <c r="D598" t="n">
-        <v>21.55424931507534</v>
+        <v>21.55425120005985</v>
       </c>
       <c r="E598" t="n">
-        <v>22.58629521521496</v>
+        <v>22.58629719045501</v>
       </c>
       <c r="F598" t="n">
         <v>1776300</v>
@@ -12392,16 +12392,16 @@
         <v>44635</v>
       </c>
       <c r="B599" t="n">
-        <v>21.83737754821777</v>
+        <v>21.83737564086914</v>
       </c>
       <c r="C599" t="n">
-        <v>22.04743973440702</v>
+        <v>22.04743780871086</v>
       </c>
       <c r="D599" t="n">
-        <v>21.1797908924035</v>
+        <v>21.17978904249065</v>
       </c>
       <c r="E599" t="n">
-        <v>22.01090801342303</v>
+        <v>22.01090609091768</v>
       </c>
       <c r="F599" t="n">
         <v>1768200</v>
@@ -12412,16 +12412,16 @@
         <v>44636</v>
       </c>
       <c r="B600" t="n">
-        <v>21.89217567443848</v>
+        <v>21.89217758178711</v>
       </c>
       <c r="C600" t="n">
-        <v>22.5040972344004</v>
+        <v>22.5040991950625</v>
       </c>
       <c r="D600" t="n">
-        <v>21.39898612543066</v>
+        <v>21.39898798981032</v>
       </c>
       <c r="E600" t="n">
-        <v>22.25750333090219</v>
+        <v>22.25750527007987</v>
       </c>
       <c r="F600" t="n">
         <v>1335900</v>
@@ -12452,16 +12452,16 @@
         <v>44638</v>
       </c>
       <c r="B602" t="n">
-        <v>23.75534057617188</v>
+        <v>23.75533866882324</v>
       </c>
       <c r="C602" t="n">
-        <v>24.03846794361094</v>
+        <v>24.03846601352962</v>
       </c>
       <c r="D602" t="n">
-        <v>21.66384687415755</v>
+        <v>21.6638451347378</v>
       </c>
       <c r="E602" t="n">
-        <v>22.43103216955036</v>
+        <v>22.43103036853225</v>
       </c>
       <c r="F602" t="n">
         <v>2359200</v>
@@ -12492,16 +12492,16 @@
         <v>44642</v>
       </c>
       <c r="B604" t="n">
-        <v>23.56354141235352</v>
+        <v>23.56354331970215</v>
       </c>
       <c r="C604" t="n">
-        <v>23.60920823684157</v>
+        <v>23.6092101478867</v>
       </c>
       <c r="D604" t="n">
-        <v>22.90595481782664</v>
+        <v>22.90595667194699</v>
       </c>
       <c r="E604" t="n">
-        <v>22.95161990030346</v>
+        <v>22.95162175812017</v>
       </c>
       <c r="F604" t="n">
         <v>1289700</v>
@@ -12512,16 +12512,16 @@
         <v>44643</v>
       </c>
       <c r="B605" t="n">
-        <v>24.26679801940918</v>
+        <v>24.26679611206055</v>
       </c>
       <c r="C605" t="n">
-        <v>24.36726330447025</v>
+        <v>24.36726138922514</v>
       </c>
       <c r="D605" t="n">
-        <v>23.2347520385518</v>
+        <v>23.23475021232106</v>
       </c>
       <c r="E605" t="n">
-        <v>23.39914914428394</v>
+        <v>23.39914730513173</v>
       </c>
       <c r="F605" t="n">
         <v>1217600</v>
@@ -12532,16 +12532,16 @@
         <v>44644</v>
       </c>
       <c r="B606" t="n">
-        <v>24.77825164794922</v>
+        <v>24.77825355529785</v>
       </c>
       <c r="C606" t="n">
-        <v>24.95178210101803</v>
+        <v>24.95178402172447</v>
       </c>
       <c r="D606" t="n">
-        <v>23.91060286662769</v>
+        <v>23.91060470718757</v>
       </c>
       <c r="E606" t="n">
-        <v>24.20286358210489</v>
+        <v>24.20286544516204</v>
       </c>
       <c r="F606" t="n">
         <v>1668300</v>
@@ -12552,16 +12552,16 @@
         <v>44645</v>
       </c>
       <c r="B607" t="n">
-        <v>25.39017677307129</v>
+        <v>25.39017486572266</v>
       </c>
       <c r="C607" t="n">
-        <v>25.57284061714119</v>
+        <v>25.57283869607057</v>
       </c>
       <c r="D607" t="n">
-        <v>24.75085680284967</v>
+        <v>24.75085494352772</v>
       </c>
       <c r="E607" t="n">
-        <v>24.82392199207533</v>
+        <v>24.82392012726461</v>
       </c>
       <c r="F607" t="n">
         <v>1605600</v>
@@ -12572,16 +12572,16 @@
         <v>44648</v>
       </c>
       <c r="B608" t="n">
-        <v>24.7965202331543</v>
+        <v>24.79652214050293</v>
       </c>
       <c r="C608" t="n">
-        <v>25.39017507362906</v>
+        <v>25.39017702664163</v>
       </c>
       <c r="D608" t="n">
-        <v>24.42206094568508</v>
+        <v>24.42206282423029</v>
       </c>
       <c r="E608" t="n">
-        <v>25.19837961800349</v>
+        <v>25.19838155626315</v>
       </c>
       <c r="F608" t="n">
         <v>555600</v>
@@ -12752,16 +12752,16 @@
         <v>44659</v>
       </c>
       <c r="B617" t="n">
-        <v>24.60472297668457</v>
+        <v>24.6047248840332</v>
       </c>
       <c r="C617" t="n">
-        <v>24.96091550649706</v>
+        <v>24.9609174414576</v>
       </c>
       <c r="D617" t="n">
-        <v>24.07499999352261</v>
+        <v>24.07500185980733</v>
       </c>
       <c r="E617" t="n">
-        <v>24.59558961155973</v>
+        <v>24.59559151820034</v>
       </c>
       <c r="F617" t="n">
         <v>620200</v>
@@ -12812,16 +12812,16 @@
         <v>44664</v>
       </c>
       <c r="B620" t="n">
-        <v>25.16184425354004</v>
+        <v>25.16184234619141</v>
       </c>
       <c r="C620" t="n">
-        <v>25.44497334570492</v>
+        <v>25.44497141689419</v>
       </c>
       <c r="D620" t="n">
-        <v>24.34899392148068</v>
+        <v>24.34899207574871</v>
       </c>
       <c r="E620" t="n">
-        <v>24.93351535199426</v>
+        <v>24.93351346195369</v>
       </c>
       <c r="F620" t="n">
         <v>846300</v>
@@ -12832,16 +12832,16 @@
         <v>44665</v>
       </c>
       <c r="B621" t="n">
-        <v>25.11617851257324</v>
+        <v>25.11618041992188</v>
       </c>
       <c r="C621" t="n">
-        <v>25.18011032461072</v>
+        <v>25.1801122368144</v>
       </c>
       <c r="D621" t="n">
-        <v>24.86044952241209</v>
+        <v>24.8604514103404</v>
       </c>
       <c r="E621" t="n">
-        <v>25.15271197202965</v>
+        <v>25.15271388215267</v>
       </c>
       <c r="F621" t="n">
         <v>718200</v>
@@ -12872,16 +12872,16 @@
         <v>44670</v>
       </c>
       <c r="B623" t="n">
-        <v>25.30797576904297</v>
+        <v>25.30797386169434</v>
       </c>
       <c r="C623" t="n">
-        <v>25.38104269321135</v>
+        <v>25.38104078035599</v>
       </c>
       <c r="D623" t="n">
-        <v>24.78738612842271</v>
+        <v>24.78738426030858</v>
       </c>
       <c r="E623" t="n">
-        <v>24.88785140714289</v>
+        <v>24.88784953145714</v>
       </c>
       <c r="F623" t="n">
         <v>997600</v>
@@ -12892,16 +12892,16 @@
         <v>44671</v>
       </c>
       <c r="B624" t="n">
-        <v>25.07051658630371</v>
+        <v>25.07051277160645</v>
       </c>
       <c r="C624" t="n">
-        <v>25.636771343072</v>
+        <v>25.63676744221414</v>
       </c>
       <c r="D624" t="n">
-        <v>24.93351783810713</v>
+        <v>24.93351404425541</v>
       </c>
       <c r="E624" t="n">
-        <v>25.39017568673188</v>
+        <v>25.3901718233957</v>
       </c>
       <c r="F624" t="n">
         <v>677600</v>
@@ -12912,16 +12912,16 @@
         <v>44673</v>
       </c>
       <c r="B625" t="n">
-        <v>24.12979888916016</v>
+        <v>24.12980079650879</v>
       </c>
       <c r="C625" t="n">
-        <v>25.08877959888303</v>
+        <v>25.08878158203463</v>
       </c>
       <c r="D625" t="n">
-        <v>24.07500043940748</v>
+        <v>24.07500234242454</v>
       </c>
       <c r="E625" t="n">
-        <v>24.75085379306161</v>
+        <v>24.75085574950175</v>
       </c>
       <c r="F625" t="n">
         <v>379300</v>
@@ -12972,16 +12972,16 @@
         <v>44678</v>
       </c>
       <c r="B628" t="n">
-        <v>23.4356803894043</v>
+        <v>23.43567848205566</v>
       </c>
       <c r="C628" t="n">
-        <v>24.20286570585651</v>
+        <v>24.20286373606933</v>
       </c>
       <c r="D628" t="n">
-        <v>23.18908473582792</v>
+        <v>23.18908284854885</v>
       </c>
       <c r="E628" t="n">
-        <v>23.65487594524615</v>
+        <v>23.65487402005796</v>
       </c>
       <c r="F628" t="n">
         <v>920800</v>
@@ -12992,16 +12992,16 @@
         <v>44679</v>
       </c>
       <c r="B629" t="n">
-        <v>23.54528045654297</v>
+        <v>23.54527854919434</v>
       </c>
       <c r="C629" t="n">
-        <v>23.67314410298286</v>
+        <v>23.67314218527628</v>
       </c>
       <c r="D629" t="n">
-        <v>22.99729066292533</v>
+        <v>22.99728879996808</v>
       </c>
       <c r="E629" t="n">
-        <v>23.57267881391635</v>
+        <v>23.57267690434825</v>
       </c>
       <c r="F629" t="n">
         <v>522600</v>
@@ -13052,16 +13052,16 @@
         <v>44684</v>
       </c>
       <c r="B632" t="n">
-        <v>22.24065017700195</v>
+        <v>22.24065208435059</v>
       </c>
       <c r="C632" t="n">
-        <v>22.67997300251017</v>
+        <v>22.67997494753494</v>
       </c>
       <c r="D632" t="n">
-        <v>21.96607493855276</v>
+        <v>21.96607682235394</v>
       </c>
       <c r="E632" t="n">
-        <v>22.67997300251017</v>
+        <v>22.67997494753494</v>
       </c>
       <c r="F632" t="n">
         <v>746900</v>
@@ -13092,16 +13092,16 @@
         <v>44686</v>
       </c>
       <c r="B634" t="n">
-        <v>21.78302192687988</v>
+        <v>21.78302383422852</v>
       </c>
       <c r="C634" t="n">
-        <v>22.58844558977574</v>
+        <v>22.58844756764827</v>
       </c>
       <c r="D634" t="n">
-        <v>21.11488761827097</v>
+        <v>21.11488946711692</v>
       </c>
       <c r="E634" t="n">
-        <v>22.58844558977574</v>
+        <v>22.58844756764827</v>
       </c>
       <c r="F634" t="n">
         <v>1138400</v>
@@ -13152,16 +13152,16 @@
         <v>44691</v>
       </c>
       <c r="B637" t="n">
-        <v>22.14912605285645</v>
+        <v>22.14912796020508</v>
       </c>
       <c r="C637" t="n">
-        <v>22.54268342540766</v>
+        <v>22.54268536664707</v>
       </c>
       <c r="D637" t="n">
-        <v>21.28878763706271</v>
+        <v>21.28878947032421</v>
       </c>
       <c r="E637" t="n">
-        <v>21.28878763706271</v>
+        <v>21.28878947032421</v>
       </c>
       <c r="F637" t="n">
         <v>926300</v>
@@ -13292,16 +13292,16 @@
         <v>44700</v>
       </c>
       <c r="B644" t="n">
-        <v>22.36878776550293</v>
+        <v>22.3687858581543</v>
       </c>
       <c r="C644" t="n">
-        <v>22.81726160534648</v>
+        <v>22.81725965975724</v>
       </c>
       <c r="D644" t="n">
-        <v>22.24980387686078</v>
+        <v>22.2498019796577</v>
       </c>
       <c r="E644" t="n">
-        <v>22.67997398020366</v>
+        <v>22.6799720463207</v>
       </c>
       <c r="F644" t="n">
         <v>678700</v>
@@ -13312,16 +13312,16 @@
         <v>44701</v>
       </c>
       <c r="B645" t="n">
-        <v>21.88370323181152</v>
+        <v>21.88370132446289</v>
       </c>
       <c r="C645" t="n">
-        <v>22.91794029513548</v>
+        <v>22.9179382976444</v>
       </c>
       <c r="D645" t="n">
-        <v>21.58166975448027</v>
+        <v>21.58166787345639</v>
       </c>
       <c r="E645" t="n">
-        <v>22.44200822609626</v>
+        <v>22.44200627008666</v>
       </c>
       <c r="F645" t="n">
         <v>1304200</v>
@@ -13472,16 +13472,16 @@
         <v>44713</v>
       </c>
       <c r="B653" t="n">
-        <v>22.26810646057129</v>
+        <v>22.26810836791992</v>
       </c>
       <c r="C653" t="n">
-        <v>22.68912376800926</v>
+        <v>22.68912571141964</v>
       </c>
       <c r="D653" t="n">
-        <v>22.01183498014354</v>
+        <v>22.01183686554154</v>
       </c>
       <c r="E653" t="n">
-        <v>22.51522520108663</v>
+        <v>22.51522712960193</v>
       </c>
       <c r="F653" t="n">
         <v>797200</v>
@@ -13492,16 +13492,16 @@
         <v>44714</v>
       </c>
       <c r="B654" t="n">
-        <v>22.36878776550293</v>
+        <v>22.3687858581543</v>
       </c>
       <c r="C654" t="n">
-        <v>22.44200794862623</v>
+        <v>22.44200603503423</v>
       </c>
       <c r="D654" t="n">
-        <v>20.9867552815572</v>
+        <v>20.98675349205213</v>
       </c>
       <c r="E654" t="n">
-        <v>22.42370246641869</v>
+        <v>22.42370055438757</v>
       </c>
       <c r="F654" t="n">
         <v>2038900</v>
@@ -13532,16 +13532,16 @@
         <v>44718</v>
       </c>
       <c r="B656" t="n">
-        <v>21.46268463134766</v>
+        <v>21.46268653869629</v>
       </c>
       <c r="C656" t="n">
-        <v>22.21319184990723</v>
+        <v>22.21319382395204</v>
       </c>
       <c r="D656" t="n">
-        <v>21.46268463134766</v>
+        <v>21.46268653869629</v>
       </c>
       <c r="E656" t="n">
-        <v>22.15827541022728</v>
+        <v>22.15827737939176</v>
       </c>
       <c r="F656" t="n">
         <v>540400</v>
@@ -13572,16 +13572,16 @@
         <v>44720</v>
       </c>
       <c r="B658" t="n">
-        <v>20.49251556396484</v>
+        <v>20.49251747131348</v>
       </c>
       <c r="C658" t="n">
-        <v>20.97760031680394</v>
+        <v>20.97760226930202</v>
       </c>
       <c r="D658" t="n">
-        <v>20.32776973297396</v>
+        <v>20.32777162498881</v>
       </c>
       <c r="E658" t="n">
-        <v>20.67556687522287</v>
+        <v>20.67556879960907</v>
       </c>
       <c r="F658" t="n">
         <v>661500</v>
@@ -13652,16 +13652,16 @@
         <v>44726</v>
       </c>
       <c r="B662" t="n">
-        <v>19.33014678955078</v>
+        <v>19.33014869689941</v>
       </c>
       <c r="C662" t="n">
-        <v>19.48573989080163</v>
+        <v>19.48574181350298</v>
       </c>
       <c r="D662" t="n">
-        <v>18.79930004629027</v>
+        <v>18.79930190125907</v>
       </c>
       <c r="E662" t="n">
-        <v>19.24777386855287</v>
+        <v>19.24777576777359</v>
       </c>
       <c r="F662" t="n">
         <v>1068100</v>
@@ -13692,16 +13692,16 @@
         <v>44729</v>
       </c>
       <c r="B664" t="n">
-        <v>20.7396354675293</v>
+        <v>20.73963737487793</v>
       </c>
       <c r="C664" t="n">
-        <v>20.78539742504355</v>
+        <v>20.78539933660075</v>
       </c>
       <c r="D664" t="n">
-        <v>20.0806538525074</v>
+        <v>20.0806556992519</v>
       </c>
       <c r="E664" t="n">
-        <v>20.72132998624088</v>
+        <v>20.72133189190603</v>
       </c>
       <c r="F664" t="n">
         <v>928600</v>
@@ -13792,16 +13792,16 @@
         <v>44736</v>
       </c>
       <c r="B669" t="n">
-        <v>20.76709175109863</v>
+        <v>20.76709365844727</v>
       </c>
       <c r="C669" t="n">
-        <v>21.14234535395173</v>
+        <v>21.14234729576544</v>
       </c>
       <c r="D669" t="n">
-        <v>20.37353266866573</v>
+        <v>20.37353453986802</v>
       </c>
       <c r="E669" t="n">
-        <v>21.14234535395173</v>
+        <v>21.14234729576544</v>
       </c>
       <c r="F669" t="n">
         <v>1555200</v>
@@ -13872,16 +13872,16 @@
         <v>44742</v>
       </c>
       <c r="B673" t="n">
-        <v>20.11726379394531</v>
+        <v>20.11726188659668</v>
       </c>
       <c r="C673" t="n">
-        <v>20.37353530409296</v>
+        <v>20.37353337244683</v>
       </c>
       <c r="D673" t="n">
-        <v>19.56811155546141</v>
+        <v>19.56810970017874</v>
       </c>
       <c r="E673" t="n">
-        <v>19.90675598866698</v>
+        <v>19.90675410127692</v>
       </c>
       <c r="F673" t="n">
         <v>505800</v>
@@ -13952,16 +13952,16 @@
         <v>44748</v>
       </c>
       <c r="B677" t="n">
-        <v>20.34607887268066</v>
+        <v>20.34607696533203</v>
       </c>
       <c r="C677" t="n">
-        <v>20.61150314717327</v>
+        <v>20.61150121494236</v>
       </c>
       <c r="D677" t="n">
-        <v>19.92506322505281</v>
+        <v>19.9250613571724</v>
       </c>
       <c r="E677" t="n">
-        <v>20.0165888971436</v>
+        <v>20.0165870206831</v>
       </c>
       <c r="F677" t="n">
         <v>946100</v>
@@ -13972,16 +13972,16 @@
         <v>44749</v>
       </c>
       <c r="B678" t="n">
-        <v>21.05082321166992</v>
+        <v>21.05082130432129</v>
       </c>
       <c r="C678" t="n">
-        <v>21.40777139445899</v>
+        <v>21.4077694547684</v>
       </c>
       <c r="D678" t="n">
-        <v>20.35523058301687</v>
+        <v>20.35522873869369</v>
       </c>
       <c r="E678" t="n">
-        <v>20.55658565484792</v>
+        <v>20.55658379228059</v>
       </c>
       <c r="F678" t="n">
         <v>2985600</v>
@@ -13992,16 +13992,16 @@
         <v>44750</v>
       </c>
       <c r="B679" t="n">
-        <v>20.74878883361816</v>
+        <v>20.74878692626953</v>
       </c>
       <c r="C679" t="n">
-        <v>21.21556814630249</v>
+        <v>21.2155661960448</v>
       </c>
       <c r="D679" t="n">
-        <v>20.45590810700216</v>
+        <v>20.45590622657681</v>
       </c>
       <c r="E679" t="n">
-        <v>20.97760211950028</v>
+        <v>20.9776001911178</v>
       </c>
       <c r="F679" t="n">
         <v>771800</v>
@@ -14112,16 +14112,16 @@
         <v>44760</v>
       </c>
       <c r="B685" t="n">
-        <v>18.96404266357422</v>
+        <v>18.96404457092285</v>
       </c>
       <c r="C685" t="n">
-        <v>19.6596351945813</v>
+        <v>19.65963717189063</v>
       </c>
       <c r="D685" t="n">
-        <v>18.9274334491563</v>
+        <v>18.92743535282288</v>
       </c>
       <c r="E685" t="n">
-        <v>19.65048245455016</v>
+        <v>19.65048443093892</v>
       </c>
       <c r="F685" t="n">
         <v>720800</v>
@@ -14132,16 +14132,16 @@
         <v>44761</v>
       </c>
       <c r="B686" t="n">
-        <v>19.31184196472168</v>
+        <v>19.31184005737305</v>
       </c>
       <c r="C686" t="n">
-        <v>19.44912958915078</v>
+        <v>19.44912766824283</v>
       </c>
       <c r="D686" t="n">
-        <v>18.79930068552315</v>
+        <v>18.79929882879605</v>
       </c>
       <c r="E686" t="n">
-        <v>19.11963789395545</v>
+        <v>19.11963600558999</v>
       </c>
       <c r="F686" t="n">
         <v>670300</v>
@@ -14172,16 +14172,16 @@
         <v>44763</v>
       </c>
       <c r="B688" t="n">
-        <v>19.54980850219727</v>
+        <v>19.54980659484863</v>
       </c>
       <c r="C688" t="n">
-        <v>20.33692505067233</v>
+        <v>20.33692306652982</v>
       </c>
       <c r="D688" t="n">
-        <v>19.54980850219727</v>
+        <v>19.54980659484863</v>
       </c>
       <c r="E688" t="n">
-        <v>20.04404431210423</v>
+        <v>20.0440423565362</v>
       </c>
       <c r="F688" t="n">
         <v>451400</v>
@@ -14332,16 +14332,16 @@
         <v>44775</v>
       </c>
       <c r="B696" t="n">
-        <v>20.66641616821289</v>
+        <v>20.66641426086426</v>
       </c>
       <c r="C696" t="n">
-        <v>20.99590786260945</v>
+        <v>20.99590592485131</v>
       </c>
       <c r="D696" t="n">
-        <v>20.47421384361947</v>
+        <v>20.47421195400961</v>
       </c>
       <c r="E696" t="n">
-        <v>20.63895794511089</v>
+        <v>20.63895604029644</v>
       </c>
       <c r="F696" t="n">
         <v>609000</v>
@@ -14412,16 +14412,16 @@
         <v>44781</v>
       </c>
       <c r="B700" t="n">
-        <v>21.92031478881836</v>
+        <v>21.92031288146973</v>
       </c>
       <c r="C700" t="n">
-        <v>22.46031431525638</v>
+        <v>22.46031236092086</v>
       </c>
       <c r="D700" t="n">
-        <v>21.77387441680537</v>
+        <v>21.77387252219892</v>
       </c>
       <c r="E700" t="n">
-        <v>21.98438223336068</v>
+        <v>21.98438032043736</v>
       </c>
       <c r="F700" t="n">
         <v>957700</v>
@@ -14432,16 +14432,16 @@
         <v>44782</v>
       </c>
       <c r="B701" t="n">
-        <v>20.68472099304199</v>
+        <v>20.68471908569336</v>
       </c>
       <c r="C701" t="n">
-        <v>22.19488830153054</v>
+        <v>22.19488625492862</v>
       </c>
       <c r="D701" t="n">
-        <v>20.593195331317</v>
+        <v>20.593193432408</v>
       </c>
       <c r="E701" t="n">
-        <v>22.11251538054873</v>
+        <v>22.11251334154245</v>
       </c>
       <c r="F701" t="n">
         <v>1171700</v>
@@ -14612,16 +14612,16 @@
         <v>44795</v>
       </c>
       <c r="B710" t="n">
-        <v>21.88370323181152</v>
+        <v>21.88370132446289</v>
       </c>
       <c r="C710" t="n">
-        <v>21.98438163949091</v>
+        <v>21.9843797233673</v>
       </c>
       <c r="D710" t="n">
-        <v>21.26133079471514</v>
+        <v>21.2613289416115</v>
       </c>
       <c r="E710" t="n">
-        <v>21.85624500816072</v>
+        <v>21.8562431032053</v>
       </c>
       <c r="F710" t="n">
         <v>729800</v>
@@ -14672,16 +14672,16 @@
         <v>44798</v>
       </c>
       <c r="B713" t="n">
-        <v>23.51285362243652</v>
+        <v>23.51285171508789</v>
       </c>
       <c r="C713" t="n">
-        <v>23.63183576235873</v>
+        <v>23.63183384535833</v>
       </c>
       <c r="D713" t="n">
-        <v>23.09183627085918</v>
+        <v>23.09183439766322</v>
       </c>
       <c r="E713" t="n">
-        <v>23.17420919300025</v>
+        <v>23.17420731312225</v>
       </c>
       <c r="F713" t="n">
         <v>764100</v>
@@ -14692,16 +14692,16 @@
         <v>44799</v>
       </c>
       <c r="B714" t="n">
-        <v>23.35725975036621</v>
+        <v>23.35725784301758</v>
       </c>
       <c r="C714" t="n">
-        <v>23.78742808295239</v>
+        <v>23.7874261404763</v>
       </c>
       <c r="D714" t="n">
-        <v>23.30234330694152</v>
+        <v>23.30234140407735</v>
       </c>
       <c r="E714" t="n">
-        <v>23.52200558922676</v>
+        <v>23.52200366842502</v>
       </c>
       <c r="F714" t="n">
         <v>901600</v>
@@ -14712,16 +14712,16 @@
         <v>44802</v>
       </c>
       <c r="B715" t="n">
-        <v>23.51285362243652</v>
+        <v>23.51285171508789</v>
       </c>
       <c r="C715" t="n">
-        <v>23.7691233840249</v>
+        <v>23.76912145588782</v>
       </c>
       <c r="D715" t="n">
-        <v>23.0094633487181</v>
+        <v>23.00946148220419</v>
       </c>
       <c r="E715" t="n">
-        <v>23.26573485601331</v>
+        <v>23.2657329687108</v>
       </c>
       <c r="F715" t="n">
         <v>465300</v>
@@ -14792,16 +14792,16 @@
         <v>44806</v>
       </c>
       <c r="B719" t="n">
-        <v>23.54945945739746</v>
+        <v>23.54946136474609</v>
       </c>
       <c r="C719" t="n">
-        <v>24.64776376437191</v>
+        <v>24.64776576067584</v>
       </c>
       <c r="D719" t="n">
-        <v>23.54030671784024</v>
+        <v>23.54030862444757</v>
       </c>
       <c r="E719" t="n">
-        <v>24.37318681477501</v>
+        <v>24.37318878884005</v>
       </c>
       <c r="F719" t="n">
         <v>919400</v>
@@ -15112,16 +15112,16 @@
         <v>44831</v>
       </c>
       <c r="B735" t="n">
-        <v>23.96132850646973</v>
+        <v>23.96132659912109</v>
       </c>
       <c r="C735" t="n">
-        <v>24.29082020954882</v>
+        <v>24.29081827597227</v>
       </c>
       <c r="D735" t="n">
-        <v>23.77827717237981</v>
+        <v>23.77827527960227</v>
       </c>
       <c r="E735" t="n">
-        <v>24.16268357740312</v>
+        <v>24.16268165402639</v>
       </c>
       <c r="F735" t="n">
         <v>505800</v>
@@ -15132,16 +15132,16 @@
         <v>44832</v>
       </c>
       <c r="B736" t="n">
-        <v>24.09861373901367</v>
+        <v>24.0986156463623</v>
       </c>
       <c r="C736" t="n">
-        <v>24.33657975139627</v>
+        <v>24.33658167757936</v>
       </c>
       <c r="D736" t="n">
-        <v>23.43047940369333</v>
+        <v>23.4304812581607</v>
       </c>
       <c r="E736" t="n">
-        <v>23.43963214405882</v>
+        <v>23.43963399925061</v>
       </c>
       <c r="F736" t="n">
         <v>632500</v>
@@ -15192,16 +15192,16 @@
         <v>44837</v>
       </c>
       <c r="B739" t="n">
-        <v>25.62708473205566</v>
+        <v>25.6270866394043</v>
       </c>
       <c r="C739" t="n">
-        <v>26.03894929210349</v>
+        <v>26.03895123010599</v>
       </c>
       <c r="D739" t="n">
-        <v>24.85827205043747</v>
+        <v>24.85827390056563</v>
       </c>
       <c r="E739" t="n">
-        <v>25.04132335394908</v>
+        <v>25.04132521770121</v>
       </c>
       <c r="F739" t="n">
         <v>1595500</v>
@@ -15392,16 +15392,16 @@
         <v>44852</v>
       </c>
       <c r="B749" t="n">
-        <v>23.9796314239502</v>
+        <v>23.97963333129883</v>
       </c>
       <c r="C749" t="n">
-        <v>24.67522222938887</v>
+        <v>24.67522419206505</v>
       </c>
       <c r="D749" t="n">
-        <v>23.20166595584636</v>
+        <v>23.20166780131533</v>
       </c>
       <c r="E749" t="n">
-        <v>24.39149426303572</v>
+        <v>24.39149620314408</v>
       </c>
       <c r="F749" t="n">
         <v>1982200</v>
@@ -15432,16 +15432,16 @@
         <v>44854</v>
       </c>
       <c r="B751" t="n">
-        <v>23.00946044921875</v>
+        <v>23.00946235656738</v>
       </c>
       <c r="C751" t="n">
-        <v>23.89725699915234</v>
+        <v>23.89725898009408</v>
       </c>
       <c r="D751" t="n">
-        <v>22.57013941696457</v>
+        <v>22.57014128789607</v>
       </c>
       <c r="E751" t="n">
-        <v>23.89725699915234</v>
+        <v>23.89725898009408</v>
       </c>
       <c r="F751" t="n">
         <v>4181800</v>
@@ -15492,16 +15492,16 @@
         <v>44859</v>
       </c>
       <c r="B754" t="n">
-        <v>23.07353210449219</v>
+        <v>23.07353019714355</v>
       </c>
       <c r="C754" t="n">
-        <v>23.93387059273025</v>
+        <v>23.93386861426267</v>
       </c>
       <c r="D754" t="n">
-        <v>23.07353210449219</v>
+        <v>23.07353019714355</v>
       </c>
       <c r="E754" t="n">
-        <v>23.80573570463134</v>
+        <v>23.80573373675589</v>
       </c>
       <c r="F754" t="n">
         <v>661700</v>
@@ -15512,16 +15512,16 @@
         <v>44860</v>
       </c>
       <c r="B755" t="n">
-        <v>22.63421058654785</v>
+        <v>22.63420867919922</v>
       </c>
       <c r="C755" t="n">
-        <v>22.94539680553622</v>
+        <v>22.94539487196443</v>
       </c>
       <c r="D755" t="n">
-        <v>22.21319496421469</v>
+        <v>22.21319309234437</v>
       </c>
       <c r="E755" t="n">
-        <v>22.89048210386383</v>
+        <v>22.89048017491961</v>
       </c>
       <c r="F755" t="n">
         <v>1513300</v>
@@ -15532,16 +15532,16 @@
         <v>44861</v>
       </c>
       <c r="B756" t="n">
-        <v>23.43047904968262</v>
+        <v>23.43048095703125</v>
       </c>
       <c r="C756" t="n">
-        <v>23.70505427367191</v>
+        <v>23.70505620337222</v>
       </c>
       <c r="D756" t="n">
-        <v>22.37793836344808</v>
+        <v>22.37794018511507</v>
       </c>
       <c r="E756" t="n">
-        <v>22.63420810698296</v>
+        <v>22.63420994951148</v>
       </c>
       <c r="F756" t="n">
         <v>1190200</v>
@@ -15572,16 +15572,16 @@
         <v>44865</v>
       </c>
       <c r="B758" t="n">
-        <v>24.53793525695801</v>
+        <v>24.53793716430664</v>
       </c>
       <c r="C758" t="n">
-        <v>24.59285170016845</v>
+        <v>24.59285361178577</v>
       </c>
       <c r="D758" t="n">
-        <v>22.82641292815456</v>
+        <v>22.82641470246552</v>
       </c>
       <c r="E758" t="n">
-        <v>23.21997204262896</v>
+        <v>23.21997384753151</v>
       </c>
       <c r="F758" t="n">
         <v>1272100</v>
@@ -15632,16 +15632,16 @@
         <v>44869</v>
       </c>
       <c r="B761" t="n">
-        <v>24.55624198913574</v>
+        <v>24.55624008178711</v>
       </c>
       <c r="C761" t="n">
-        <v>25.22437637087589</v>
+        <v>25.22437441163148</v>
       </c>
       <c r="D761" t="n">
-        <v>24.46471632482865</v>
+        <v>24.46471442458906</v>
       </c>
       <c r="E761" t="n">
-        <v>24.98641034196018</v>
+        <v>24.98640840119923</v>
       </c>
       <c r="F761" t="n">
         <v>1048900</v>
@@ -15652,16 +15652,16 @@
         <v>44872</v>
       </c>
       <c r="B762" t="n">
-        <v>23.43047904968262</v>
+        <v>23.43048095703125</v>
       </c>
       <c r="C762" t="n">
-        <v>24.6111546076846</v>
+        <v>24.61115661114565</v>
       </c>
       <c r="D762" t="n">
-        <v>23.3664116137989</v>
+        <v>23.36641351593214</v>
       </c>
       <c r="E762" t="n">
-        <v>24.50132521637156</v>
+        <v>24.50132721089199</v>
       </c>
       <c r="F762" t="n">
         <v>1285200</v>
@@ -15692,16 +15692,16 @@
         <v>44874</v>
       </c>
       <c r="B764" t="n">
-        <v>23.07353210449219</v>
+        <v>23.07353019714355</v>
       </c>
       <c r="C764" t="n">
-        <v>23.41217655323392</v>
+        <v>23.41217461789161</v>
       </c>
       <c r="D764" t="n">
-        <v>22.93624447499951</v>
+        <v>22.93624257899961</v>
       </c>
       <c r="E764" t="n">
-        <v>23.3389563677907</v>
+        <v>23.33895443850106</v>
       </c>
       <c r="F764" t="n">
         <v>1350700</v>
@@ -15772,16 +15772,16 @@
         <v>44881</v>
       </c>
       <c r="B768" t="n">
-        <v>20.62980651855469</v>
+        <v>20.62980461120605</v>
       </c>
       <c r="C768" t="n">
-        <v>21.42607576909265</v>
+        <v>21.42607378812418</v>
       </c>
       <c r="D768" t="n">
-        <v>20.135568987291</v>
+        <v>20.13556712563758</v>
       </c>
       <c r="E768" t="n">
-        <v>21.2979408887088</v>
+        <v>21.29793891958716</v>
       </c>
       <c r="F768" t="n">
         <v>2155500</v>
@@ -15812,16 +15812,16 @@
         <v>44883</v>
       </c>
       <c r="B770" t="n">
-        <v>20.64810943603516</v>
+        <v>20.64811134338379</v>
       </c>
       <c r="C770" t="n">
-        <v>21.15149968818696</v>
+        <v>21.15150164203577</v>
       </c>
       <c r="D770" t="n">
-        <v>20.30946676681408</v>
+        <v>20.30946864288093</v>
       </c>
       <c r="E770" t="n">
-        <v>20.34607598302677</v>
+        <v>20.34607786247537</v>
       </c>
       <c r="F770" t="n">
         <v>958500</v>
@@ -15852,16 +15852,16 @@
         <v>44887</v>
       </c>
       <c r="B772" t="n">
-        <v>20.59319496154785</v>
+        <v>20.59319305419922</v>
       </c>
       <c r="C772" t="n">
-        <v>21.50844807094998</v>
+        <v>21.5084460788303</v>
       </c>
       <c r="D772" t="n">
-        <v>20.37353442477615</v>
+        <v>20.37353253777255</v>
       </c>
       <c r="E772" t="n">
-        <v>21.30709301533595</v>
+        <v>21.30709104186584</v>
       </c>
       <c r="F772" t="n">
         <v>859200</v>
@@ -15912,16 +15912,16 @@
         <v>44890</v>
       </c>
       <c r="B775" t="n">
-        <v>20.58403968811035</v>
+        <v>20.58404159545898</v>
       </c>
       <c r="C775" t="n">
-        <v>21.2521739567906</v>
+        <v>21.25217592604958</v>
       </c>
       <c r="D775" t="n">
-        <v>19.88844720107233</v>
+        <v>19.8884490439663</v>
       </c>
       <c r="E775" t="n">
-        <v>21.2521739567906</v>
+        <v>21.25217592604958</v>
       </c>
       <c r="F775" t="n">
         <v>1041600</v>
@@ -16072,16 +16072,16 @@
         <v>44902</v>
       </c>
       <c r="B783" t="n">
-        <v>20.38268661499023</v>
+        <v>20.38268852233887</v>
       </c>
       <c r="C783" t="n">
-        <v>20.46505953226877</v>
+        <v>20.4650614473256</v>
       </c>
       <c r="D783" t="n">
-        <v>19.76946697842044</v>
+        <v>19.76946882838588</v>
       </c>
       <c r="E783" t="n">
-        <v>19.76946697842044</v>
+        <v>19.76946882838588</v>
       </c>
       <c r="F783" t="n">
         <v>1435600</v>
@@ -16112,16 +16112,16 @@
         <v>44904</v>
       </c>
       <c r="B785" t="n">
-        <v>19.33014678955078</v>
+        <v>19.33014869689941</v>
       </c>
       <c r="C785" t="n">
-        <v>19.87014452784946</v>
+        <v>19.87014648848087</v>
       </c>
       <c r="D785" t="n">
-        <v>19.19285742408307</v>
+        <v>19.19285931788506</v>
       </c>
       <c r="E785" t="n">
-        <v>19.86099353281129</v>
+        <v>19.86099549253975</v>
       </c>
       <c r="F785" t="n">
         <v>1046400</v>
@@ -16172,16 +16172,16 @@
         <v>44909</v>
       </c>
       <c r="B788" t="n">
-        <v>17.76506042480469</v>
+        <v>17.76506233215332</v>
       </c>
       <c r="C788" t="n">
-        <v>18.03963562396351</v>
+        <v>18.03963756079196</v>
       </c>
       <c r="D788" t="n">
-        <v>17.38980683795791</v>
+        <v>17.38980870501738</v>
       </c>
       <c r="E788" t="n">
-        <v>17.76506042480469</v>
+        <v>17.76506233215332</v>
       </c>
       <c r="F788" t="n">
         <v>1946000</v>
@@ -16212,16 +16212,16 @@
         <v>44911</v>
       </c>
       <c r="B790" t="n">
-        <v>17.71014595031738</v>
+        <v>17.71014785766602</v>
       </c>
       <c r="C790" t="n">
-        <v>17.99387389233942</v>
+        <v>17.99387583024501</v>
       </c>
       <c r="D790" t="n">
-        <v>17.60946756140036</v>
+        <v>17.60946945790612</v>
       </c>
       <c r="E790" t="n">
-        <v>17.82912807255031</v>
+        <v>17.82912999271309</v>
       </c>
       <c r="F790" t="n">
         <v>1904600</v>
@@ -16332,16 +16332,16 @@
         <v>44921</v>
       </c>
       <c r="B796" t="n">
-        <v>19.42167091369629</v>
+        <v>19.42167282104492</v>
       </c>
       <c r="C796" t="n">
-        <v>19.87929748160748</v>
+        <v>19.87929943389835</v>
       </c>
       <c r="D796" t="n">
-        <v>19.42167091369629</v>
+        <v>19.42167282104492</v>
       </c>
       <c r="E796" t="n">
-        <v>19.5589602806351</v>
+        <v>19.55896220146654</v>
       </c>
       <c r="F796" t="n">
         <v>573600</v>
@@ -16352,16 +16352,16 @@
         <v>44922</v>
       </c>
       <c r="B797" t="n">
-        <v>19.06472206115723</v>
+        <v>19.06472015380859</v>
       </c>
       <c r="C797" t="n">
-        <v>19.65048348831267</v>
+        <v>19.65048152236096</v>
       </c>
       <c r="D797" t="n">
-        <v>18.88167074231778</v>
+        <v>18.88166885328269</v>
       </c>
       <c r="E797" t="n">
-        <v>19.48573939620526</v>
+        <v>19.48573744673554</v>
       </c>
       <c r="F797" t="n">
         <v>744400</v>
@@ -16392,16 +16392,16 @@
         <v>44924</v>
       </c>
       <c r="B799" t="n">
-        <v>20.52912712097168</v>
+        <v>20.52912902832031</v>
       </c>
       <c r="C799" t="n">
-        <v>20.82200783092881</v>
+        <v>20.82200976548881</v>
       </c>
       <c r="D799" t="n">
-        <v>19.8701437778614</v>
+        <v>19.8701456239843</v>
       </c>
       <c r="E799" t="n">
-        <v>19.92506022025842</v>
+        <v>19.92506207148356</v>
       </c>
       <c r="F799" t="n">
         <v>1888800</v>
@@ -16512,16 +16512,16 @@
         <v>44935</v>
       </c>
       <c r="B805" t="n">
-        <v>19.29353523254395</v>
+        <v>19.29353713989258</v>
       </c>
       <c r="C805" t="n">
-        <v>19.62302690639088</v>
+        <v>19.62302884631288</v>
       </c>
       <c r="D805" t="n">
-        <v>18.60709540916733</v>
+        <v>18.60709724865488</v>
       </c>
       <c r="E805" t="n">
-        <v>18.62540089009365</v>
+        <v>18.62540273139088</v>
       </c>
       <c r="F805" t="n">
         <v>696300</v>
@@ -16552,16 +16552,16 @@
         <v>44937</v>
       </c>
       <c r="B807" t="n">
-        <v>20.23624801635742</v>
+        <v>20.23624610900879</v>
       </c>
       <c r="C807" t="n">
-        <v>20.69387459839567</v>
+        <v>20.69387264791387</v>
       </c>
       <c r="D807" t="n">
-        <v>19.92506180091486</v>
+        <v>19.9250599228968</v>
       </c>
       <c r="E807" t="n">
-        <v>20.40099386520429</v>
+        <v>20.40099194232769</v>
       </c>
       <c r="F807" t="n">
         <v>717700</v>
@@ -16572,16 +16572,16 @@
         <v>44938</v>
       </c>
       <c r="B808" t="n">
-        <v>19.9433650970459</v>
+        <v>19.94336700439453</v>
       </c>
       <c r="C808" t="n">
-        <v>20.47421180419248</v>
+        <v>20.47421376231036</v>
       </c>
       <c r="D808" t="n">
-        <v>19.61387343546986</v>
+        <v>19.61387531130648</v>
       </c>
       <c r="E808" t="n">
-        <v>20.09895644200494</v>
+        <v>20.09895836423406</v>
       </c>
       <c r="F808" t="n">
         <v>963600</v>
@@ -16612,16 +16612,16 @@
         <v>44942</v>
       </c>
       <c r="B810" t="n">
-        <v>19.15624809265137</v>
+        <v>19.15624618530273</v>
       </c>
       <c r="C810" t="n">
-        <v>19.33014667435583</v>
+        <v>19.33014474969247</v>
       </c>
       <c r="D810" t="n">
-        <v>18.6437068339352</v>
+        <v>18.64370497761926</v>
       </c>
       <c r="E810" t="n">
-        <v>19.03726420938266</v>
+        <v>19.03726231388101</v>
       </c>
       <c r="F810" t="n">
         <v>764800</v>
@@ -16692,16 +16692,16 @@
         <v>44946</v>
       </c>
       <c r="B814" t="n">
-        <v>20.07150268554688</v>
+        <v>20.07150077819824</v>
       </c>
       <c r="C814" t="n">
-        <v>20.33692520221192</v>
+        <v>20.3369232696408</v>
       </c>
       <c r="D814" t="n">
-        <v>19.39421553613462</v>
+        <v>19.39421369314703</v>
       </c>
       <c r="E814" t="n">
-        <v>19.82438390589855</v>
+        <v>19.82438202203305</v>
       </c>
       <c r="F814" t="n">
         <v>1394100</v>
@@ -16732,16 +16732,16 @@
         <v>44950</v>
       </c>
       <c r="B816" t="n">
-        <v>20.95929718017578</v>
+        <v>20.95929527282715</v>
       </c>
       <c r="C816" t="n">
-        <v>21.42607650494234</v>
+        <v>21.42607455511562</v>
       </c>
       <c r="D816" t="n">
-        <v>20.19963712121221</v>
+        <v>20.19963528299455</v>
       </c>
       <c r="E816" t="n">
-        <v>20.21794260352624</v>
+        <v>20.21794076364274</v>
       </c>
       <c r="F816" t="n">
         <v>2227800</v>
@@ -16752,16 +16752,16 @@
         <v>44951</v>
       </c>
       <c r="B817" t="n">
-        <v>20.95929718017578</v>
+        <v>20.95929527282715</v>
       </c>
       <c r="C817" t="n">
-        <v>21.38946728602115</v>
+        <v>21.38946533952596</v>
       </c>
       <c r="D817" t="n">
-        <v>20.37353571178176</v>
+        <v>20.3735338577389</v>
       </c>
       <c r="E817" t="n">
-        <v>20.8677715143125</v>
+        <v>20.86776961529293</v>
       </c>
       <c r="F817" t="n">
         <v>3255900</v>
@@ -16792,16 +16792,16 @@
         <v>44953</v>
       </c>
       <c r="B819" t="n">
-        <v>21.42607307434082</v>
+        <v>21.42607498168945</v>
       </c>
       <c r="C819" t="n">
-        <v>21.75556472040986</v>
+        <v>21.75556665708984</v>
       </c>
       <c r="D819" t="n">
-        <v>20.99590478307803</v>
+        <v>20.99590665213309</v>
       </c>
       <c r="E819" t="n">
-        <v>21.36200564220664</v>
+        <v>21.36200754385199</v>
       </c>
       <c r="F819" t="n">
         <v>1103900</v>
@@ -16812,16 +16812,16 @@
         <v>44956</v>
       </c>
       <c r="B820" t="n">
-        <v>21.69149780273438</v>
+        <v>21.69149971008301</v>
       </c>
       <c r="C820" t="n">
-        <v>21.86539462387816</v>
+        <v>21.86539654651767</v>
       </c>
       <c r="D820" t="n">
-        <v>21.46268454213889</v>
+        <v>21.46268642936781</v>
       </c>
       <c r="E820" t="n">
-        <v>21.46268454213889</v>
+        <v>21.46268642936781</v>
       </c>
       <c r="F820" t="n">
         <v>1099700</v>
@@ -16872,16 +16872,16 @@
         <v>44959</v>
       </c>
       <c r="B823" t="n">
-        <v>22.64336395263672</v>
+        <v>22.64336204528809</v>
       </c>
       <c r="C823" t="n">
-        <v>23.09183781103546</v>
+        <v>23.09183586590993</v>
       </c>
       <c r="D823" t="n">
-        <v>22.04844972193255</v>
+        <v>22.04844786469612</v>
       </c>
       <c r="E823" t="n">
-        <v>22.04844972193255</v>
+        <v>22.04844786469612</v>
       </c>
       <c r="F823" t="n">
         <v>1654000</v>
@@ -16892,16 +16892,16 @@
         <v>44960</v>
       </c>
       <c r="B824" t="n">
-        <v>21.75556945800781</v>
+        <v>21.75556755065918</v>
       </c>
       <c r="C824" t="n">
-        <v>22.72573738239372</v>
+        <v>22.72573538998878</v>
       </c>
       <c r="D824" t="n">
-        <v>21.74641671632313</v>
+        <v>21.74641480977693</v>
       </c>
       <c r="E824" t="n">
-        <v>22.54268604011397</v>
+        <v>22.54268406375746</v>
       </c>
       <c r="F824" t="n">
         <v>1001400</v>
@@ -16952,16 +16952,16 @@
         <v>44965</v>
       </c>
       <c r="B827" t="n">
-        <v>21.05082321166992</v>
+        <v>21.05082130432129</v>
       </c>
       <c r="C827" t="n">
-        <v>21.26133102481696</v>
+        <v>21.26132909839488</v>
       </c>
       <c r="D827" t="n">
-        <v>20.83116265720689</v>
+        <v>20.83116076976101</v>
       </c>
       <c r="E827" t="n">
-        <v>21.0691286943019</v>
+        <v>21.06912678529466</v>
       </c>
       <c r="F827" t="n">
         <v>827200</v>
@@ -17012,16 +17012,16 @@
         <v>44970</v>
       </c>
       <c r="B830" t="n">
-        <v>20.68472099304199</v>
+        <v>20.68471908569336</v>
       </c>
       <c r="C830" t="n">
-        <v>21.04166915349198</v>
+        <v>21.04166721322897</v>
       </c>
       <c r="D830" t="n">
-        <v>20.14472150914202</v>
+        <v>20.14471965158702</v>
       </c>
       <c r="E830" t="n">
-        <v>20.24539991161019</v>
+        <v>20.24539804477158</v>
       </c>
       <c r="F830" t="n">
         <v>815800</v>
@@ -17032,16 +17032,16 @@
         <v>44971</v>
       </c>
       <c r="B831" t="n">
-        <v>20.11726379394531</v>
+        <v>20.11726188659668</v>
       </c>
       <c r="C831" t="n">
-        <v>21.08743338869272</v>
+        <v>21.08743138936082</v>
       </c>
       <c r="D831" t="n">
-        <v>20.0165871346465</v>
+        <v>20.01658523684317</v>
       </c>
       <c r="E831" t="n">
-        <v>20.98675498368707</v>
+        <v>20.98675299390064</v>
       </c>
       <c r="F831" t="n">
         <v>634400</v>
@@ -17072,16 +17072,16 @@
         <v>44973</v>
       </c>
       <c r="B833" t="n">
-        <v>20.47421455383301</v>
+        <v>20.47421264648438</v>
       </c>
       <c r="C833" t="n">
-        <v>20.75794255290158</v>
+        <v>20.75794061912125</v>
       </c>
       <c r="D833" t="n">
-        <v>20.09895914124952</v>
+        <v>20.09895726885915</v>
       </c>
       <c r="E833" t="n">
-        <v>20.31862144227149</v>
+        <v>20.31861954941768</v>
       </c>
       <c r="F833" t="n">
         <v>1422600</v>
@@ -17252,16 +17252,16 @@
         <v>44988</v>
       </c>
       <c r="B842" t="n">
-        <v>18.57963562011719</v>
+        <v>18.57963752746582</v>
       </c>
       <c r="C842" t="n">
-        <v>19.0464148701135</v>
+        <v>19.04641682538077</v>
       </c>
       <c r="D842" t="n">
-        <v>18.40573880310988</v>
+        <v>18.40574069260661</v>
       </c>
       <c r="E842" t="n">
-        <v>18.79929788128559</v>
+        <v>18.79929981118432</v>
       </c>
       <c r="F842" t="n">
         <v>1514000</v>
@@ -17352,16 +17352,16 @@
         <v>44995</v>
       </c>
       <c r="B847" t="n">
-        <v>20.22709465026855</v>
+        <v>20.22709274291992</v>
       </c>
       <c r="C847" t="n">
-        <v>20.50166989272511</v>
+        <v>20.50166795948493</v>
       </c>
       <c r="D847" t="n">
-        <v>19.62302772029868</v>
+        <v>19.62302586991157</v>
       </c>
       <c r="E847" t="n">
-        <v>20.46506067506075</v>
+        <v>20.4650587452727</v>
       </c>
       <c r="F847" t="n">
         <v>1496500</v>
@@ -17372,16 +17372,16 @@
         <v>44998</v>
       </c>
       <c r="B848" t="n">
-        <v>20.23624801635742</v>
+        <v>20.23624610900879</v>
       </c>
       <c r="C848" t="n">
-        <v>20.6664163750189</v>
+        <v>20.66641442712515</v>
       </c>
       <c r="D848" t="n">
-        <v>19.88845083641251</v>
+        <v>19.88844896184517</v>
       </c>
       <c r="E848" t="n">
-        <v>20.08980764976173</v>
+        <v>20.0898057562157</v>
       </c>
       <c r="F848" t="n">
         <v>994600</v>
@@ -17412,16 +17412,16 @@
         <v>45000</v>
       </c>
       <c r="B850" t="n">
-        <v>20.38268661499023</v>
+        <v>20.38268852233887</v>
       </c>
       <c r="C850" t="n">
-        <v>20.45590679193707</v>
+        <v>20.45590870613742</v>
       </c>
       <c r="D850" t="n">
-        <v>19.22031477846578</v>
+        <v>19.22031657704326</v>
       </c>
       <c r="E850" t="n">
-        <v>19.54980644757992</v>
+        <v>19.54980827699021</v>
       </c>
       <c r="F850" t="n">
         <v>1415900</v>
@@ -17432,16 +17432,16 @@
         <v>45001</v>
       </c>
       <c r="B851" t="n">
-        <v>20.3552303314209</v>
+        <v>20.35522842407227</v>
       </c>
       <c r="C851" t="n">
-        <v>20.71217850979799</v>
+        <v>20.7121765690022</v>
       </c>
       <c r="D851" t="n">
-        <v>20.0715023369598</v>
+        <v>20.07150045619736</v>
       </c>
       <c r="E851" t="n">
-        <v>20.31862111231635</v>
+        <v>20.31861920839811</v>
       </c>
       <c r="F851" t="n">
         <v>1259200</v>
@@ -17452,16 +17452,16 @@
         <v>45002</v>
       </c>
       <c r="B852" t="n">
-        <v>20.59319496154785</v>
+        <v>20.59319305419922</v>
       </c>
       <c r="C852" t="n">
-        <v>21.65488842879778</v>
+        <v>21.65488642311474</v>
       </c>
       <c r="D852" t="n">
-        <v>20.27285602411575</v>
+        <v>20.27285414643702</v>
       </c>
       <c r="E852" t="n">
-        <v>20.73048257881682</v>
+        <v>20.73048065875256</v>
       </c>
       <c r="F852" t="n">
         <v>5019200</v>
@@ -17492,16 +17492,16 @@
         <v>45006</v>
       </c>
       <c r="B854" t="n">
-        <v>20.07150268554688</v>
+        <v>20.07150077819824</v>
       </c>
       <c r="C854" t="n">
-        <v>20.41014538739954</v>
+        <v>20.41014344787047</v>
       </c>
       <c r="D854" t="n">
-        <v>19.69624901824694</v>
+        <v>19.69624714655779</v>
       </c>
       <c r="E854" t="n">
-        <v>19.82438390589855</v>
+        <v>19.82438202203305</v>
       </c>
       <c r="F854" t="n">
         <v>11448300</v>
@@ -17592,16 +17592,16 @@
         <v>45013</v>
       </c>
       <c r="B859" t="n">
-        <v>20.85861778259277</v>
+        <v>20.85861968994141</v>
       </c>
       <c r="C859" t="n">
-        <v>21.15149847836918</v>
+        <v>21.15150041249934</v>
       </c>
       <c r="D859" t="n">
-        <v>19.8884482957001</v>
+        <v>19.88845011433473</v>
       </c>
       <c r="E859" t="n">
-        <v>20.36438029919009</v>
+        <v>20.36438216134478</v>
       </c>
       <c r="F859" t="n">
         <v>1803200</v>
@@ -17612,16 +17612,16 @@
         <v>45014</v>
       </c>
       <c r="B860" t="n">
-        <v>20.44675445556641</v>
+        <v>20.44675254821777</v>
       </c>
       <c r="C860" t="n">
-        <v>20.84946630958365</v>
+        <v>20.84946436466857</v>
       </c>
       <c r="D860" t="n">
-        <v>20.08065356359925</v>
+        <v>20.08065169040186</v>
       </c>
       <c r="E860" t="n">
-        <v>20.74878790965265</v>
+        <v>20.74878597412922</v>
       </c>
       <c r="F860" t="n">
         <v>1543800</v>
@@ -17652,16 +17652,16 @@
         <v>45016</v>
       </c>
       <c r="B862" t="n">
-        <v>20.22709465026855</v>
+        <v>20.22709274291992</v>
       </c>
       <c r="C862" t="n">
-        <v>21.20641522625891</v>
+        <v>21.20641322656356</v>
       </c>
       <c r="D862" t="n">
-        <v>20.18133094605458</v>
+        <v>20.18132904302132</v>
       </c>
       <c r="E862" t="n">
-        <v>21.0965840818522</v>
+        <v>21.09658209251356</v>
       </c>
       <c r="F862" t="n">
         <v>2009300</v>
@@ -17712,16 +17712,16 @@
         <v>45021</v>
       </c>
       <c r="B865" t="n">
-        <v>19.17455101013184</v>
+        <v>19.17455291748047</v>
       </c>
       <c r="C865" t="n">
-        <v>19.89759997092581</v>
+        <v>19.89760195019823</v>
       </c>
       <c r="D865" t="n">
-        <v>18.43319482469816</v>
+        <v>18.43319665830193</v>
       </c>
       <c r="E865" t="n">
-        <v>19.78777058874</v>
+        <v>19.78777255708738</v>
       </c>
       <c r="F865" t="n">
         <v>4218800</v>
@@ -17752,16 +17752,16 @@
         <v>45026</v>
       </c>
       <c r="B867" t="n">
-        <v>19.46743583679199</v>
+        <v>19.46743392944336</v>
       </c>
       <c r="C867" t="n">
-        <v>19.7694693206958</v>
+        <v>19.76946738375502</v>
       </c>
       <c r="D867" t="n">
-        <v>19.21116431426179</v>
+        <v>19.21116243202171</v>
       </c>
       <c r="E867" t="n">
-        <v>19.7694693206958</v>
+        <v>19.76946738375502</v>
       </c>
       <c r="F867" t="n">
         <v>1236600</v>
@@ -17772,16 +17772,16 @@
         <v>45027</v>
       </c>
       <c r="B868" t="n">
-        <v>20.22709465026855</v>
+        <v>20.22709274291992</v>
       </c>
       <c r="C868" t="n">
-        <v>20.95929646062392</v>
+        <v>20.95929448423106</v>
       </c>
       <c r="D868" t="n">
-        <v>19.66878967880583</v>
+        <v>19.66878782410352</v>
       </c>
       <c r="E868" t="n">
-        <v>19.70540064217701</v>
+        <v>19.70539878402241</v>
       </c>
       <c r="F868" t="n">
         <v>2926500</v>
@@ -17812,16 +17812,16 @@
         <v>45029</v>
       </c>
       <c r="B870" t="n">
-        <v>20.92268753051758</v>
+        <v>20.92268943786621</v>
       </c>
       <c r="C870" t="n">
-        <v>21.38031410470593</v>
+        <v>21.3803160537726</v>
       </c>
       <c r="D870" t="n">
-        <v>20.17218022816178</v>
+        <v>20.17218206709286</v>
       </c>
       <c r="E870" t="n">
-        <v>20.61150132041295</v>
+        <v>20.61150319939331</v>
       </c>
       <c r="F870" t="n">
         <v>2770400</v>
@@ -17832,16 +17832,16 @@
         <v>45030</v>
       </c>
       <c r="B871" t="n">
-        <v>20.3552303314209</v>
+        <v>20.35522842407227</v>
       </c>
       <c r="C871" t="n">
-        <v>20.86777161883283</v>
+        <v>20.86776966345747</v>
       </c>
       <c r="D871" t="n">
-        <v>20.29116288870777</v>
+        <v>20.29116098736245</v>
       </c>
       <c r="E871" t="n">
-        <v>20.84946788213399</v>
+        <v>20.84946592847376</v>
       </c>
       <c r="F871" t="n">
         <v>1825700</v>
@@ -17872,16 +17872,16 @@
         <v>45034</v>
       </c>
       <c r="B873" t="n">
-        <v>19.31184196472168</v>
+        <v>19.31184005737305</v>
       </c>
       <c r="C873" t="n">
-        <v>20.57489055345904</v>
+        <v>20.57488852136446</v>
       </c>
       <c r="D873" t="n">
-        <v>19.20201081775428</v>
+        <v>19.2020089212532</v>
       </c>
       <c r="E873" t="n">
-        <v>20.42845018797375</v>
+        <v>20.42844817034246</v>
       </c>
       <c r="F873" t="n">
         <v>2662000</v>
@@ -17912,16 +17912,16 @@
         <v>45036</v>
       </c>
       <c r="B875" t="n">
-        <v>19.01895904541016</v>
+        <v>19.01896095275879</v>
       </c>
       <c r="C875" t="n">
-        <v>19.01895904541016</v>
+        <v>19.01896095275879</v>
       </c>
       <c r="D875" t="n">
-        <v>18.13116246788614</v>
+        <v>18.13116428620058</v>
       </c>
       <c r="E875" t="n">
-        <v>18.31421377653411</v>
+        <v>18.31421561320617</v>
       </c>
       <c r="F875" t="n">
         <v>1812500</v>
@@ -17932,16 +17932,16 @@
         <v>45040</v>
       </c>
       <c r="B876" t="n">
-        <v>18.98235130310059</v>
+        <v>18.98234939575195</v>
       </c>
       <c r="C876" t="n">
-        <v>19.16540264277763</v>
+        <v>19.16540071703598</v>
       </c>
       <c r="D876" t="n">
-        <v>18.82675818808718</v>
+        <v>18.82675629637256</v>
       </c>
       <c r="E876" t="n">
-        <v>19.00980952776423</v>
+        <v>19.00980761765659</v>
       </c>
       <c r="F876" t="n">
         <v>1200800</v>
@@ -34812,19 +34812,39 @@
         <v>46274</v>
       </c>
       <c r="B1720" t="n">
-        <v>22.38</v>
+        <v>22.3799991607666</v>
       </c>
       <c r="C1720" t="n">
         <v>22.75</v>
       </c>
       <c r="D1720" t="n">
-        <v>22.15</v>
+        <v>22.14999961853027</v>
       </c>
       <c r="E1720" t="n">
         <v>22.75</v>
       </c>
       <c r="F1720" t="n">
         <v>1298400</v>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1721" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="C1721" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="D1721" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="E1721" t="n">
+        <v>22.37</v>
+      </c>
+      <c r="F1721" t="n">
+        <v>1962800</v>
       </c>
     </row>
   </sheetData>
